--- a/input/cursos.xlsx
+++ b/input/cursos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2714" uniqueCount="1641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="1821">
   <si>
     <t>course_id</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>Educação</t>
+  </si>
+  <si>
+    <t>Aprenda pintura, escultura e desenho com abordagem crítica e integrativa, voltada à educação e à expressão de ideias com sensibilidade artística.</t>
   </si>
   <si>
     <t>A Licenciatura em Artes Visuais semipresencial, foca sua formação na área da educação, fornecendo conhecimentos com abordagem crítica, analítica e integrativa. Os estudantes são imergidos com ampla visão sobre o cenário artístico global, os tornando aptos para manifestar ideias por meio de artes visuais, como pintura, escultura e desenho, com sensibilidade artística e uma abordagem centrada no humano. A duração do curso é de 8 semestres (4 anos).</t>
@@ -562,6 +565,30 @@
     <t>Desenvolva sua expressão artística com o curso de Artes Visuais com flexibilidade e baixo custo. Vestibular On-line em EAD reconhecida. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Pintura e desenho na educação em artes</t>
+  </si>
+  <si>
+    <t>Educadora de artes de cerca de 27 anos, mulher de pele morena, cabelo cacheado preso em coque alto, avental de algodão sobre camiseta clara e calça jeans, atenção voltada à tela.</t>
+  </si>
+  <si>
+    <t>Sala de artes de escola brasileira contemporânea, cavaletes alinhados, janelas amplas, piso fácil de limpar, pias ao fundo, espaço organizado e acessível.</t>
+  </si>
+  <si>
+    <t>cavalete, paleta de tintas, pincéis, tela em branco, pote de água</t>
+  </si>
+  <si>
+    <t>Aplica tinta à tela no cavalete e demonstra um traço com o pincel, em pé à direita da sala, sem posar.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita junto ao cavalete, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural das janelas, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; artista faminto; galeria de luxo; nudez; estereótipo de gênio incompreendido; tinta no chão de forma precária; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Educadora de artes, mulher de pele morena, cerca de 27 anos, cabelo cacheado em coque, avental sobre camiseta, em sala de artes escolar contemporânea, aplicando tinta à tela no cavalete. Objetos: cavalete, paleta de tintas, pincéis, tela e pote de água. Sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>naturologia-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -569,6 +596,9 @@
   </si>
   <si>
     <t>naturologia</t>
+  </si>
+  <si>
+    <t>Desenvolva práticas integrativas com recursos naturais, meditativos e corporais para promover harmonia, saúde e bem-estar.</t>
   </si>
   <si>
     <t>O curso de Naturologia semipresencial da Cruzeiro do Sul Virtual capacita profissionais para desenvolver e implementar planos de tratamento integrativos. Utilizando métodos da medicina chinesa e recursos naturais, manuais, práticas meditativas e corporais, o curso visa ensinar ao estudante como promover harmonia, saúde e bem-estar. Os naturologistas são preparados para aplicar tratamentos naturais preventivos, de recuperação e de promoção da saúde, abordando disfunções através de uma análise dos desequilíbrios energéticos. Com uma grade curricular completa e atualizada, o curso tem duração de 6 semestres (3 anos) e confere o título de bacharel, preparando os estudantes de forma abrangente para o mercado de trabalho.</t>
@@ -606,6 +636,30 @@
     <t>Estude Naturologia a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Avaliação integrativa e planejamento de bem-estar</t>
+  </si>
+  <si>
+    <t>Naturologista de cerca de 31 anos, mulher de pele clara, cabelo liso castanho na altura dos ombros, blusa de linho areia e calça de algodão, atenção à escuta.</t>
+  </si>
+  <si>
+    <t>Sala de atendimento integrativo em clínica acessível brasileira, mesa de conversa com duas cadeiras, planta à janela, prateleira discreta ao fundo, sem estética de spa de luxo.</t>
+  </si>
+  <si>
+    <t>caderno de planejamento, caneta, copo d'água, diagrama de hábitos sem escritos, frascos de óleos na prateleira ao fundo</t>
+  </si>
+  <si>
+    <t>Escuta a pessoa atendida e anota um plano de bem-estar no caderno, sentada à direita da mesa, com os frascos apenas na prateleira ao fundo.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentada à direita da mesa, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da janela, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico; prescrição médica; jaleco; estetoscópio; spa de luxo; cristais místicos; sexualização; aromaterapia como cena principal; mistura de óleos em primeiro plano; hospital; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Naturologista, mulher de pele clara, cerca de 31 anos, cabelo liso castanho, blusa de linho, em sala de atendimento integrativo, sentada à mesa escutando a pessoa atendida e anotando um plano de bem-estar no caderno. Sobre a mesa: caderno de planejamento, caneta, copo d'água e diagrama de hábitos sem escritos. Frascos de óleos apenas na prateleira ao fundo, fora do foco principal. Sem diagnóstico, sem jaleco, sem spa de luxo, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciberseguranca-ead-tecnologo</t>
   </si>
   <si>
@@ -616,6 +670,9 @@
   </si>
   <si>
     <t>Engenharia e Tecnologia</t>
+  </si>
+  <si>
+    <t>Prepare-se para planejar e executar técnicas de proteção de sistemas, máquinas, programas e redes contra ameaças digitais.</t>
   </si>
   <si>
     <t>O curso de Cibersegurança EAD da Cruzeiro do Sul Virtual forma especialistas capacitados para criar, planejar e executar ações e técnicas para a segurança de sistemas, máquinas, programas e redes, sendo responsáveis por proteger sistemas, redes e dados contra ameaças cibernéticas. Com duração de 4 semestres ( 2 anos), o curso oferece a titulação de tecnólogo em Cibersegurança.</t>
@@ -650,6 +707,30 @@
     <t>Desenvolva habilidades em Cibersegurança com flexibilidade e baixo custo. Vestibular On-line em EAD reconhecida. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Monitoramento da proteção de sistemas e redes</t>
+  </si>
+  <si>
+    <t>Analista de segurança digital de cerca de 28 anos, homem de pele negra, cabelo crespo curto, camisa social grafite e calça preta, fone no pescoço, olhar nos monitores.</t>
+  </si>
+  <si>
+    <t>Sala de operações de segurança em empresa brasileira contemporânea, dois monitores, rack de servidores ao fundo, iluminação controlada, espaço limpo e funcional.</t>
+  </si>
+  <si>
+    <t>dois monitores, rack de servidores, headset, caderno de incidentes, teclado</t>
+  </si>
+  <si>
+    <t>Compara alertas nos dois monitores e anota um encaminhamento no caderno de incidentes, sentado à direita, sem olhar para a câmera.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentado à direita diante dos monitores, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; hacker de capuz; código verde de filme; quarto escuro; telas com escritos legíveis; estereótipo de invasor; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional suave. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de segurança digital, homem de pele negra, cerca de 28 anos, camisa social grafite, sentado em sala de operações com rack de servidores ao fundo, comparando os dois monitores e anotando no caderno de incidentes. Objetos: dois monitores, rack, headset, caderno e teclado. Telas sem escritos visíveis. Sem capuz, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>coding-ead-tecnologo</t>
   </si>
   <si>
@@ -657,6 +738,9 @@
   </si>
   <si>
     <t>coding</t>
+  </si>
+  <si>
+    <t>Domine o desenvolvimento, o teste e a implementação de algoritmos e programas para web, desktop e plataformas móveis.</t>
   </si>
   <si>
     <t>O curso de Coding EAD na Cruzeiro do Sul fomenta desenvolvedores a elaborar projetos de computação utilizando novas linguagens de programação, capacitado para solucionar problemas de maneira inovadora e eficiente, em diversas áreas de atuação no campo dos desenvolvedores de web. O profissional graduado em Coding é habilitado para desenvolver, projetar, testar e implementar algoritmos e programas de computador para vários meios digitais, buscando soluções para web, desktop e plataformas móveis. Com duração de 4 semestres (2 anos), o curso oferece o título de tecnólogo em Coding.</t>
@@ -691,6 +775,30 @@
     <t>Aprenda Programação a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Escrita e teste de programas para web e dispositivos</t>
+  </si>
+  <si>
+    <t>Desenvolvedora de cerca de 24 anos, mulher de pele clara com sardas, cabelo ondulado castanho-claro solto, moletom cinza e calça jeans, sentada diante do notebook.</t>
+  </si>
+  <si>
+    <t>Coworking brasileiro contemporâneo e acessível, mesas compartilhadas, janela lateral, plantas pequenas, um notebook aberto, sem quadro de fluxos e sem escritório corporativo de luxo.</t>
+  </si>
+  <si>
+    <t>notebook, mouse, fone de ouvido, copo, caderno de anotações</t>
+  </si>
+  <si>
+    <t>Digita e testa um trecho de programa no notebook, conferindo o resultado na tela com linhas técnicas não legíveis, sentada à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentada à direita diante do notebook, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da janela, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; código legível; fluxos de telas; quadro de UX; capuz de hacker; estética de filme de invasão; escritório de luxo; celular comparado à tela; diagramas de banco de dados; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Desenvolvedora, mulher de pele clara com sardas, cerca de 24 anos, moletom cinza, sentada em coworking acessível, digitando e testando um programa no notebook. Tela com linhas técnicas desfocadas, sem escritos legíveis. Objetos: notebook, mouse, fone de ouvido, copo e caderno. Sem quadro de fluxos, sem capuz, sem interfaces flutuantes, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>producao-midiatica-ead-tecnologo</t>
   </si>
   <si>
@@ -698,6 +806,9 @@
   </si>
   <si>
     <t>producao-midiatica</t>
+  </si>
+  <si>
+    <t>Explore o planejamento e a produção de conteúdos para vídeo, áudio e mídias digitais, da concepção à edição e à finalização.</t>
   </si>
   <si>
     <t>O curso de Filmmaker EAD da Cruzeiro do Sul Virtual, com duração de 4 semestres (2 anos), é uma jornada intensiva projetada para aqueles que almejam contar histórias através do cinema e da produção audiovisual. Os estudantes são capacitados em todas as etapas essenciais da criação cinematográfica, desde a concepção inicial até a finalização do projeto, incluindo pré-produção, roteiro, edição, e pós-produção. Com uma abordagem dinâmica e adaptável à aprendizagem, o curso utiliza materiais multimídia e interativos para facilitar o processo de ensino e manter os estudantes atualizados com as mudanças constantes na indústria de conteúdo audiovisual. Ao final, os formandos, com certificação de tecnologia em Filmmaker, estarão preparados para iniciar suas carreiras como profissionais versáteis e talentosos, prontos para se destacar no campo do filmmaking.</t>
@@ -730,6 +841,30 @@
     <t>Desenvolva habilidades em produção cinematográfica EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Coordenação de conteúdo para vídeo, áudio e mídia digital</t>
+  </si>
+  <si>
+    <t>Produtor de conteúdo midiático de cerca de 26 anos, homem de pele morena, cabelo ondulado escuro, camisa de malha e calça chino, fone no pescoço, atenção à pauta.</t>
+  </si>
+  <si>
+    <t>Sala de produção de conteúdo contemporânea brasileira, mesa de planejamento, lousa de pauta ao fundo, janela, espaço organizado e acessível, sem set de filmagem na rua.</t>
+  </si>
+  <si>
+    <t>caderno de pauta, tablet, fone de ouvido, gravador de áudio, câmera compacta pousada na mesa</t>
+  </si>
+  <si>
+    <t>Organiza a pauta no caderno e confere o tablet, em pé à direita da mesa, com a câmera compacta apenas pousada ao lado, sem operá-la.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita junto à mesa de planejamento, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da janela, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; câmera no ombro; cinegrafista; boom; claquete; set externo; colete utilitário; estúdio hollywoodiano; paparazzi; lousa com escritos; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Produtor de conteúdo midiático, homem de pele morena, cerca de 26 anos, camisa de malha, fone no pescoço, em sala de produção, organizando a pauta no caderno e conferindo o tablet. Sobre a mesa: caderno de pauta, tablet, fone, gravador de áudio e câmera compacta apenas pousada, fora da ação principal. Sem câmera no ombro, sem set de rua, sem claquete, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>teologia-ead-bacharelado</t>
   </si>
   <si>
@@ -737,6 +872,9 @@
   </si>
   <si>
     <t>teologia</t>
+  </si>
+  <si>
+    <t>Estude história das religiões, estudos bíblicos, ética, filosofia e pastoral para o ensino, o aconselhamento e a pesquisa.</t>
   </si>
   <si>
     <t>O curso de Teologia EAD da Cruzeiro do Sul Virtual. Com duração de 6 semestres (3 anos), o curso confere o título de bacharel em Teologia. O currículo é abrangente, abordando temas como história das religiões, estudos bíblicos, ética, filosofia e pastoral. Além disso, o curso proporciona uma sólida formação acadêmica e espiritual, capacitando os alunos para atuarem em diversas áreas, como liderança religiosa, ensino, aconselhamento e pesquisa teológica.Os estudantes têm acesso a aulas gravadas, materiais didáticos de qualidade, e um ambiente virtual de aprendizagem interativo, que facilita o desenvolvimento de competências teológicas e habilidades práticas. Ao final do curso, os graduados estarão preparados para atuar em comunidades religiosas, instituições educacionais e organizações sociais.</t>
@@ -774,6 +912,30 @@
     <t>Estude Teologia a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Estudo comparado de religiões e pastoral</t>
+  </si>
+  <si>
+    <t>Pesquisadora teológica de cerca de 33 anos, mulher de pele negra, cabelo trançado médio, camisa social off-white e cardigan, leitura atenta.</t>
+  </si>
+  <si>
+    <t>Sala de estudos de centro comunitário brasileiro, estante de livros, mesa de madeira clara, janela com luz suave, espaço silencioso e acessível.</t>
+  </si>
+  <si>
+    <t>livros empilhados, caderno, caneta, óculos de leitura, abajur simples</t>
+  </si>
+  <si>
+    <t>Compara dois livros abertos e anota no caderno, sentada à direita da mesa de estudos, sem olhar para a câmera.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentada à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; páginas com escritos legíveis; púlpito; batina; vitrais de igreja de luxo; estereótipo clerical; ambiente precário; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional suave. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Pesquisadora teológica, mulher de pele negra, cerca de 33 anos, cabelo trançado, camisa off-white e cardigan, em sala de estudos comunitária, comparando dois livros e anotando no caderno. Objetos: livros, caderno, caneta, óculos de leitura e abajur simples. Páginas sem escritos visíveis. Sem púlpito, sem batina, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>inteligencia-artificial-ead-tecnologo</t>
   </si>
   <si>
@@ -781,6 +943,9 @@
   </si>
   <si>
     <t>inteligencia-artificial</t>
+  </si>
+  <si>
+    <t>Conheça técnicas de machine learning, chatbots e recursos de nuvem para implementar códigos e otimizar processos organizacionais.</t>
   </si>
   <si>
     <t>O curso tecnólogo em Inteligência Artificial EAD da Cruzeiro do, é uma formação abrangente, que é feita em apenas 4 semestres (2 anos), e aborda um currículo amplo que trabalha temas voltados para implementação de códigos, recursos de nuvem, desenvolvimento de aplicativos com tecnologias inovadoras e muito mais. O estudante terá grandes chances de ser altamente capacitado para lidar com técnicas de Machine Learning, chatbots e recursos variados, com o objetivo de otimizar processos de organizações.</t>
@@ -815,6 +980,30 @@
     <t>Aprenda sobre Inteligência Artificial a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Análise de dados para modelos de machine learning</t>
+  </si>
+  <si>
+    <t>Desenvolvedora de modelos preditivos de cerca de 29 anos, mulher de pele clara, cabelo liso preto em rabo baixo, camisa azul-clara e calça preta, expressão analítica.</t>
+  </si>
+  <si>
+    <t>Sala de análise em empresa brasileira contemporânea, mesa longa, um monitor extra com gráfico abstrato, persiana, sem laboratório futurista.</t>
+  </si>
+  <si>
+    <t>monitor extra, impressões de gráficos, tablet, caneta, notebook aberto</t>
+  </si>
+  <si>
+    <t>Compara um gráfico impresso com a visualização no monitor extra e anota no tablet, sentada à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentada à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da persiana, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; cérebro holográfico; robô humanóide; gráficos com escritos; estúdio futurista; estereótipo de gênio; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Desenvolvedora de modelos preditivos, mulher de pele clara, cerca de 29 anos, cabelo liso preto, camisa azul-clara, em sala de análise, comparando gráfico impresso com o monitor extra e anotando no tablet. Objetos: monitor extra, impressões de gráficos, tablet, caneta e notebook. Gráficos e telas sem escritos visíveis. Sem hologramas, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>design-de-moda-ead-tecnologo</t>
   </si>
   <si>
@@ -825,6 +1014,9 @@
   </si>
   <si>
     <t>Arquitetura, Design</t>
+  </si>
+  <si>
+    <t>Crie coleções com desenho, modelagem, costura e estamparia, analisando tendências de cores, formatos, texturas e acabamentos.</t>
   </si>
   <si>
     <t>O curso de Design de Moda EAD da Cruzeiro do Sul Virtual prepara profissionais completos, capacitados não apenas para criar produtos e coleções, mas também para dominar desenhos, ilustrações, modelagem, costura, acabamento e estamparia. Além das habilidades técnicas, o curso abrange conhecimentos em comunicação, marketing, eventos e produção. Também são oferecidas noções essenciais de negócios, logística, distribuição e branding, proporcionando uma formação abrangente e alinhada às demandas do mercado de moda atual. O curso tem duração de 4 semestres (2 anos) e confere o título de tecnólogo em Design de Moda, com conceito 4 no MEC, ensinando a desenvolver e coordenar projetos para a indústria de confecção de roupas e acessórios; analisar tendências de comportamento, cores, formatos, texturas e acabamentos; realizar portfólios e dossiês; fazer a representação visual de suas criações; e analisar a viabilidade técnica do projeto.</t>
@@ -862,6 +1054,30 @@
     <t>Estude Design de Moda EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Modelagem e representação visual de coleções</t>
+  </si>
+  <si>
+    <t>Designer de moda de cerca de 25 anos, mulher de pele morena clara, cabelo cacheado solto, camisa de viscose e avental de ateliê, mãos no tecido.</t>
+  </si>
+  <si>
+    <t>Ateliê de costura contemporâneo brasileiro, manequim de costura, mesa de corte, prateleira de tecidos dobrados, luz de janela, espaço acessível.</t>
+  </si>
+  <si>
+    <t>manequim de costura, fita métrica, tesoura de alfaiate, amostras de tecido, giz de tecido</t>
+  </si>
+  <si>
+    <t>Alfineta um tecido no manequim e confere a queda da modelagem, em pé à direita do ateliê, sem posar.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem em pé na região superior direita junto ao manequim, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; passarela de luxo; sexualização; modelo posando; estereótipo de fashionista; ateliê precário; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Designer de moda, mulher de pele morena clara, cerca de 25 anos, cabelo cacheado, avental de ateliê, alfinetando tecido no manequim de costura. Objetos: manequim, fita métrica, tesoura de alfaiate, amostras de tecido e giz de tecido. Sem passarela, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-do-agronegocio-ead-tecnologo</t>
   </si>
   <si>
@@ -872,6 +1088,9 @@
   </si>
   <si>
     <t>Gestão e Negócios</t>
+  </si>
+  <si>
+    <t>Planeje a gestão e as operações das cadeias produtivas, desenvolvendo soluções para o setor agrícola e o desenvolvimento rural.</t>
   </si>
   <si>
     <t>O curso de Gestão do Agronegócio EAD da Cruzeiro do Sul capacitará os estudantes para dominar os processos de gestão e operações das cadeias produtivas, desenvolvendo soluções competitivas e eficazes para o setor. Há oportunidades tanto no setor privado quanto no público, com foco na formulação e execução de políticas de desenvolvimento agrícola e rural. Com certificação profissional pelo Conselho Regional de Administração de São Paulo (CRA-SP), a formação, de 6 semestres (3 anos), oferece título de tecnólogo e visa tornar os alunos aptos a otimizar o negócio, tomando decisões eficazes.</t>
@@ -905,6 +1124,30 @@
     <t>Estude Gestão do Agronegócio a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Gestão das cadeias produtivas agrícolas</t>
+  </si>
+  <si>
+    <t>Gestor de agronegócio de cerca de 32 anos, homem de pele morena, cabelo curto liso, camisa social bege e calça khaki, expressão objetiva.</t>
+  </si>
+  <si>
+    <t>Escritório anexo a galpão de grãos no interior brasileiro, mesa com pastas, janela com silos ao fundo, ambiente funcional e limpo, sem fazenda de luxo.</t>
+  </si>
+  <si>
+    <t>bandeja com amostra de grãos, calculadora, pastas, tablet, caneta</t>
+  </si>
+  <si>
+    <t>Pesa visualmente a amostra de grãos na bandeja e confere números no tablet, em pé à direita junto à mesa do escritório.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da janela, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; chapéu de cowboy; fazenda de luxo; lavoura precária; animais; estereótipo de peão; telas com escritos; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestor de agronegócio, homem de pele morena, cerca de 32 anos, camisa social bege, em escritório anexo a galpão com silos ao fundo, conferindo amostra de grãos na bandeja e o tablet. Objetos: bandeja com grãos, calculadora, pastas, tablet e caneta. Sem chapéu, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-de-cooperativas-ead-tecnologo</t>
   </si>
   <si>
@@ -912,6 +1155,9 @@
   </si>
   <si>
     <t>gestao-de-cooperativas</t>
+  </si>
+  <si>
+    <t>Organize a administração de cooperativas com gestão estratégica, finanças, legislação específica e responsabilidade social.</t>
   </si>
   <si>
     <t>O curso de Gestão de Cooperativas EAD da Universidade Cruzeiro do Sul Virtual, com duração de 4 semestres (2 anos) e certificação de tecnólogo em Gestão de Cooperativas, forma profissionais capacitados para liderar e administrar organizações cooperativas de forma eficiente. O programa visa desenvolver habilidades em áreas fundamentais como gestão estratégica de negócios, finanças cooperativas, legislação específica e responsabilidade social. Durante a formação, os alunos estudam disciplinas essenciais como Gestão Estratégica de Negócios, Cooperativismo e Economia Solidária, Legislação Cooperativista, e Princípios de Administração e Marketing. Com esses conhecimentos, os graduados adquirem uma compreensão abrangente do funcionamento das cooperativas, estando preparados para enfrentar os desafios do setor e contribuir para o crescimento sustentável das organizações cooperativistas.</t>
@@ -945,6 +1191,30 @@
     <t>Aprenda a gerir cooperativas a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Administração e assembleia de cooperativa</t>
+  </si>
+  <si>
+    <t>Gestora de cooperativa de cerca de 31 anos, mulher de pele negra, cabelo crespo curto, blazer simples verde-musgo sobre blusa clara, postura de reunião.</t>
+  </si>
+  <si>
+    <t>Sede simples de cooperativa brasileira, mesa redonda, cadeiras iguais, mural interno, janela para o pátio, espaço comunitário organizado.</t>
+  </si>
+  <si>
+    <t>pastas de associados, calculadora, caderno de ata fechado, caneta, jarra de água</t>
+  </si>
+  <si>
+    <t>Distribui pastas de associados ao redor da mesa redonda e confere o caderno de ata, em pé à direita da sede.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento aberto, personagem na região superior direita junto à mesa redonda, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; escritório corporativo de luxo; crachás legíveis; ata aberta com escritos; estereótipo sindical caricato; ambiente precário; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora de cooperativa, mulher de pele negra, cerca de 31 anos, cabelo crespo curto, blazer verde-musgo, em sede simples com mesa redonda, distribuindo pastas de associados e conferindo o caderno de ata fechado. Objetos: pastas, calculadora, caderno de ata, caneta e jarra de água. Sem escritos visíveis, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-do-terceiro-setor-ead-tecnologo</t>
   </si>
   <si>
@@ -952,6 +1222,9 @@
   </si>
   <si>
     <t>gestao-do-terceiro-setor</t>
+  </si>
+  <si>
+    <t>Aprofunde a coordenação de organizações da sociedade civil, com planejamento de projetos sociais e administração de recursos e orçamento.</t>
   </si>
   <si>
     <t>O curso de Gestão do Terceiro Setor EAD da universidade Cruzeiro do Sul Virtual capacita alunos para a coordenação de organizações que tem como propósito ajudar pessoas, através de aprendizado moderno. Durante a formação, o estudante terá disciplinas voltadas para conhecimentos como Gestão, Marketing, Administração, Finanças, entre outros, oferecendo conhecimento atual para formar profissionais de gestão com competência teórica e prática combinadas. O curso tem duração de 4 semestres (2 anos), e confere o título de tecnologia em Gestão do Terceiro Setor.</t>
@@ -984,6 +1257,30 @@
     <t>Aprenda a gerir organizações do terceiro setor a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Planejamento de projetos sociais</t>
+  </si>
+  <si>
+    <t>Gestora de organização social de cerca de 28 anos, mulher de pele clara, cabelo ondulado castanho, camisa jeans clara e calça social, montando o mural.</t>
+  </si>
+  <si>
+    <t>Sala de associação comunitária brasileira contemporânea, mural de cortiça, mesa compartilhada, cadeiras diversas iguais, luz de janela, ambiente acolhedor e organizado.</t>
+  </si>
+  <si>
+    <t>mural de cortiça, cartões coloridos em branco, mapa impresso sem nomes, canetas coloridas, pasta de projeto</t>
+  </si>
+  <si>
+    <t>Fixa cartões coloridos no mural e cruza informações com o mapa impresso, em pé à direita da sala comunitária.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita diante do mural, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; pobreza espetacularizada; fundação de luxo; cartazes com escritos; estereótipo de caridade; ambiente precário; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora de organização social, mulher de pele clara, cerca de 28 anos, cabelo ondulado, camisa jeans, em associação comunitária, fixando cartões coloridos no mural de cortiça e consultando o mapa impresso. Objetos: mural, cartões em branco, mapa sem nomes, canetas coloridas e pasta. Sem escritos visíveis, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>redes-de-computadores-ead-tecnologo</t>
   </si>
   <si>
@@ -991,6 +1288,9 @@
   </si>
   <si>
     <t>redes-de-computadores</t>
+  </si>
+  <si>
+    <t>Pratique o projeto, a implementação e o gerenciamento de redes locais e de longa distância, com infraestrutura e soluções de conectividade.</t>
   </si>
   <si>
     <t>O curso Tecnólogo em Redes de Computadores EAD é voltado para a formação de profissionais capacitados a projetar, implementar e gerenciar redes de comunicação de dados. Com uma grade curricular abrangente, o curso inclui disciplinas como segurança da informação, administração de redes e infraestrutura de tecnologia da informação. Os alunos adquirem habilidades práticas e teóricas essenciais para configurar e manter redes locais (LAN), redes de longa distância (WAN), além de desenvolverem competências em soluções de conectividade, suporte técnico e otimização de redes. Com conceito 5 na classificação do MEC, o curso tem duração de 4 semestres (2 anos) e confere o título de tecnólogo.</t>
@@ -1025,6 +1325,30 @@
     <t>Aprenda sobre Redes de Computadores a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem e teste de infraestrutura de rede</t>
+  </si>
+  <si>
+    <t>Administrador de redes de cerca de 27 anos, homem de pele clara, cabelo liso castanho, polo azul-marinho e calça chino, de pé junto ao rack.</t>
+  </si>
+  <si>
+    <t>Sala de infraestrutura de TI em prédio comercial brasileiro, rack aberto, piso elevado, iluminação fria suave, espaço limpo e organizado.</t>
+  </si>
+  <si>
+    <t>patch panel, testador de cabo, cabos de rede, chave de fenda, rack</t>
+  </si>
+  <si>
+    <t>Encaixa um cabo no patch panel e verifica o testador de cabo, em pé à direita diante do rack aberto.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita junto ao rack, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária profissional, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; emaranhado precário de fios; data center de luxo; telas com escritos; estereótipo de técnico desleixado; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Administrador de redes, homem de pele clara, cerca de 27 anos, polo azul-marinho, em sala de infraestrutura, encaixando cabo no patch panel e conferindo o testador. Objetos: patch panel, testador de cabo, cabos de rede, chave de fenda e rack. Sem emaranhado de fios, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>quimica-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -1032,6 +1356,9 @@
   </si>
   <si>
     <t>quimica</t>
+  </si>
+  <si>
+    <t>Estude química geral, orgânica, inorgânica e analítica para pesquisa, controle de qualidade, desenvolvimento de produtos e meio ambiente.</t>
   </si>
   <si>
     <t>O curso de Química semipresencial da Cruzeiro do Sul Virtual fornece formação sólida e abrangente, formando profissionais preparados para atuar em indústrias, pesquisa e educação. Com uma grade curricular abrangente, inclui disciplinas como química geral, orgânica, inorgânica e analítica, além de matemática, física e processos biológicos. Os alunos desenvolvem habilidades de pesquisa, análise crítica e resolução de problemas, capacitando-se para enfrentar desafios no controle de qualidade, desenvolvimento de produtos e meio ambiente. O curso tem duração de 6 semestres (3 anos) e confere o título de bacharel em Química.</t>
@@ -1071,6 +1398,30 @@
     <t>Aprofunde-se em Química a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Análise química em laboratório</t>
+  </si>
+  <si>
+    <t>Profissional de laboratório químico de cerca de 26 anos, mulher de pele morena, cabelo liso preso, jaleco branco, óculos de proteção na testa, expressão concentrada.</t>
+  </si>
+  <si>
+    <t>Laboratório didático contemporâneo brasileiro, bancada com pia, capela ao fundo, prateleira de vidrarias, iluminação clara, espaço limpo.</t>
+  </si>
+  <si>
+    <t>béquer, pipeta, erlenmeyer, óculos de proteção, caderno de laboratório</t>
+  </si>
+  <si>
+    <t>Transfere líquido com a pipeta para o béquer e observa a coloração, em pé à direita da bancada.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita na bancada, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária clara, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; explosão; cientista maluco; rótulos legíveis; indústria de luxo; laboratório precário; atividade insegura; vidraria deformada.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional clara. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Profissional de laboratório químico, mulher de pele morena, cerca de 26 anos, jaleco branco, cabelo preso, pipetando líquido para o béquer na bancada de laboratório didático. Objetos: béquer, pipeta, erlenmeyer, óculos de proteção e caderno de laboratório. Sem rótulos visíveis, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>agronomia-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -1078,6 +1429,9 @@
   </si>
   <si>
     <t>agronomia</t>
+  </si>
+  <si>
+    <t>Aplique conhecimentos de ciência agrícola na produção de alimentos, no manejo do solo e da água e em práticas sustentáveis no campo.</t>
   </si>
   <si>
     <t>O curso EAD Semipresencial de Agronomia da Universidade Cruzeiro do Sul Virtual forma profissionais qualificados para enfrentar desafios relacionados à produção de alimentos, manejo sustentável dos recursos naturais e desenvolvimento da agricultura. Com uma abordagem abrangente, o curso oferece uma sólida formação em ciência agrícola, focando na otimização da produção, preservação ambiental e promoção de práticas agrícolas sustentáveis. Os alunos têm acesso a aulas teóricas e práticas, utilizando recursos tecnológicos avançados, que preparam para atuar em diversas áreas do setor agrícola, sempre com uma perspectiva de sustentabilidade e inovação. Com duração de 10 semestres (5 anos), o curso confere o título de Bacharel em Agronomia.</t>
@@ -1114,6 +1468,30 @@
     <t>Estude Agronomia com flexibilidade e qualidade. Vestibular On-line em EAD de referência. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Manejo do solo e cultivo agrícola sustentável</t>
+  </si>
+  <si>
+    <t>Agrônoma de cerca de 30 anos, mulher de pele morena, cabelo cacheado preso, camisa de mangas dobradas e botinas limpas, examinando o solo.</t>
+  </si>
+  <si>
+    <t>Talhão agrícola contemporâneo no interior brasileiro, linhas de cultivo ao fundo, céu de manhã clara, solo úmido organizado, sem fazenda de luxo.</t>
+  </si>
+  <si>
+    <t>trado de solo, amostra de terra, tesoura de poda, prancheta, luva de campo</t>
+  </si>
+  <si>
+    <t>Retira amostra de terra com o trado e registra a observação na prancheta, agachada à direita entre as linhas de cultivo.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem à direita em primeiro plano no talhão, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural matinal, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; chapéu de cowboy; lavoura precária; agronegócio de luxo; agrotóxico teatral; estereótipo rural caricato; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional da manhã. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Agrônoma, mulher de pele morena, cerca de 30 anos, cabelo cacheado preso, camisa de mangas dobradas, em talhão agrícola, retirando amostra de terra com o trado e anotando na prancheta. Objetos: trado, amostra de terra, tesoura de poda, prancheta e luva. Sem chapéu de cowboy, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>jogos-digitais-ead-tecnologo</t>
   </si>
   <si>
@@ -1121,6 +1499,9 @@
   </si>
   <si>
     <t>jogos-digitais</t>
+  </si>
+  <si>
+    <t>Crie programas e ambientes de games da concepção ao lançamento, com roteiros, narrativas, algoritmos e linguagens de programação.</t>
   </si>
   <si>
     <t>O curso de Jogos Digitais EAD da Cruzeiro do Sul Virtual se trata de uma graduação de nível tecnológico e com duração de 4 semestres (2 anos). Os estudantes contam com um plano de disciplinas relacionadas à criação de programas e ambientes de jogos, utilizando ferramentas de informática. Ao cursar Jogos Digitais EAD, o aluno passa por toda a cadeia de produção dos games, desde o conceito, desenvolvimento, produção, lançamento até o jogo estar concluído. Ao longo da formação, serão abordados temas como matemática e física aplicada a jogos, algoritmos e linguagens de programação, o que irá exercitar a criatividade do estudante, que irá aprender a desenvolver roteiros e narrativas.</t>
@@ -1162,6 +1543,30 @@
     <t>Desenvolva habilidades em criação de Jogos Digitais a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Concepção visual e narrativa de games</t>
+  </si>
+  <si>
+    <t>Game designer de cerca de 23 anos, homem de pele negra, cabelo crespo volumoso curto, camiseta mostarda e calça jeans, desenhando no tablet gráfico.</t>
+  </si>
+  <si>
+    <t>Sala pequena de produção de games em prédio comercial brasileiro, mural de sketches, mesa com um computador ao fundo, luz de janela, espaço criativo acessível.</t>
+  </si>
+  <si>
+    <t>tablet gráfico, caneta digital, controle de videogame, folhas de storyboard, fone de ouvido</t>
+  </si>
+  <si>
+    <t>Desenha um personagem no tablet gráfico e consulta o storyboard ao lado, sentado à direita, controle sobre a mesa.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentado à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; quarto escuro de gamer; energia de refrigerante; violência gráfica na tela; sketches com escritos; ambiente luxuoso ou precário; pose para câmera.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Game designer, homem de pele negra, cerca de 23 anos, camiseta mostarda, em sala de produção de games, desenhando no tablet gráfico e consultando o storyboard. Objetos: tablet gráfico, caneta digital, controle de videogame, folhas de storyboard e fone. Folhas e telas sem escritos visíveis. Sem quarto escuro, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gerontologia-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -1169,6 +1574,9 @@
   </si>
   <si>
     <t>gerontologia</t>
+  </si>
+  <si>
+    <t>Entenda o envelhecimento ativo e a gestão de serviços de saúde, bem-estar e políticas públicas voltados à qualidade de vida da pessoa idosa.</t>
   </si>
   <si>
     <t>A graduação de Gerontologia semipresencial da Cruzeiro do Sul Virtual, garante diversos conhecimentos em variadas áreas relacionadas ao processo de envelhecimento, como Psicologia, Nutrição, entre outros. O curso é focado para profissionais que já atuem na área da Saúde e desejam se aprofundar ou realizar uma transição de carreira. Ao longo do curso de Bacharelado, os estudantes têm acesso a um currículo abrangente, que integra conhecimentos voltados para saúde, bem-estar, políticas públicas e gestão de serviços voltados ao atendimento qualificado da população idosa. O objetivo principal da Cruzeiro do Sul Virtual ao disponibilizar essa formação é tornar aptos profissionais que agirão diretamente na contribuição, assistência, proteção e suporte aos idosos. A duração do curso é de 6 semestres, 3 anos.</t>
@@ -1204,6 +1612,30 @@
     <t>Desenvolva habilidades em Gerontologia a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Gestão de serviços para envelhecimento ativo</t>
+  </si>
+  <si>
+    <t>Gerontologista de cerca de 34 anos, mulher de pele clara, cabelo castanho médio preso, camisa de viscose discreta e calça confortável, conversando em pé.</t>
+  </si>
+  <si>
+    <t>Jardim de centro de convivência brasileiro contemporâneo, caminho largo, bancos, canteiros, luz da manhã, espaço acessível para caminhada autônoma.</t>
+  </si>
+  <si>
+    <t>pasta de programação, tablet, garrafa de água, banco ao fundo, canteiro com hortaliças</t>
+  </si>
+  <si>
+    <t>Caminha ao lado de um adulto idoso autônomo e mostra a programação na pasta, ambos em pé à direita, em conversa respeitosa de iguais.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagens na região superior direita do caminho, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural matinal, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; jogo de memória; infantilização; andador obrigatório; cadeira de rodas como regra; leito hospitalar; jaleco; asilo precário; pena; fragilidade forçada; clínica de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional da manhã. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoas e fundo. Gerontologista, mulher de pele clara, cerca de 34 anos, cabelo preso, camisa de viscose, caminhando no jardim de um centro de convivência ao lado de um adulto idoso autônomo, ambos em pé, ela mostrando a programação na pasta. Objetos: pasta de programação, tablet, garrafa de água, banco ao fundo e canteiro. Sem jogo de memória, sem andador, sem jaleco, sem leito hospitalar, sem infantilização, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>criminologia-ead-tecnologo</t>
   </si>
   <si>
@@ -1214,6 +1646,9 @@
   </si>
   <si>
     <t>Direito</t>
+  </si>
+  <si>
+    <t>Analise teorias criminológicas, políticas de segurança pública e justiça criminal para atuar na prevenção e na formulação de políticas públicas.</t>
   </si>
   <si>
     <t>O curso de Criminologia EAD da Universidade Cruzeiro do Sul Virtual, com as modalidades de aulas gravadas ou ao vivo, proporciona uma formação completa em apenas 4 semestres (2 anos). Os alunos exploram teorias criminológicas, investigação criminal, políticas de segurança pública e justiça criminal, preparando-se para atuar de forma estratégica na prevenção e combate ao crime. Ao concluir, obtêm o título de tecnólogo em Criminologia, pronto para ingressar no mercado de trabalho com conhecimentos atualizados e especializados.</t>
@@ -1249,6 +1684,30 @@
     <t>Estude Criminologia a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Estudo institucional de fenômenos criminais e políticas de segurança</t>
+  </si>
+  <si>
+    <t>Pesquisador em criminologia de cerca de 29 anos, homem de pele morena, cabelo curto, barba rala, óculos de aro fino, camisa social clara, leitura atenta.</t>
+  </si>
+  <si>
+    <t>Sala de pesquisa institucional brasileira, mesa larga, estante de livros, persiana, ambiente sóbrio e organizado, sem gabinete policial e sem interrogatório.</t>
+  </si>
+  <si>
+    <t>livros, relatórios impressos, gráficos sem legendas, caneta, notebook fechado</t>
+  </si>
+  <si>
+    <t>Compara um gráfico impresso com um relatório aberto e consulta um livro ao lado, sentado à direita da mesa de pesquisa.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentado à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da persiana, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; mapa de ocorrências; algemas; arma; distintivo; suspeito; fita de cena de crime; uniforme policial; investigação de campo; estética de série policial; escritos legíveis; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Pesquisador em criminologia, homem de pele morena, cerca de 29 anos, óculos, camisa social, em sala de pesquisa institucional, comparando gráfico impresso e relatório aberto, com livros ao lado. Objetos: livros, relatórios impressos, gráficos sem legendas, caneta e notebook fechado. Gráficos e relatórios sem escritos visíveis. Sem mapa de ocorrências, sem arma, sem distintivo, sem uniforme, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>matematica-licenciatura-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -1256,6 +1715,9 @@
   </si>
   <si>
     <t>matematica-licenciatura</t>
+  </si>
+  <si>
+    <t>Aprenda geometria, análise, estatística e álgebra para ensinar no fundamental e no médio, com tecnologias e situações reais.</t>
   </si>
   <si>
     <t>A Licenciatura em Matemática semipresencial da Cruzeiro do Sul Virtual, garante capacitação completa e profunda para futuros educadores da disciplina. Através de uma grade integrada entre teoria e prática, os alunos permeiam seus conhecimentos para diversas áreas da matemática, como geometria, análise matemática, estatística e álgebra. O curso desenvolve competência para solucionar problemas avançados, empregar conceitos matemáticos em situações reais e fazer uso de tecnologias no ensino da matemática. O foco da formação é aplicar conhecimentos para que os futuros matemáticos lecionem nos ensinos fundamental e médio, os tornando aptos também a fazer parte de pesquisas do âmbito, incentivando o crescimento da matemática e suas práticas educacionais.</t>
@@ -1290,6 +1752,30 @@
     <t>Prepare-se para lecionar Matemática a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Ensino de geometria com materiais concretos</t>
+  </si>
+  <si>
+    <t>Professora de matemática de cerca de 27 anos, mulher de pele negra, cabelo crespo solto na altura dos ombros, blusa coral e calça preta, demonstrando no quadro.</t>
+  </si>
+  <si>
+    <t>Sala de aula de ensino fundamental brasileira contemporânea, carteiras alinhadas, quadro branco, janelas, espaço claro e organizado.</t>
+  </si>
+  <si>
+    <t>sólidos geométricos, compasso, régua, apagador, quadro branco</t>
+  </si>
+  <si>
+    <t>Mostra um sólido geométrico para a turma e desenha a figura correspondente no quadro, em pé à direita, sem escritos no quadro.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem em pé na região superior direita junto ao quadro, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; números e fórmulas legíveis; estereótipo de gênio; sala precária; lousa antiga quebrada; atividade tecnicamente incorreta; ambiente de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de matemática, mulher de pele negra, cerca de 27 anos, cabelo crespo, blusa coral, em sala de aula contemporânea, mostrando um sólido geométrico e desenhando a figura no quadro branco. Objetos: sólidos geométricos, compasso, régua, apagador e quadro. Quadro sem números, sem fórmulas e sem escritos visíveis. Sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>desenvolvimento-full-stack-ead-tecnologo</t>
   </si>
   <si>
@@ -1297,6 +1783,9 @@
   </si>
   <si>
     <t>desenvolvimento-full-stack</t>
+  </si>
+  <si>
+    <t>Desenvolva o ciclo completo de software, do lado do cliente ao servidor, integrando linguagens e tecnologias de todo o sistema.</t>
   </si>
   <si>
     <t>O curso de Desenvolvimento Full Stack EAD da Universidade Cruzeiro do Sul Virtual tem duração de 4 semestres (2 anos), e forma profissionais capacitados para atuar em todos os aspectos de projetos de software, abrangendo tanto o desenvolvimento do lado do cliente (front-end) quanto do lado do servidor (back-end). Os especialistas desta área são reconhecidos pela habilidade de compreender o ciclo completo de desenvolvimento de software, dominando diversas linguagens, códigos e tecnologias para garantir a funcionalidade e integração harmoniosa de todas as partes do sistema. Ao final do curso, o profissional terá a titulação de tecnólogo em Desenvolvimento Full Stack.</t>
@@ -1331,6 +1820,30 @@
     <t>Desenvolva habilidades em programação Full Stack a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Integração entre interface do cliente e servidor</t>
+  </si>
+  <si>
+    <t>Desenvolvedor de software de cerca de 25 anos, homem de pele morena, cabelo cacheado, camisa xadrez aberta sobre camiseta branca, em pé na mesa alta.</t>
+  </si>
+  <si>
+    <t>Escritório residencial em apartamento brasileiro contemporâneo, mesa alta junto à janela, uma planta, prateleira simples, espaço doméstico organizado.</t>
+  </si>
+  <si>
+    <t>monitor, teclado, smartphone em suporte, caderno de anotações, copo</t>
+  </si>
+  <si>
+    <t>Compara o layout no smartphone com o monitor e anota no caderno, em pé à direita na mesa alta, sem olhar para a câmera.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita na mesa alta, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da janela, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; telas com escritos; escritório de big tech; quarto bagunçado; estereótipo de nerd; atividade tecnicamente incorreta; ambiente luxuoso.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Desenvolvedor de software, homem de pele morena, cerca de 25 anos, cabelo cacheado, camisa xadrez, em escritório residencial, em pé na mesa alta, comparando o smartphone com o monitor e anotando no caderno. Objetos: monitor, teclado, smartphone em suporte, caderno e copo. Telas sem escritos visíveis. Sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>analise-e-desenvolvimento-de-sistemas-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -1338,6 +1851,9 @@
   </si>
   <si>
     <t>analise-e-desenvolvimento-de-sistemas</t>
+  </si>
+  <si>
+    <t>Domine linguagens de programação, arquitetura de software e gestão de banco de dados para analisar e construir sistemas.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Análise e Desenvolvimento de Sistemas (ADS) da Cruzeiro do Sul Virtual é a formação ideal para quem busca inserção rápida no mercado de TI.
@@ -1378,6 +1894,30 @@
   </si>
   <si>
     <t>Desenvolva habilidades em Análise e Desenvolvimento de Sistemas de forma flexível e acessível. Bolsas de até 100%!</t>
+  </si>
+  <si>
+    <t>Modelagem de sistemas e banco de dados</t>
+  </si>
+  <si>
+    <t>Analista de sistemas de cerca de 31 anos, mulher de pele clara, cabelo liso escuro preso com presilha, óculos retangulares, colete de malha sobre blusa e calça de alfaiataria, desenhando o diagrama.</t>
+  </si>
+  <si>
+    <t>Sala de reunião pequena em empresa brasileira, flipchart, mesa oval, cadeiras iguais, persiana, ambiente corporativo acessível.</t>
+  </si>
+  <si>
+    <t>flipchart, canetões, folhas com diagramas em caixas, laptop fechado, adesivos em branco</t>
+  </si>
+  <si>
+    <t>Desenha caixas e setas de um modelo de dados no flipchart e aponta uma folha na mesa, sentada à direita, laptop fechado.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentada à direita junto ao flipchart, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da persiana, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagramas com escritos; sala de diretoria de luxo; código na tela; estereótipo de TI; atividade tecnicamente incorreta; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de sistemas, mulher de pele clara, cerca de 31 anos, cabelo liso preso, óculos retangulares, colete de malha, em sala de reunião, desenhando caixas e setas no flipchart com o laptop fechado. Objetos: flipchart, canetões, folhas com diagramas em caixas, laptop fechado e adesivos em branco. Flipchart e folhas sem escritos visíveis. Sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
   </si>
   <si>
     <t>gestao-publica-ead-tecnologo</t>
@@ -6640,26 +7180,29 @@
       <c r="G7" t="s">
         <v>158</v>
       </c>
+      <c r="H7" t="s">
+        <v>159</v>
+      </c>
       <c r="I7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q7" t="s">
         <v>47</v>
@@ -6668,30 +7211,57 @@
         <v>48</v>
       </c>
       <c r="S7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="U7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="V7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X7" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>172</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>175</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>176</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>177</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>178</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
@@ -6705,23 +7275,26 @@
       <c r="G8" t="s">
         <v>89</v>
       </c>
+      <c r="H8" t="s">
+        <v>182</v>
+      </c>
       <c r="I8" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="J8" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="K8" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L8" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="M8" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="N8" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="O8" t="s">
         <v>141</v>
@@ -6736,27 +7309,54 @@
         <v>48</v>
       </c>
       <c r="T8" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="U8" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="V8" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X8" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>195</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>196</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>197</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>198</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>199</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C9" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="D9" t="s">
         <v>65</v>
@@ -6768,25 +7368,28 @@
         <v>66</v>
       </c>
       <c r="G9" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H9" t="s">
+        <v>204</v>
       </c>
       <c r="I9" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="J9" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="K9" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="L9" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="M9" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="N9" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="P9" t="s">
         <v>46</v>
@@ -6798,27 +7401,54 @@
         <v>48</v>
       </c>
       <c r="T9" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="U9" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="V9" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X9" t="s">
+        <v>214</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>216</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>217</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>219</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>220</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>221</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="C10" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
         <v>65</v>
@@ -6830,25 +7460,28 @@
         <v>66</v>
       </c>
       <c r="G10" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H10" t="s">
+        <v>225</v>
       </c>
       <c r="I10" t="s">
-        <v>198</v>
+        <v>226</v>
       </c>
       <c r="J10" t="s">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="K10" t="s">
-        <v>200</v>
+        <v>228</v>
       </c>
       <c r="L10" t="s">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="M10" t="s">
-        <v>202</v>
+        <v>230</v>
       </c>
       <c r="N10" t="s">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="P10" t="s">
         <v>46</v>
@@ -6860,27 +7493,54 @@
         <v>48</v>
       </c>
       <c r="T10" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="U10" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="V10" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X10" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>236</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>238</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>239</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>241</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>242</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>244</v>
       </c>
       <c r="C11" t="s">
-        <v>209</v>
+        <v>245</v>
       </c>
       <c r="D11" t="s">
         <v>65</v>
@@ -6894,23 +7554,26 @@
       <c r="G11" t="s">
         <v>38</v>
       </c>
+      <c r="H11" t="s">
+        <v>246</v>
+      </c>
       <c r="I11" t="s">
-        <v>210</v>
+        <v>247</v>
       </c>
       <c r="J11" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="K11" t="s">
-        <v>212</v>
+        <v>249</v>
       </c>
       <c r="L11" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="M11" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="N11" t="s">
-        <v>215</v>
+        <v>252</v>
       </c>
       <c r="P11" t="s">
         <v>46</v>
@@ -6922,27 +7585,54 @@
         <v>48</v>
       </c>
       <c r="T11" t="s">
-        <v>216</v>
+        <v>253</v>
       </c>
       <c r="U11" t="s">
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="V11" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="W11" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X11" t="s">
+        <v>256</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>259</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>263</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>264</v>
       </c>
       <c r="B12" t="s">
-        <v>220</v>
+        <v>265</v>
       </c>
       <c r="C12" t="s">
-        <v>221</v>
+        <v>266</v>
       </c>
       <c r="D12" t="s">
         <v>35</v>
@@ -6956,23 +7646,26 @@
       <c r="G12" t="s">
         <v>158</v>
       </c>
+      <c r="H12" t="s">
+        <v>267</v>
+      </c>
       <c r="I12" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="J12" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="K12" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="L12" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="M12" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="N12" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="P12" t="s">
         <v>46</v>
@@ -6984,27 +7677,54 @@
         <v>48</v>
       </c>
       <c r="T12" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="U12" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="V12" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X12" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>278</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>279</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>280</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>281</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>283</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>284</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>231</v>
+        <v>285</v>
       </c>
       <c r="B13" t="s">
-        <v>232</v>
+        <v>286</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>287</v>
       </c>
       <c r="D13" t="s">
         <v>65</v>
@@ -7016,25 +7736,28 @@
         <v>66</v>
       </c>
       <c r="G13" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H13" t="s">
+        <v>288</v>
       </c>
       <c r="I13" t="s">
-        <v>234</v>
+        <v>289</v>
       </c>
       <c r="J13" t="s">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="K13" t="s">
-        <v>236</v>
+        <v>291</v>
       </c>
       <c r="L13" t="s">
-        <v>237</v>
+        <v>292</v>
       </c>
       <c r="M13" t="s">
-        <v>238</v>
+        <v>293</v>
       </c>
       <c r="N13" t="s">
-        <v>239</v>
+        <v>294</v>
       </c>
       <c r="P13" t="s">
         <v>46</v>
@@ -7046,27 +7769,54 @@
         <v>48</v>
       </c>
       <c r="T13" t="s">
-        <v>240</v>
+        <v>295</v>
       </c>
       <c r="U13" t="s">
-        <v>241</v>
+        <v>296</v>
       </c>
       <c r="V13" t="s">
-        <v>242</v>
+        <v>297</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X13" t="s">
+        <v>298</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>299</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>300</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>301</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>302</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>303</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>304</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>305</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="B14" t="s">
-        <v>244</v>
+        <v>307</v>
       </c>
       <c r="C14" t="s">
-        <v>245</v>
+        <v>308</v>
       </c>
       <c r="D14" t="s">
         <v>65</v>
@@ -7078,25 +7828,28 @@
         <v>66</v>
       </c>
       <c r="G14" t="s">
-        <v>246</v>
+        <v>309</v>
+      </c>
+      <c r="H14" t="s">
+        <v>310</v>
       </c>
       <c r="I14" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="J14" t="s">
-        <v>248</v>
+        <v>312</v>
       </c>
       <c r="K14" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="L14" t="s">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="M14" t="s">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="N14" t="s">
-        <v>252</v>
+        <v>316</v>
       </c>
       <c r="P14" t="s">
         <v>46</v>
@@ -7108,27 +7861,54 @@
         <v>48</v>
       </c>
       <c r="T14" t="s">
-        <v>253</v>
+        <v>317</v>
       </c>
       <c r="U14" t="s">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="V14" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="W14" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X14" t="s">
+        <v>320</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>321</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>322</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>323</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>324</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>325</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>326</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>327</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>256</v>
+        <v>328</v>
       </c>
       <c r="B15" t="s">
-        <v>257</v>
+        <v>329</v>
       </c>
       <c r="C15" t="s">
-        <v>258</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
         <v>65</v>
@@ -7140,25 +7920,28 @@
         <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>259</v>
+        <v>331</v>
+      </c>
+      <c r="H15" t="s">
+        <v>332</v>
       </c>
       <c r="I15" t="s">
-        <v>260</v>
+        <v>333</v>
       </c>
       <c r="J15" t="s">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="K15" t="s">
-        <v>262</v>
+        <v>335</v>
       </c>
       <c r="L15" t="s">
-        <v>263</v>
+        <v>336</v>
       </c>
       <c r="M15" t="s">
-        <v>264</v>
+        <v>337</v>
       </c>
       <c r="N15" t="s">
-        <v>265</v>
+        <v>338</v>
       </c>
       <c r="P15" t="s">
         <v>46</v>
@@ -7170,27 +7953,54 @@
         <v>48</v>
       </c>
       <c r="T15" t="s">
-        <v>266</v>
+        <v>339</v>
       </c>
       <c r="U15" t="s">
-        <v>267</v>
+        <v>340</v>
       </c>
       <c r="V15" t="s">
-        <v>268</v>
+        <v>341</v>
       </c>
       <c r="W15" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X15" t="s">
+        <v>342</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>343</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>344</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>345</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>346</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>347</v>
+      </c>
+      <c r="AD15" t="s">
+        <v>348</v>
+      </c>
+      <c r="AE15" t="s">
+        <v>349</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>269</v>
+        <v>350</v>
       </c>
       <c r="B16" t="s">
-        <v>270</v>
+        <v>351</v>
       </c>
       <c r="C16" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
       <c r="D16" t="s">
         <v>65</v>
@@ -7202,25 +8012,28 @@
         <v>66</v>
       </c>
       <c r="G16" t="s">
-        <v>259</v>
+        <v>331</v>
+      </c>
+      <c r="H16" t="s">
+        <v>353</v>
       </c>
       <c r="I16" t="s">
-        <v>272</v>
+        <v>354</v>
       </c>
       <c r="J16" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="K16" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
       <c r="L16" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="M16" t="s">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="N16" t="s">
-        <v>277</v>
+        <v>359</v>
       </c>
       <c r="P16" t="s">
         <v>46</v>
@@ -7232,27 +8045,54 @@
         <v>48</v>
       </c>
       <c r="T16" t="s">
-        <v>278</v>
+        <v>360</v>
       </c>
       <c r="U16" t="s">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="V16" t="s">
-        <v>280</v>
+        <v>362</v>
       </c>
       <c r="W16" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X16" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>364</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>365</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>366</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>367</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>368</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>369</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>370</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>281</v>
+        <v>371</v>
       </c>
       <c r="B17" t="s">
-        <v>282</v>
+        <v>372</v>
       </c>
       <c r="C17" t="s">
-        <v>283</v>
+        <v>373</v>
       </c>
       <c r="D17" t="s">
         <v>65</v>
@@ -7264,25 +8104,28 @@
         <v>66</v>
       </c>
       <c r="G17" t="s">
-        <v>259</v>
+        <v>331</v>
+      </c>
+      <c r="H17" t="s">
+        <v>374</v>
       </c>
       <c r="I17" t="s">
-        <v>284</v>
+        <v>375</v>
       </c>
       <c r="J17" t="s">
-        <v>285</v>
+        <v>376</v>
       </c>
       <c r="K17" t="s">
-        <v>286</v>
+        <v>377</v>
       </c>
       <c r="L17" t="s">
-        <v>287</v>
+        <v>378</v>
       </c>
       <c r="M17" t="s">
-        <v>288</v>
+        <v>379</v>
       </c>
       <c r="N17" t="s">
-        <v>289</v>
+        <v>380</v>
       </c>
       <c r="P17" t="s">
         <v>46</v>
@@ -7294,27 +8137,54 @@
         <v>48</v>
       </c>
       <c r="T17" t="s">
-        <v>290</v>
+        <v>381</v>
       </c>
       <c r="U17" t="s">
-        <v>291</v>
+        <v>382</v>
       </c>
       <c r="V17" t="s">
-        <v>292</v>
+        <v>383</v>
       </c>
       <c r="W17" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X17" t="s">
+        <v>384</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>385</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>386</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>387</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>388</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>389</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>390</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>391</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="B18" t="s">
-        <v>294</v>
+        <v>393</v>
       </c>
       <c r="C18" t="s">
-        <v>295</v>
+        <v>394</v>
       </c>
       <c r="D18" t="s">
         <v>65</v>
@@ -7326,25 +8196,28 @@
         <v>66</v>
       </c>
       <c r="G18" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H18" t="s">
+        <v>395</v>
       </c>
       <c r="I18" t="s">
-        <v>296</v>
+        <v>396</v>
       </c>
       <c r="J18" t="s">
-        <v>297</v>
+        <v>397</v>
       </c>
       <c r="K18" t="s">
-        <v>298</v>
+        <v>398</v>
       </c>
       <c r="L18" t="s">
-        <v>299</v>
+        <v>399</v>
       </c>
       <c r="M18" t="s">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N18" t="s">
-        <v>301</v>
+        <v>401</v>
       </c>
       <c r="P18" t="s">
         <v>46</v>
@@ -7356,27 +8229,54 @@
         <v>48</v>
       </c>
       <c r="T18" t="s">
-        <v>302</v>
+        <v>402</v>
       </c>
       <c r="U18" t="s">
-        <v>303</v>
+        <v>403</v>
       </c>
       <c r="V18" t="s">
-        <v>304</v>
+        <v>404</v>
       </c>
       <c r="W18" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X18" t="s">
+        <v>405</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>406</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>407</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>408</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>409</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>410</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>411</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>412</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>305</v>
+        <v>413</v>
       </c>
       <c r="B19" t="s">
-        <v>306</v>
+        <v>414</v>
       </c>
       <c r="C19" t="s">
-        <v>307</v>
+        <v>415</v>
       </c>
       <c r="D19" t="s">
         <v>35</v>
@@ -7390,26 +8290,29 @@
       <c r="G19" t="s">
         <v>158</v>
       </c>
+      <c r="H19" t="s">
+        <v>416</v>
+      </c>
       <c r="I19" t="s">
-        <v>308</v>
+        <v>417</v>
       </c>
       <c r="J19" t="s">
-        <v>309</v>
+        <v>418</v>
       </c>
       <c r="K19" t="s">
-        <v>310</v>
+        <v>419</v>
       </c>
       <c r="L19" t="s">
-        <v>311</v>
+        <v>420</v>
       </c>
       <c r="M19" t="s">
-        <v>312</v>
+        <v>421</v>
       </c>
       <c r="N19" t="s">
-        <v>313</v>
+        <v>422</v>
       </c>
       <c r="P19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q19" t="s">
         <v>47</v>
@@ -7418,30 +8321,57 @@
         <v>48</v>
       </c>
       <c r="S19" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T19" t="s">
-        <v>314</v>
+        <v>423</v>
       </c>
       <c r="U19" t="s">
-        <v>315</v>
+        <v>424</v>
       </c>
       <c r="V19" t="s">
-        <v>316</v>
+        <v>425</v>
       </c>
       <c r="W19" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X19" t="s">
+        <v>426</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>427</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>428</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>429</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>430</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>431</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>432</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>433</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>317</v>
+        <v>434</v>
       </c>
       <c r="B20" t="s">
-        <v>318</v>
+        <v>435</v>
       </c>
       <c r="C20" t="s">
-        <v>319</v>
+        <v>436</v>
       </c>
       <c r="D20" t="s">
         <v>35</v>
@@ -7453,28 +8383,31 @@
         <v>133</v>
       </c>
       <c r="G20" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H20" t="s">
+        <v>437</v>
       </c>
       <c r="I20" t="s">
-        <v>320</v>
+        <v>438</v>
       </c>
       <c r="J20" t="s">
-        <v>321</v>
+        <v>439</v>
       </c>
       <c r="K20" t="s">
-        <v>322</v>
+        <v>440</v>
       </c>
       <c r="L20" t="s">
-        <v>323</v>
+        <v>441</v>
       </c>
       <c r="M20" t="s">
-        <v>324</v>
+        <v>442</v>
       </c>
       <c r="N20" t="s">
-        <v>325</v>
+        <v>443</v>
       </c>
       <c r="P20" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q20" t="s">
         <v>47</v>
@@ -7483,30 +8416,57 @@
         <v>48</v>
       </c>
       <c r="S20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T20" t="s">
-        <v>326</v>
+        <v>444</v>
       </c>
       <c r="U20" t="s">
-        <v>327</v>
+        <v>445</v>
       </c>
       <c r="V20" t="s">
-        <v>328</v>
+        <v>446</v>
       </c>
       <c r="W20" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X20" t="s">
+        <v>447</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>448</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>449</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>450</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>451</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>452</v>
+      </c>
+      <c r="AD20" t="s">
+        <v>453</v>
+      </c>
+      <c r="AE20" t="s">
+        <v>454</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>329</v>
+        <v>455</v>
       </c>
       <c r="B21" t="s">
-        <v>330</v>
+        <v>456</v>
       </c>
       <c r="C21" t="s">
-        <v>331</v>
+        <v>457</v>
       </c>
       <c r="D21" t="s">
         <v>65</v>
@@ -7518,25 +8478,28 @@
         <v>66</v>
       </c>
       <c r="G21" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H21" t="s">
+        <v>458</v>
       </c>
       <c r="I21" t="s">
-        <v>332</v>
+        <v>459</v>
       </c>
       <c r="J21" t="s">
-        <v>333</v>
+        <v>460</v>
       </c>
       <c r="K21" t="s">
-        <v>334</v>
+        <v>461</v>
       </c>
       <c r="L21" t="s">
-        <v>335</v>
+        <v>462</v>
       </c>
       <c r="M21" t="s">
-        <v>336</v>
+        <v>463</v>
       </c>
       <c r="N21" t="s">
-        <v>337</v>
+        <v>464</v>
       </c>
       <c r="P21" t="s">
         <v>46</v>
@@ -7548,27 +8511,54 @@
         <v>48</v>
       </c>
       <c r="T21" t="s">
-        <v>338</v>
+        <v>465</v>
       </c>
       <c r="U21" t="s">
-        <v>339</v>
+        <v>466</v>
       </c>
       <c r="V21" t="s">
-        <v>340</v>
+        <v>467</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X21" t="s">
+        <v>468</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>469</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>470</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>471</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>472</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD21" t="s">
+        <v>474</v>
+      </c>
+      <c r="AE21" t="s">
+        <v>475</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>341</v>
+        <v>476</v>
       </c>
       <c r="B22" t="s">
-        <v>342</v>
+        <v>477</v>
       </c>
       <c r="C22" t="s">
-        <v>343</v>
+        <v>478</v>
       </c>
       <c r="D22" t="s">
         <v>65</v>
@@ -7582,26 +8572,29 @@
       <c r="G22" t="s">
         <v>89</v>
       </c>
+      <c r="H22" t="s">
+        <v>479</v>
+      </c>
       <c r="I22" t="s">
-        <v>344</v>
+        <v>480</v>
       </c>
       <c r="J22" t="s">
-        <v>345</v>
+        <v>481</v>
       </c>
       <c r="K22" t="s">
-        <v>346</v>
+        <v>482</v>
       </c>
       <c r="L22" t="s">
-        <v>347</v>
+        <v>483</v>
       </c>
       <c r="M22" t="s">
-        <v>348</v>
+        <v>484</v>
       </c>
       <c r="N22" t="s">
-        <v>349</v>
+        <v>485</v>
       </c>
       <c r="P22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q22" t="s">
         <v>47</v>
@@ -7610,30 +8603,57 @@
         <v>48</v>
       </c>
       <c r="S22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T22" t="s">
-        <v>350</v>
+        <v>486</v>
       </c>
       <c r="U22" t="s">
-        <v>351</v>
+        <v>487</v>
       </c>
       <c r="V22" t="s">
-        <v>352</v>
+        <v>488</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X22" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>490</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>491</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>492</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>493</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>494</v>
+      </c>
+      <c r="AD22" t="s">
+        <v>495</v>
+      </c>
+      <c r="AE22" t="s">
+        <v>496</v>
+      </c>
+      <c r="AF22" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>353</v>
+        <v>497</v>
       </c>
       <c r="B23" t="s">
-        <v>354</v>
+        <v>498</v>
       </c>
       <c r="C23" t="s">
-        <v>355</v>
+        <v>499</v>
       </c>
       <c r="D23" t="s">
         <v>65</v>
@@ -7645,25 +8665,28 @@
         <v>66</v>
       </c>
       <c r="G23" t="s">
-        <v>356</v>
+        <v>500</v>
+      </c>
+      <c r="H23" t="s">
+        <v>501</v>
       </c>
       <c r="I23" t="s">
-        <v>357</v>
+        <v>502</v>
       </c>
       <c r="J23" t="s">
-        <v>358</v>
+        <v>503</v>
       </c>
       <c r="K23" t="s">
-        <v>359</v>
+        <v>504</v>
       </c>
       <c r="L23" t="s">
-        <v>360</v>
+        <v>505</v>
       </c>
       <c r="M23" t="s">
-        <v>361</v>
+        <v>506</v>
       </c>
       <c r="N23" t="s">
-        <v>362</v>
+        <v>507</v>
       </c>
       <c r="P23" t="s">
         <v>46</v>
@@ -7675,27 +8698,54 @@
         <v>48</v>
       </c>
       <c r="T23" t="s">
-        <v>363</v>
+        <v>508</v>
       </c>
       <c r="U23" t="s">
-        <v>364</v>
+        <v>509</v>
       </c>
       <c r="V23" t="s">
-        <v>365</v>
+        <v>510</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X23" t="s">
+        <v>511</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>512</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>513</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>514</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>515</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>516</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE23" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF23" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>366</v>
+        <v>519</v>
       </c>
       <c r="B24" t="s">
-        <v>367</v>
+        <v>520</v>
       </c>
       <c r="C24" t="s">
-        <v>368</v>
+        <v>521</v>
       </c>
       <c r="D24" t="s">
         <v>157</v>
@@ -7709,26 +8759,29 @@
       <c r="G24" t="s">
         <v>158</v>
       </c>
+      <c r="H24" t="s">
+        <v>522</v>
+      </c>
       <c r="I24" t="s">
-        <v>369</v>
+        <v>523</v>
       </c>
       <c r="J24" t="s">
-        <v>370</v>
+        <v>524</v>
       </c>
       <c r="K24" t="s">
-        <v>371</v>
+        <v>525</v>
       </c>
       <c r="L24" t="s">
-        <v>372</v>
+        <v>526</v>
       </c>
       <c r="M24" t="s">
-        <v>373</v>
+        <v>527</v>
       </c>
       <c r="N24" t="s">
-        <v>374</v>
+        <v>528</v>
       </c>
       <c r="P24" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q24" t="s">
         <v>47</v>
@@ -7737,30 +8790,57 @@
         <v>48</v>
       </c>
       <c r="S24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T24" t="s">
-        <v>375</v>
+        <v>529</v>
       </c>
       <c r="U24" t="s">
-        <v>376</v>
+        <v>530</v>
       </c>
       <c r="V24" t="s">
-        <v>377</v>
+        <v>531</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X24" t="s">
+        <v>532</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>533</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>534</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>535</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>536</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>537</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>538</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>539</v>
+      </c>
+      <c r="AF24" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>378</v>
+        <v>540</v>
       </c>
       <c r="B25" t="s">
-        <v>379</v>
+        <v>541</v>
       </c>
       <c r="C25" t="s">
-        <v>380</v>
+        <v>542</v>
       </c>
       <c r="D25" t="s">
         <v>65</v>
@@ -7772,25 +8852,28 @@
         <v>66</v>
       </c>
       <c r="G25" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H25" t="s">
+        <v>543</v>
       </c>
       <c r="I25" t="s">
-        <v>381</v>
+        <v>544</v>
       </c>
       <c r="J25" t="s">
-        <v>382</v>
+        <v>545</v>
       </c>
       <c r="K25" t="s">
-        <v>383</v>
+        <v>546</v>
       </c>
       <c r="L25" t="s">
-        <v>384</v>
+        <v>547</v>
       </c>
       <c r="M25" t="s">
-        <v>385</v>
+        <v>548</v>
       </c>
       <c r="N25" t="s">
-        <v>386</v>
+        <v>549</v>
       </c>
       <c r="P25" t="s">
         <v>46</v>
@@ -7802,27 +8885,54 @@
         <v>48</v>
       </c>
       <c r="T25" t="s">
-        <v>387</v>
+        <v>550</v>
       </c>
       <c r="U25" t="s">
-        <v>388</v>
+        <v>551</v>
       </c>
       <c r="V25" t="s">
-        <v>389</v>
+        <v>552</v>
       </c>
       <c r="W25" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X25" t="s">
+        <v>553</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>554</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>555</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>556</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>557</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>558</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>559</v>
+      </c>
+      <c r="AE25" t="s">
+        <v>560</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>390</v>
+        <v>561</v>
       </c>
       <c r="B26" t="s">
-        <v>391</v>
+        <v>562</v>
       </c>
       <c r="C26" t="s">
-        <v>392</v>
+        <v>563</v>
       </c>
       <c r="D26" t="s">
         <v>65</v>
@@ -7834,25 +8944,28 @@
         <v>66</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>203</v>
+      </c>
+      <c r="H26" t="s">
+        <v>564</v>
       </c>
       <c r="I26" t="s">
-        <v>393</v>
+        <v>565</v>
       </c>
       <c r="J26" t="s">
-        <v>394</v>
+        <v>566</v>
       </c>
       <c r="K26" t="s">
-        <v>395</v>
+        <v>567</v>
       </c>
       <c r="L26" t="s">
-        <v>396</v>
+        <v>568</v>
       </c>
       <c r="M26" t="s">
-        <v>397</v>
+        <v>569</v>
       </c>
       <c r="N26" t="s">
-        <v>398</v>
+        <v>570</v>
       </c>
       <c r="O26" t="s">
         <v>141</v>
@@ -7867,27 +8980,54 @@
         <v>48</v>
       </c>
       <c r="T26" t="s">
-        <v>399</v>
+        <v>571</v>
       </c>
       <c r="U26" t="s">
-        <v>400</v>
+        <v>572</v>
       </c>
       <c r="V26" t="s">
-        <v>401</v>
+        <v>573</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X26" t="s">
+        <v>574</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>575</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>576</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>578</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>579</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>580</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>581</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>402</v>
+        <v>582</v>
       </c>
       <c r="B27" t="s">
-        <v>403</v>
+        <v>583</v>
       </c>
       <c r="C27" t="s">
-        <v>404</v>
+        <v>584</v>
       </c>
       <c r="D27" t="s">
         <v>65</v>
@@ -7899,25 +9039,25 @@
         <v>66</v>
       </c>
       <c r="G27" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I27" t="s">
-        <v>405</v>
+        <v>585</v>
       </c>
       <c r="J27" t="s">
-        <v>406</v>
+        <v>586</v>
       </c>
       <c r="K27" t="s">
-        <v>407</v>
+        <v>587</v>
       </c>
       <c r="L27" t="s">
-        <v>408</v>
+        <v>588</v>
       </c>
       <c r="M27" t="s">
-        <v>409</v>
+        <v>589</v>
       </c>
       <c r="N27" t="s">
-        <v>410</v>
+        <v>590</v>
       </c>
       <c r="P27" t="s">
         <v>46</v>
@@ -7929,13 +9069,13 @@
         <v>48</v>
       </c>
       <c r="T27" t="s">
-        <v>411</v>
+        <v>591</v>
       </c>
       <c r="U27" t="s">
-        <v>412</v>
+        <v>592</v>
       </c>
       <c r="V27" t="s">
-        <v>413</v>
+        <v>593</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>52</v>
@@ -7943,13 +9083,13 @@
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>414</v>
+        <v>594</v>
       </c>
       <c r="B28" t="s">
-        <v>415</v>
+        <v>595</v>
       </c>
       <c r="C28" t="s">
-        <v>416</v>
+        <v>596</v>
       </c>
       <c r="D28" t="s">
         <v>65</v>
@@ -7961,25 +9101,25 @@
         <v>66</v>
       </c>
       <c r="G28" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I28" t="s">
-        <v>417</v>
+        <v>597</v>
       </c>
       <c r="J28" t="s">
-        <v>418</v>
+        <v>598</v>
       </c>
       <c r="K28" t="s">
-        <v>419</v>
+        <v>599</v>
       </c>
       <c r="L28" t="s">
-        <v>420</v>
+        <v>600</v>
       </c>
       <c r="M28" t="s">
-        <v>421</v>
+        <v>601</v>
       </c>
       <c r="N28" t="s">
-        <v>422</v>
+        <v>602</v>
       </c>
       <c r="P28" t="s">
         <v>46</v>
@@ -7991,13 +9131,13 @@
         <v>48</v>
       </c>
       <c r="T28" t="s">
-        <v>423</v>
+        <v>603</v>
       </c>
       <c r="U28" t="s">
-        <v>424</v>
+        <v>604</v>
       </c>
       <c r="V28" t="s">
-        <v>425</v>
+        <v>605</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>52</v>
@@ -8005,13 +9145,13 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>426</v>
+        <v>606</v>
       </c>
       <c r="B29" t="s">
-        <v>427</v>
+        <v>607</v>
       </c>
       <c r="C29" t="s">
-        <v>428</v>
+        <v>608</v>
       </c>
       <c r="D29" t="s">
         <v>35</v>
@@ -8026,22 +9166,22 @@
         <v>89</v>
       </c>
       <c r="I29" t="s">
-        <v>429</v>
+        <v>609</v>
       </c>
       <c r="J29" t="s">
-        <v>430</v>
+        <v>610</v>
       </c>
       <c r="K29" t="s">
-        <v>431</v>
+        <v>611</v>
       </c>
       <c r="L29" t="s">
-        <v>432</v>
+        <v>612</v>
       </c>
       <c r="M29" t="s">
-        <v>433</v>
+        <v>613</v>
       </c>
       <c r="N29" t="s">
-        <v>434</v>
+        <v>614</v>
       </c>
       <c r="O29" t="s">
         <v>141</v>
@@ -8056,13 +9196,13 @@
         <v>48</v>
       </c>
       <c r="T29" t="s">
-        <v>435</v>
+        <v>615</v>
       </c>
       <c r="U29" t="s">
-        <v>436</v>
+        <v>616</v>
       </c>
       <c r="V29" t="s">
-        <v>437</v>
+        <v>617</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>52</v>
@@ -8070,13 +9210,13 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>438</v>
+        <v>618</v>
       </c>
       <c r="B30" t="s">
-        <v>439</v>
+        <v>619</v>
       </c>
       <c r="C30" t="s">
-        <v>440</v>
+        <v>620</v>
       </c>
       <c r="D30" t="s">
         <v>35</v>
@@ -8091,25 +9231,25 @@
         <v>158</v>
       </c>
       <c r="I30" t="s">
-        <v>441</v>
+        <v>621</v>
       </c>
       <c r="J30" t="s">
-        <v>442</v>
+        <v>622</v>
       </c>
       <c r="K30" t="s">
-        <v>443</v>
+        <v>623</v>
       </c>
       <c r="L30" t="s">
-        <v>444</v>
+        <v>624</v>
       </c>
       <c r="M30" t="s">
-        <v>445</v>
+        <v>625</v>
       </c>
       <c r="N30" t="s">
-        <v>446</v>
+        <v>626</v>
       </c>
       <c r="P30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q30" t="s">
         <v>47</v>
@@ -8118,16 +9258,16 @@
         <v>48</v>
       </c>
       <c r="S30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T30" t="s">
-        <v>447</v>
+        <v>627</v>
       </c>
       <c r="U30" t="s">
-        <v>448</v>
+        <v>628</v>
       </c>
       <c r="V30" t="s">
-        <v>449</v>
+        <v>629</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>52</v>
@@ -8135,13 +9275,13 @@
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>450</v>
+        <v>630</v>
       </c>
       <c r="B31" t="s">
-        <v>451</v>
+        <v>631</v>
       </c>
       <c r="C31" t="s">
-        <v>452</v>
+        <v>632</v>
       </c>
       <c r="D31" t="s">
         <v>65</v>
@@ -8153,25 +9293,25 @@
         <v>66</v>
       </c>
       <c r="G31" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I31" t="s">
-        <v>453</v>
+        <v>633</v>
       </c>
       <c r="J31" t="s">
-        <v>454</v>
+        <v>634</v>
       </c>
       <c r="K31" t="s">
-        <v>455</v>
+        <v>635</v>
       </c>
       <c r="L31" t="s">
-        <v>456</v>
+        <v>636</v>
       </c>
       <c r="M31" t="s">
-        <v>457</v>
+        <v>637</v>
       </c>
       <c r="N31" t="s">
-        <v>458</v>
+        <v>638</v>
       </c>
       <c r="P31" t="s">
         <v>46</v>
@@ -8183,13 +9323,13 @@
         <v>48</v>
       </c>
       <c r="T31" t="s">
-        <v>459</v>
+        <v>639</v>
       </c>
       <c r="U31" t="s">
-        <v>460</v>
+        <v>640</v>
       </c>
       <c r="V31" t="s">
-        <v>461</v>
+        <v>641</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>52</v>
@@ -8197,13 +9337,13 @@
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>462</v>
+        <v>642</v>
       </c>
       <c r="B32" t="s">
-        <v>463</v>
+        <v>643</v>
       </c>
       <c r="C32" t="s">
-        <v>464</v>
+        <v>644</v>
       </c>
       <c r="D32" t="s">
         <v>65</v>
@@ -8215,31 +9355,31 @@
         <v>66</v>
       </c>
       <c r="G32" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I32" t="s">
-        <v>465</v>
+        <v>645</v>
       </c>
       <c r="J32" t="s">
-        <v>466</v>
+        <v>646</v>
       </c>
       <c r="K32" t="s">
-        <v>467</v>
+        <v>647</v>
       </c>
       <c r="L32" t="s">
-        <v>468</v>
+        <v>648</v>
       </c>
       <c r="M32" t="s">
-        <v>469</v>
+        <v>649</v>
       </c>
       <c r="N32" t="s">
-        <v>470</v>
+        <v>650</v>
       </c>
       <c r="O32" t="s">
         <v>141</v>
       </c>
       <c r="P32" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q32" t="s">
         <v>47</v>
@@ -8248,16 +9388,16 @@
         <v>48</v>
       </c>
       <c r="S32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T32" t="s">
-        <v>472</v>
+        <v>652</v>
       </c>
       <c r="U32" t="s">
-        <v>473</v>
+        <v>653</v>
       </c>
       <c r="V32" t="s">
-        <v>474</v>
+        <v>654</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>52</v>
@@ -8265,13 +9405,13 @@
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>475</v>
+        <v>655</v>
       </c>
       <c r="B33" t="s">
-        <v>476</v>
+        <v>656</v>
       </c>
       <c r="C33" t="s">
-        <v>477</v>
+        <v>657</v>
       </c>
       <c r="D33" t="s">
         <v>157</v>
@@ -8286,22 +9426,22 @@
         <v>158</v>
       </c>
       <c r="I33" t="s">
-        <v>478</v>
+        <v>658</v>
       </c>
       <c r="J33" t="s">
-        <v>479</v>
+        <v>659</v>
       </c>
       <c r="K33" t="s">
-        <v>480</v>
+        <v>660</v>
       </c>
       <c r="L33" t="s">
-        <v>481</v>
+        <v>661</v>
       </c>
       <c r="M33" t="s">
-        <v>482</v>
+        <v>662</v>
       </c>
       <c r="N33" t="s">
-        <v>483</v>
+        <v>663</v>
       </c>
       <c r="O33" t="s">
         <v>141</v>
@@ -8316,13 +9456,13 @@
         <v>48</v>
       </c>
       <c r="T33" t="s">
-        <v>484</v>
+        <v>664</v>
       </c>
       <c r="U33" t="s">
-        <v>485</v>
+        <v>665</v>
       </c>
       <c r="V33" t="s">
-        <v>486</v>
+        <v>666</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>52</v>
@@ -8330,13 +9470,13 @@
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>487</v>
+        <v>667</v>
       </c>
       <c r="B34" t="s">
-        <v>488</v>
+        <v>668</v>
       </c>
       <c r="C34" t="s">
-        <v>489</v>
+        <v>669</v>
       </c>
       <c r="D34" t="s">
         <v>35</v>
@@ -8348,25 +9488,25 @@
         <v>133</v>
       </c>
       <c r="G34" t="s">
-        <v>246</v>
+        <v>309</v>
       </c>
       <c r="I34" t="s">
-        <v>490</v>
+        <v>670</v>
       </c>
       <c r="J34" t="s">
-        <v>491</v>
+        <v>671</v>
       </c>
       <c r="K34" t="s">
-        <v>492</v>
+        <v>672</v>
       </c>
       <c r="L34" t="s">
-        <v>493</v>
+        <v>673</v>
       </c>
       <c r="M34" t="s">
-        <v>494</v>
+        <v>674</v>
       </c>
       <c r="N34" t="s">
-        <v>495</v>
+        <v>675</v>
       </c>
       <c r="O34" t="s">
         <v>141</v>
@@ -8381,13 +9521,13 @@
         <v>48</v>
       </c>
       <c r="T34" t="s">
-        <v>496</v>
+        <v>676</v>
       </c>
       <c r="U34" t="s">
-        <v>497</v>
+        <v>677</v>
       </c>
       <c r="V34" t="s">
-        <v>498</v>
+        <v>678</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>52</v>
@@ -8395,13 +9535,13 @@
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>499</v>
+        <v>679</v>
       </c>
       <c r="B35" t="s">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="C35" t="s">
-        <v>501</v>
+        <v>681</v>
       </c>
       <c r="D35" t="s">
         <v>157</v>
@@ -8416,25 +9556,25 @@
         <v>158</v>
       </c>
       <c r="I35" t="s">
-        <v>502</v>
+        <v>682</v>
       </c>
       <c r="J35" t="s">
-        <v>503</v>
+        <v>683</v>
       </c>
       <c r="K35" t="s">
-        <v>504</v>
+        <v>684</v>
       </c>
       <c r="L35" t="s">
-        <v>505</v>
+        <v>685</v>
       </c>
       <c r="M35" t="s">
-        <v>506</v>
+        <v>686</v>
       </c>
       <c r="N35" t="s">
-        <v>507</v>
+        <v>687</v>
       </c>
       <c r="P35" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q35" t="s">
         <v>47</v>
@@ -8443,16 +9583,16 @@
         <v>48</v>
       </c>
       <c r="S35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T35" t="s">
-        <v>508</v>
+        <v>688</v>
       </c>
       <c r="U35" t="s">
-        <v>509</v>
+        <v>689</v>
       </c>
       <c r="V35" t="s">
-        <v>510</v>
+        <v>690</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>52</v>
@@ -8460,13 +9600,13 @@
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>511</v>
+        <v>691</v>
       </c>
       <c r="B36" t="s">
-        <v>512</v>
+        <v>692</v>
       </c>
       <c r="C36" t="s">
-        <v>513</v>
+        <v>693</v>
       </c>
       <c r="D36" t="s">
         <v>157</v>
@@ -8481,25 +9621,25 @@
         <v>158</v>
       </c>
       <c r="I36" t="s">
-        <v>514</v>
+        <v>694</v>
       </c>
       <c r="J36" t="s">
-        <v>515</v>
+        <v>695</v>
       </c>
       <c r="K36" t="s">
-        <v>516</v>
+        <v>696</v>
       </c>
       <c r="L36" t="s">
-        <v>517</v>
+        <v>697</v>
       </c>
       <c r="M36" t="s">
-        <v>518</v>
+        <v>698</v>
       </c>
       <c r="N36" t="s">
-        <v>519</v>
+        <v>699</v>
       </c>
       <c r="P36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q36" t="s">
         <v>47</v>
@@ -8508,16 +9648,16 @@
         <v>48</v>
       </c>
       <c r="S36" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T36" t="s">
-        <v>520</v>
+        <v>700</v>
       </c>
       <c r="U36" t="s">
-        <v>521</v>
+        <v>701</v>
       </c>
       <c r="V36" t="s">
-        <v>522</v>
+        <v>702</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>52</v>
@@ -8525,13 +9665,13 @@
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>523</v>
+        <v>703</v>
       </c>
       <c r="B37" t="s">
-        <v>524</v>
+        <v>704</v>
       </c>
       <c r="C37" t="s">
-        <v>525</v>
+        <v>705</v>
       </c>
       <c r="D37" t="s">
         <v>65</v>
@@ -8543,25 +9683,25 @@
         <v>66</v>
       </c>
       <c r="G37" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I37" t="s">
-        <v>526</v>
+        <v>706</v>
       </c>
       <c r="J37" t="s">
-        <v>527</v>
+        <v>707</v>
       </c>
       <c r="K37" t="s">
-        <v>528</v>
+        <v>708</v>
       </c>
       <c r="L37" t="s">
-        <v>529</v>
+        <v>709</v>
       </c>
       <c r="M37" t="s">
-        <v>530</v>
+        <v>710</v>
       </c>
       <c r="N37" t="s">
-        <v>531</v>
+        <v>711</v>
       </c>
       <c r="P37" t="s">
         <v>46</v>
@@ -8573,13 +9713,13 @@
         <v>48</v>
       </c>
       <c r="T37" t="s">
-        <v>532</v>
+        <v>712</v>
       </c>
       <c r="U37" t="s">
-        <v>533</v>
+        <v>713</v>
       </c>
       <c r="V37" t="s">
-        <v>534</v>
+        <v>714</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>52</v>
@@ -8587,13 +9727,13 @@
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>535</v>
+        <v>715</v>
       </c>
       <c r="B38" t="s">
-        <v>536</v>
+        <v>716</v>
       </c>
       <c r="C38" t="s">
-        <v>537</v>
+        <v>717</v>
       </c>
       <c r="D38" t="s">
         <v>65</v>
@@ -8605,25 +9745,25 @@
         <v>66</v>
       </c>
       <c r="G38" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I38" t="s">
-        <v>538</v>
+        <v>718</v>
       </c>
       <c r="J38" t="s">
-        <v>539</v>
+        <v>719</v>
       </c>
       <c r="K38" t="s">
-        <v>540</v>
+        <v>720</v>
       </c>
       <c r="L38" t="s">
-        <v>541</v>
+        <v>721</v>
       </c>
       <c r="M38" t="s">
-        <v>542</v>
+        <v>722</v>
       </c>
       <c r="N38" t="s">
-        <v>543</v>
+        <v>723</v>
       </c>
       <c r="P38" t="s">
         <v>46</v>
@@ -8635,13 +9775,13 @@
         <v>48</v>
       </c>
       <c r="T38" t="s">
-        <v>544</v>
+        <v>724</v>
       </c>
       <c r="U38" t="s">
-        <v>545</v>
+        <v>725</v>
       </c>
       <c r="V38" t="s">
-        <v>546</v>
+        <v>726</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>52</v>
@@ -8649,13 +9789,13 @@
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>547</v>
+        <v>727</v>
       </c>
       <c r="B39" t="s">
-        <v>548</v>
+        <v>728</v>
       </c>
       <c r="C39" t="s">
-        <v>549</v>
+        <v>729</v>
       </c>
       <c r="D39" t="s">
         <v>65</v>
@@ -8667,25 +9807,25 @@
         <v>66</v>
       </c>
       <c r="G39" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I39" t="s">
-        <v>550</v>
+        <v>730</v>
       </c>
       <c r="J39" t="s">
-        <v>551</v>
+        <v>731</v>
       </c>
       <c r="K39" t="s">
-        <v>552</v>
+        <v>732</v>
       </c>
       <c r="L39" t="s">
-        <v>553</v>
+        <v>733</v>
       </c>
       <c r="M39" t="s">
-        <v>554</v>
+        <v>734</v>
       </c>
       <c r="N39" t="s">
-        <v>555</v>
+        <v>735</v>
       </c>
       <c r="P39" t="s">
         <v>46</v>
@@ -8697,13 +9837,13 @@
         <v>48</v>
       </c>
       <c r="T39" t="s">
-        <v>556</v>
+        <v>736</v>
       </c>
       <c r="U39" t="s">
-        <v>557</v>
+        <v>737</v>
       </c>
       <c r="V39" t="s">
-        <v>558</v>
+        <v>738</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>52</v>
@@ -8711,13 +9851,13 @@
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>559</v>
+        <v>739</v>
       </c>
       <c r="B40" t="s">
-        <v>560</v>
+        <v>740</v>
       </c>
       <c r="C40" t="s">
-        <v>561</v>
+        <v>741</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -8729,25 +9869,25 @@
         <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I40" t="s">
-        <v>562</v>
+        <v>742</v>
       </c>
       <c r="J40" t="s">
-        <v>563</v>
+        <v>743</v>
       </c>
       <c r="K40" t="s">
-        <v>564</v>
+        <v>744</v>
       </c>
       <c r="L40" t="s">
-        <v>565</v>
+        <v>745</v>
       </c>
       <c r="M40" t="s">
-        <v>566</v>
+        <v>746</v>
       </c>
       <c r="N40" t="s">
-        <v>567</v>
+        <v>747</v>
       </c>
       <c r="P40" t="s">
         <v>46</v>
@@ -8759,13 +9899,13 @@
         <v>48</v>
       </c>
       <c r="T40" t="s">
-        <v>568</v>
+        <v>748</v>
       </c>
       <c r="U40" t="s">
-        <v>569</v>
+        <v>749</v>
       </c>
       <c r="V40" t="s">
-        <v>570</v>
+        <v>750</v>
       </c>
       <c r="W40" s="1" t="s">
         <v>52</v>
@@ -8773,13 +9913,13 @@
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>571</v>
+        <v>751</v>
       </c>
       <c r="B41" t="s">
-        <v>572</v>
+        <v>752</v>
       </c>
       <c r="C41" t="s">
-        <v>573</v>
+        <v>753</v>
       </c>
       <c r="D41" t="s">
         <v>65</v>
@@ -8794,22 +9934,22 @@
         <v>89</v>
       </c>
       <c r="I41" t="s">
-        <v>574</v>
+        <v>754</v>
       </c>
       <c r="J41" t="s">
-        <v>575</v>
+        <v>755</v>
       </c>
       <c r="K41" t="s">
-        <v>576</v>
+        <v>756</v>
       </c>
       <c r="L41" t="s">
-        <v>577</v>
+        <v>757</v>
       </c>
       <c r="M41" t="s">
-        <v>578</v>
+        <v>758</v>
       </c>
       <c r="N41" t="s">
-        <v>579</v>
+        <v>759</v>
       </c>
       <c r="O41" t="s">
         <v>141</v>
@@ -8824,13 +9964,13 @@
         <v>48</v>
       </c>
       <c r="T41" t="s">
-        <v>580</v>
+        <v>760</v>
       </c>
       <c r="U41" t="s">
-        <v>581</v>
+        <v>761</v>
       </c>
       <c r="V41" t="s">
-        <v>582</v>
+        <v>762</v>
       </c>
       <c r="W41" s="1" t="s">
         <v>52</v>
@@ -8838,13 +9978,13 @@
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>583</v>
+        <v>763</v>
       </c>
       <c r="B42" t="s">
-        <v>584</v>
+        <v>764</v>
       </c>
       <c r="C42" t="s">
-        <v>585</v>
+        <v>765</v>
       </c>
       <c r="D42" t="s">
         <v>65</v>
@@ -8859,22 +9999,22 @@
         <v>38</v>
       </c>
       <c r="I42" t="s">
-        <v>586</v>
+        <v>766</v>
       </c>
       <c r="J42" t="s">
-        <v>587</v>
+        <v>767</v>
       </c>
       <c r="K42" t="s">
-        <v>588</v>
+        <v>768</v>
       </c>
       <c r="L42" t="s">
-        <v>589</v>
+        <v>769</v>
       </c>
       <c r="M42" t="s">
-        <v>590</v>
+        <v>770</v>
       </c>
       <c r="N42" t="s">
-        <v>591</v>
+        <v>771</v>
       </c>
       <c r="P42" t="s">
         <v>46</v>
@@ -8886,13 +10026,13 @@
         <v>48</v>
       </c>
       <c r="T42" t="s">
-        <v>592</v>
+        <v>772</v>
       </c>
       <c r="U42" t="s">
-        <v>593</v>
+        <v>773</v>
       </c>
       <c r="V42" t="s">
-        <v>594</v>
+        <v>774</v>
       </c>
       <c r="W42" s="1" t="s">
         <v>52</v>
@@ -8900,13 +10040,13 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>595</v>
+        <v>775</v>
       </c>
       <c r="B43" t="s">
-        <v>596</v>
+        <v>776</v>
       </c>
       <c r="C43" t="s">
-        <v>597</v>
+        <v>777</v>
       </c>
       <c r="D43" t="s">
         <v>65</v>
@@ -8921,28 +10061,28 @@
         <v>89</v>
       </c>
       <c r="I43" t="s">
-        <v>598</v>
+        <v>778</v>
       </c>
       <c r="J43" t="s">
-        <v>599</v>
+        <v>779</v>
       </c>
       <c r="K43" t="s">
-        <v>600</v>
+        <v>780</v>
       </c>
       <c r="L43" t="s">
-        <v>601</v>
+        <v>781</v>
       </c>
       <c r="M43" t="s">
-        <v>602</v>
+        <v>782</v>
       </c>
       <c r="N43" t="s">
-        <v>603</v>
+        <v>783</v>
       </c>
       <c r="O43" t="s">
         <v>141</v>
       </c>
       <c r="P43" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q43" t="s">
         <v>47</v>
@@ -8951,16 +10091,16 @@
         <v>48</v>
       </c>
       <c r="S43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T43" t="s">
-        <v>604</v>
+        <v>784</v>
       </c>
       <c r="U43" t="s">
-        <v>605</v>
+        <v>785</v>
       </c>
       <c r="V43" t="s">
-        <v>606</v>
+        <v>786</v>
       </c>
       <c r="W43" s="1" t="s">
         <v>52</v>
@@ -8968,13 +10108,13 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>607</v>
+        <v>787</v>
       </c>
       <c r="B44" t="s">
-        <v>608</v>
+        <v>788</v>
       </c>
       <c r="C44" t="s">
-        <v>609</v>
+        <v>789</v>
       </c>
       <c r="D44" t="s">
         <v>65</v>
@@ -8986,25 +10126,25 @@
         <v>66</v>
       </c>
       <c r="G44" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I44" t="s">
-        <v>610</v>
+        <v>790</v>
       </c>
       <c r="J44" t="s">
-        <v>611</v>
+        <v>791</v>
       </c>
       <c r="K44" t="s">
-        <v>612</v>
+        <v>792</v>
       </c>
       <c r="L44" t="s">
-        <v>613</v>
+        <v>793</v>
       </c>
       <c r="M44" t="s">
-        <v>614</v>
+        <v>794</v>
       </c>
       <c r="N44" t="s">
-        <v>615</v>
+        <v>795</v>
       </c>
       <c r="P44" t="s">
         <v>46</v>
@@ -9016,13 +10156,13 @@
         <v>48</v>
       </c>
       <c r="T44" t="s">
-        <v>616</v>
+        <v>796</v>
       </c>
       <c r="U44" t="s">
-        <v>617</v>
+        <v>797</v>
       </c>
       <c r="V44" t="s">
-        <v>618</v>
+        <v>798</v>
       </c>
       <c r="W44" s="1" t="s">
         <v>52</v>
@@ -9030,13 +10170,13 @@
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>619</v>
+        <v>799</v>
       </c>
       <c r="B45" t="s">
-        <v>620</v>
+        <v>800</v>
       </c>
       <c r="C45" t="s">
-        <v>621</v>
+        <v>801</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -9048,25 +10188,25 @@
         <v>66</v>
       </c>
       <c r="G45" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I45" t="s">
-        <v>622</v>
+        <v>802</v>
       </c>
       <c r="J45" t="s">
-        <v>623</v>
+        <v>803</v>
       </c>
       <c r="K45" t="s">
-        <v>624</v>
+        <v>804</v>
       </c>
       <c r="L45" t="s">
-        <v>625</v>
+        <v>805</v>
       </c>
       <c r="M45" t="s">
-        <v>626</v>
+        <v>806</v>
       </c>
       <c r="N45" t="s">
-        <v>627</v>
+        <v>807</v>
       </c>
       <c r="P45" t="s">
         <v>46</v>
@@ -9078,13 +10218,13 @@
         <v>48</v>
       </c>
       <c r="T45" t="s">
-        <v>628</v>
+        <v>808</v>
       </c>
       <c r="U45" t="s">
-        <v>629</v>
+        <v>809</v>
       </c>
       <c r="V45" t="s">
-        <v>630</v>
+        <v>810</v>
       </c>
       <c r="W45" s="1" t="s">
         <v>52</v>
@@ -9092,13 +10232,13 @@
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>631</v>
+        <v>811</v>
       </c>
       <c r="B46" t="s">
-        <v>632</v>
+        <v>812</v>
       </c>
       <c r="C46" t="s">
-        <v>633</v>
+        <v>813</v>
       </c>
       <c r="D46" t="s">
         <v>65</v>
@@ -9110,28 +10250,28 @@
         <v>88</v>
       </c>
       <c r="G46" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I46" t="s">
-        <v>634</v>
+        <v>814</v>
       </c>
       <c r="J46" t="s">
-        <v>635</v>
+        <v>815</v>
       </c>
       <c r="K46" t="s">
-        <v>636</v>
+        <v>816</v>
       </c>
       <c r="L46" t="s">
-        <v>637</v>
+        <v>817</v>
       </c>
       <c r="M46" t="s">
-        <v>638</v>
+        <v>818</v>
       </c>
       <c r="N46" t="s">
-        <v>639</v>
+        <v>819</v>
       </c>
       <c r="P46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q46" t="s">
         <v>47</v>
@@ -9140,16 +10280,16 @@
         <v>48</v>
       </c>
       <c r="S46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T46" t="s">
-        <v>640</v>
+        <v>820</v>
       </c>
       <c r="U46" t="s">
-        <v>641</v>
+        <v>821</v>
       </c>
       <c r="V46" t="s">
-        <v>642</v>
+        <v>822</v>
       </c>
       <c r="W46" s="1" t="s">
         <v>52</v>
@@ -9157,13 +10297,13 @@
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>643</v>
+        <v>823</v>
       </c>
       <c r="B47" t="s">
-        <v>644</v>
+        <v>824</v>
       </c>
       <c r="C47" t="s">
-        <v>645</v>
+        <v>825</v>
       </c>
       <c r="D47" t="s">
         <v>65</v>
@@ -9175,25 +10315,25 @@
         <v>66</v>
       </c>
       <c r="G47" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I47" t="s">
-        <v>646</v>
+        <v>826</v>
       </c>
       <c r="J47" t="s">
-        <v>647</v>
+        <v>827</v>
       </c>
       <c r="K47" t="s">
-        <v>648</v>
+        <v>828</v>
       </c>
       <c r="L47" t="s">
-        <v>649</v>
+        <v>829</v>
       </c>
       <c r="M47" t="s">
-        <v>650</v>
+        <v>830</v>
       </c>
       <c r="N47" t="s">
-        <v>651</v>
+        <v>831</v>
       </c>
       <c r="P47" t="s">
         <v>46</v>
@@ -9205,13 +10345,13 @@
         <v>48</v>
       </c>
       <c r="T47" t="s">
-        <v>652</v>
+        <v>832</v>
       </c>
       <c r="U47" t="s">
-        <v>653</v>
+        <v>833</v>
       </c>
       <c r="V47" t="s">
-        <v>654</v>
+        <v>834</v>
       </c>
       <c r="W47" s="1" t="s">
         <v>52</v>
@@ -9219,13 +10359,13 @@
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>655</v>
+        <v>835</v>
       </c>
       <c r="B48" t="s">
-        <v>656</v>
+        <v>836</v>
       </c>
       <c r="C48" t="s">
-        <v>657</v>
+        <v>837</v>
       </c>
       <c r="D48" t="s">
         <v>35</v>
@@ -9240,22 +10380,22 @@
         <v>158</v>
       </c>
       <c r="I48" t="s">
-        <v>658</v>
+        <v>838</v>
       </c>
       <c r="J48" t="s">
-        <v>659</v>
+        <v>839</v>
       </c>
       <c r="K48" t="s">
-        <v>660</v>
+        <v>840</v>
       </c>
       <c r="L48" t="s">
-        <v>661</v>
+        <v>841</v>
       </c>
       <c r="M48" t="s">
-        <v>662</v>
+        <v>842</v>
       </c>
       <c r="N48" t="s">
-        <v>663</v>
+        <v>843</v>
       </c>
       <c r="P48" t="s">
         <v>46</v>
@@ -9267,13 +10407,13 @@
         <v>48</v>
       </c>
       <c r="T48" t="s">
-        <v>664</v>
+        <v>844</v>
       </c>
       <c r="U48" t="s">
-        <v>665</v>
+        <v>845</v>
       </c>
       <c r="V48" t="s">
-        <v>666</v>
+        <v>846</v>
       </c>
       <c r="W48" s="1" t="s">
         <v>52</v>
@@ -9281,13 +10421,13 @@
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>667</v>
+        <v>847</v>
       </c>
       <c r="B49" t="s">
-        <v>668</v>
+        <v>848</v>
       </c>
       <c r="C49" t="s">
-        <v>669</v>
+        <v>849</v>
       </c>
       <c r="D49" t="s">
         <v>35</v>
@@ -9299,31 +10439,31 @@
         <v>133</v>
       </c>
       <c r="G49" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I49" t="s">
-        <v>670</v>
+        <v>850</v>
       </c>
       <c r="J49" t="s">
-        <v>671</v>
+        <v>851</v>
       </c>
       <c r="K49" t="s">
-        <v>672</v>
+        <v>852</v>
       </c>
       <c r="L49" t="s">
-        <v>673</v>
+        <v>853</v>
       </c>
       <c r="M49" t="s">
-        <v>674</v>
+        <v>854</v>
       </c>
       <c r="N49" t="s">
-        <v>675</v>
+        <v>855</v>
       </c>
       <c r="O49" t="s">
         <v>141</v>
       </c>
       <c r="P49" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q49" t="s">
         <v>47</v>
@@ -9332,16 +10472,16 @@
         <v>48</v>
       </c>
       <c r="S49" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T49" t="s">
-        <v>676</v>
+        <v>856</v>
       </c>
       <c r="U49" t="s">
-        <v>677</v>
+        <v>857</v>
       </c>
       <c r="V49" t="s">
-        <v>678</v>
+        <v>858</v>
       </c>
       <c r="W49" s="1" t="s">
         <v>52</v>
@@ -9349,13 +10489,13 @@
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>679</v>
+        <v>859</v>
       </c>
       <c r="B50" t="s">
-        <v>680</v>
+        <v>860</v>
       </c>
       <c r="C50" t="s">
-        <v>681</v>
+        <v>861</v>
       </c>
       <c r="D50" t="s">
         <v>65</v>
@@ -9367,31 +10507,31 @@
         <v>66</v>
       </c>
       <c r="G50" t="s">
-        <v>680</v>
+        <v>860</v>
       </c>
       <c r="I50" t="s">
-        <v>682</v>
+        <v>862</v>
       </c>
       <c r="J50" t="s">
-        <v>683</v>
+        <v>863</v>
       </c>
       <c r="K50" t="s">
-        <v>684</v>
+        <v>864</v>
       </c>
       <c r="L50" t="s">
-        <v>685</v>
+        <v>865</v>
       </c>
       <c r="M50" t="s">
-        <v>686</v>
+        <v>866</v>
       </c>
       <c r="N50" t="s">
-        <v>687</v>
+        <v>867</v>
       </c>
       <c r="O50" t="s">
         <v>141</v>
       </c>
       <c r="P50" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q50" t="s">
         <v>47</v>
@@ -9400,16 +10540,16 @@
         <v>48</v>
       </c>
       <c r="S50" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T50" t="s">
-        <v>688</v>
+        <v>868</v>
       </c>
       <c r="U50" t="s">
-        <v>689</v>
+        <v>869</v>
       </c>
       <c r="V50" t="s">
-        <v>690</v>
+        <v>870</v>
       </c>
       <c r="W50" s="1" t="s">
         <v>52</v>
@@ -9417,13 +10557,13 @@
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>691</v>
+        <v>871</v>
       </c>
       <c r="B51" t="s">
-        <v>692</v>
+        <v>872</v>
       </c>
       <c r="C51" t="s">
-        <v>693</v>
+        <v>873</v>
       </c>
       <c r="D51" t="s">
         <v>65</v>
@@ -9438,22 +10578,22 @@
         <v>89</v>
       </c>
       <c r="I51" t="s">
-        <v>694</v>
+        <v>874</v>
       </c>
       <c r="J51" t="s">
-        <v>695</v>
+        <v>875</v>
       </c>
       <c r="K51" t="s">
-        <v>696</v>
+        <v>876</v>
       </c>
       <c r="L51" t="s">
-        <v>697</v>
+        <v>877</v>
       </c>
       <c r="M51" t="s">
-        <v>698</v>
+        <v>878</v>
       </c>
       <c r="N51" t="s">
-        <v>699</v>
+        <v>879</v>
       </c>
       <c r="O51" t="s">
         <v>141</v>
@@ -9468,13 +10608,13 @@
         <v>48</v>
       </c>
       <c r="T51" t="s">
-        <v>700</v>
+        <v>880</v>
       </c>
       <c r="U51" t="s">
-        <v>701</v>
+        <v>881</v>
       </c>
       <c r="V51" t="s">
-        <v>702</v>
+        <v>882</v>
       </c>
       <c r="W51" s="1" t="s">
         <v>52</v>
@@ -9482,13 +10622,13 @@
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>703</v>
+        <v>883</v>
       </c>
       <c r="B52" t="s">
-        <v>704</v>
+        <v>884</v>
       </c>
       <c r="C52" t="s">
-        <v>705</v>
+        <v>885</v>
       </c>
       <c r="D52" t="s">
         <v>65</v>
@@ -9500,25 +10640,25 @@
         <v>66</v>
       </c>
       <c r="G52" t="s">
-        <v>356</v>
+        <v>500</v>
       </c>
       <c r="I52" t="s">
-        <v>706</v>
+        <v>886</v>
       </c>
       <c r="J52" t="s">
-        <v>707</v>
+        <v>887</v>
       </c>
       <c r="K52" t="s">
-        <v>708</v>
+        <v>888</v>
       </c>
       <c r="L52" t="s">
-        <v>709</v>
+        <v>889</v>
       </c>
       <c r="M52" t="s">
-        <v>710</v>
+        <v>890</v>
       </c>
       <c r="N52" t="s">
-        <v>711</v>
+        <v>891</v>
       </c>
       <c r="P52" t="s">
         <v>46</v>
@@ -9530,13 +10670,13 @@
         <v>48</v>
       </c>
       <c r="T52" t="s">
-        <v>712</v>
+        <v>892</v>
       </c>
       <c r="U52" t="s">
-        <v>713</v>
+        <v>893</v>
       </c>
       <c r="V52" t="s">
-        <v>714</v>
+        <v>894</v>
       </c>
       <c r="W52" s="1" t="s">
         <v>52</v>
@@ -9544,13 +10684,13 @@
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>715</v>
+        <v>895</v>
       </c>
       <c r="B53" t="s">
-        <v>716</v>
+        <v>896</v>
       </c>
       <c r="C53" t="s">
-        <v>717</v>
+        <v>897</v>
       </c>
       <c r="D53" t="s">
         <v>65</v>
@@ -9565,22 +10705,22 @@
         <v>38</v>
       </c>
       <c r="I53" t="s">
-        <v>718</v>
+        <v>898</v>
       </c>
       <c r="J53" t="s">
-        <v>719</v>
+        <v>899</v>
       </c>
       <c r="K53" t="s">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="L53" t="s">
-        <v>721</v>
+        <v>901</v>
       </c>
       <c r="M53" t="s">
-        <v>722</v>
+        <v>902</v>
       </c>
       <c r="N53" t="s">
-        <v>723</v>
+        <v>903</v>
       </c>
       <c r="P53" t="s">
         <v>46</v>
@@ -9592,13 +10732,13 @@
         <v>48</v>
       </c>
       <c r="T53" t="s">
-        <v>724</v>
+        <v>904</v>
       </c>
       <c r="U53" t="s">
-        <v>725</v>
+        <v>905</v>
       </c>
       <c r="V53" t="s">
-        <v>726</v>
+        <v>906</v>
       </c>
       <c r="W53" s="1" t="s">
         <v>52</v>
@@ -9606,13 +10746,13 @@
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>727</v>
+        <v>907</v>
       </c>
       <c r="B54" t="s">
-        <v>728</v>
+        <v>908</v>
       </c>
       <c r="C54" t="s">
-        <v>729</v>
+        <v>909</v>
       </c>
       <c r="D54" t="s">
         <v>35</v>
@@ -9624,25 +10764,25 @@
         <v>37</v>
       </c>
       <c r="G54" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I54" t="s">
-        <v>730</v>
+        <v>910</v>
       </c>
       <c r="J54" t="s">
-        <v>731</v>
+        <v>911</v>
       </c>
       <c r="K54" t="s">
-        <v>732</v>
+        <v>912</v>
       </c>
       <c r="L54" t="s">
-        <v>733</v>
+        <v>913</v>
       </c>
       <c r="M54" t="s">
-        <v>734</v>
+        <v>914</v>
       </c>
       <c r="N54" t="s">
-        <v>735</v>
+        <v>915</v>
       </c>
       <c r="P54" t="s">
         <v>46</v>
@@ -9654,13 +10794,13 @@
         <v>48</v>
       </c>
       <c r="T54" t="s">
-        <v>736</v>
+        <v>916</v>
       </c>
       <c r="U54" t="s">
-        <v>737</v>
+        <v>917</v>
       </c>
       <c r="V54" t="s">
-        <v>738</v>
+        <v>918</v>
       </c>
       <c r="W54" s="1" t="s">
         <v>52</v>
@@ -9668,13 +10808,13 @@
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>739</v>
+        <v>919</v>
       </c>
       <c r="B55" t="s">
-        <v>740</v>
+        <v>920</v>
       </c>
       <c r="C55" t="s">
-        <v>741</v>
+        <v>921</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
@@ -9686,25 +10826,25 @@
         <v>66</v>
       </c>
       <c r="G55" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I55" t="s">
-        <v>742</v>
+        <v>922</v>
       </c>
       <c r="J55" t="s">
-        <v>743</v>
+        <v>923</v>
       </c>
       <c r="K55" t="s">
-        <v>744</v>
+        <v>924</v>
       </c>
       <c r="L55" t="s">
-        <v>745</v>
+        <v>925</v>
       </c>
       <c r="M55" t="s">
-        <v>746</v>
+        <v>926</v>
       </c>
       <c r="N55" t="s">
-        <v>747</v>
+        <v>927</v>
       </c>
       <c r="P55" t="s">
         <v>46</v>
@@ -9716,13 +10856,13 @@
         <v>48</v>
       </c>
       <c r="T55" t="s">
-        <v>748</v>
+        <v>928</v>
       </c>
       <c r="U55" t="s">
-        <v>749</v>
+        <v>929</v>
       </c>
       <c r="V55" t="s">
-        <v>750</v>
+        <v>930</v>
       </c>
       <c r="W55" s="1" t="s">
         <v>52</v>
@@ -9730,13 +10870,13 @@
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>751</v>
+        <v>931</v>
       </c>
       <c r="B56" t="s">
-        <v>752</v>
+        <v>932</v>
       </c>
       <c r="C56" t="s">
-        <v>753</v>
+        <v>933</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -9748,25 +10888,25 @@
         <v>66</v>
       </c>
       <c r="G56" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I56" t="s">
-        <v>754</v>
+        <v>934</v>
       </c>
       <c r="J56" t="s">
-        <v>755</v>
+        <v>935</v>
       </c>
       <c r="K56" t="s">
-        <v>756</v>
+        <v>936</v>
       </c>
       <c r="L56" t="s">
-        <v>757</v>
+        <v>937</v>
       </c>
       <c r="M56" t="s">
-        <v>758</v>
+        <v>938</v>
       </c>
       <c r="N56" t="s">
-        <v>759</v>
+        <v>939</v>
       </c>
       <c r="P56" t="s">
         <v>46</v>
@@ -9778,13 +10918,13 @@
         <v>48</v>
       </c>
       <c r="T56" t="s">
-        <v>760</v>
+        <v>940</v>
       </c>
       <c r="U56" t="s">
-        <v>761</v>
+        <v>941</v>
       </c>
       <c r="V56" t="s">
-        <v>762</v>
+        <v>942</v>
       </c>
       <c r="W56" s="1" t="s">
         <v>52</v>
@@ -9792,13 +10932,13 @@
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>763</v>
+        <v>943</v>
       </c>
       <c r="B57" t="s">
-        <v>764</v>
+        <v>944</v>
       </c>
       <c r="C57" t="s">
-        <v>765</v>
+        <v>945</v>
       </c>
       <c r="D57" t="s">
         <v>65</v>
@@ -9810,25 +10950,25 @@
         <v>66</v>
       </c>
       <c r="G57" t="s">
-        <v>246</v>
+        <v>309</v>
       </c>
       <c r="I57" t="s">
-        <v>766</v>
+        <v>946</v>
       </c>
       <c r="J57" t="s">
-        <v>767</v>
+        <v>947</v>
       </c>
       <c r="K57" t="s">
-        <v>768</v>
+        <v>948</v>
       </c>
       <c r="L57" t="s">
-        <v>769</v>
+        <v>949</v>
       </c>
       <c r="M57" t="s">
-        <v>770</v>
+        <v>950</v>
       </c>
       <c r="N57" t="s">
-        <v>771</v>
+        <v>951</v>
       </c>
       <c r="P57" t="s">
         <v>46</v>
@@ -9840,13 +10980,13 @@
         <v>48</v>
       </c>
       <c r="T57" t="s">
-        <v>772</v>
+        <v>952</v>
       </c>
       <c r="U57" t="s">
-        <v>773</v>
+        <v>953</v>
       </c>
       <c r="V57" t="s">
-        <v>774</v>
+        <v>954</v>
       </c>
       <c r="W57" s="1" t="s">
         <v>52</v>
@@ -9854,13 +10994,13 @@
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>775</v>
+        <v>955</v>
       </c>
       <c r="B58" t="s">
-        <v>776</v>
+        <v>956</v>
       </c>
       <c r="C58" t="s">
-        <v>777</v>
+        <v>957</v>
       </c>
       <c r="D58" t="s">
         <v>65</v>
@@ -9872,25 +11012,25 @@
         <v>66</v>
       </c>
       <c r="G58" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I58" t="s">
-        <v>778</v>
+        <v>958</v>
       </c>
       <c r="J58" t="s">
-        <v>779</v>
+        <v>959</v>
       </c>
       <c r="K58" t="s">
-        <v>780</v>
+        <v>960</v>
       </c>
       <c r="L58" t="s">
-        <v>781</v>
+        <v>961</v>
       </c>
       <c r="M58" t="s">
-        <v>782</v>
+        <v>962</v>
       </c>
       <c r="N58" t="s">
-        <v>783</v>
+        <v>963</v>
       </c>
       <c r="P58" t="s">
         <v>46</v>
@@ -9902,13 +11042,13 @@
         <v>48</v>
       </c>
       <c r="T58" t="s">
-        <v>784</v>
+        <v>964</v>
       </c>
       <c r="U58" t="s">
-        <v>785</v>
+        <v>965</v>
       </c>
       <c r="V58" t="s">
-        <v>786</v>
+        <v>966</v>
       </c>
       <c r="W58" s="1" t="s">
         <v>52</v>
@@ -9916,13 +11056,13 @@
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>787</v>
+        <v>967</v>
       </c>
       <c r="B59" t="s">
-        <v>788</v>
+        <v>968</v>
       </c>
       <c r="C59" t="s">
-        <v>789</v>
+        <v>969</v>
       </c>
       <c r="D59" t="s">
         <v>35</v>
@@ -9937,25 +11077,25 @@
         <v>89</v>
       </c>
       <c r="I59" t="s">
-        <v>790</v>
+        <v>970</v>
       </c>
       <c r="J59" t="s">
-        <v>791</v>
+        <v>971</v>
       </c>
       <c r="K59" t="s">
-        <v>792</v>
+        <v>972</v>
       </c>
       <c r="L59" t="s">
-        <v>793</v>
+        <v>973</v>
       </c>
       <c r="M59" t="s">
-        <v>794</v>
+        <v>974</v>
       </c>
       <c r="N59" t="s">
-        <v>795</v>
+        <v>975</v>
       </c>
       <c r="P59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q59" t="s">
         <v>47</v>
@@ -9964,16 +11104,16 @@
         <v>48</v>
       </c>
       <c r="S59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T59" t="s">
-        <v>796</v>
+        <v>976</v>
       </c>
       <c r="U59" t="s">
-        <v>797</v>
+        <v>977</v>
       </c>
       <c r="V59" t="s">
-        <v>798</v>
+        <v>978</v>
       </c>
       <c r="W59" s="1" t="s">
         <v>52</v>
@@ -9981,13 +11121,13 @@
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>799</v>
+        <v>979</v>
       </c>
       <c r="B60" t="s">
-        <v>800</v>
+        <v>980</v>
       </c>
       <c r="C60" t="s">
-        <v>801</v>
+        <v>981</v>
       </c>
       <c r="D60" t="s">
         <v>65</v>
@@ -9999,25 +11139,25 @@
         <v>66</v>
       </c>
       <c r="G60" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I60" t="s">
-        <v>802</v>
+        <v>982</v>
       </c>
       <c r="J60" t="s">
-        <v>803</v>
+        <v>983</v>
       </c>
       <c r="K60" t="s">
-        <v>804</v>
+        <v>984</v>
       </c>
       <c r="L60" t="s">
-        <v>805</v>
+        <v>985</v>
       </c>
       <c r="M60" t="s">
-        <v>806</v>
+        <v>986</v>
       </c>
       <c r="N60" t="s">
-        <v>807</v>
+        <v>987</v>
       </c>
       <c r="P60" t="s">
         <v>46</v>
@@ -10029,13 +11169,13 @@
         <v>48</v>
       </c>
       <c r="T60" t="s">
-        <v>808</v>
+        <v>988</v>
       </c>
       <c r="U60" t="s">
-        <v>809</v>
+        <v>989</v>
       </c>
       <c r="V60" t="s">
-        <v>810</v>
+        <v>990</v>
       </c>
       <c r="W60" s="1" t="s">
         <v>52</v>
@@ -10043,13 +11183,13 @@
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>811</v>
+        <v>991</v>
       </c>
       <c r="B61" t="s">
-        <v>812</v>
+        <v>992</v>
       </c>
       <c r="C61" t="s">
-        <v>813</v>
+        <v>993</v>
       </c>
       <c r="D61" t="s">
         <v>65</v>
@@ -10061,28 +11201,28 @@
         <v>66</v>
       </c>
       <c r="G61" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I61" t="s">
-        <v>814</v>
+        <v>994</v>
       </c>
       <c r="J61" t="s">
-        <v>815</v>
+        <v>995</v>
       </c>
       <c r="K61" t="s">
-        <v>816</v>
+        <v>996</v>
       </c>
       <c r="L61" t="s">
-        <v>817</v>
+        <v>997</v>
       </c>
       <c r="M61" t="s">
-        <v>818</v>
+        <v>998</v>
       </c>
       <c r="N61" t="s">
-        <v>819</v>
+        <v>999</v>
       </c>
       <c r="P61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q61" t="s">
         <v>47</v>
@@ -10091,16 +11231,16 @@
         <v>48</v>
       </c>
       <c r="S61" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T61" t="s">
-        <v>820</v>
+        <v>1000</v>
       </c>
       <c r="U61" t="s">
-        <v>821</v>
+        <v>1001</v>
       </c>
       <c r="V61" t="s">
-        <v>822</v>
+        <v>1002</v>
       </c>
       <c r="W61" s="1" t="s">
         <v>52</v>
@@ -10108,13 +11248,13 @@
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>823</v>
+        <v>1003</v>
       </c>
       <c r="B62" t="s">
-        <v>824</v>
+        <v>1004</v>
       </c>
       <c r="C62" t="s">
-        <v>825</v>
+        <v>1005</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
@@ -10126,25 +11266,25 @@
         <v>66</v>
       </c>
       <c r="G62" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I62" t="s">
-        <v>826</v>
+        <v>1006</v>
       </c>
       <c r="J62" t="s">
-        <v>827</v>
+        <v>1007</v>
       </c>
       <c r="K62" t="s">
-        <v>828</v>
+        <v>1008</v>
       </c>
       <c r="L62" t="s">
-        <v>829</v>
+        <v>1009</v>
       </c>
       <c r="M62" t="s">
-        <v>830</v>
+        <v>1010</v>
       </c>
       <c r="N62" t="s">
-        <v>831</v>
+        <v>1011</v>
       </c>
       <c r="P62" t="s">
         <v>46</v>
@@ -10156,13 +11296,13 @@
         <v>48</v>
       </c>
       <c r="T62" t="s">
-        <v>832</v>
+        <v>1012</v>
       </c>
       <c r="U62" t="s">
-        <v>833</v>
+        <v>1013</v>
       </c>
       <c r="V62" t="s">
-        <v>834</v>
+        <v>1014</v>
       </c>
       <c r="W62" s="1" t="s">
         <v>52</v>
@@ -10170,13 +11310,13 @@
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>835</v>
+        <v>1015</v>
       </c>
       <c r="B63" t="s">
-        <v>836</v>
+        <v>1016</v>
       </c>
       <c r="C63" t="s">
-        <v>837</v>
+        <v>1017</v>
       </c>
       <c r="D63" t="s">
         <v>35</v>
@@ -10191,22 +11331,22 @@
         <v>38</v>
       </c>
       <c r="I63" t="s">
-        <v>838</v>
+        <v>1018</v>
       </c>
       <c r="J63" t="s">
-        <v>839</v>
+        <v>1019</v>
       </c>
       <c r="K63" t="s">
-        <v>840</v>
+        <v>1020</v>
       </c>
       <c r="L63" t="s">
-        <v>841</v>
+        <v>1021</v>
       </c>
       <c r="M63" t="s">
-        <v>842</v>
+        <v>1022</v>
       </c>
       <c r="N63" t="s">
-        <v>843</v>
+        <v>1023</v>
       </c>
       <c r="P63" t="s">
         <v>46</v>
@@ -10218,13 +11358,13 @@
         <v>48</v>
       </c>
       <c r="T63" t="s">
-        <v>844</v>
+        <v>1024</v>
       </c>
       <c r="U63" t="s">
-        <v>845</v>
+        <v>1025</v>
       </c>
       <c r="V63" t="s">
-        <v>846</v>
+        <v>1026</v>
       </c>
       <c r="W63" s="1" t="s">
         <v>52</v>
@@ -10232,13 +11372,13 @@
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>847</v>
+        <v>1027</v>
       </c>
       <c r="B64" t="s">
-        <v>848</v>
+        <v>1028</v>
       </c>
       <c r="C64" t="s">
-        <v>849</v>
+        <v>1029</v>
       </c>
       <c r="D64" t="s">
         <v>65</v>
@@ -10253,22 +11393,22 @@
         <v>38</v>
       </c>
       <c r="I64" t="s">
-        <v>850</v>
+        <v>1030</v>
       </c>
       <c r="J64" t="s">
-        <v>851</v>
+        <v>1031</v>
       </c>
       <c r="K64" t="s">
-        <v>852</v>
+        <v>1032</v>
       </c>
       <c r="L64" t="s">
-        <v>853</v>
+        <v>1033</v>
       </c>
       <c r="M64" t="s">
-        <v>854</v>
+        <v>1034</v>
       </c>
       <c r="N64" t="s">
-        <v>855</v>
+        <v>1035</v>
       </c>
       <c r="P64" t="s">
         <v>46</v>
@@ -10280,13 +11420,13 @@
         <v>48</v>
       </c>
       <c r="T64" t="s">
-        <v>856</v>
+        <v>1036</v>
       </c>
       <c r="U64" t="s">
-        <v>857</v>
+        <v>1037</v>
       </c>
       <c r="V64" t="s">
-        <v>858</v>
+        <v>1038</v>
       </c>
       <c r="W64" s="1" t="s">
         <v>52</v>
@@ -10294,13 +11434,13 @@
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>859</v>
+        <v>1039</v>
       </c>
       <c r="B65" t="s">
-        <v>860</v>
+        <v>1040</v>
       </c>
       <c r="C65" t="s">
-        <v>861</v>
+        <v>1041</v>
       </c>
       <c r="D65" t="s">
         <v>157</v>
@@ -10315,25 +11455,25 @@
         <v>158</v>
       </c>
       <c r="I65" t="s">
-        <v>862</v>
+        <v>1042</v>
       </c>
       <c r="J65" t="s">
-        <v>863</v>
+        <v>1043</v>
       </c>
       <c r="K65" t="s">
-        <v>864</v>
+        <v>1044</v>
       </c>
       <c r="L65" t="s">
-        <v>865</v>
+        <v>1045</v>
       </c>
       <c r="M65" t="s">
-        <v>866</v>
+        <v>1046</v>
       </c>
       <c r="N65" t="s">
-        <v>867</v>
+        <v>1047</v>
       </c>
       <c r="P65" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q65" t="s">
         <v>47</v>
@@ -10342,16 +11482,16 @@
         <v>48</v>
       </c>
       <c r="S65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T65" t="s">
-        <v>868</v>
+        <v>1048</v>
       </c>
       <c r="U65" t="s">
-        <v>869</v>
+        <v>1049</v>
       </c>
       <c r="V65" t="s">
-        <v>870</v>
+        <v>1050</v>
       </c>
       <c r="W65" s="1" t="s">
         <v>52</v>
@@ -10359,13 +11499,13 @@
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>871</v>
+        <v>1051</v>
       </c>
       <c r="B66" t="s">
-        <v>872</v>
+        <v>1052</v>
       </c>
       <c r="C66" t="s">
-        <v>873</v>
+        <v>1053</v>
       </c>
       <c r="D66" t="s">
         <v>35</v>
@@ -10377,31 +11517,31 @@
         <v>37</v>
       </c>
       <c r="G66" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I66" t="s">
-        <v>874</v>
+        <v>1054</v>
       </c>
       <c r="J66" t="s">
-        <v>875</v>
+        <v>1055</v>
       </c>
       <c r="K66" t="s">
-        <v>876</v>
+        <v>1056</v>
       </c>
       <c r="L66" t="s">
-        <v>877</v>
+        <v>1057</v>
       </c>
       <c r="M66" t="s">
-        <v>878</v>
+        <v>1058</v>
       </c>
       <c r="N66" t="s">
-        <v>879</v>
+        <v>1059</v>
       </c>
       <c r="O66" t="s">
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q66" t="s">
         <v>47</v>
@@ -10410,16 +11550,16 @@
         <v>48</v>
       </c>
       <c r="S66" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T66" t="s">
-        <v>880</v>
+        <v>1060</v>
       </c>
       <c r="U66" t="s">
-        <v>881</v>
+        <v>1061</v>
       </c>
       <c r="V66" t="s">
-        <v>882</v>
+        <v>1062</v>
       </c>
       <c r="W66" s="1" t="s">
         <v>52</v>
@@ -10427,13 +11567,13 @@
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>883</v>
+        <v>1063</v>
       </c>
       <c r="B67" t="s">
-        <v>884</v>
+        <v>1064</v>
       </c>
       <c r="C67" t="s">
-        <v>885</v>
+        <v>1065</v>
       </c>
       <c r="D67" t="s">
         <v>35</v>
@@ -10448,22 +11588,22 @@
         <v>89</v>
       </c>
       <c r="I67" t="s">
-        <v>886</v>
+        <v>1066</v>
       </c>
       <c r="J67" t="s">
-        <v>887</v>
+        <v>1067</v>
       </c>
       <c r="K67" t="s">
-        <v>888</v>
+        <v>1068</v>
       </c>
       <c r="L67" t="s">
-        <v>889</v>
+        <v>1069</v>
       </c>
       <c r="M67" t="s">
-        <v>890</v>
+        <v>1070</v>
       </c>
       <c r="N67" t="s">
-        <v>891</v>
+        <v>1071</v>
       </c>
       <c r="O67" t="s">
         <v>141</v>
@@ -10478,13 +11618,13 @@
         <v>48</v>
       </c>
       <c r="T67" t="s">
-        <v>892</v>
+        <v>1072</v>
       </c>
       <c r="U67" t="s">
-        <v>893</v>
+        <v>1073</v>
       </c>
       <c r="V67" t="s">
-        <v>894</v>
+        <v>1074</v>
       </c>
       <c r="W67" s="1" t="s">
         <v>52</v>
@@ -10492,13 +11632,13 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>895</v>
+        <v>1075</v>
       </c>
       <c r="B68" t="s">
-        <v>896</v>
+        <v>1076</v>
       </c>
       <c r="C68" t="s">
-        <v>897</v>
+        <v>1077</v>
       </c>
       <c r="D68" t="s">
         <v>157</v>
@@ -10513,22 +11653,22 @@
         <v>158</v>
       </c>
       <c r="I68" t="s">
-        <v>898</v>
+        <v>1078</v>
       </c>
       <c r="J68" t="s">
-        <v>899</v>
+        <v>1079</v>
       </c>
       <c r="K68" t="s">
-        <v>900</v>
+        <v>1080</v>
       </c>
       <c r="L68" t="s">
-        <v>901</v>
+        <v>1081</v>
       </c>
       <c r="M68" t="s">
-        <v>902</v>
+        <v>1082</v>
       </c>
       <c r="N68" t="s">
-        <v>903</v>
+        <v>1083</v>
       </c>
       <c r="P68" t="s">
         <v>46</v>
@@ -10540,13 +11680,13 @@
         <v>48</v>
       </c>
       <c r="T68" t="s">
-        <v>904</v>
+        <v>1084</v>
       </c>
       <c r="U68" t="s">
-        <v>905</v>
+        <v>1085</v>
       </c>
       <c r="V68" t="s">
-        <v>906</v>
+        <v>1086</v>
       </c>
       <c r="W68" s="1" t="s">
         <v>52</v>
@@ -10554,13 +11694,13 @@
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>907</v>
+        <v>1087</v>
       </c>
       <c r="B69" t="s">
-        <v>908</v>
+        <v>1088</v>
       </c>
       <c r="C69" t="s">
-        <v>909</v>
+        <v>1089</v>
       </c>
       <c r="D69" t="s">
         <v>35</v>
@@ -10575,22 +11715,22 @@
         <v>89</v>
       </c>
       <c r="I69" t="s">
-        <v>910</v>
+        <v>1090</v>
       </c>
       <c r="J69" t="s">
-        <v>911</v>
+        <v>1091</v>
       </c>
       <c r="K69" t="s">
-        <v>912</v>
+        <v>1092</v>
       </c>
       <c r="L69" t="s">
-        <v>913</v>
+        <v>1093</v>
       </c>
       <c r="M69" t="s">
-        <v>914</v>
+        <v>1094</v>
       </c>
       <c r="N69" t="s">
-        <v>915</v>
+        <v>1095</v>
       </c>
       <c r="O69" t="s">
         <v>141</v>
@@ -10605,13 +11745,13 @@
         <v>48</v>
       </c>
       <c r="T69" t="s">
-        <v>916</v>
+        <v>1096</v>
       </c>
       <c r="U69" t="s">
-        <v>917</v>
+        <v>1097</v>
       </c>
       <c r="V69" t="s">
-        <v>918</v>
+        <v>1098</v>
       </c>
       <c r="W69" s="1" t="s">
         <v>52</v>
@@ -10619,13 +11759,13 @@
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>919</v>
+        <v>1099</v>
       </c>
       <c r="B70" t="s">
-        <v>920</v>
+        <v>1100</v>
       </c>
       <c r="C70" t="s">
-        <v>921</v>
+        <v>1101</v>
       </c>
       <c r="D70" t="s">
         <v>35</v>
@@ -10640,22 +11780,22 @@
         <v>89</v>
       </c>
       <c r="I70" t="s">
-        <v>922</v>
+        <v>1102</v>
       </c>
       <c r="J70" t="s">
-        <v>923</v>
+        <v>1103</v>
       </c>
       <c r="K70" t="s">
-        <v>924</v>
+        <v>1104</v>
       </c>
       <c r="L70" t="s">
-        <v>925</v>
+        <v>1105</v>
       </c>
       <c r="M70" t="s">
-        <v>926</v>
+        <v>1106</v>
       </c>
       <c r="N70" t="s">
-        <v>927</v>
+        <v>1107</v>
       </c>
       <c r="O70" t="s">
         <v>141</v>
@@ -10670,13 +11810,13 @@
         <v>48</v>
       </c>
       <c r="T70" t="s">
-        <v>928</v>
+        <v>1108</v>
       </c>
       <c r="U70" t="s">
-        <v>929</v>
+        <v>1109</v>
       </c>
       <c r="V70" t="s">
-        <v>930</v>
+        <v>1110</v>
       </c>
       <c r="W70" s="1" t="s">
         <v>52</v>
@@ -10684,13 +11824,13 @@
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>931</v>
+        <v>1111</v>
       </c>
       <c r="B71" t="s">
-        <v>932</v>
+        <v>1112</v>
       </c>
       <c r="C71" t="s">
-        <v>933</v>
+        <v>1113</v>
       </c>
       <c r="D71" t="s">
         <v>35</v>
@@ -10705,25 +11845,25 @@
         <v>158</v>
       </c>
       <c r="I71" t="s">
-        <v>934</v>
+        <v>1114</v>
       </c>
       <c r="J71" t="s">
-        <v>935</v>
+        <v>1115</v>
       </c>
       <c r="K71" t="s">
-        <v>936</v>
+        <v>1116</v>
       </c>
       <c r="L71" t="s">
-        <v>937</v>
+        <v>1117</v>
       </c>
       <c r="M71" t="s">
-        <v>938</v>
+        <v>1118</v>
       </c>
       <c r="N71" t="s">
-        <v>939</v>
+        <v>1119</v>
       </c>
       <c r="P71" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q71" t="s">
         <v>47</v>
@@ -10732,16 +11872,16 @@
         <v>48</v>
       </c>
       <c r="S71" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T71" t="s">
-        <v>940</v>
+        <v>1120</v>
       </c>
       <c r="U71" t="s">
-        <v>941</v>
+        <v>1121</v>
       </c>
       <c r="V71" t="s">
-        <v>942</v>
+        <v>1122</v>
       </c>
       <c r="W71" s="1" t="s">
         <v>52</v>
@@ -10749,16 +11889,16 @@
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>943</v>
+        <v>1123</v>
       </c>
       <c r="B72" t="s">
-        <v>944</v>
+        <v>1124</v>
       </c>
       <c r="C72" t="s">
-        <v>945</v>
+        <v>1125</v>
       </c>
       <c r="D72" t="s">
-        <v>946</v>
+        <v>1126</v>
       </c>
       <c r="E72" t="s">
         <v>132</v>
@@ -10770,25 +11910,25 @@
         <v>158</v>
       </c>
       <c r="I72" t="s">
-        <v>947</v>
+        <v>1127</v>
       </c>
       <c r="J72" t="s">
-        <v>948</v>
+        <v>1128</v>
       </c>
       <c r="K72" t="s">
-        <v>949</v>
+        <v>1129</v>
       </c>
       <c r="L72" t="s">
-        <v>950</v>
+        <v>1130</v>
       </c>
       <c r="M72" t="s">
-        <v>951</v>
+        <v>1131</v>
       </c>
       <c r="N72" t="s">
-        <v>952</v>
+        <v>1132</v>
       </c>
       <c r="P72" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q72" t="s">
         <v>47</v>
@@ -10797,16 +11937,16 @@
         <v>48</v>
       </c>
       <c r="S72" t="s">
-        <v>953</v>
+        <v>1133</v>
       </c>
       <c r="T72" t="s">
-        <v>954</v>
+        <v>1134</v>
       </c>
       <c r="U72" t="s">
-        <v>955</v>
+        <v>1135</v>
       </c>
       <c r="V72" t="s">
-        <v>956</v>
+        <v>1136</v>
       </c>
       <c r="W72" s="1" t="s">
         <v>52</v>
@@ -10814,13 +11954,13 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>957</v>
+        <v>1137</v>
       </c>
       <c r="B73" t="s">
-        <v>958</v>
+        <v>1138</v>
       </c>
       <c r="C73" t="s">
-        <v>959</v>
+        <v>1139</v>
       </c>
       <c r="D73" t="s">
         <v>157</v>
@@ -10829,25 +11969,25 @@
         <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>960</v>
+        <v>1140</v>
       </c>
       <c r="G73" t="s">
         <v>158</v>
       </c>
       <c r="I73" t="s">
-        <v>961</v>
+        <v>1141</v>
       </c>
       <c r="J73" t="s">
-        <v>962</v>
+        <v>1142</v>
       </c>
       <c r="K73" t="s">
-        <v>963</v>
+        <v>1143</v>
       </c>
       <c r="M73" t="s">
-        <v>964</v>
+        <v>1144</v>
       </c>
       <c r="N73" t="s">
-        <v>965</v>
+        <v>1145</v>
       </c>
       <c r="O73" t="s">
         <v>141</v>
@@ -10862,30 +12002,30 @@
         <v>48</v>
       </c>
       <c r="S73" t="s">
-        <v>966</v>
+        <v>1146</v>
       </c>
       <c r="T73" t="s">
-        <v>967</v>
+        <v>1147</v>
       </c>
       <c r="U73" t="s">
-        <v>968</v>
+        <v>1148</v>
       </c>
       <c r="V73" t="s">
-        <v>969</v>
+        <v>1149</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>970</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>971</v>
+        <v>1151</v>
       </c>
       <c r="B74" t="s">
-        <v>972</v>
+        <v>1152</v>
       </c>
       <c r="C74" t="s">
-        <v>973</v>
+        <v>1153</v>
       </c>
       <c r="D74" t="s">
         <v>65</v>
@@ -10897,25 +12037,25 @@
         <v>66</v>
       </c>
       <c r="G74" t="s">
-        <v>356</v>
+        <v>500</v>
       </c>
       <c r="I74" t="s">
-        <v>974</v>
+        <v>1154</v>
       </c>
       <c r="J74" t="s">
-        <v>975</v>
+        <v>1155</v>
       </c>
       <c r="K74" t="s">
-        <v>976</v>
+        <v>1156</v>
       </c>
       <c r="L74" t="s">
-        <v>977</v>
+        <v>1157</v>
       </c>
       <c r="M74" t="s">
-        <v>978</v>
+        <v>1158</v>
       </c>
       <c r="N74" t="s">
-        <v>979</v>
+        <v>1159</v>
       </c>
       <c r="P74" t="s">
         <v>46</v>
@@ -10927,13 +12067,13 @@
         <v>48</v>
       </c>
       <c r="T74" t="s">
-        <v>980</v>
+        <v>1160</v>
       </c>
       <c r="U74" t="s">
-        <v>981</v>
+        <v>1161</v>
       </c>
       <c r="V74" t="s">
-        <v>982</v>
+        <v>1162</v>
       </c>
       <c r="W74" s="1" t="s">
         <v>52</v>
@@ -10941,13 +12081,13 @@
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>983</v>
+        <v>1163</v>
       </c>
       <c r="B75" t="s">
-        <v>984</v>
+        <v>1164</v>
       </c>
       <c r="C75" t="s">
-        <v>985</v>
+        <v>1165</v>
       </c>
       <c r="D75" t="s">
         <v>65</v>
@@ -10959,25 +12099,25 @@
         <v>66</v>
       </c>
       <c r="G75" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I75" t="s">
-        <v>986</v>
+        <v>1166</v>
       </c>
       <c r="J75" t="s">
-        <v>987</v>
+        <v>1167</v>
       </c>
       <c r="K75" t="s">
-        <v>988</v>
+        <v>1168</v>
       </c>
       <c r="L75" t="s">
-        <v>989</v>
+        <v>1169</v>
       </c>
       <c r="M75" t="s">
-        <v>990</v>
+        <v>1170</v>
       </c>
       <c r="N75" t="s">
-        <v>991</v>
+        <v>1171</v>
       </c>
       <c r="P75" t="s">
         <v>46</v>
@@ -10989,13 +12129,13 @@
         <v>48</v>
       </c>
       <c r="T75" t="s">
-        <v>992</v>
+        <v>1172</v>
       </c>
       <c r="U75" t="s">
-        <v>993</v>
+        <v>1173</v>
       </c>
       <c r="V75" t="s">
-        <v>994</v>
+        <v>1174</v>
       </c>
       <c r="W75" s="1" t="s">
         <v>52</v>
@@ -11003,13 +12143,13 @@
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>995</v>
+        <v>1175</v>
       </c>
       <c r="B76" t="s">
-        <v>996</v>
+        <v>1176</v>
       </c>
       <c r="C76" t="s">
-        <v>997</v>
+        <v>1177</v>
       </c>
       <c r="D76" t="s">
         <v>65</v>
@@ -11024,22 +12164,22 @@
         <v>38</v>
       </c>
       <c r="I76" t="s">
-        <v>998</v>
+        <v>1178</v>
       </c>
       <c r="J76" t="s">
-        <v>999</v>
+        <v>1179</v>
       </c>
       <c r="K76" t="s">
-        <v>1000</v>
+        <v>1180</v>
       </c>
       <c r="L76" t="s">
-        <v>1001</v>
+        <v>1181</v>
       </c>
       <c r="M76" t="s">
-        <v>1002</v>
+        <v>1182</v>
       </c>
       <c r="N76" t="s">
-        <v>1003</v>
+        <v>1183</v>
       </c>
       <c r="P76" t="s">
         <v>46</v>
@@ -11051,13 +12191,13 @@
         <v>48</v>
       </c>
       <c r="T76" t="s">
-        <v>1004</v>
+        <v>1184</v>
       </c>
       <c r="U76" t="s">
-        <v>1005</v>
+        <v>1185</v>
       </c>
       <c r="V76" t="s">
-        <v>1006</v>
+        <v>1186</v>
       </c>
       <c r="W76" s="1" t="s">
         <v>52</v>
@@ -11065,13 +12205,13 @@
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1007</v>
+        <v>1187</v>
       </c>
       <c r="B77" t="s">
-        <v>1008</v>
+        <v>1188</v>
       </c>
       <c r="C77" t="s">
-        <v>1009</v>
+        <v>1189</v>
       </c>
       <c r="D77" t="s">
         <v>35</v>
@@ -11083,25 +12223,25 @@
         <v>37</v>
       </c>
       <c r="G77" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I77" t="s">
-        <v>1010</v>
+        <v>1190</v>
       </c>
       <c r="J77" t="s">
-        <v>1011</v>
+        <v>1191</v>
       </c>
       <c r="K77" t="s">
-        <v>1012</v>
+        <v>1192</v>
       </c>
       <c r="L77" t="s">
-        <v>1013</v>
+        <v>1193</v>
       </c>
       <c r="M77" t="s">
-        <v>1014</v>
+        <v>1194</v>
       </c>
       <c r="N77" t="s">
-        <v>1015</v>
+        <v>1195</v>
       </c>
       <c r="P77" t="s">
         <v>46</v>
@@ -11113,13 +12253,13 @@
         <v>48</v>
       </c>
       <c r="T77" t="s">
-        <v>1016</v>
+        <v>1196</v>
       </c>
       <c r="U77" t="s">
-        <v>1017</v>
+        <v>1197</v>
       </c>
       <c r="V77" t="s">
-        <v>1018</v>
+        <v>1198</v>
       </c>
       <c r="W77" s="1" t="s">
         <v>52</v>
@@ -11127,13 +12267,13 @@
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1019</v>
+        <v>1199</v>
       </c>
       <c r="B78" t="s">
-        <v>1020</v>
+        <v>1200</v>
       </c>
       <c r="C78" t="s">
-        <v>1021</v>
+        <v>1201</v>
       </c>
       <c r="D78" t="s">
         <v>35</v>
@@ -11148,22 +12288,22 @@
         <v>89</v>
       </c>
       <c r="I78" t="s">
-        <v>1022</v>
+        <v>1202</v>
       </c>
       <c r="J78" t="s">
-        <v>1023</v>
+        <v>1203</v>
       </c>
       <c r="K78" t="s">
-        <v>1024</v>
+        <v>1204</v>
       </c>
       <c r="L78" t="s">
-        <v>1025</v>
+        <v>1205</v>
       </c>
       <c r="M78" t="s">
-        <v>1026</v>
+        <v>1206</v>
       </c>
       <c r="N78" t="s">
-        <v>1027</v>
+        <v>1207</v>
       </c>
       <c r="O78" t="s">
         <v>141</v>
@@ -11178,13 +12318,13 @@
         <v>48</v>
       </c>
       <c r="T78" t="s">
-        <v>1028</v>
+        <v>1208</v>
       </c>
       <c r="U78" t="s">
-        <v>1029</v>
+        <v>1209</v>
       </c>
       <c r="V78" t="s">
-        <v>1030</v>
+        <v>1210</v>
       </c>
       <c r="W78" s="1" t="s">
         <v>52</v>
@@ -11192,13 +12332,13 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1031</v>
+        <v>1211</v>
       </c>
       <c r="B79" t="s">
-        <v>1032</v>
+        <v>1212</v>
       </c>
       <c r="C79" t="s">
-        <v>1033</v>
+        <v>1213</v>
       </c>
       <c r="D79" t="s">
         <v>35</v>
@@ -11210,31 +12350,31 @@
         <v>37</v>
       </c>
       <c r="G79" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I79" t="s">
-        <v>1034</v>
+        <v>1214</v>
       </c>
       <c r="J79" t="s">
-        <v>1035</v>
+        <v>1215</v>
       </c>
       <c r="K79" t="s">
-        <v>1036</v>
+        <v>1216</v>
       </c>
       <c r="L79" t="s">
-        <v>1037</v>
+        <v>1217</v>
       </c>
       <c r="M79" t="s">
-        <v>1038</v>
+        <v>1218</v>
       </c>
       <c r="N79" t="s">
-        <v>1039</v>
+        <v>1219</v>
       </c>
       <c r="O79" t="s">
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q79" t="s">
         <v>47</v>
@@ -11243,16 +12383,16 @@
         <v>48</v>
       </c>
       <c r="S79" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T79" t="s">
-        <v>1040</v>
+        <v>1220</v>
       </c>
       <c r="U79" t="s">
-        <v>1041</v>
+        <v>1221</v>
       </c>
       <c r="V79" t="s">
-        <v>1042</v>
+        <v>1222</v>
       </c>
       <c r="W79" s="1" t="s">
         <v>52</v>
@@ -11260,13 +12400,13 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1043</v>
+        <v>1223</v>
       </c>
       <c r="B80" t="s">
-        <v>1044</v>
+        <v>1224</v>
       </c>
       <c r="C80" t="s">
-        <v>1045</v>
+        <v>1225</v>
       </c>
       <c r="D80" t="s">
         <v>35</v>
@@ -11278,25 +12418,25 @@
         <v>37</v>
       </c>
       <c r="G80" t="s">
-        <v>356</v>
+        <v>500</v>
       </c>
       <c r="I80" t="s">
-        <v>1046</v>
+        <v>1226</v>
       </c>
       <c r="J80" t="s">
-        <v>1047</v>
+        <v>1227</v>
       </c>
       <c r="K80" t="s">
-        <v>1048</v>
+        <v>1228</v>
       </c>
       <c r="L80" t="s">
-        <v>1049</v>
+        <v>1229</v>
       </c>
       <c r="M80" t="s">
-        <v>1050</v>
+        <v>1230</v>
       </c>
       <c r="N80" t="s">
-        <v>1051</v>
+        <v>1231</v>
       </c>
       <c r="P80" t="s">
         <v>46</v>
@@ -11308,13 +12448,13 @@
         <v>48</v>
       </c>
       <c r="T80" t="s">
-        <v>1052</v>
+        <v>1232</v>
       </c>
       <c r="U80" t="s">
-        <v>1053</v>
+        <v>1233</v>
       </c>
       <c r="V80" t="s">
-        <v>1054</v>
+        <v>1234</v>
       </c>
       <c r="W80" s="1" t="s">
         <v>52</v>
@@ -11322,13 +12462,13 @@
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1055</v>
+        <v>1235</v>
       </c>
       <c r="B81" t="s">
-        <v>1056</v>
+        <v>1236</v>
       </c>
       <c r="C81" t="s">
-        <v>1057</v>
+        <v>1237</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
@@ -11340,25 +12480,25 @@
         <v>66</v>
       </c>
       <c r="G81" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I81" t="s">
-        <v>1058</v>
+        <v>1238</v>
       </c>
       <c r="J81" t="s">
-        <v>1059</v>
+        <v>1239</v>
       </c>
       <c r="K81" t="s">
-        <v>1060</v>
+        <v>1240</v>
       </c>
       <c r="L81" t="s">
-        <v>1061</v>
+        <v>1241</v>
       </c>
       <c r="M81" t="s">
-        <v>1062</v>
+        <v>1242</v>
       </c>
       <c r="N81" t="s">
-        <v>1063</v>
+        <v>1243</v>
       </c>
       <c r="P81" t="s">
         <v>46</v>
@@ -11370,13 +12510,13 @@
         <v>48</v>
       </c>
       <c r="T81" t="s">
-        <v>1064</v>
+        <v>1244</v>
       </c>
       <c r="U81" t="s">
-        <v>1065</v>
+        <v>1245</v>
       </c>
       <c r="V81" t="s">
-        <v>1066</v>
+        <v>1246</v>
       </c>
       <c r="W81" s="1" t="s">
         <v>52</v>
@@ -11384,13 +12524,13 @@
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1067</v>
+        <v>1247</v>
       </c>
       <c r="B82" t="s">
-        <v>1068</v>
+        <v>1248</v>
       </c>
       <c r="C82" t="s">
-        <v>1069</v>
+        <v>1249</v>
       </c>
       <c r="D82" t="s">
         <v>157</v>
@@ -11405,25 +12545,25 @@
         <v>158</v>
       </c>
       <c r="I82" t="s">
-        <v>1070</v>
+        <v>1250</v>
       </c>
       <c r="J82" t="s">
-        <v>1071</v>
+        <v>1251</v>
       </c>
       <c r="K82" t="s">
-        <v>1072</v>
+        <v>1252</v>
       </c>
       <c r="L82" t="s">
-        <v>1073</v>
+        <v>1253</v>
       </c>
       <c r="M82" t="s">
-        <v>1074</v>
+        <v>1254</v>
       </c>
       <c r="N82" t="s">
-        <v>1075</v>
+        <v>1255</v>
       </c>
       <c r="P82" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q82" t="s">
         <v>47</v>
@@ -11432,16 +12572,16 @@
         <v>48</v>
       </c>
       <c r="S82" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T82" t="s">
-        <v>1076</v>
+        <v>1256</v>
       </c>
       <c r="U82" t="s">
-        <v>1077</v>
+        <v>1257</v>
       </c>
       <c r="V82" t="s">
-        <v>1078</v>
+        <v>1258</v>
       </c>
       <c r="W82" s="1" t="s">
         <v>52</v>
@@ -11449,13 +12589,13 @@
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1079</v>
+        <v>1259</v>
       </c>
       <c r="B83" t="s">
-        <v>1080</v>
+        <v>1260</v>
       </c>
       <c r="C83" t="s">
-        <v>1081</v>
+        <v>1261</v>
       </c>
       <c r="D83" t="s">
         <v>35</v>
@@ -11467,25 +12607,25 @@
         <v>133</v>
       </c>
       <c r="G83" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I83" t="s">
-        <v>1082</v>
+        <v>1262</v>
       </c>
       <c r="J83" t="s">
-        <v>1083</v>
+        <v>1263</v>
       </c>
       <c r="K83" t="s">
-        <v>1084</v>
+        <v>1264</v>
       </c>
       <c r="L83" t="s">
-        <v>1085</v>
+        <v>1265</v>
       </c>
       <c r="M83" t="s">
-        <v>1086</v>
+        <v>1266</v>
       </c>
       <c r="N83" t="s">
-        <v>1087</v>
+        <v>1267</v>
       </c>
       <c r="O83" t="s">
         <v>141</v>
@@ -11500,13 +12640,13 @@
         <v>48</v>
       </c>
       <c r="T83" t="s">
-        <v>1088</v>
+        <v>1268</v>
       </c>
       <c r="U83" t="s">
-        <v>1089</v>
+        <v>1269</v>
       </c>
       <c r="V83" t="s">
-        <v>1090</v>
+        <v>1270</v>
       </c>
       <c r="W83" s="1" t="s">
         <v>52</v>
@@ -11514,13 +12654,13 @@
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1091</v>
+        <v>1271</v>
       </c>
       <c r="B84" t="s">
-        <v>1092</v>
+        <v>1272</v>
       </c>
       <c r="C84" t="s">
-        <v>1093</v>
+        <v>1273</v>
       </c>
       <c r="D84" t="s">
         <v>65</v>
@@ -11532,25 +12672,25 @@
         <v>88</v>
       </c>
       <c r="G84" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I84" t="s">
-        <v>1094</v>
+        <v>1274</v>
       </c>
       <c r="J84" t="s">
-        <v>1095</v>
+        <v>1275</v>
       </c>
       <c r="K84" t="s">
-        <v>1096</v>
+        <v>1276</v>
       </c>
       <c r="L84" t="s">
-        <v>1097</v>
+        <v>1277</v>
       </c>
       <c r="M84" t="s">
-        <v>1098</v>
+        <v>1278</v>
       </c>
       <c r="N84" t="s">
-        <v>1099</v>
+        <v>1279</v>
       </c>
       <c r="P84" t="s">
         <v>46</v>
@@ -11562,13 +12702,13 @@
         <v>48</v>
       </c>
       <c r="T84" t="s">
-        <v>1100</v>
+        <v>1280</v>
       </c>
       <c r="U84" t="s">
-        <v>1101</v>
+        <v>1281</v>
       </c>
       <c r="V84" t="s">
-        <v>1102</v>
+        <v>1282</v>
       </c>
       <c r="W84" s="1" t="s">
         <v>52</v>
@@ -11576,13 +12716,13 @@
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1103</v>
+        <v>1283</v>
       </c>
       <c r="B85" t="s">
-        <v>1104</v>
+        <v>1284</v>
       </c>
       <c r="C85" t="s">
-        <v>1105</v>
+        <v>1285</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -11594,25 +12734,25 @@
         <v>66</v>
       </c>
       <c r="G85" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I85" t="s">
-        <v>1106</v>
+        <v>1286</v>
       </c>
       <c r="J85" t="s">
-        <v>1107</v>
+        <v>1287</v>
       </c>
       <c r="K85" t="s">
-        <v>1108</v>
+        <v>1288</v>
       </c>
       <c r="L85" t="s">
-        <v>1109</v>
+        <v>1289</v>
       </c>
       <c r="M85" t="s">
-        <v>1110</v>
+        <v>1290</v>
       </c>
       <c r="N85" t="s">
-        <v>1111</v>
+        <v>1291</v>
       </c>
       <c r="P85" t="s">
         <v>46</v>
@@ -11624,13 +12764,13 @@
         <v>48</v>
       </c>
       <c r="T85" t="s">
-        <v>1112</v>
+        <v>1292</v>
       </c>
       <c r="U85" t="s">
-        <v>1113</v>
+        <v>1293</v>
       </c>
       <c r="V85" t="s">
-        <v>1114</v>
+        <v>1294</v>
       </c>
       <c r="W85" s="1" t="s">
         <v>52</v>
@@ -11638,13 +12778,13 @@
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1115</v>
+        <v>1295</v>
       </c>
       <c r="B86" t="s">
-        <v>1116</v>
+        <v>1296</v>
       </c>
       <c r="C86" t="s">
-        <v>1117</v>
+        <v>1297</v>
       </c>
       <c r="D86" t="s">
         <v>65</v>
@@ -11656,25 +12796,25 @@
         <v>66</v>
       </c>
       <c r="G86" t="s">
-        <v>356</v>
+        <v>500</v>
       </c>
       <c r="I86" t="s">
-        <v>1118</v>
+        <v>1298</v>
       </c>
       <c r="J86" t="s">
-        <v>1119</v>
+        <v>1299</v>
       </c>
       <c r="K86" t="s">
-        <v>1120</v>
+        <v>1300</v>
       </c>
       <c r="L86" t="s">
-        <v>1121</v>
+        <v>1301</v>
       </c>
       <c r="M86" t="s">
-        <v>1122</v>
+        <v>1302</v>
       </c>
       <c r="N86" t="s">
-        <v>1123</v>
+        <v>1303</v>
       </c>
       <c r="P86" t="s">
         <v>46</v>
@@ -11686,13 +12826,13 @@
         <v>48</v>
       </c>
       <c r="T86" t="s">
-        <v>1124</v>
+        <v>1304</v>
       </c>
       <c r="U86" t="s">
-        <v>1125</v>
+        <v>1305</v>
       </c>
       <c r="V86" t="s">
-        <v>1126</v>
+        <v>1306</v>
       </c>
       <c r="W86" s="1" t="s">
         <v>52</v>
@@ -11700,13 +12840,13 @@
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1127</v>
+        <v>1307</v>
       </c>
       <c r="B87" t="s">
-        <v>1128</v>
+        <v>1308</v>
       </c>
       <c r="C87" t="s">
-        <v>1129</v>
+        <v>1309</v>
       </c>
       <c r="D87" t="s">
         <v>35</v>
@@ -11721,22 +12861,22 @@
         <v>89</v>
       </c>
       <c r="I87" t="s">
-        <v>1130</v>
+        <v>1310</v>
       </c>
       <c r="J87" t="s">
-        <v>1131</v>
+        <v>1311</v>
       </c>
       <c r="K87" t="s">
-        <v>1132</v>
+        <v>1312</v>
       </c>
       <c r="L87" t="s">
-        <v>1133</v>
+        <v>1313</v>
       </c>
       <c r="M87" t="s">
-        <v>1134</v>
+        <v>1314</v>
       </c>
       <c r="N87" t="s">
-        <v>1135</v>
+        <v>1315</v>
       </c>
       <c r="O87" t="s">
         <v>141</v>
@@ -11751,13 +12891,13 @@
         <v>48</v>
       </c>
       <c r="T87" t="s">
-        <v>1136</v>
+        <v>1316</v>
       </c>
       <c r="U87" t="s">
-        <v>1137</v>
+        <v>1317</v>
       </c>
       <c r="V87" t="s">
-        <v>1138</v>
+        <v>1318</v>
       </c>
       <c r="W87" s="1" t="s">
         <v>52</v>
@@ -11765,13 +12905,13 @@
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1139</v>
+        <v>1319</v>
       </c>
       <c r="B88" t="s">
-        <v>1140</v>
+        <v>1320</v>
       </c>
       <c r="C88" t="s">
-        <v>1141</v>
+        <v>1321</v>
       </c>
       <c r="D88" t="s">
         <v>157</v>
@@ -11786,25 +12926,25 @@
         <v>158</v>
       </c>
       <c r="I88" t="s">
-        <v>1142</v>
+        <v>1322</v>
       </c>
       <c r="J88" t="s">
-        <v>1143</v>
+        <v>1323</v>
       </c>
       <c r="K88" t="s">
-        <v>1144</v>
+        <v>1324</v>
       </c>
       <c r="L88" t="s">
-        <v>1145</v>
+        <v>1325</v>
       </c>
       <c r="M88" t="s">
-        <v>1146</v>
+        <v>1326</v>
       </c>
       <c r="N88" t="s">
-        <v>1147</v>
+        <v>1327</v>
       </c>
       <c r="P88" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q88" t="s">
         <v>47</v>
@@ -11813,16 +12953,16 @@
         <v>48</v>
       </c>
       <c r="S88" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T88" t="s">
-        <v>1148</v>
+        <v>1328</v>
       </c>
       <c r="U88" t="s">
-        <v>1149</v>
+        <v>1329</v>
       </c>
       <c r="V88" t="s">
-        <v>1150</v>
+        <v>1330</v>
       </c>
       <c r="W88" s="1" t="s">
         <v>52</v>
@@ -11830,13 +12970,13 @@
     </row>
     <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1151</v>
+        <v>1331</v>
       </c>
       <c r="B89" t="s">
-        <v>1152</v>
+        <v>1332</v>
       </c>
       <c r="C89" t="s">
-        <v>1153</v>
+        <v>1333</v>
       </c>
       <c r="D89" t="s">
         <v>65</v>
@@ -11848,25 +12988,25 @@
         <v>66</v>
       </c>
       <c r="G89" t="s">
-        <v>246</v>
+        <v>309</v>
       </c>
       <c r="I89" t="s">
-        <v>1154</v>
+        <v>1334</v>
       </c>
       <c r="J89" t="s">
-        <v>1155</v>
+        <v>1335</v>
       </c>
       <c r="K89" t="s">
-        <v>1156</v>
+        <v>1336</v>
       </c>
       <c r="L89" t="s">
-        <v>1157</v>
+        <v>1337</v>
       </c>
       <c r="M89" t="s">
-        <v>1158</v>
+        <v>1338</v>
       </c>
       <c r="N89" t="s">
-        <v>1159</v>
+        <v>1339</v>
       </c>
       <c r="P89" t="s">
         <v>46</v>
@@ -11878,13 +13018,13 @@
         <v>48</v>
       </c>
       <c r="T89" t="s">
-        <v>1160</v>
+        <v>1340</v>
       </c>
       <c r="U89" t="s">
-        <v>1161</v>
+        <v>1341</v>
       </c>
       <c r="V89" t="s">
-        <v>1162</v>
+        <v>1342</v>
       </c>
       <c r="W89" s="1" t="s">
         <v>52</v>
@@ -11892,13 +13032,13 @@
     </row>
     <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1163</v>
+        <v>1343</v>
       </c>
       <c r="B90" t="s">
-        <v>1164</v>
+        <v>1344</v>
       </c>
       <c r="C90" t="s">
-        <v>1165</v>
+        <v>1345</v>
       </c>
       <c r="D90" t="s">
         <v>65</v>
@@ -11910,25 +13050,25 @@
         <v>66</v>
       </c>
       <c r="G90" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I90" t="s">
-        <v>1166</v>
+        <v>1346</v>
       </c>
       <c r="J90" t="s">
-        <v>1167</v>
+        <v>1347</v>
       </c>
       <c r="K90" t="s">
-        <v>1168</v>
+        <v>1348</v>
       </c>
       <c r="L90" t="s">
-        <v>1169</v>
+        <v>1349</v>
       </c>
       <c r="M90" t="s">
-        <v>1170</v>
+        <v>1350</v>
       </c>
       <c r="N90" t="s">
-        <v>1171</v>
+        <v>1351</v>
       </c>
       <c r="P90" t="s">
         <v>46</v>
@@ -11940,13 +13080,13 @@
         <v>48</v>
       </c>
       <c r="T90" t="s">
-        <v>1172</v>
+        <v>1352</v>
       </c>
       <c r="U90" t="s">
-        <v>1173</v>
+        <v>1353</v>
       </c>
       <c r="V90" t="s">
-        <v>1174</v>
+        <v>1354</v>
       </c>
       <c r="W90" s="1" t="s">
         <v>52</v>
@@ -11954,13 +13094,13 @@
     </row>
     <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1175</v>
+        <v>1355</v>
       </c>
       <c r="B91" t="s">
-        <v>1176</v>
+        <v>1356</v>
       </c>
       <c r="C91" t="s">
-        <v>1177</v>
+        <v>1357</v>
       </c>
       <c r="D91" t="s">
         <v>65</v>
@@ -11972,25 +13112,25 @@
         <v>66</v>
       </c>
       <c r="G91" t="s">
-        <v>356</v>
+        <v>500</v>
       </c>
       <c r="I91" t="s">
-        <v>1178</v>
+        <v>1358</v>
       </c>
       <c r="J91" t="s">
-        <v>1179</v>
+        <v>1359</v>
       </c>
       <c r="K91" t="s">
-        <v>1180</v>
+        <v>1360</v>
       </c>
       <c r="L91" t="s">
-        <v>1181</v>
+        <v>1361</v>
       </c>
       <c r="M91" t="s">
-        <v>1182</v>
+        <v>1362</v>
       </c>
       <c r="N91" t="s">
-        <v>1183</v>
+        <v>1363</v>
       </c>
       <c r="P91" t="s">
         <v>46</v>
@@ -12002,13 +13142,13 @@
         <v>48</v>
       </c>
       <c r="T91" t="s">
-        <v>1184</v>
+        <v>1364</v>
       </c>
       <c r="U91" t="s">
-        <v>1185</v>
+        <v>1365</v>
       </c>
       <c r="V91" t="s">
-        <v>1186</v>
+        <v>1366</v>
       </c>
       <c r="W91" s="1" t="s">
         <v>52</v>
@@ -12016,13 +13156,13 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1187</v>
+        <v>1367</v>
       </c>
       <c r="B92" t="s">
-        <v>1188</v>
+        <v>1368</v>
       </c>
       <c r="C92" t="s">
-        <v>1189</v>
+        <v>1369</v>
       </c>
       <c r="D92" t="s">
         <v>157</v>
@@ -12037,25 +13177,25 @@
         <v>158</v>
       </c>
       <c r="I92" t="s">
-        <v>1190</v>
+        <v>1370</v>
       </c>
       <c r="J92" t="s">
-        <v>1191</v>
+        <v>1371</v>
       </c>
       <c r="K92" t="s">
-        <v>1192</v>
+        <v>1372</v>
       </c>
       <c r="L92" t="s">
-        <v>1193</v>
+        <v>1373</v>
       </c>
       <c r="M92" t="s">
-        <v>1194</v>
+        <v>1374</v>
       </c>
       <c r="N92" t="s">
-        <v>1195</v>
+        <v>1375</v>
       </c>
       <c r="P92" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q92" t="s">
         <v>47</v>
@@ -12064,16 +13204,16 @@
         <v>48</v>
       </c>
       <c r="S92" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T92" t="s">
-        <v>1196</v>
+        <v>1376</v>
       </c>
       <c r="U92" t="s">
-        <v>1197</v>
+        <v>1377</v>
       </c>
       <c r="V92" t="s">
-        <v>1198</v>
+        <v>1378</v>
       </c>
       <c r="W92" s="1" t="s">
         <v>52</v>
@@ -12081,13 +13221,13 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1199</v>
+        <v>1379</v>
       </c>
       <c r="B93" t="s">
-        <v>1200</v>
+        <v>1380</v>
       </c>
       <c r="C93" t="s">
-        <v>1201</v>
+        <v>1381</v>
       </c>
       <c r="D93" t="s">
         <v>35</v>
@@ -12099,31 +13239,31 @@
         <v>88</v>
       </c>
       <c r="G93" t="s">
-        <v>356</v>
+        <v>500</v>
       </c>
       <c r="I93" t="s">
-        <v>1202</v>
+        <v>1382</v>
       </c>
       <c r="J93" t="s">
-        <v>1203</v>
+        <v>1383</v>
       </c>
       <c r="K93" t="s">
-        <v>1204</v>
+        <v>1384</v>
       </c>
       <c r="L93" t="s">
-        <v>1205</v>
+        <v>1385</v>
       </c>
       <c r="M93" t="s">
-        <v>1206</v>
+        <v>1386</v>
       </c>
       <c r="N93" t="s">
-        <v>1207</v>
+        <v>1387</v>
       </c>
       <c r="O93" t="s">
         <v>141</v>
       </c>
       <c r="P93" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q93" t="s">
         <v>47</v>
@@ -12132,16 +13272,16 @@
         <v>48</v>
       </c>
       <c r="S93" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T93" t="s">
-        <v>1208</v>
+        <v>1388</v>
       </c>
       <c r="U93" t="s">
-        <v>1209</v>
+        <v>1389</v>
       </c>
       <c r="V93" t="s">
-        <v>1210</v>
+        <v>1390</v>
       </c>
       <c r="W93" s="1" t="s">
         <v>52</v>
@@ -12149,13 +13289,13 @@
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1211</v>
+        <v>1391</v>
       </c>
       <c r="B94" t="s">
-        <v>1212</v>
+        <v>1392</v>
       </c>
       <c r="C94" t="s">
-        <v>1213</v>
+        <v>1393</v>
       </c>
       <c r="D94" t="s">
         <v>65</v>
@@ -12167,25 +13307,25 @@
         <v>66</v>
       </c>
       <c r="G94" t="s">
-        <v>246</v>
+        <v>309</v>
       </c>
       <c r="I94" t="s">
-        <v>1214</v>
+        <v>1394</v>
       </c>
       <c r="J94" t="s">
-        <v>1215</v>
+        <v>1395</v>
       </c>
       <c r="K94" t="s">
-        <v>1216</v>
+        <v>1396</v>
       </c>
       <c r="L94" t="s">
-        <v>1217</v>
+        <v>1397</v>
       </c>
       <c r="M94" t="s">
-        <v>1218</v>
+        <v>1398</v>
       </c>
       <c r="N94" t="s">
-        <v>1219</v>
+        <v>1399</v>
       </c>
       <c r="P94" t="s">
         <v>46</v>
@@ -12197,13 +13337,13 @@
         <v>48</v>
       </c>
       <c r="T94" t="s">
-        <v>1220</v>
+        <v>1400</v>
       </c>
       <c r="U94" t="s">
-        <v>1221</v>
+        <v>1401</v>
       </c>
       <c r="V94" t="s">
-        <v>1222</v>
+        <v>1402</v>
       </c>
       <c r="W94" s="1" t="s">
         <v>52</v>
@@ -12211,13 +13351,13 @@
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1223</v>
+        <v>1403</v>
       </c>
       <c r="B95" t="s">
-        <v>1224</v>
+        <v>1404</v>
       </c>
       <c r="C95" t="s">
-        <v>1225</v>
+        <v>1405</v>
       </c>
       <c r="D95" t="s">
         <v>35</v>
@@ -12232,22 +13372,22 @@
         <v>158</v>
       </c>
       <c r="I95" t="s">
-        <v>1226</v>
+        <v>1406</v>
       </c>
       <c r="J95" t="s">
-        <v>1227</v>
+        <v>1407</v>
       </c>
       <c r="K95" t="s">
-        <v>1228</v>
+        <v>1408</v>
       </c>
       <c r="L95" t="s">
-        <v>1229</v>
+        <v>1409</v>
       </c>
       <c r="M95" t="s">
-        <v>1230</v>
+        <v>1410</v>
       </c>
       <c r="N95" t="s">
-        <v>1231</v>
+        <v>1411</v>
       </c>
       <c r="P95" t="s">
         <v>46</v>
@@ -12259,13 +13399,13 @@
         <v>48</v>
       </c>
       <c r="T95" t="s">
-        <v>1232</v>
+        <v>1412</v>
       </c>
       <c r="U95" t="s">
-        <v>1233</v>
+        <v>1413</v>
       </c>
       <c r="V95" t="s">
-        <v>1234</v>
+        <v>1414</v>
       </c>
       <c r="W95" s="1" t="s">
         <v>52</v>
@@ -12273,13 +13413,13 @@
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1235</v>
+        <v>1415</v>
       </c>
       <c r="B96" t="s">
-        <v>1236</v>
+        <v>1416</v>
       </c>
       <c r="C96" t="s">
-        <v>1237</v>
+        <v>1417</v>
       </c>
       <c r="D96" t="s">
         <v>35</v>
@@ -12294,22 +13434,22 @@
         <v>158</v>
       </c>
       <c r="I96" t="s">
-        <v>1238</v>
+        <v>1418</v>
       </c>
       <c r="J96" t="s">
-        <v>1239</v>
+        <v>1419</v>
       </c>
       <c r="K96" t="s">
-        <v>1240</v>
+        <v>1420</v>
       </c>
       <c r="L96" t="s">
-        <v>1241</v>
+        <v>1421</v>
       </c>
       <c r="M96" t="s">
-        <v>1242</v>
+        <v>1422</v>
       </c>
       <c r="N96" t="s">
-        <v>1243</v>
+        <v>1423</v>
       </c>
       <c r="P96" t="s">
         <v>46</v>
@@ -12321,13 +13461,13 @@
         <v>48</v>
       </c>
       <c r="T96" t="s">
-        <v>1244</v>
+        <v>1424</v>
       </c>
       <c r="U96" t="s">
-        <v>1245</v>
+        <v>1425</v>
       </c>
       <c r="V96" t="s">
-        <v>1246</v>
+        <v>1426</v>
       </c>
       <c r="W96" s="1" t="s">
         <v>52</v>
@@ -12335,13 +13475,13 @@
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1247</v>
+        <v>1427</v>
       </c>
       <c r="B97" t="s">
-        <v>1248</v>
+        <v>1428</v>
       </c>
       <c r="C97" t="s">
-        <v>1249</v>
+        <v>1429</v>
       </c>
       <c r="D97" t="s">
         <v>35</v>
@@ -12356,25 +13496,25 @@
         <v>158</v>
       </c>
       <c r="I97" t="s">
-        <v>1250</v>
+        <v>1430</v>
       </c>
       <c r="J97" t="s">
-        <v>1251</v>
+        <v>1431</v>
       </c>
       <c r="K97" t="s">
-        <v>1252</v>
+        <v>1432</v>
       </c>
       <c r="L97" t="s">
-        <v>1253</v>
+        <v>1433</v>
       </c>
       <c r="M97" t="s">
-        <v>1254</v>
+        <v>1434</v>
       </c>
       <c r="N97" t="s">
-        <v>1255</v>
+        <v>1435</v>
       </c>
       <c r="P97" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q97" t="s">
         <v>47</v>
@@ -12383,16 +13523,16 @@
         <v>48</v>
       </c>
       <c r="S97" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T97" t="s">
-        <v>1256</v>
+        <v>1436</v>
       </c>
       <c r="U97" t="s">
-        <v>1257</v>
+        <v>1437</v>
       </c>
       <c r="V97" t="s">
-        <v>1258</v>
+        <v>1438</v>
       </c>
       <c r="W97" s="1" t="s">
         <v>52</v>
@@ -12400,13 +13540,13 @@
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1259</v>
+        <v>1439</v>
       </c>
       <c r="B98" t="s">
-        <v>1260</v>
+        <v>1440</v>
       </c>
       <c r="C98" t="s">
-        <v>1261</v>
+        <v>1441</v>
       </c>
       <c r="D98" t="s">
         <v>157</v>
@@ -12415,25 +13555,25 @@
         <v>132</v>
       </c>
       <c r="F98" t="s">
-        <v>960</v>
+        <v>1140</v>
       </c>
       <c r="G98" t="s">
         <v>158</v>
       </c>
       <c r="I98" t="s">
-        <v>1262</v>
+        <v>1442</v>
       </c>
       <c r="J98" t="s">
-        <v>1263</v>
+        <v>1443</v>
       </c>
       <c r="K98" t="s">
-        <v>1264</v>
+        <v>1444</v>
       </c>
       <c r="M98" t="s">
-        <v>1265</v>
+        <v>1445</v>
       </c>
       <c r="N98" t="s">
-        <v>1266</v>
+        <v>1446</v>
       </c>
       <c r="O98" t="s">
         <v>141</v>
@@ -12448,30 +13588,30 @@
         <v>48</v>
       </c>
       <c r="S98" t="s">
-        <v>966</v>
+        <v>1146</v>
       </c>
       <c r="T98" t="s">
-        <v>1267</v>
+        <v>1447</v>
       </c>
       <c r="U98" t="s">
-        <v>1268</v>
+        <v>1448</v>
       </c>
       <c r="V98" t="s">
-        <v>1269</v>
+        <v>1449</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>970</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1270</v>
+        <v>1450</v>
       </c>
       <c r="B99" t="s">
-        <v>1271</v>
+        <v>1451</v>
       </c>
       <c r="C99" t="s">
-        <v>1272</v>
+        <v>1452</v>
       </c>
       <c r="D99" t="s">
         <v>35</v>
@@ -12486,22 +13626,22 @@
         <v>89</v>
       </c>
       <c r="I99" t="s">
-        <v>1273</v>
+        <v>1453</v>
       </c>
       <c r="J99" t="s">
-        <v>1274</v>
+        <v>1454</v>
       </c>
       <c r="K99" t="s">
-        <v>1275</v>
+        <v>1455</v>
       </c>
       <c r="L99" t="s">
-        <v>1276</v>
+        <v>1456</v>
       </c>
       <c r="M99" t="s">
-        <v>1277</v>
+        <v>1457</v>
       </c>
       <c r="N99" t="s">
-        <v>1278</v>
+        <v>1458</v>
       </c>
       <c r="O99" t="s">
         <v>141</v>
@@ -12516,13 +13656,13 @@
         <v>48</v>
       </c>
       <c r="T99" t="s">
-        <v>1279</v>
+        <v>1459</v>
       </c>
       <c r="U99" t="s">
-        <v>1280</v>
+        <v>1460</v>
       </c>
       <c r="V99" t="s">
-        <v>1281</v>
+        <v>1461</v>
       </c>
       <c r="W99" s="1" t="s">
         <v>52</v>
@@ -12530,13 +13670,13 @@
     </row>
     <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1282</v>
+        <v>1462</v>
       </c>
       <c r="B100" t="s">
-        <v>1283</v>
+        <v>1463</v>
       </c>
       <c r="C100" t="s">
-        <v>1284</v>
+        <v>1464</v>
       </c>
       <c r="D100" t="s">
         <v>35</v>
@@ -12548,25 +13688,25 @@
         <v>133</v>
       </c>
       <c r="G100" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I100" t="s">
-        <v>1285</v>
+        <v>1465</v>
       </c>
       <c r="J100" t="s">
-        <v>1286</v>
+        <v>1466</v>
       </c>
       <c r="K100" t="s">
-        <v>1287</v>
+        <v>1467</v>
       </c>
       <c r="L100" t="s">
-        <v>1288</v>
+        <v>1468</v>
       </c>
       <c r="M100" t="s">
-        <v>1289</v>
+        <v>1469</v>
       </c>
       <c r="N100" t="s">
-        <v>1290</v>
+        <v>1470</v>
       </c>
       <c r="O100" t="s">
         <v>141</v>
@@ -12581,13 +13721,13 @@
         <v>48</v>
       </c>
       <c r="T100" t="s">
-        <v>1291</v>
+        <v>1471</v>
       </c>
       <c r="U100" t="s">
-        <v>1292</v>
+        <v>1472</v>
       </c>
       <c r="V100" t="s">
-        <v>1293</v>
+        <v>1473</v>
       </c>
       <c r="W100" s="1" t="s">
         <v>52</v>
@@ -12595,13 +13735,13 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1294</v>
+        <v>1474</v>
       </c>
       <c r="B101" t="s">
-        <v>1295</v>
+        <v>1475</v>
       </c>
       <c r="C101" t="s">
-        <v>1296</v>
+        <v>1476</v>
       </c>
       <c r="D101" t="s">
         <v>35</v>
@@ -12616,28 +13756,28 @@
         <v>89</v>
       </c>
       <c r="I101" t="s">
-        <v>1297</v>
+        <v>1477</v>
       </c>
       <c r="J101" t="s">
-        <v>1298</v>
+        <v>1478</v>
       </c>
       <c r="K101" t="s">
-        <v>1299</v>
+        <v>1479</v>
       </c>
       <c r="L101" t="s">
-        <v>1300</v>
+        <v>1480</v>
       </c>
       <c r="M101" t="s">
-        <v>1301</v>
+        <v>1481</v>
       </c>
       <c r="N101" t="s">
-        <v>1302</v>
+        <v>1482</v>
       </c>
       <c r="O101" t="s">
         <v>141</v>
       </c>
       <c r="P101" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q101" t="s">
         <v>47</v>
@@ -12646,16 +13786,16 @@
         <v>48</v>
       </c>
       <c r="S101" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T101" t="s">
-        <v>1303</v>
+        <v>1483</v>
       </c>
       <c r="U101" t="s">
-        <v>1304</v>
+        <v>1484</v>
       </c>
       <c r="V101" t="s">
-        <v>1305</v>
+        <v>1485</v>
       </c>
       <c r="W101" s="1" t="s">
         <v>52</v>
@@ -12663,13 +13803,13 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1306</v>
+        <v>1486</v>
       </c>
       <c r="B102" t="s">
-        <v>1307</v>
+        <v>1487</v>
       </c>
       <c r="C102" t="s">
-        <v>1308</v>
+        <v>1488</v>
       </c>
       <c r="D102" t="s">
         <v>35</v>
@@ -12681,25 +13821,25 @@
         <v>133</v>
       </c>
       <c r="G102" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I102" t="s">
-        <v>1309</v>
+        <v>1489</v>
       </c>
       <c r="J102" t="s">
-        <v>1310</v>
+        <v>1490</v>
       </c>
       <c r="K102" t="s">
-        <v>1311</v>
+        <v>1491</v>
       </c>
       <c r="L102" t="s">
-        <v>1312</v>
+        <v>1492</v>
       </c>
       <c r="M102" t="s">
-        <v>1313</v>
+        <v>1493</v>
       </c>
       <c r="N102" t="s">
-        <v>1314</v>
+        <v>1494</v>
       </c>
       <c r="O102" t="s">
         <v>141</v>
@@ -12714,13 +13854,13 @@
         <v>48</v>
       </c>
       <c r="T102" t="s">
-        <v>1315</v>
+        <v>1495</v>
       </c>
       <c r="U102" t="s">
-        <v>1316</v>
+        <v>1496</v>
       </c>
       <c r="V102" t="s">
-        <v>1317</v>
+        <v>1497</v>
       </c>
       <c r="W102" s="1" t="s">
         <v>52</v>
@@ -12728,13 +13868,13 @@
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1318</v>
+        <v>1498</v>
       </c>
       <c r="B103" t="s">
-        <v>1319</v>
+        <v>1499</v>
       </c>
       <c r="C103" t="s">
-        <v>1320</v>
+        <v>1500</v>
       </c>
       <c r="D103" t="s">
         <v>35</v>
@@ -12746,25 +13886,25 @@
         <v>133</v>
       </c>
       <c r="G103" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I103" t="s">
-        <v>1321</v>
+        <v>1501</v>
       </c>
       <c r="J103" t="s">
-        <v>1322</v>
+        <v>1502</v>
       </c>
       <c r="K103" t="s">
-        <v>1323</v>
+        <v>1503</v>
       </c>
       <c r="L103" t="s">
-        <v>1324</v>
+        <v>1504</v>
       </c>
       <c r="M103" t="s">
-        <v>1325</v>
+        <v>1505</v>
       </c>
       <c r="N103" t="s">
-        <v>1326</v>
+        <v>1506</v>
       </c>
       <c r="O103" t="s">
         <v>141</v>
@@ -12779,13 +13919,13 @@
         <v>48</v>
       </c>
       <c r="T103" t="s">
-        <v>1327</v>
+        <v>1507</v>
       </c>
       <c r="U103" t="s">
-        <v>1328</v>
+        <v>1508</v>
       </c>
       <c r="V103" t="s">
-        <v>1329</v>
+        <v>1509</v>
       </c>
       <c r="W103" s="1" t="s">
         <v>52</v>
@@ -12793,13 +13933,13 @@
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1330</v>
+        <v>1510</v>
       </c>
       <c r="B104" t="s">
-        <v>1331</v>
+        <v>1511</v>
       </c>
       <c r="C104" t="s">
-        <v>1332</v>
+        <v>1512</v>
       </c>
       <c r="D104" t="s">
         <v>157</v>
@@ -12814,25 +13954,25 @@
         <v>158</v>
       </c>
       <c r="I104" t="s">
-        <v>1333</v>
+        <v>1513</v>
       </c>
       <c r="J104" t="s">
-        <v>1334</v>
+        <v>1514</v>
       </c>
       <c r="K104" t="s">
-        <v>1335</v>
+        <v>1515</v>
       </c>
       <c r="L104" t="s">
-        <v>1336</v>
+        <v>1516</v>
       </c>
       <c r="M104" t="s">
-        <v>1337</v>
+        <v>1517</v>
       </c>
       <c r="N104" t="s">
-        <v>1338</v>
+        <v>1518</v>
       </c>
       <c r="P104" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q104" t="s">
         <v>47</v>
@@ -12841,16 +13981,16 @@
         <v>48</v>
       </c>
       <c r="S104" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T104" t="s">
-        <v>1339</v>
+        <v>1519</v>
       </c>
       <c r="U104" t="s">
-        <v>1340</v>
+        <v>1520</v>
       </c>
       <c r="V104" t="s">
-        <v>1341</v>
+        <v>1521</v>
       </c>
       <c r="W104" s="1" t="s">
         <v>52</v>
@@ -12858,13 +13998,13 @@
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1342</v>
+        <v>1522</v>
       </c>
       <c r="B105" t="s">
-        <v>1343</v>
+        <v>1523</v>
       </c>
       <c r="C105" t="s">
-        <v>1344</v>
+        <v>1524</v>
       </c>
       <c r="D105" t="s">
         <v>157</v>
@@ -12879,25 +14019,25 @@
         <v>158</v>
       </c>
       <c r="I105" t="s">
-        <v>1345</v>
+        <v>1525</v>
       </c>
       <c r="J105" t="s">
-        <v>1346</v>
+        <v>1526</v>
       </c>
       <c r="K105" t="s">
-        <v>1347</v>
+        <v>1527</v>
       </c>
       <c r="L105" t="s">
-        <v>1348</v>
+        <v>1528</v>
       </c>
       <c r="M105" t="s">
-        <v>1349</v>
+        <v>1529</v>
       </c>
       <c r="N105" t="s">
-        <v>1350</v>
+        <v>1530</v>
       </c>
       <c r="P105" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q105" t="s">
         <v>47</v>
@@ -12906,16 +14046,16 @@
         <v>48</v>
       </c>
       <c r="S105" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T105" t="s">
-        <v>1351</v>
+        <v>1531</v>
       </c>
       <c r="U105" t="s">
-        <v>1352</v>
+        <v>1532</v>
       </c>
       <c r="V105" t="s">
-        <v>1353</v>
+        <v>1533</v>
       </c>
       <c r="W105" s="1" t="s">
         <v>52</v>
@@ -12923,13 +14063,13 @@
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1354</v>
+        <v>1534</v>
       </c>
       <c r="B106" t="s">
-        <v>1355</v>
+        <v>1535</v>
       </c>
       <c r="C106" t="s">
-        <v>1356</v>
+        <v>1536</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -12941,25 +14081,25 @@
         <v>66</v>
       </c>
       <c r="G106" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I106" t="s">
-        <v>1357</v>
+        <v>1537</v>
       </c>
       <c r="J106" t="s">
-        <v>1358</v>
+        <v>1538</v>
       </c>
       <c r="K106" t="s">
-        <v>1359</v>
+        <v>1539</v>
       </c>
       <c r="L106" t="s">
-        <v>1360</v>
+        <v>1540</v>
       </c>
       <c r="M106" t="s">
-        <v>1361</v>
+        <v>1541</v>
       </c>
       <c r="N106" t="s">
-        <v>1362</v>
+        <v>1542</v>
       </c>
       <c r="P106" t="s">
         <v>46</v>
@@ -12971,13 +14111,13 @@
         <v>48</v>
       </c>
       <c r="T106" t="s">
-        <v>1363</v>
+        <v>1543</v>
       </c>
       <c r="U106" t="s">
-        <v>1364</v>
+        <v>1544</v>
       </c>
       <c r="V106" t="s">
-        <v>1365</v>
+        <v>1545</v>
       </c>
       <c r="W106" s="1" t="s">
         <v>52</v>
@@ -12985,13 +14125,13 @@
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1366</v>
+        <v>1546</v>
       </c>
       <c r="B107" t="s">
-        <v>1367</v>
+        <v>1547</v>
       </c>
       <c r="C107" t="s">
-        <v>1368</v>
+        <v>1548</v>
       </c>
       <c r="D107" t="s">
         <v>35</v>
@@ -13006,22 +14146,22 @@
         <v>158</v>
       </c>
       <c r="I107" t="s">
-        <v>1369</v>
+        <v>1549</v>
       </c>
       <c r="J107" t="s">
-        <v>1370</v>
+        <v>1550</v>
       </c>
       <c r="K107" t="s">
-        <v>1371</v>
+        <v>1551</v>
       </c>
       <c r="L107" t="s">
-        <v>1372</v>
+        <v>1552</v>
       </c>
       <c r="M107" t="s">
-        <v>1373</v>
+        <v>1553</v>
       </c>
       <c r="N107" t="s">
-        <v>1374</v>
+        <v>1554</v>
       </c>
       <c r="P107" t="s">
         <v>46</v>
@@ -13033,13 +14173,13 @@
         <v>48</v>
       </c>
       <c r="T107" t="s">
-        <v>1375</v>
+        <v>1555</v>
       </c>
       <c r="U107" t="s">
-        <v>1376</v>
+        <v>1556</v>
       </c>
       <c r="V107" t="s">
-        <v>1377</v>
+        <v>1557</v>
       </c>
       <c r="W107" s="1" t="s">
         <v>52</v>
@@ -13047,13 +14187,13 @@
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1378</v>
+        <v>1558</v>
       </c>
       <c r="B108" t="s">
-        <v>1379</v>
+        <v>1559</v>
       </c>
       <c r="C108" t="s">
-        <v>1380</v>
+        <v>1560</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
@@ -13065,25 +14205,25 @@
         <v>66</v>
       </c>
       <c r="G108" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I108" t="s">
-        <v>1381</v>
+        <v>1561</v>
       </c>
       <c r="J108" t="s">
-        <v>1382</v>
+        <v>1562</v>
       </c>
       <c r="K108" t="s">
-        <v>1383</v>
+        <v>1563</v>
       </c>
       <c r="L108" t="s">
-        <v>1384</v>
+        <v>1564</v>
       </c>
       <c r="M108" t="s">
-        <v>1385</v>
+        <v>1565</v>
       </c>
       <c r="N108" t="s">
-        <v>1386</v>
+        <v>1566</v>
       </c>
       <c r="P108" t="s">
         <v>46</v>
@@ -13095,13 +14235,13 @@
         <v>48</v>
       </c>
       <c r="T108" t="s">
-        <v>1387</v>
+        <v>1567</v>
       </c>
       <c r="U108" t="s">
-        <v>1388</v>
+        <v>1568</v>
       </c>
       <c r="V108" t="s">
-        <v>1389</v>
+        <v>1569</v>
       </c>
       <c r="W108" s="1" t="s">
         <v>52</v>
@@ -13109,13 +14249,13 @@
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1390</v>
+        <v>1570</v>
       </c>
       <c r="B109" t="s">
-        <v>1391</v>
+        <v>1571</v>
       </c>
       <c r="C109" t="s">
-        <v>1392</v>
+        <v>1572</v>
       </c>
       <c r="D109" t="s">
         <v>157</v>
@@ -13130,25 +14270,25 @@
         <v>158</v>
       </c>
       <c r="I109" t="s">
-        <v>1393</v>
+        <v>1573</v>
       </c>
       <c r="J109" t="s">
-        <v>1394</v>
+        <v>1574</v>
       </c>
       <c r="K109" t="s">
-        <v>1395</v>
+        <v>1575</v>
       </c>
       <c r="L109" t="s">
-        <v>1396</v>
+        <v>1576</v>
       </c>
       <c r="M109" t="s">
-        <v>1397</v>
+        <v>1577</v>
       </c>
       <c r="N109" t="s">
-        <v>1398</v>
+        <v>1578</v>
       </c>
       <c r="P109" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q109" t="s">
         <v>47</v>
@@ -13157,16 +14297,16 @@
         <v>48</v>
       </c>
       <c r="S109" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T109" t="s">
-        <v>1399</v>
+        <v>1579</v>
       </c>
       <c r="U109" t="s">
-        <v>1400</v>
+        <v>1580</v>
       </c>
       <c r="V109" t="s">
-        <v>1401</v>
+        <v>1581</v>
       </c>
       <c r="W109" s="1" t="s">
         <v>52</v>
@@ -13174,13 +14314,13 @@
     </row>
     <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1402</v>
+        <v>1582</v>
       </c>
       <c r="B110" t="s">
-        <v>1403</v>
+        <v>1583</v>
       </c>
       <c r="C110" t="s">
-        <v>1404</v>
+        <v>1584</v>
       </c>
       <c r="D110" t="s">
         <v>157</v>
@@ -13195,25 +14335,25 @@
         <v>158</v>
       </c>
       <c r="I110" t="s">
-        <v>1405</v>
+        <v>1585</v>
       </c>
       <c r="J110" t="s">
-        <v>1406</v>
+        <v>1586</v>
       </c>
       <c r="K110" t="s">
-        <v>1407</v>
+        <v>1587</v>
       </c>
       <c r="L110" t="s">
-        <v>1408</v>
+        <v>1588</v>
       </c>
       <c r="M110" t="s">
-        <v>1409</v>
+        <v>1589</v>
       </c>
       <c r="N110" t="s">
-        <v>1410</v>
+        <v>1590</v>
       </c>
       <c r="P110" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q110" t="s">
         <v>47</v>
@@ -13222,16 +14362,16 @@
         <v>48</v>
       </c>
       <c r="S110" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T110" t="s">
-        <v>1411</v>
+        <v>1591</v>
       </c>
       <c r="U110" t="s">
-        <v>1412</v>
+        <v>1592</v>
       </c>
       <c r="V110" t="s">
-        <v>1413</v>
+        <v>1593</v>
       </c>
       <c r="W110" s="1" t="s">
         <v>52</v>
@@ -13239,13 +14379,13 @@
     </row>
     <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1414</v>
+        <v>1594</v>
       </c>
       <c r="B111" t="s">
-        <v>1415</v>
+        <v>1595</v>
       </c>
       <c r="C111" t="s">
-        <v>1416</v>
+        <v>1596</v>
       </c>
       <c r="D111" t="s">
         <v>65</v>
@@ -13260,25 +14400,25 @@
         <v>89</v>
       </c>
       <c r="I111" t="s">
-        <v>1417</v>
+        <v>1597</v>
       </c>
       <c r="J111" t="s">
-        <v>1418</v>
+        <v>1598</v>
       </c>
       <c r="K111" t="s">
-        <v>1419</v>
+        <v>1599</v>
       </c>
       <c r="L111" t="s">
-        <v>1420</v>
+        <v>1600</v>
       </c>
       <c r="M111" t="s">
-        <v>1421</v>
+        <v>1601</v>
       </c>
       <c r="N111" t="s">
-        <v>1422</v>
+        <v>1602</v>
       </c>
       <c r="P111" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q111" t="s">
         <v>47</v>
@@ -13287,16 +14427,16 @@
         <v>48</v>
       </c>
       <c r="S111" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T111" t="s">
-        <v>1423</v>
+        <v>1603</v>
       </c>
       <c r="U111" t="s">
-        <v>1424</v>
+        <v>1604</v>
       </c>
       <c r="V111" t="s">
-        <v>1425</v>
+        <v>1605</v>
       </c>
       <c r="W111" s="1" t="s">
         <v>52</v>
@@ -13304,13 +14444,13 @@
     </row>
     <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1426</v>
+        <v>1606</v>
       </c>
       <c r="B112" t="s">
-        <v>1427</v>
+        <v>1607</v>
       </c>
       <c r="C112" t="s">
-        <v>1428</v>
+        <v>1608</v>
       </c>
       <c r="D112" t="s">
         <v>65</v>
@@ -13322,31 +14462,31 @@
         <v>66</v>
       </c>
       <c r="G112" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I112" t="s">
-        <v>1429</v>
+        <v>1609</v>
       </c>
       <c r="J112" t="s">
-        <v>1430</v>
+        <v>1610</v>
       </c>
       <c r="K112" t="s">
-        <v>1431</v>
+        <v>1611</v>
       </c>
       <c r="L112" t="s">
-        <v>1432</v>
+        <v>1612</v>
       </c>
       <c r="M112" t="s">
-        <v>1433</v>
+        <v>1613</v>
       </c>
       <c r="N112" t="s">
-        <v>1434</v>
+        <v>1614</v>
       </c>
       <c r="O112" t="s">
         <v>141</v>
       </c>
       <c r="P112" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q112" t="s">
         <v>47</v>
@@ -13355,16 +14495,16 @@
         <v>48</v>
       </c>
       <c r="S112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T112" t="s">
-        <v>1435</v>
+        <v>1615</v>
       </c>
       <c r="U112" t="s">
-        <v>1436</v>
+        <v>1616</v>
       </c>
       <c r="V112" t="s">
-        <v>1437</v>
+        <v>1617</v>
       </c>
       <c r="W112" s="1" t="s">
         <v>52</v>
@@ -13372,13 +14512,13 @@
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1438</v>
+        <v>1618</v>
       </c>
       <c r="B113" t="s">
-        <v>1439</v>
+        <v>1619</v>
       </c>
       <c r="C113" t="s">
-        <v>1440</v>
+        <v>1620</v>
       </c>
       <c r="D113" t="s">
         <v>65</v>
@@ -13390,31 +14530,31 @@
         <v>66</v>
       </c>
       <c r="G113" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I113" t="s">
-        <v>1441</v>
+        <v>1621</v>
       </c>
       <c r="J113" t="s">
-        <v>1442</v>
+        <v>1622</v>
       </c>
       <c r="K113" t="s">
-        <v>1443</v>
+        <v>1623</v>
       </c>
       <c r="L113" t="s">
-        <v>1444</v>
+        <v>1624</v>
       </c>
       <c r="M113" t="s">
-        <v>1445</v>
+        <v>1625</v>
       </c>
       <c r="N113" t="s">
-        <v>1446</v>
+        <v>1626</v>
       </c>
       <c r="O113" t="s">
         <v>141</v>
       </c>
       <c r="P113" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q113" t="s">
         <v>47</v>
@@ -13423,16 +14563,16 @@
         <v>48</v>
       </c>
       <c r="S113" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T113" t="s">
-        <v>1447</v>
+        <v>1627</v>
       </c>
       <c r="U113" t="s">
-        <v>1448</v>
+        <v>1628</v>
       </c>
       <c r="V113" t="s">
-        <v>1449</v>
+        <v>1629</v>
       </c>
       <c r="W113" s="1" t="s">
         <v>52</v>
@@ -13440,13 +14580,13 @@
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1450</v>
+        <v>1630</v>
       </c>
       <c r="B114" t="s">
-        <v>1451</v>
+        <v>1631</v>
       </c>
       <c r="C114" t="s">
-        <v>1452</v>
+        <v>1632</v>
       </c>
       <c r="D114" t="s">
         <v>35</v>
@@ -13458,25 +14598,25 @@
         <v>37</v>
       </c>
       <c r="G114" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I114" t="s">
-        <v>1453</v>
+        <v>1633</v>
       </c>
       <c r="J114" t="s">
-        <v>1454</v>
+        <v>1634</v>
       </c>
       <c r="K114" t="s">
-        <v>1455</v>
+        <v>1635</v>
       </c>
       <c r="L114" t="s">
-        <v>1456</v>
+        <v>1636</v>
       </c>
       <c r="M114" t="s">
-        <v>1457</v>
+        <v>1637</v>
       </c>
       <c r="N114" t="s">
-        <v>1458</v>
+        <v>1638</v>
       </c>
       <c r="P114" t="s">
         <v>46</v>
@@ -13488,13 +14628,13 @@
         <v>48</v>
       </c>
       <c r="T114" t="s">
-        <v>1459</v>
+        <v>1639</v>
       </c>
       <c r="U114" t="s">
-        <v>1460</v>
+        <v>1640</v>
       </c>
       <c r="V114" t="s">
-        <v>1461</v>
+        <v>1641</v>
       </c>
       <c r="W114" s="1" t="s">
         <v>52</v>
@@ -13502,13 +14642,13 @@
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1462</v>
+        <v>1642</v>
       </c>
       <c r="B115" t="s">
-        <v>1463</v>
+        <v>1643</v>
       </c>
       <c r="C115" t="s">
-        <v>1464</v>
+        <v>1644</v>
       </c>
       <c r="D115" t="s">
         <v>65</v>
@@ -13520,25 +14660,25 @@
         <v>66</v>
       </c>
       <c r="G115" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I115" t="s">
-        <v>1465</v>
+        <v>1645</v>
       </c>
       <c r="J115" t="s">
-        <v>1466</v>
+        <v>1646</v>
       </c>
       <c r="K115" t="s">
-        <v>1467</v>
+        <v>1647</v>
       </c>
       <c r="L115" t="s">
-        <v>1468</v>
+        <v>1648</v>
       </c>
       <c r="M115" t="s">
-        <v>1469</v>
+        <v>1649</v>
       </c>
       <c r="N115" t="s">
-        <v>1470</v>
+        <v>1650</v>
       </c>
       <c r="P115" t="s">
         <v>46</v>
@@ -13550,13 +14690,13 @@
         <v>48</v>
       </c>
       <c r="T115" t="s">
-        <v>1471</v>
+        <v>1651</v>
       </c>
       <c r="U115" t="s">
-        <v>1472</v>
+        <v>1652</v>
       </c>
       <c r="V115" t="s">
-        <v>1473</v>
+        <v>1653</v>
       </c>
       <c r="W115" s="1" t="s">
         <v>52</v>
@@ -13564,13 +14704,13 @@
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1474</v>
+        <v>1654</v>
       </c>
       <c r="B116" t="s">
-        <v>1475</v>
+        <v>1655</v>
       </c>
       <c r="C116" t="s">
-        <v>1476</v>
+        <v>1656</v>
       </c>
       <c r="D116" t="s">
         <v>65</v>
@@ -13582,25 +14722,25 @@
         <v>66</v>
       </c>
       <c r="G116" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I116" t="s">
-        <v>1477</v>
+        <v>1657</v>
       </c>
       <c r="J116" t="s">
-        <v>1478</v>
+        <v>1658</v>
       </c>
       <c r="K116" t="s">
-        <v>1479</v>
+        <v>1659</v>
       </c>
       <c r="L116" t="s">
-        <v>1480</v>
+        <v>1660</v>
       </c>
       <c r="M116" t="s">
-        <v>1481</v>
+        <v>1661</v>
       </c>
       <c r="N116" t="s">
-        <v>1482</v>
+        <v>1662</v>
       </c>
       <c r="P116" t="s">
         <v>46</v>
@@ -13612,13 +14752,13 @@
         <v>48</v>
       </c>
       <c r="T116" t="s">
-        <v>1483</v>
+        <v>1663</v>
       </c>
       <c r="U116" t="s">
-        <v>1484</v>
+        <v>1664</v>
       </c>
       <c r="V116" t="s">
-        <v>1485</v>
+        <v>1665</v>
       </c>
       <c r="W116" s="1" t="s">
         <v>52</v>
@@ -13626,13 +14766,13 @@
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1486</v>
+        <v>1666</v>
       </c>
       <c r="B117" t="s">
-        <v>1487</v>
+        <v>1667</v>
       </c>
       <c r="C117" t="s">
-        <v>1488</v>
+        <v>1668</v>
       </c>
       <c r="D117" t="s">
         <v>35</v>
@@ -13644,31 +14784,31 @@
         <v>37</v>
       </c>
       <c r="G117" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I117" t="s">
-        <v>1489</v>
+        <v>1669</v>
       </c>
       <c r="J117" t="s">
-        <v>1490</v>
+        <v>1670</v>
       </c>
       <c r="K117" t="s">
-        <v>1491</v>
+        <v>1671</v>
       </c>
       <c r="L117" t="s">
-        <v>1492</v>
+        <v>1672</v>
       </c>
       <c r="M117" t="s">
-        <v>1493</v>
+        <v>1673</v>
       </c>
       <c r="N117" t="s">
-        <v>1494</v>
+        <v>1674</v>
       </c>
       <c r="O117" t="s">
         <v>141</v>
       </c>
       <c r="P117" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q117" t="s">
         <v>47</v>
@@ -13677,16 +14817,16 @@
         <v>48</v>
       </c>
       <c r="S117" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T117" t="s">
-        <v>1495</v>
+        <v>1675</v>
       </c>
       <c r="U117" t="s">
-        <v>1496</v>
+        <v>1676</v>
       </c>
       <c r="V117" t="s">
-        <v>1497</v>
+        <v>1677</v>
       </c>
       <c r="W117" s="1" t="s">
         <v>52</v>
@@ -13694,13 +14834,13 @@
     </row>
     <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1498</v>
+        <v>1678</v>
       </c>
       <c r="B118" t="s">
-        <v>1499</v>
+        <v>1679</v>
       </c>
       <c r="C118" t="s">
-        <v>1500</v>
+        <v>1680</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -13715,25 +14855,25 @@
         <v>158</v>
       </c>
       <c r="I118" t="s">
-        <v>1501</v>
+        <v>1681</v>
       </c>
       <c r="J118" t="s">
-        <v>1502</v>
+        <v>1682</v>
       </c>
       <c r="K118" t="s">
-        <v>1503</v>
+        <v>1683</v>
       </c>
       <c r="L118" t="s">
-        <v>1504</v>
+        <v>1684</v>
       </c>
       <c r="M118" t="s">
-        <v>1505</v>
+        <v>1685</v>
       </c>
       <c r="N118" t="s">
-        <v>1506</v>
+        <v>1686</v>
       </c>
       <c r="P118" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Q118" t="s">
         <v>47</v>
@@ -13742,16 +14882,16 @@
         <v>48</v>
       </c>
       <c r="S118" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T118" t="s">
-        <v>1507</v>
+        <v>1687</v>
       </c>
       <c r="U118" t="s">
-        <v>1508</v>
+        <v>1688</v>
       </c>
       <c r="V118" t="s">
-        <v>1509</v>
+        <v>1689</v>
       </c>
       <c r="W118" s="1" t="s">
         <v>52</v>
@@ -13759,13 +14899,13 @@
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1510</v>
+        <v>1690</v>
       </c>
       <c r="B119" t="s">
-        <v>1511</v>
+        <v>1691</v>
       </c>
       <c r="C119" t="s">
-        <v>1512</v>
+        <v>1692</v>
       </c>
       <c r="D119" t="s">
         <v>35</v>
@@ -13777,25 +14917,25 @@
         <v>133</v>
       </c>
       <c r="G119" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I119" t="s">
-        <v>1513</v>
+        <v>1693</v>
       </c>
       <c r="J119" t="s">
-        <v>1514</v>
+        <v>1694</v>
       </c>
       <c r="K119" t="s">
-        <v>1515</v>
+        <v>1695</v>
       </c>
       <c r="L119" t="s">
-        <v>1516</v>
+        <v>1696</v>
       </c>
       <c r="M119" t="s">
-        <v>1517</v>
+        <v>1697</v>
       </c>
       <c r="N119" t="s">
-        <v>1518</v>
+        <v>1698</v>
       </c>
       <c r="O119" t="s">
         <v>141</v>
@@ -13810,13 +14950,13 @@
         <v>48</v>
       </c>
       <c r="T119" t="s">
-        <v>1519</v>
+        <v>1699</v>
       </c>
       <c r="U119" t="s">
-        <v>1520</v>
+        <v>1700</v>
       </c>
       <c r="V119" t="s">
-        <v>1521</v>
+        <v>1701</v>
       </c>
       <c r="W119" s="1" t="s">
         <v>52</v>
@@ -13824,13 +14964,13 @@
     </row>
     <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1522</v>
+        <v>1702</v>
       </c>
       <c r="B120" t="s">
-        <v>1523</v>
+        <v>1703</v>
       </c>
       <c r="C120" t="s">
-        <v>1524</v>
+        <v>1704</v>
       </c>
       <c r="D120" t="s">
         <v>65</v>
@@ -13842,25 +14982,25 @@
         <v>66</v>
       </c>
       <c r="G120" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I120" t="s">
-        <v>1525</v>
+        <v>1705</v>
       </c>
       <c r="J120" t="s">
-        <v>1526</v>
+        <v>1706</v>
       </c>
       <c r="K120" t="s">
-        <v>1527</v>
+        <v>1707</v>
       </c>
       <c r="L120" t="s">
-        <v>1528</v>
+        <v>1708</v>
       </c>
       <c r="M120" t="s">
-        <v>1529</v>
+        <v>1709</v>
       </c>
       <c r="N120" t="s">
-        <v>1530</v>
+        <v>1710</v>
       </c>
       <c r="P120" t="s">
         <v>46</v>
@@ -13872,13 +15012,13 @@
         <v>48</v>
       </c>
       <c r="T120" t="s">
-        <v>1531</v>
+        <v>1711</v>
       </c>
       <c r="U120" t="s">
-        <v>1532</v>
+        <v>1712</v>
       </c>
       <c r="V120" t="s">
-        <v>1533</v>
+        <v>1713</v>
       </c>
       <c r="W120" s="1" t="s">
         <v>52</v>
@@ -13886,13 +15026,13 @@
     </row>
     <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1534</v>
+        <v>1714</v>
       </c>
       <c r="B121" t="s">
-        <v>1535</v>
+        <v>1715</v>
       </c>
       <c r="C121" t="s">
-        <v>1536</v>
+        <v>1716</v>
       </c>
       <c r="D121" t="s">
         <v>35</v>
@@ -13907,22 +15047,22 @@
         <v>89</v>
       </c>
       <c r="I121" t="s">
-        <v>1537</v>
+        <v>1717</v>
       </c>
       <c r="J121" t="s">
-        <v>1538</v>
+        <v>1718</v>
       </c>
       <c r="K121" t="s">
-        <v>1539</v>
+        <v>1719</v>
       </c>
       <c r="L121" t="s">
-        <v>1540</v>
+        <v>1720</v>
       </c>
       <c r="M121" t="s">
-        <v>1541</v>
+        <v>1721</v>
       </c>
       <c r="N121" t="s">
-        <v>1542</v>
+        <v>1722</v>
       </c>
       <c r="O121" t="s">
         <v>141</v>
@@ -13937,13 +15077,13 @@
         <v>48</v>
       </c>
       <c r="T121" t="s">
-        <v>1543</v>
+        <v>1723</v>
       </c>
       <c r="U121" t="s">
-        <v>1544</v>
+        <v>1724</v>
       </c>
       <c r="V121" t="s">
-        <v>1545</v>
+        <v>1725</v>
       </c>
       <c r="W121" s="1" t="s">
         <v>52</v>
@@ -13951,13 +15091,13 @@
     </row>
     <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1546</v>
+        <v>1726</v>
       </c>
       <c r="B122" t="s">
-        <v>1547</v>
+        <v>1727</v>
       </c>
       <c r="C122" t="s">
-        <v>1548</v>
+        <v>1728</v>
       </c>
       <c r="D122" t="s">
         <v>65</v>
@@ -13969,25 +15109,25 @@
         <v>66</v>
       </c>
       <c r="G122" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I122" t="s">
-        <v>1549</v>
+        <v>1729</v>
       </c>
       <c r="J122" t="s">
-        <v>1550</v>
+        <v>1730</v>
       </c>
       <c r="K122" t="s">
-        <v>1551</v>
+        <v>1731</v>
       </c>
       <c r="L122" t="s">
-        <v>1552</v>
+        <v>1732</v>
       </c>
       <c r="M122" t="s">
-        <v>1553</v>
+        <v>1733</v>
       </c>
       <c r="N122" t="s">
-        <v>1554</v>
+        <v>1734</v>
       </c>
       <c r="P122" t="s">
         <v>46</v>
@@ -13999,13 +15139,13 @@
         <v>48</v>
       </c>
       <c r="T122" t="s">
-        <v>1555</v>
+        <v>1735</v>
       </c>
       <c r="U122" t="s">
-        <v>1556</v>
+        <v>1736</v>
       </c>
       <c r="V122" t="s">
-        <v>1557</v>
+        <v>1737</v>
       </c>
       <c r="W122" s="1" t="s">
         <v>52</v>
@@ -14013,13 +15153,13 @@
     </row>
     <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1558</v>
+        <v>1738</v>
       </c>
       <c r="B123" t="s">
-        <v>1559</v>
+        <v>1739</v>
       </c>
       <c r="C123" t="s">
-        <v>1560</v>
+        <v>1740</v>
       </c>
       <c r="D123" t="s">
         <v>65</v>
@@ -14031,25 +15171,25 @@
         <v>66</v>
       </c>
       <c r="G123" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I123" t="s">
-        <v>1561</v>
+        <v>1741</v>
       </c>
       <c r="J123" t="s">
-        <v>1562</v>
+        <v>1742</v>
       </c>
       <c r="K123" t="s">
-        <v>1563</v>
+        <v>1743</v>
       </c>
       <c r="L123" t="s">
-        <v>1564</v>
+        <v>1744</v>
       </c>
       <c r="M123" t="s">
-        <v>1565</v>
+        <v>1745</v>
       </c>
       <c r="N123" t="s">
-        <v>1566</v>
+        <v>1746</v>
       </c>
       <c r="P123" t="s">
         <v>46</v>
@@ -14061,13 +15201,13 @@
         <v>48</v>
       </c>
       <c r="T123" t="s">
-        <v>1567</v>
+        <v>1747</v>
       </c>
       <c r="U123" t="s">
-        <v>1568</v>
+        <v>1748</v>
       </c>
       <c r="V123" t="s">
-        <v>1569</v>
+        <v>1749</v>
       </c>
       <c r="W123" s="1" t="s">
         <v>52</v>
@@ -14075,13 +15215,13 @@
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1570</v>
+        <v>1750</v>
       </c>
       <c r="B124" t="s">
-        <v>1571</v>
+        <v>1751</v>
       </c>
       <c r="C124" t="s">
-        <v>1572</v>
+        <v>1752</v>
       </c>
       <c r="D124" t="s">
         <v>65</v>
@@ -14093,25 +15233,25 @@
         <v>66</v>
       </c>
       <c r="G124" t="s">
-        <v>259</v>
+        <v>331</v>
       </c>
       <c r="I124" t="s">
-        <v>1573</v>
+        <v>1753</v>
       </c>
       <c r="J124" t="s">
-        <v>1574</v>
+        <v>1754</v>
       </c>
       <c r="K124" t="s">
-        <v>1575</v>
+        <v>1755</v>
       </c>
       <c r="L124" t="s">
-        <v>1576</v>
+        <v>1756</v>
       </c>
       <c r="M124" t="s">
-        <v>1577</v>
+        <v>1757</v>
       </c>
       <c r="N124" t="s">
-        <v>1578</v>
+        <v>1758</v>
       </c>
       <c r="P124" t="s">
         <v>46</v>
@@ -14123,13 +15263,13 @@
         <v>48</v>
       </c>
       <c r="T124" t="s">
-        <v>1579</v>
+        <v>1759</v>
       </c>
       <c r="U124" t="s">
-        <v>1580</v>
+        <v>1760</v>
       </c>
       <c r="V124" t="s">
-        <v>1581</v>
+        <v>1761</v>
       </c>
       <c r="W124" s="1" t="s">
         <v>52</v>
@@ -14137,13 +15277,13 @@
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1582</v>
+        <v>1762</v>
       </c>
       <c r="B125" t="s">
-        <v>1583</v>
+        <v>1763</v>
       </c>
       <c r="C125" t="s">
-        <v>1584</v>
+        <v>1764</v>
       </c>
       <c r="D125" t="s">
         <v>35</v>
@@ -14155,25 +15295,25 @@
         <v>133</v>
       </c>
       <c r="G125" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I125" t="s">
-        <v>1585</v>
+        <v>1765</v>
       </c>
       <c r="J125" t="s">
-        <v>1586</v>
+        <v>1766</v>
       </c>
       <c r="K125" t="s">
-        <v>1587</v>
+        <v>1767</v>
       </c>
       <c r="L125" t="s">
-        <v>1588</v>
+        <v>1768</v>
       </c>
       <c r="M125" t="s">
-        <v>1589</v>
+        <v>1769</v>
       </c>
       <c r="N125" t="s">
-        <v>1590</v>
+        <v>1770</v>
       </c>
       <c r="O125" t="s">
         <v>141</v>
@@ -14188,13 +15328,13 @@
         <v>48</v>
       </c>
       <c r="T125" t="s">
-        <v>1591</v>
+        <v>1771</v>
       </c>
       <c r="U125" t="s">
-        <v>1592</v>
+        <v>1772</v>
       </c>
       <c r="V125" t="s">
-        <v>1593</v>
+        <v>1773</v>
       </c>
       <c r="W125" s="1" t="s">
         <v>52</v>
@@ -14202,13 +15342,13 @@
     </row>
     <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1594</v>
+        <v>1774</v>
       </c>
       <c r="B126" t="s">
-        <v>1595</v>
+        <v>1775</v>
       </c>
       <c r="C126" t="s">
-        <v>1596</v>
+        <v>1776</v>
       </c>
       <c r="D126" t="s">
         <v>65</v>
@@ -14223,28 +15363,28 @@
         <v>38</v>
       </c>
       <c r="I126" t="s">
-        <v>1597</v>
+        <v>1777</v>
       </c>
       <c r="J126" t="s">
-        <v>1598</v>
+        <v>1778</v>
       </c>
       <c r="K126" t="s">
-        <v>1599</v>
+        <v>1779</v>
       </c>
       <c r="L126" t="s">
-        <v>1600</v>
+        <v>1780</v>
       </c>
       <c r="M126" t="s">
-        <v>1601</v>
+        <v>1781</v>
       </c>
       <c r="N126" t="s">
-        <v>1602</v>
+        <v>1782</v>
       </c>
       <c r="O126" t="s">
         <v>141</v>
       </c>
       <c r="P126" t="s">
-        <v>471</v>
+        <v>651</v>
       </c>
       <c r="Q126" t="s">
         <v>47</v>
@@ -14253,16 +15393,16 @@
         <v>48</v>
       </c>
       <c r="S126" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="T126" t="s">
-        <v>1603</v>
+        <v>1783</v>
       </c>
       <c r="U126" t="s">
-        <v>1604</v>
+        <v>1784</v>
       </c>
       <c r="V126" t="s">
-        <v>1605</v>
+        <v>1785</v>
       </c>
       <c r="W126" s="1" t="s">
         <v>52</v>
@@ -14270,13 +15410,13 @@
     </row>
     <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1606</v>
+        <v>1786</v>
       </c>
       <c r="B127" t="s">
-        <v>1607</v>
+        <v>1787</v>
       </c>
       <c r="C127" t="s">
-        <v>1608</v>
+        <v>1788</v>
       </c>
       <c r="D127" t="s">
         <v>157</v>
@@ -14285,25 +15425,25 @@
         <v>132</v>
       </c>
       <c r="F127" t="s">
-        <v>960</v>
+        <v>1140</v>
       </c>
       <c r="G127" t="s">
         <v>158</v>
       </c>
       <c r="I127" t="s">
-        <v>1609</v>
+        <v>1789</v>
       </c>
       <c r="J127" t="s">
-        <v>1610</v>
+        <v>1790</v>
       </c>
       <c r="K127" t="s">
-        <v>1611</v>
+        <v>1791</v>
       </c>
       <c r="M127" t="s">
-        <v>1612</v>
+        <v>1792</v>
       </c>
       <c r="N127" t="s">
-        <v>1613</v>
+        <v>1793</v>
       </c>
       <c r="O127" t="s">
         <v>141</v>
@@ -14318,30 +15458,30 @@
         <v>48</v>
       </c>
       <c r="S127" t="s">
-        <v>966</v>
+        <v>1146</v>
       </c>
       <c r="T127" t="s">
-        <v>1614</v>
+        <v>1794</v>
       </c>
       <c r="U127" t="s">
-        <v>1615</v>
+        <v>1795</v>
       </c>
       <c r="V127" t="s">
-        <v>1616</v>
+        <v>1796</v>
       </c>
       <c r="W127" s="1" t="s">
-        <v>970</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1617</v>
+        <v>1797</v>
       </c>
       <c r="B128" t="s">
-        <v>1618</v>
+        <v>1798</v>
       </c>
       <c r="C128" t="s">
-        <v>1619</v>
+        <v>1799</v>
       </c>
       <c r="D128" t="s">
         <v>65</v>
@@ -14353,25 +15493,25 @@
         <v>66</v>
       </c>
       <c r="G128" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I128" t="s">
-        <v>1620</v>
+        <v>1800</v>
       </c>
       <c r="J128" t="s">
-        <v>1621</v>
+        <v>1801</v>
       </c>
       <c r="K128" t="s">
-        <v>1622</v>
+        <v>1802</v>
       </c>
       <c r="L128" t="s">
-        <v>1623</v>
+        <v>1803</v>
       </c>
       <c r="M128" t="s">
-        <v>1624</v>
+        <v>1804</v>
       </c>
       <c r="N128" t="s">
-        <v>1625</v>
+        <v>1805</v>
       </c>
       <c r="P128" t="s">
         <v>46</v>
@@ -14383,13 +15523,13 @@
         <v>48</v>
       </c>
       <c r="T128" t="s">
-        <v>1626</v>
+        <v>1806</v>
       </c>
       <c r="U128" t="s">
-        <v>1627</v>
+        <v>1807</v>
       </c>
       <c r="V128" t="s">
-        <v>1628</v>
+        <v>1808</v>
       </c>
       <c r="W128" s="1" t="s">
         <v>52</v>
@@ -14397,13 +15537,13 @@
     </row>
     <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>1629</v>
+        <v>1809</v>
       </c>
       <c r="B129" t="s">
-        <v>1630</v>
+        <v>1810</v>
       </c>
       <c r="C129" t="s">
-        <v>1631</v>
+        <v>1811</v>
       </c>
       <c r="D129" t="s">
         <v>35</v>
@@ -14415,25 +15555,25 @@
         <v>37</v>
       </c>
       <c r="G129" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="I129" t="s">
-        <v>1632</v>
+        <v>1812</v>
       </c>
       <c r="J129" t="s">
-        <v>1633</v>
+        <v>1813</v>
       </c>
       <c r="K129" t="s">
-        <v>1634</v>
+        <v>1814</v>
       </c>
       <c r="L129" t="s">
-        <v>1635</v>
+        <v>1815</v>
       </c>
       <c r="M129" t="s">
-        <v>1636</v>
+        <v>1816</v>
       </c>
       <c r="N129" t="s">
-        <v>1637</v>
+        <v>1817</v>
       </c>
       <c r="P129" t="s">
         <v>46</v>
@@ -14445,13 +15585,13 @@
         <v>48</v>
       </c>
       <c r="T129" t="s">
-        <v>1638</v>
+        <v>1818</v>
       </c>
       <c r="U129" t="s">
-        <v>1639</v>
+        <v>1819</v>
       </c>
       <c r="V129" t="s">
-        <v>1640</v>
+        <v>1820</v>
       </c>
       <c r="W129" s="1" t="s">
         <v>52</v>

--- a/input/cursos.xlsx
+++ b/input/cursos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2914" uniqueCount="1821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="2116">
   <si>
     <t>course_id</t>
   </si>
@@ -1929,6 +1929,9 @@
     <t>gestao-publica</t>
   </si>
   <si>
+    <t>Planeje a melhoria de serviços públicos municipais, com qualidade, produtividade e uso eficiente de recursos e bens públicos.</t>
+  </si>
+  <si>
     <t>O curso de Gestão Pública EAD da Cruzeiro do Sul Virtual forma profissionais competitivos no mercado, alinhados às tendências de administração e aptos a vivenciar desafios nas organizações. Com conteúdos voltados para ações de planejamento, qualidade, produtividade, gestão e empreendedorismo, a formação prepara o estudante para o mercado de trabalho. O curso combina a teoria com a prática, tornando o aluno pronto para buscar soluções inovadoras para a gestão, utilizando recursos e bens públicos como meio de tomada de decisão eficiente, realizando políticas públicas de qualidade. Com 4 semestres de duração (2 anos) e conceito 5 na classificação do MEC, o aluno terá o título de tecnólogo em Gestão Pública.</t>
   </si>
   <si>
@@ -1960,6 +1963,30 @@
     <t>Prepare-se para atuar na Gestão Pública a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Reorganização do fluxo de atendimento ao cidadão</t>
+  </si>
+  <si>
+    <t>Gestor de serviços municipais de cerca de 35 anos, homem de pele negra, cabelo raspado, barba curta, óculos redondos, colete de linho verde sobre camisa branca, atenção ao fluxo da sala.</t>
+  </si>
+  <si>
+    <t>Centro de atendimento ao cidadão contemporâneo brasileiro, balcões iguais, fitas de fila, painel apagado, janelas, salão claro e organizado, sem tribuna e sem bandeiras.</t>
+  </si>
+  <si>
+    <t>cartões de senha em branco, fita de fila, prancheta, caneta, totens de direcionamento sem escritos</t>
+  </si>
+  <si>
+    <t>Reposiciona a fita de fila e anota o novo percurso de atendimento na prancheta, em pé à direita do salão.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; plenário; palanque; votação; campanha; político; bandeiras; tribuna; projeto de lei; estética legislativa; gabinete de luxo; unidade de saúde; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestor de serviços municipais, homem de pele negra, cerca de 35 anos, cabelo raspado, óculos redondos, colete de linho verde, em centro de atendimento ao cidadão, reposicionando a fita de fila e anotando o novo percurso na prancheta. Objetos: cartões de senha em branco, fita de fila, prancheta, caneta e totens sem escritos. Sem plenário, sem tribuna, sem bandeiras, sem palanque, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>seguranca-publica-ead-tecnologo</t>
   </si>
   <si>
@@ -1967,6 +1994,9 @@
   </si>
   <si>
     <t>seguranca-publica</t>
+  </si>
+  <si>
+    <t>Organize a coordenação de serviços de prevenção e controle, com olhar para desafios sociais, jurídicos e estratégicos.</t>
   </si>
   <si>
     <t>A graduação de Segurança Pública EAD da Cruzeiro do Sul Virtual, é destinada a indivíduos que já estão conectados aos serviços de segurança pública, mas que buscam especialização na área. O curso habilita os estudantes para a estruturação e coordenação de múltiplos serviços ligados à prevenção e controle de crimes, resultando na mitigação de conflitos e proporcionando maior serenidade no convívio social. Ao longo da formação, os alunos são preparados para ter um olhar voltado totalmente à resolução de desafios sociais, jurídicos e estratégicos, podendo até fazer parte da reestruturação de políticas públicas. A duração do curso é de 4 semestres (2 anos) e a Cruzeiro do Sul Virtual possui avaliação com conceito 4 no MEC.</t>
@@ -2001,6 +2031,30 @@
     <t>Prepare-se para atuar na área de Segurança Pública a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Coordenação civil de prevenção e políticas de segurança</t>
+  </si>
+  <si>
+    <t>Coordenador de segurança pública de cerca de 30 anos, homem de pele negra, cabelo crespo curto, camisa social cinza e calça social, sem uniforme, postura de reunião.</t>
+  </si>
+  <si>
+    <t>Sala de coordenação intersetorial em prédio público brasileiro, mesa oval, mural com fluxos em branco, persiana, ambiente sóbrio e organizado.</t>
+  </si>
+  <si>
+    <t>pastas, caderno de pauta, caneta, copos, flipchart com caixas vazias</t>
+  </si>
+  <si>
+    <t>Conduz a reunião apontando o flipchart de fluxos de prevenção, em pé à direita, sem arma e sem distintivo.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; arma; distintivo; uniforme policial; viatura; cena de crime; suspeito; estética de série policial; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Coordenador de segurança pública, homem de pele negra, cerca de 30 anos, camisa social cinza, em sala de coordenação, apontando o flipchart de fluxos de prevenção. Objetos: pastas, caderno, caneta, copos e flipchart com caixas vazias. Sem arma, sem uniforme, sem distintivo, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>optica-e-optometria-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -2008,6 +2062,9 @@
   </si>
   <si>
     <t>optica-e-optometria</t>
+  </si>
+  <si>
+    <t>Aprenda a avaliar e medir aspectos funcionais e comportamentais da visão e a indicar métodos ópticos de correção.</t>
   </si>
   <si>
     <t>O curso de Óptica e Optometria semipresencial, capacita profissionais para aplicação de técnicas de avaliação qualitativa e quantitativa do sistema de visão do paciente. O graduado é capaz de identificar a presença de qualquer alteração ocular para encaminhá-lo para o especialista. Com a graduação, o aluno está pronto para avaliar e medir a estrutura da visão em aspectos funcionais e comportamentais, podendo até recomendar métodos ópticos para correção da possível alteração. Com duração de 8 semestres (4 anos), o curso confere o título de bacharel.</t>
@@ -2042,6 +2099,30 @@
     <t>Desenvolva habilidades em Óptica e Optometria a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Avaliação óptica e medição funcional da visão</t>
+  </si>
+  <si>
+    <t>Optometrista de cerca de 27 anos, mulher de pele clara, cabelo liso castanho preso, jaleco branco sobre blusa, óculos no topo da cabeça, atenção ao exame.</t>
+  </si>
+  <si>
+    <t>Consultório de óptica contemporâneo brasileiro, cadeira de avaliação, coluna de lentes de prova, janela com persiana, espaço limpo e acessível.</t>
+  </si>
+  <si>
+    <t>caixa de lentes de prova, régua de distância pupilar, lente avulsa, caderno de medidas, armação de prova</t>
+  </si>
+  <si>
+    <t>Troca uma lente de prova na armação e anota a medida no caderno, em pé à direita junto à pessoa atendida, sem diagnosticar.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico médico; cirurgia; cura; tabela com letras legíveis; luxo de clínica; ambiente precário; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Optometrista, mulher de pele clara, cerca de 27 anos, jaleco branco, em consultório de óptica, trocando lente de prova na armação e anotando medidas. Objetos: caixa de lentes de prova, régua pupilar, lente avulsa, caderno e armação de prova. Sem letras de tabela visíveis, sem diagnóstico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>matematica-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -2049,6 +2130,9 @@
   </si>
   <si>
     <t>matematica</t>
+  </si>
+  <si>
+    <t>Analise problemas complexos com álgebra, geometria, análise, estatística e probabilidade, articulando matemática e tecnologias.</t>
   </si>
   <si>
     <t>O curso de Matemática semipresencial da Cruzeiro do Sul Virtual oferece uma formação completa e especializada, combinando teoria avançada e aplicação prática em disciplinas como álgebra, geometria, análise matemática, estatística, probabilidade e matemática aplicada. O projeto pedagógico foi desenvolvido para ampliar a capacidade de raciocínio lógico e postura crítica dos estudantes diante dos desafios contemporâneos. O curso promove uma sólida base de conteúdo matemático, preparando os alunos para formular, interpretar e resolver problemas complexos, explorando a interface da matemática com diversos campos do saber e suas tecnologias. Com duração de 6 semestres (3 anos) e confere o título de bacharel em Matemática.</t>
@@ -2084,6 +2168,27 @@
     <t>Estude Matemática a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Resolução aplicada de problemas matemáticos</t>
+  </si>
+  <si>
+    <t>Pesquisador em matemática de cerca de 26 anos, homem de pele clara, cabelo ondulado castanho, camisa xadrez e calça jeans, óculos, concentração no papel.</t>
+  </si>
+  <si>
+    <t>Sala de pesquisa aplicada em centro de dados brasileiro, mesa com papéis, um monitor com gráfico abstrato, estante de livros, luz de janela.</t>
+  </si>
+  <si>
+    <t>folhas com cálculos, calculadora científica, caneta, monitor com gráfico, livros fechados</t>
+  </si>
+  <si>
+    <t>Compara um gráfico no monitor com anotações manuscritas e testa um resultado na calculadora, sentado à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; sala de aula escolar; sólidos geométricos de ensino; fórmulas legíveis; estereótipo de gênio; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Pesquisador em matemática, homem de pele clara, cerca de 26 anos, camisa xadrez, em sala de pesquisa, comparando gráfico abstrato no monitor com anotações e a calculadora. Folhas e tela sem escritos legíveis. Objetos: folhas, calculadora científica, caneta, monitor e livros. Sem sala de aula, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-financeira-ead-tecnologo</t>
   </si>
   <si>
@@ -2091,6 +2196,9 @@
   </si>
   <si>
     <t>gestao-financeira</t>
+  </si>
+  <si>
+    <t>Aplique fundamentos contábeis, tesouraria e estratégias de investimento na administração financeira das empresas.</t>
   </si>
   <si>
     <t>O curso de Gestão Financeira EAD proporciona aos alunos a oportunidade de aprimorar seus conhecimentos em uma área essencial para o sucesso de empresas. Com foco na administração eficiente dos recursos financeiros, a Cruzeiro do Sul Virtual oferece uma plataforma flexível e acessível para compreender os princípios fundamentais da gestão financeira. Durante a trajetória do curso, o aluno terá uma bagagem de conhecimentos como Estratégias de investimento, fundamentos contábeis, entre outros conteúdos, o que fará diferença no momento de tomada de decisão na carreira financeira. Com 4 semestres de duração (2 anos), o curso de Gestão Financeira EAD da Cruzeiro do Sul Virtual fornece a certificação de tecnólogo, possui avaliação de conceito 4 pelo MEC, e os resultados satisfatórios no ENADE, confirmando a excelência da formação.</t>
@@ -2128,6 +2236,30 @@
     <t>Desenvolva habilidades em Gestão Financeira a distância EAD com flexibilidade e baixo custo. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Planejamento financeiro e análise de investimentos</t>
+  </si>
+  <si>
+    <t>Analista financeira de cerca de 29 anos, mulher de pele negra, cabelo crespo preso, camisa social branca e colete de malha, expressão atenta aos números.</t>
+  </si>
+  <si>
+    <t>Sala de controladoria em empresa brasileira contemporânea, mesa com impressos, calculadora, janela, ambiente corporativo acessível.</t>
+  </si>
+  <si>
+    <t>calculadora financeira, gráficos de linhas sem legendas, pasta de planejamento, caneta, notebook</t>
+  </si>
+  <si>
+    <t>Compara um gráfico de linhas com a calculadora financeira e anota no caderno de planejamento, sentada à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentada à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; cédulas ostensivas; ouro; tela da bolsa com escritos; escritório de luxo; vitrine de varejo; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista financeira, mulher de pele negra, cerca de 29 anos, camisa branca e colete, em sala de controladoria, comparando gráfico de linhas com a calculadora financeira. Objetos: calculadora, gráficos sem legendas, pasta, caneta e notebook. Sem cédulas, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-de-recursos-humanos-ead-tecnologo</t>
   </si>
   <si>
@@ -2135,6 +2267,9 @@
   </si>
   <si>
     <t>gestao-de-recursos-humanos</t>
+  </si>
+  <si>
+    <t>Desenvolva recrutamento, seleção, integração e o planejamento estratégico de pessoas nas organizações.</t>
   </si>
   <si>
     <t>O curso tecnólogo de Gestão de Recursos Humanos EAD da Cruzeiro do Sul qualifica futuros profissionais para o mercado de recursos humanos, a fim de habilitá-los para tomar responsabilidade sobre uma das maiores dificuldades das empresas nos dias atuais: gestão e retenção de pessoas e talentos. Através dos conhecimentos fornecidos através da graduação, os estudantes aprendem fatores determinantes para empreender, impulsionar melhorias organizacionais e contribuir para o bem-estar coletivo dentro das empresas. Por meio da abrangência do currículo do curso, a universidade aplica conhecimentos para competências em planejamento estratégico organizacional, gestão de recursos humanos, sempre voltados para o olhar completo e interconectado da corporação.</t>
@@ -2174,6 +2309,27 @@
     <t>Aprofunde-se em Gestão de Recursos Humanos a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Recrutamento e integração de equipes</t>
+  </si>
+  <si>
+    <t>Gestora de pessoas de cerca de 31 anos, mulher de pele morena, cabelo cacheado na altura dos ombros, blazer mostarda sobre blusa, postura de entrevista.</t>
+  </si>
+  <si>
+    <t>Sala de entrevistas em empresa brasileira contemporânea, duas poltronas, mesa baixa, planta, janela, espaço acolhedor e profissional.</t>
+  </si>
+  <si>
+    <t>pasta de seleção, caneta, copo d'água, bloco de anotações, crachá em branco</t>
+  </si>
+  <si>
+    <t>Conduz uma conversa de seleção e anota no bloco, sentada à direita, sem ler papéis com escritos visíveis.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; currículos legíveis; estereótipo de chefe ríspida; sala de luxo; ambiente precário; pose para foto.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora de pessoas, mulher de pele morena, cerca de 31 anos, blazer mostarda, em sala de entrevistas, conversando e anotando no bloco. Objetos: pasta de seleção, caneta, copo, bloco e crachá em branco. Papéis sem escritos visíveis. Sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>pedagogia-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -2181,6 +2337,9 @@
   </si>
   <si>
     <t>pedagogia</t>
+  </si>
+  <si>
+    <t>Elabore, execute e avalie projetos educativos para a educação infantil e os anos iniciais, em espaços escolares e não escolares.</t>
   </si>
   <si>
     <t>O curso de Pedagogia semipresencial da Cruzeiro do Sul Virtual visa formar professores qualificados para atuar na educação infantil e nos anos iniciais do Ensino Fundamental, tanto em instituições de ensino quanto em outras áreas educativas. Com duração de 8 semestres (4 anos), o curso oferece certificação de Licenciatura e abrange o planejamento, execução, coordenação, acompanhamento e avaliação de projetos educativos em ambientes escolares e não escolares.</t>
@@ -2222,6 +2381,30 @@
     <t>Prepare-se para atuar na área da Pedagogia a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Planejamento e mediação pedagógica nos anos iniciais</t>
+  </si>
+  <si>
+    <t>Pedagoga de cerca de 28 anos, mulher de pele negra, cabelo trançado médio, blusa verde e calça, de pé junto ao quadro de atividades.</t>
+  </si>
+  <si>
+    <t>Sala dos anos iniciais em escola pública brasileira contemporânea, carteiras, estante de livros infantis, janelas, espaço claro e organizado, sem berçário.</t>
+  </si>
+  <si>
+    <t>alfabeto móvel, livros didáticos fechados, caderno de planejamento, lápis de cor, cartaz ilustrado sem escritos</t>
+  </si>
+  <si>
+    <t>Organiza o alfabeto móvel na mesa e consulta o caderno de planejamento, em pé à direita, preparando uma sequência didática.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; berço; mamadeira; creche de bebês; infantilização da professora; sala precária; escola de luxo; letras soltas formando palavras legíveis.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Pedagoga, mulher de pele negra, cerca de 28 anos, blusa verde, em sala dos anos iniciais, organizando alfabeto móvel e consultando o caderno de planejamento. Objetos: alfabeto móvel, livros fechados, caderno, lápis de cor e cartaz ilustrado sem escritos. Sem berçário, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>arquitetura-e-urbanismo-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -2229,6 +2412,9 @@
   </si>
   <si>
     <t>arquitetura-e-urbanismo</t>
+  </si>
+  <si>
+    <t>Crie projetos de edificação, interiores, paisagismo e espaços urbanos com atenção a sustentabilidade, acessibilidade e conforto.</t>
   </si>
   <si>
     <t>A graduação de Arquitetura e Urbanismo da Cruzeiro do Sul Virtual está disponível nos formatos Semipresencial. Ao longo da formação, os estudantes são capacitados para criar projetos urbanos, paisagísticos, de edificação e de interiores de alto nível, fazendo com o que o sonho de seus clientes saiam do papel, sendo preparados para todo tipo de projeto, desde os mais conservadores até os mais inovadores. Na Cruzeiro do Sul, a prioridade é criar profissionais diversificados, prontos para trabalhar seguindo os critérios de sustentabilidade, acessibilidade, conforto ambiental e bem-estar, além de serem preparados para proporcionar melhorias para a vida nas áreas urbanas. A graduação tem a duração de 10 semestres (5 anos).</t>
@@ -2263,6 +2449,27 @@
     <t>Estude Arquitetura e Urbanismo com a qualidade do presencial e a flexibilidade do EAD. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Projeto de edificação e maquete urbana</t>
+  </si>
+  <si>
+    <t>Arquiteto de cerca de 33 anos, homem de pele clara, cabelo curto, camisa de linho e calça chino, óculos, inclinando-se sobre a maquete.</t>
+  </si>
+  <si>
+    <t>Ateliê de arquitetura contemporâneo brasileiro, prancheta, maquetes, prateleira de materiais, janela ampla, espaço de trabalho acessível.</t>
+  </si>
+  <si>
+    <t>maquete de edifício, régua escalímetro, esquadros, lápis, amostras de revestimento</t>
+  </si>
+  <si>
+    <t>Ajusta um volume na maquete e confere a escala com o escalímetro, em pé à direita da prancheta.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; penthouse de luxo; canteiro precário; planta com escritos; estereótipo de gênio; atividade tecnicamente incorreta.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Arquiteto, homem de pele clara, cerca de 33 anos, camisa de linho, em ateliê, ajustando a maquete de edifício e conferindo o escalímetro. Objetos: maquete, escalímetro, esquadros, lápis e amostras de revestimento. Sem escritos nas plantas, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>fisica-licenciatura-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -2270,6 +2477,9 @@
   </si>
   <si>
     <t>fisica-licenciatura</t>
+  </si>
+  <si>
+    <t>Pratique o ensino de física no fundamental e no médio, com didática, experimentos e tecnologias para temas científicos.</t>
   </si>
   <si>
     <t>O curso de Licenciatura em Física semipresencial da Cruzeiro do Sul Virtual, com duração de 8 semestres (4 anos). Este curso prepara futuros professores para o ensino fundamental II e médio, abordando desde ciências físicas até os fundamentos teóricos clássicos e física moderna. Os estudantes exploram áreas como física geral, didática e práticas pedagógicas específicas para o ensino de ciências, utilizando tecnologias modernas para a aprendizagem de temas científicos. Ao concluir, os alunos recebem o título de Licenciado em Física, aptos a lecionar no ensino fundamental e médio, além de participar de projetos educacionais e de pesquisa.</t>
@@ -2304,6 +2514,30 @@
     <t>Prepare-se para lecionar Física a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Demonstração didática de experimento de física</t>
+  </si>
+  <si>
+    <t>Professora de física de cerca de 25 anos, mulher de pele morena, cabelo cacheado preso, jaleco aberto sobre blusa coral, demonstrando o experimento.</t>
+  </si>
+  <si>
+    <t>Laboratório didático de escola brasileira contemporânea, bancada, quadro ao fundo, carteiras, janelas, espaço organizado para ensino.</t>
+  </si>
+  <si>
+    <t>trilho de dinâmica, carrinhos, cronômetro, giz, quadro</t>
+  </si>
+  <si>
+    <t>Libera o carrinho no trilho e aponta o cronômetro para a turma, em pé à direita da bancada, quadro sem escritos.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem em pé na região superior direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; laboratório de pesquisa avançada; explosão; fórmulas legíveis; estereótipo de cientista maluco; ambiente precário ou de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de física, mulher de pele morena, cerca de 25 anos, jaleco aberto, em laboratório didático escolar, liberando o carrinho no trilho e mostrando o cronômetro. Objetos: trilho, carrinhos, cronômetro, giz e quadro sem escritos. Sem fórmulas visíveis, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>letras-libras-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -2311,6 +2545,9 @@
   </si>
   <si>
     <t>letras-libras</t>
+  </si>
+  <si>
+    <t>Estude Libras, cultura surda e práticas pedagógicas para o ensino da língua, a inclusão e a comunicação acessível.</t>
   </si>
   <si>
     <t>O curso de Letras - Libras semipresencial da Cruzeiro do Sul Virtual tem como objetivo capacitar profissionais para promoverem acessibilidade e comunicação efetiva com a comunidade surda, desempenhando um papel crucial na construção de uma sociedade mais inclusiva. O curso não apenas foca no estudo aprofundado de Libras, mas também na compreensão da cultura surda e no desenvolvimento de competências pedagógicas para o ensino da língua. Ao longo dos 8 semestres (4 anos), os alunos irão permear por temas como Educação Inclusiva, Educação de surdos, Ensino de português com L2 para surdos, Produção de materiais didáticos em libras, e muito mais. O curso confere o título de licenciatura em Letras - Libras.</t>
@@ -2347,6 +2584,30 @@
     <t>Estude Letras - Libras a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Ensino de Libras com material didático ilustrado</t>
+  </si>
+  <si>
+    <t>Professora surda de Libras de cerca de 30 anos, mulher de pele morena clara, cabelo liso preto na altura dos ombros, camisa amarela, expressão atenta ao ensino.</t>
+  </si>
+  <si>
+    <t>Sala de aula inclusiva contemporânea brasileira, cadeiras em U, espelho de prática ao fundo, janela, espaço claro e acessível.</t>
+  </si>
+  <si>
+    <t>cartões ilustrados de configurações de mão, livro didático fechado, apagador, quadro, suporte de tablet desligado</t>
+  </si>
+  <si>
+    <t>Mostra um cartão ilustrado de configuração de mão e dialoga em Libras com a turma, em pé à direita, sem nomear o sinal.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; gesto aleatório apresentado como sinal específico; estereótipo de surdez; infantilização; legendas; ambiente precário ou de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora surda de Libras, mulher de pele morena clara, cerca de 30 anos, camisa amarela, em sala inclusiva, mostrando cartão ilustrado de configuração de mão e dialogando em Libras. Objetos: cartões ilustrados, livro fechado, apagador, quadro e tablet desligado. Sem nomear sinais, sem legendas, sem palavras visíveis, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>processos-gerenciais-ead-tecnologo</t>
   </si>
   <si>
@@ -2354,6 +2615,9 @@
   </si>
   <si>
     <t>processos-gerenciais</t>
+  </si>
+  <si>
+    <t>Domine planejamento, organização, direção e controle, identificando gargalos e melhorando fluxos de trabalho na rotina empresarial.</t>
   </si>
   <si>
     <t>O curso de Processos Gerenciais EAD da Cruzeiro do Sul Virtual prepara profissionais para a gestão e otimização de processos organizacionais. Com foco em planejamento, organização, direção e controle, o curso abrange finanças, administração, marketing, logística, demonstração contábil, avaliação de estoques, acompanhamento do faturamento e fluxo de caixa. Durante o curso, são abordados temas que permitem a inserção de procedimentos e ferramentas na atividade profissional, e ao final dos 4 semestres (2 anos), os graduados estarão aptos a atuar em diversos setores, contribuindo para o sucesso e crescimento das organizações e terão a titulação de tecnólogo.</t>
@@ -2387,6 +2651,27 @@
     <t>Desenvolva habilidades em Processos Gerenciais a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Mapeamento de fluxo de trabalho e gargalos</t>
+  </si>
+  <si>
+    <t>Analista de processos de cerca de 28 anos, mulher de pele clara, cabelo ondulado ruivo natural preso, camisa jeans e calça, atenção ao mapa de etapas.</t>
+  </si>
+  <si>
+    <t>Sala operacional de pequena empresa brasileira contemporânea, mesas de trabalho, parede com papel pardo, janela, espaço acessível, sem prateleiras de estoque.</t>
+  </si>
+  <si>
+    <t>papel pardo na parede, adesivos coloridos em branco, caneta, notebook fechado, relógio de mesa</t>
+  </si>
+  <si>
+    <t>Liga etapas com setas no mapa de fluxo e destaca um gargalo com um adesivo, em pé à direita da parede.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; estoque; pallets; caixas; código de barras; transporte; almoxarifado; calculadora financeira; amostras de venda; sala de entrevistas de RH; escritos no mapa; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de processos, mulher de pele clara, cerca de 28 anos, cabelo ruivo preso, camisa jeans, em sala operacional de pequena empresa, ligando etapas com setas no papel pardo e destacando um gargalo com adesivo. Objetos: papel pardo, adesivos em branco, caneta, notebook fechado e relógio de mesa. Sem estoque, sem caixas, sem pallets, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>desenvolvimento-mobile-ead-tecnologo</t>
   </si>
   <si>
@@ -2394,6 +2679,9 @@
   </si>
   <si>
     <t>desenvolvimento-mobile</t>
+  </si>
+  <si>
+    <t>Construa aplicativos e soluções para dispositivos móveis, com programação, design mobile e recursos de nuvem.</t>
   </si>
   <si>
     <t>O curso EAD de Desenvolvimento Mobile prepara profissionais para criar aplicativos e tecnologias voltadas para dispositivos móveis. Com uma base sólida em programação, o curso oferece conteúdo sobre linguagens tecnológicas, ferramentas, processos e design focado em mobile.Durante a jornada de estudos, as disciplinas visam, através da resolução de problemas, desenvolver soluções adequadas para a implementação de códigos em dispositivos móveis. Portanto, a formação em Desenvolvimento Mobile possui uma base teórica voltada para inovação, software e aplicativos.Além disso, o estudante aprenderá a utilizar recursos de nuvem (AWS e Azure) para programação mobile, visando aumentar a segurança e a produtividade do processo de desenvolvimento. Com duração de 4 semestres (4 anos), a formação confere o título de tecnólogo em Desenvolvimento Mobile.</t>
@@ -2428,6 +2716,27 @@
     <t>Aprenda Desenvolvimento Mobile EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Programação e teste de aplicativo em dispositivo móvel</t>
+  </si>
+  <si>
+    <t>Desenvolvedora mobile de cerca de 24 anos, mulher de pele negra, cabelo black curto, moletom lavanda e calça jeans, atenção ao celular e ao notebook.</t>
+  </si>
+  <si>
+    <t>Mesa de desenvolvimento em café coworking brasileiro contemporâneo, tomada à vista, planta, janela, espaço acessível.</t>
+  </si>
+  <si>
+    <t>smartphone em suporte, notebook, cabo, fone, caderno de anotações</t>
+  </si>
+  <si>
+    <t>Testa o aplicativo no smartphone apoiado e corrige o código no notebook, sentada à direita, telas sem escritos legíveis.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; tela de rede social; tripé de influenciador; código legível; hacker; diagrama de banco de dados; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Desenvolvedora mobile, mulher de pele negra, cerca de 24 anos, moletom lavanda, em café coworking, testando o app no smartphone e corrigindo no notebook. Telas com blocos coloridos desfocados, sem escritos. Objetos: smartphone em suporte, notebook, cabo, fone e caderno. Sem tripé, sem redes sociais, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>eventos-ead-tecnologo</t>
   </si>
   <si>
@@ -2435,6 +2744,9 @@
   </si>
   <si>
     <t>eventos</t>
+  </si>
+  <si>
+    <t>Estruture e implemente serviços para eventos sociais, corporativos, culturais, esportivos e educacionais.</t>
   </si>
   <si>
     <t>O curso de Eventos EAD da Cruzeiro do Sul Virtual capacita os alunos a utilizar todas as ferramentas essenciais para desenvolver, estruturar e implementar serviços personalizados e adequados para qualquer tipo de evento, incluindo os sociais, corporativos, esportivos, culturais, acadêmicos, educacionais, científicos, artísticos, de lazer, moda, entretenimento e outros. Com duração de 4 semestres (2 anos), o curso confere o título de tecnólogo em eventos e oferece um plano pedagógico atualizado, alinhado com as tendências do mercado, preparando os estudantes para proporcionar experiências memoráveis aos clientes.</t>
@@ -2471,6 +2783,27 @@
     <t>Aprenda a organizar eventos de sucesso a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem logística e planta de evento</t>
+  </si>
+  <si>
+    <t>Produtor de eventos de cerca de 27 anos, homem de pele morena, cabelo ondulado, camisa polo e calça cargo, rádio no cinturão, gesto de coordenação.</t>
+  </si>
+  <si>
+    <t>Salão de eventos contemporâneo brasileiro vazio em montagem, cadeiras empilhadas, palco simples ao fundo, luz natural da entrada, sem decoração de gala.</t>
+  </si>
+  <si>
+    <t>planta baixa do salão, fita métrica, rádio comunicador, prancheta, fita crepe</t>
+  </si>
+  <si>
+    <t>Sinaliza no chão a posição das mesas com fita crepe e confere a planta baixa, em pé à direita do salão.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; microfone de coletiva; media training; tapete vermelho; champagne; cerimonialista de luxo; arranjos de gala; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Produtor de eventos, homem de pele morena, cerca de 27 anos, polo e calça cargo, em salão em montagem, sinalizando o chão com fita crepe e conferindo a planta baixa. Objetos: planta, fita métrica, rádio, prancheta e fita crepe. Sem microfone de coletiva, sem gala, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-comercial-ead-tecnologo</t>
   </si>
   <si>
@@ -2478,6 +2811,9 @@
   </si>
   <si>
     <t>gestao-comercial</t>
+  </si>
+  <si>
+    <t>Defina estratégias de venda, alinhe equipes e analise dados de mercado para a gestão comercial no varejo e no atacado.</t>
   </si>
   <si>
     <t>O curso de Gestão Comercial EAD da Cruzeiro do Sul Virtual busca capacitar alunos para realinhar metas, reconduzir contatos de clientes, buscar rentabilidade e lucratividade, definir estratégias de venda, alinhar equipes a fim do sucesso da empresa, e muito mais! Para o perfil de líder, bom comunicador e negociador, o curso trará boas oportunidades profissionais. Com duração de 4 semestres (2 anos) e certificação de tecnólogo, o curso EAD da Cruzeiro do Sul Virtual forma alunos para se destacarem no mercado comercial contemporâneo.</t>
@@ -2517,6 +2853,27 @@
     <t>Desenvolva habilidades em Gestão Comercial a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Estratégia de vendas e análise de mercado</t>
+  </si>
+  <si>
+    <t>Gestora comercial de cerca de 32 anos, mulher de pele clara, cabelo ondulado castanho, blazer terracota, em pé diante de um painel de metas vazio.</t>
+  </si>
+  <si>
+    <t>Sala de equipe comercial em empresa brasileira, mesa compartilhada, amostras de produto na lateral, janela, espaço contemporâneo acessível.</t>
+  </si>
+  <si>
+    <t>amostras de embalagem genérica, gráfico de barras sem legendas, caneta, tablet, bloco de metas em branco</t>
+  </si>
+  <si>
+    <t>Mostra o gráfico de barras à equipe e anota no tablet um ajuste de estratégia, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; calculadora financeira como centro; estoque de almoxarifado; cédulas; loja de luxo; balcão precário; rótulos comerciais.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora comercial, mulher de pele clara, cerca de 32 anos, blazer terracota, em sala de equipe, mostrando gráfico de barras e anotando no tablet. Objetos: amostras genéricas, gráfico sem legendas, caneta, tablet e bloco em branco. Sem rótulos, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>estetica-e-cosmetica-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -2524,6 +2881,9 @@
   </si>
   <si>
     <t>estetica-e-cosmetica</t>
+  </si>
+  <si>
+    <t>Conheça técnicas de estética facial, corporal e capilar, com pareceres técnicos e consultoria em cosmética.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Estética e Cosmética Semipresencial oferecido pela Cruzeiro do Sul Virtual busca formar profissionais aptos a trabalhar em áreas como; estética corporal, facial, terapia capilar, spaterapia e muito mais!
@@ -2561,6 +2921,30 @@
     <t>Desenvolva habilidades em Estética e Cosmética EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Protocolo técnico de estética facial</t>
+  </si>
+  <si>
+    <t>Esteticista de cerca de 26 anos, mulher de pele morena, cabelo preso em coque, jaleco de estética e luvas, atenção ao protocolo.</t>
+  </si>
+  <si>
+    <t>Sala de estética contemporânea brasileira, maca com lençol claro, luminária de procedimento, bancada organizada, sem spa de luxo.</t>
+  </si>
+  <si>
+    <t>tigela de cosmética, pincel de máscara, touca, gazes, frasco genérico sem rótulo</t>
+  </si>
+  <si>
+    <t>Aplica uma máscara facial com o pincel na pessoa deitada, em pé à direita da maca, gesto técnico e respeitoso.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária profissional suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; sexualização; lingerie; cirurgia; cura; resultado milagroso; spa de luxo; ambiente precário; rótulos de produtos.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional suave. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Esteticista, mulher de pele morena, cerca de 26 anos, jaleco de estética e luvas, aplicando máscara facial com pincel em sala técnica contemporânea. Objetos: tigela, pincel, touca, gazes e frasco sem rótulo. Sem sexualização, sem spa de luxo, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>fotografia-ead-tecnologo</t>
   </si>
   <si>
@@ -2568,6 +2952,9 @@
   </si>
   <si>
     <t>fotografia</t>
+  </si>
+  <si>
+    <t>Explore composição, iluminação, edição e estética da imagem para registrar e documentar com técnica fotográfica.</t>
   </si>
   <si>
     <t>O curso de Fotografia EAD da Universidade Cruzeiro do Sul Virtual oferece uma formação completa e flexível, com duração de 4 semestres (2 anos). Com conceito 4 no MEC, o curso abrange desde técnicas básicas até avançadas, edição de imagens e conceitos estéticos. Utilizando uma plataforma online interativa, os alunos estudam no seu próprio ritmo, com orientação personalizada de tutores experientes. Ao concluir, os graduados recebem o título de Tecnólogo em Fotografia, estando preparados para atuar em diversas áreas.</t>
@@ -2606,6 +2993,30 @@
     <t>Aprenda Fotografia a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Composição e iluminação de fotografia still</t>
+  </si>
+  <si>
+    <t>Fotógrafa de cerca de 25 anos, mulher de pele clara com sardas, cabelo curto ondulado, camisa preta e calça, olho no visor.</t>
+  </si>
+  <si>
+    <t>Estúdio fotográfico simples brasileiro, fundo infinito cinza, janela, um softbox, mesa de still com objeto, espaço acessível.</t>
+  </si>
+  <si>
+    <t>câmera no tripé, softbox, refletor, mesa de still, objeto cerâmico</t>
+  </si>
+  <si>
+    <t>Ajusta o softbox e dispara a câmera no tripé, fotografando o objeto na mesa, em pé à direita do still.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária controlada, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; câmera no ombro de cinegrafista; claquete; boom; mesa de pauta multimídia; paparazzi; estúdio de luxo; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Fotógrafa, mulher de pele clara com sardas, cerca de 25 anos, camisa preta, em estúdio simples, ajustando o softbox e fotografando um objeto cerâmico na mesa de still. Objetos: câmera no tripé, softbox, refletor, mesa e objeto. Sem cinegrafia, sem claquete, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>terapias-integrativas-complementares-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -2613,6 +3024,9 @@
   </si>
   <si>
     <t>terapias-integrativas-complementares</t>
+  </si>
+  <si>
+    <t>Aprofunde práticas integrativas e complementares para promover bem-estar físico, mental e emocional, com ética e gestão.</t>
   </si>
   <si>
     <t>O curso de Terapias Integrativas e Complementares EAD oferece uma ampla base sobre terapias integrativas e sua contribuição para os tratamentos convencionais, fazendo com que os alunos desenvolvam habilidades de gestão e ética para trabalhar em clínicas, consultórios ou instituições de saúde. O curso, que tem duração de 4 semestres (2 anos) , confere o título de tecnólogo e torna os futuros profissionais aptos a utilizar práticas integrativas e complementares para promover o bem-estar físico, mental e emocional de seus pacientes. A graduação conta com disciplinas abrangentes que abordam conhecimentos teóricos e práticos sobre o corpo humano e seus sistemas, como Anatomofisiologia humana, Biologia celular e tecidual, entre outras.</t>
@@ -2650,6 +3064,27 @@
     <t>Desenvolva habilidades em Terapias Integrativas Complementares a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Condução de prática meditativa de bem-estar</t>
+  </si>
+  <si>
+    <t>Terapeuta integrativa de cerca de 33 anos, mulher de pele negra, cabelo crespo solto, blusa de algodão areia e calça, postura serena de orientação.</t>
+  </si>
+  <si>
+    <t>Sala ampla de práticas em clínica acessível brasileira, tapetes, almofadas alinhadas, janela, planta, sem spa de luxo e sem maca de procedimento.</t>
+  </si>
+  <si>
+    <t>almofadas, tigela tibetana, planta, jarra de água, cronômetro de sessão</t>
+  </si>
+  <si>
+    <t>Orienta um grupo sentado em almofadas e soa a tigela para iniciar a prática, em pé à direita da sala.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; cura; diagnóstico; prescrição; jaleco médico; óleos em primeiro plano; cristais místicos; spa de luxo; sexualização; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Terapeuta integrativa, mulher de pele negra, cerca de 33 anos, blusa areia, em sala de práticas, orientando o grupo e soando a tigela. Objetos: almofadas, tigela, planta, jarra e cronômetro. Sem maca, sem óleos em destaque, sem diagnóstico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>seguranca-da-informacao-ead-tecnologo</t>
   </si>
   <si>
@@ -2657,6 +3092,9 @@
   </si>
   <si>
     <t>seguranca-da-informacao</t>
+  </si>
+  <si>
+    <t>Identifique riscos digitais e proteja sistemas e dados com criptografia, gestão de riscos e ética digital.</t>
   </si>
   <si>
     <t>A graduação de Segurança da Informação EAD da Cruzeiro do Sul Virtual é focada em desenvolver profissionais para garantir a segurança de sistemas e dados contra perigos cibernéticos. Além de apresentar uma abordagem integrada e abrangente, o currículo contempla o estudo de criptografia, gestão de riscos e ética digital, ensinando aos estudantes competências técnicas, desde os fundamentos da computação até as mais avançadas questões de segurança. O tecnólogo tem duração de 4 semestres (2 anos), e a todo momento realça a importância de sensibilizar e capacitar continuamente as possíveis equipes para minimizar os riscos que surgem no cenário digital atual.</t>
@@ -2692,6 +3130,27 @@
     <t>Estude Segurança da Informação a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Gestão de riscos e classificação de informações</t>
+  </si>
+  <si>
+    <t>Analista de segurança da informação de cerca de 29 anos, homem de pele clara, cabelo liso, camisa social vinho e calça, óculos, atenção à matriz.</t>
+  </si>
+  <si>
+    <t>Sala de reunião de governança em empresa brasileira, mesa clara, lousa com matriz de riscos em branco, persiana, sem rack de servidores.</t>
+  </si>
+  <si>
+    <t>matriz de riscos impressa sem escritos, pastas classificadas, cadeado físico, caneta, notebook fechado</t>
+  </si>
+  <si>
+    <t>Classifica pastas na mesa e aponta a matriz de riscos, sentado à direita, sem telas de monitoramento.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; hacker de capuz; sala de operações com rack; dois monitores de alerta; código verde; arma; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de segurança da informação, homem de pele clara, cerca de 29 anos, camisa vinho, em sala de governança, classificando pastas e apontando a matriz de riscos. Objetos: matriz sem escritos, pastas, cadeado, caneta e notebook fechado. Sem rack, sem capuz, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-de-qualidade-ead-tecnologo</t>
   </si>
   <si>
@@ -2699,6 +3158,9 @@
   </si>
   <si>
     <t>gestao-de-qualidade</t>
+  </si>
+  <si>
+    <t>Prepare-se para acompanhar padrões e normas de produção, com auditorias, melhoria contínua e ferramentas da qualidade.</t>
   </si>
   <si>
     <t>O curso de Gestão de Qualidade EAD, forma profissionais capazes de prevenir contratempos em produtos e serviços, garantindo que os padrões e normas de produção sejam seguidos. Os alunos são preparados para o foco no acompanhamento rigoroso de procedimentos essenciais na Gestão da Qualidade, como orientação ao cliente, desenvolvimento de pessoal, desenvolvimento contínuo e abordagem sistêmica. Ao longo dos 4 semestres (2 anos) do curso de graduação, os futuros gestores de qualidade serão capazes de identificar situações delicadas, que necessitam de sistemas e auditorias de qualidade, aptos a estabelecer métodos para condução de projetos, fazendo o uso de ferramentas de qualidade nos processos de produção organizacionais, de acordo com os sistemas de certificação, como ISO, ABNT e Inmetro. Além disso, o curso de Gestão de Qualidade da Cruzeiro do Sul EAD possui conceito 5 de classificação do MEC.</t>
@@ -2734,6 +3196,30 @@
     <t>Estude Gestão de Qualidade a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Inspeção de conformidade e auditoria da qualidade</t>
+  </si>
+  <si>
+    <t>Gestora da qualidade de cerca de 31 anos, mulher de pele morena, cabelo liso preso, jaleco de inspeção e óculos de proteção na cabeça, paquímetro na mão.</t>
+  </si>
+  <si>
+    <t>Laboratório de qualidade em indústria brasileira contemporânea, bancada branca, amostras alinhadas, iluminação clara, espaço limpo.</t>
+  </si>
+  <si>
+    <t>paquímetro, amostra de peça, checklist em branco, caneta, bandeja de inspeção</t>
+  </si>
+  <si>
+    <t>Mede a peça com o paquímetro e registra o resultado no checklist, em pé à direita da bancada.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária clara, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; linha de montagem completa; selos de certificação visíveis; chão de fábrica como cena principal; ambiente precário ou de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional clara. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora da qualidade, mulher de pele morena, cerca de 31 anos, jaleco de inspeção, medindo uma peça com paquímetro na bancada de laboratório. Objetos: paquímetro, peça, checklist em branco, caneta e bandeja. Sem selos visíveis, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-hospitalar-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -2741,6 +3227,9 @@
   </si>
   <si>
     <t>gestao-hospitalar</t>
+  </si>
+  <si>
+    <t>Entenda compras, hotelaria hospitalar, controle de insumos e a liderança de equipes em serviços de saúde.</t>
   </si>
   <si>
     <t>O curso de Gestão Hospitalar semipresencial da Cruzeiro do Sul Virtual visa formar profissionais com vivência na área da saúde, com uma abordagem focada na gestão eficiente, na melhoria de serviços hospitalares e competências administrativas, proporcionando aos estudantes capacidades para tratar de temas como contabilidade, recursos financeiros, controle de compras e custos, recursos humanos, planejamento estratégico, marketing, logística, entre outros. Ao concluir o curso, os profissionais estarão aptos a liderar equipes multidisciplinares, implementar políticas de saúde e contribuir para o desenvolvimento do setor hospitalar, tanto no setor público quanto privado. Com duração de 6 semestres (3 anos), o curso possui conceito 5 na classificação do MEC e confere o título de tecnólogo em Gestão Hospitalar.</t>
@@ -2777,6 +3266,30 @@
     <t>Estude Gestão Hospitalar a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Administração de compras e hotelaria hospitalar</t>
+  </si>
+  <si>
+    <t>Gestora hospitalar de cerca de 34 anos, mulher de pele clara, cabelo castanho em ondas, camisa social e crachá virado, expressão de gestão.</t>
+  </si>
+  <si>
+    <t>Almoxarifado hospitalar organizado no Brasil, prateleiras de insumos lacrados, mesa de conferência, iluminação clara, sem leitos ao fundo.</t>
+  </si>
+  <si>
+    <t>listas de pedido em branco, caixas de insumo genéricas, tablet, caneta, carrinho de abastecimento</t>
+  </si>
+  <si>
+    <t>Confere caixas no carrinho e registra o pedido no tablet, em pé à direita do corredor de insumos.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária clara, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; jaleco clínico; cirurgia; leito; estetoscópio; fila de pacientes; hospital de luxo; unidade de saúde pública como prefeitura; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora hospitalar, mulher de pele clara, cerca de 34 anos, camisa social, em almoxarifado hospitalar, conferindo caixas no carrinho e registrando no tablet. Objetos: listas em branco, caixas genéricas, tablet, caneta e carrinho. Sem leito, sem jaleco clínico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>seguranca-no-transito-ead-tecnologo</t>
   </si>
   <si>
@@ -2784,6 +3297,9 @@
   </si>
   <si>
     <t>seguranca-no-transito</t>
+  </si>
+  <si>
+    <t>Analise o planejamento, a fiscalização e a educação no trânsito urbano e rodoviário, com foco na prevenção de acidentes.</t>
   </si>
   <si>
     <t>O curso de Segurança no Trânsito EAD oferecido pela Cruzeiro do Sul Virtual é direcionado a profissionais já inseridos no serviço de segurança pública, interessados em se especializar na gestão do trânsito urbano e rodoviário, bem como nas atividades relacionadas à segurança de motoristas, pedestres e demais usuários das vias. Durante a formação, os estudantes desenvolvem habilidades para planejar, analisar, fiscalizar e executar serviços conforme regulamentação do Sistema Nacional de Trânsito. Além disso, adquirem uma compreensão ampla dos órgãos de trânsito em âmbito federal, estadual e municipal, capacitando-os a elaborar estratégias de conscientização, educação e prevenção de acidentes. O curso possui duração de 4 semestres (2 anos), conferindo titulação de tecnólogo e é avaliado com conceito 4 pelo MEC.</t>
@@ -2816,6 +3332,27 @@
     <t>Aprenda sobre Segurança no Trânsito a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Educação e planejamento de segurança viária</t>
+  </si>
+  <si>
+    <t>Agente de educação de trânsito de cerca de 28 anos, homem de pele morena, cabelo curto, colete refletivo sobre camisa, sem arma, atenção à maquete.</t>
+  </si>
+  <si>
+    <t>Sala de educação de trânsito em órgão municipal brasileiro, maquete de cruzamento, cadeiras, janela, espaço didático organizado.</t>
+  </si>
+  <si>
+    <t>maquete de via, cones em miniatura, pasta educativa, caneta, faixa de pedestre em tecido</t>
+  </si>
+  <si>
+    <t>Move um cone na maquete de cruzamento e explica o fluxo a um grupo, em pé à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; arma; viatura em perseguição; acidente real; radar com números; uniforme ostensivo; estética policial; ambiente precário ou de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Agente de educação de trânsito, homem de pele morena, cerca de 28 anos, colete refletivo, em sala didática, movendo cone na maquete de cruzamento. Objetos: maquete, cones em miniatura, pasta, caneta e faixa de pedestre. Sem arma, sem viatura, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>filosofia-ead-bacharelado</t>
   </si>
   <si>
@@ -2823,6 +3360,9 @@
   </si>
   <si>
     <t>filosofia</t>
+  </si>
+  <si>
+    <t>Estude história da filosofia, ética, lógica, filosofia política e estética para análise crítica e debate.</t>
   </si>
   <si>
     <t>O curso de Filosofia EAD da Universidade Cruzeiro do Sul Virtual tem duração de 6 semestres (3 anos) e confere o título de bacharel em Filosofia. Este curso proporciona uma formação abrangente nas diversas áreas da filosofia, abordando temas como história da filosofia, ética, lógica, filosofia política, estética, entre outros. O curso conta com a modalidade EAD, que permite que os alunos estudem de forma flexível, com acesso a materiais didáticos, videoaulas, fóruns de discussão e suporte de tutores online. Ao final do curso, os graduados estarão preparados para análise crítica, reflexão teórica e contribuição para debates intelectuais em diversas áreas do conhecimento e da sociedade.</t>
@@ -2860,6 +3400,27 @@
     <t>Aprofunde-se em Filosofia a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Leitura crítica e debate filosófico</t>
+  </si>
+  <si>
+    <t>Estudiosa de filosofia de cerca de 27 anos, mulher de pele clara, cabelo ondulado longo, suéter e saia midi, óculos, leitura atenta.</t>
+  </si>
+  <si>
+    <t>Sala de seminário contemporânea brasileira, mesa comprida, estante, janela, quadro apagado, espaço de estudo acessível.</t>
+  </si>
+  <si>
+    <t>livros empilhados, caderno, caneta, copo, óculos de leitura</t>
+  </si>
+  <si>
+    <t>Destaca um trecho no livro e argumenta apontando o caderno, sentada à direita da mesa de seminário.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; páginas com escritos legíveis; púlpito religioso; batina; toga acadêmica de luxo; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional suave. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Estudiosa de filosofia, mulher de pele clara, cerca de 27 anos, suéter, em sala de seminário, destacando o livro e argumentando com o caderno. Páginas sem escritos visíveis. Objetos: livros, caderno, caneta, copo e óculos. Sem púlpito, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-de-producao-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -2867,6 +3428,9 @@
   </si>
   <si>
     <t>engenharia-de-producao</t>
+  </si>
+  <si>
+    <t>Otimize processos de fabricação e custos de produção, com planejamento, projeto e gestão de produtos e serviços.</t>
   </si>
   <si>
     <t>O curso de Engenharia de Produção Semipresenciais da Cruzeiro do Sul Virtual contém conceito 5 na classificação do MEC e visa capacitar profissionais para atuação em várias áreas, focando no aumento da produtividade organizacional e na otimização de custos de produção, levando em consideração a questão ambiental e sustentável. Por isso, o curso aborda temas de planejamento, projeto e gestão, a fim de desenvolver competências para melhoria de produtos e serviços. Com duração de 10 semestres (5 anos), o curso confere o título de bacharel em Engenharia de Produção.</t>
@@ -2904,6 +3468,30 @@
     <t>Desenvolva habilidades em Engenharia de Produção EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Otimização de linha e layout de produção</t>
+  </si>
+  <si>
+    <t>Engenheiro de produção de cerca de 31 anos, homem de pele negra, cabelo curto, capacete branco e colete, prancheta, atenção à linha.</t>
+  </si>
+  <si>
+    <t>Chão de fábrica contemporâneo brasileiro, linha de montagem organizada, piso delimitado, iluminação industrial, sem aspecto precário.</t>
+  </si>
+  <si>
+    <t>prancheta de tempos, cronômetro, capacete, fita adesiva de piso, rádio</t>
+  </si>
+  <si>
+    <t>Cronometra uma estação da linha e anota na prancheta, em pé à direita do corredor de produção.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem à direita em primeiro plano, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária industrial suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; paquímetro de laboratório como cena principal; fábrica abandonada; indústria de luxo; selos de norma; atividade insegura.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheiro de produção, homem de pele negra, cerca de 31 anos, capacete e colete, no chão de fábrica, cronometrando uma estação e anotando na prancheta. Objetos: prancheta, cronômetro, capacete, fita de piso e rádio. Sem paquímetro em destaque, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gastronomia-ead-tecnologo</t>
   </si>
   <si>
@@ -2911,6 +3499,9 @@
   </si>
   <si>
     <t>gastronomia</t>
+  </si>
+  <si>
+    <t>Aprenda técnicas culinárias, panificação e gestão de alimentos, bebidas e equipes em cozinha profissional.</t>
   </si>
   <si>
     <t>O curso de Gastronomia EAD, oferece uma formação completa e reconhecida com conceito 4 pelo MEC. Com duração de 4 semestres (2 anos), o curso tem como objetivo capacitar os alunos nas técnicas e procedimentos das artes culinárias, preparando-os para planejar, administrar e gerenciar alimentos, bebidas e equipes. Os estudantes também se tornam especialistas na organização de eventos internos e externos, aprendem a arte da panificação, a seleção de vinhos e outras bebidas, e dominam técnicas da cozinha internacional.O projeto pedagógico integra teoria e prática, proporcionando um período dedicado ao ensino focado na elaboração de pratos e na gestão de negócios gastronômicos, preparando os alunos para uma carreira dinâmica e desafiadora no setor.</t>
@@ -2948,6 +3539,30 @@
     <t>Curso de Gastronomia EAD: forme-se em 2 anos com flexibilidade, conteúdo inovador e práticas reais. Aprenda online e destaque-se no mercado gastronômico!</t>
   </si>
   <si>
+    <t>Preparo e empratamento em cozinha profissional</t>
+  </si>
+  <si>
+    <t>Chef de cerca de 29 anos, mulher de pele morena, cabelo preso com touca, dolmã branca e avental, atenção ao prato.</t>
+  </si>
+  <si>
+    <t>Cozinha profissional brasileira contemporânea, bancada inox, fogão ao fundo, iluminação clara, equipe desfocada, sem câmeras nem tripé.</t>
+  </si>
+  <si>
+    <t>faca de chef, tábua, pinça, prato branco, panela</t>
+  </si>
+  <si>
+    <t>Finaliza o empratamento com a pinça e ajusta o molho, em pé à direita da bancada, sem filmar.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária de cozinha, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; smartphone no tripé; ring light; cozinha residencial de influenciador; restaurante de luxo; sujeira precária; pose para câmera.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Chef, mulher de pele morena, cerca de 29 anos, dolmã e touca, em cozinha profissional de inox, finalizando o empratamento com a pinça. Objetos: faca, tábua, pinça, prato e panela. Sem smartphone, sem tripé, sem ring light, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>radiologia-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -2955,6 +3570,9 @@
   </si>
   <si>
     <t>radiologia</t>
+  </si>
+  <si>
+    <t>Prepare-se para operar equipamentos de imagem, orientar exames e garantir qualidade e segurança nos procedimentos.</t>
   </si>
   <si>
     <t>A Graduação de Radiologia semipresencial da Cruzeiro do Sul Virtual, que combina transmissões ao vivo com encontros presenciais no campus equipado, garante uma formação abrangente e forma profissionais aptos e qualificados para orientar, monitorar, estruturar, analisar e disponibilizar assistência em exames de imagem por ressonância, exames de tomografia, radiografia mamária, tratamentos por radiação e exames cardíacos invasivos. Ao longo do curso de bacharelado, serão abordadas de forma abrangente, temas relacionados à anatomia, fisiologia, radiologia geral e ressonância magnética. O foco do curso é fornecer conhecimento para tornar os profissionais capazes de garantir qualidade e segurança nos procedimentos de operação de equipamentos de imagem, realização de exames e diagnóstico. O processo de formação tem duração de 6 semestres (3 anos).</t>
@@ -2988,6 +3606,30 @@
     <t>Desenvolva habilidades em Radiologia a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Operação segura de equipamento de imagem</t>
+  </si>
+  <si>
+    <t>Tecnóloga em radiologia de cerca de 26 anos, mulher de pele negra, cabelo preso, jaleco e avental plumbífero, atenção ao painel do equipamento.</t>
+  </si>
+  <si>
+    <t>Sala de exames de imagem contemporânea brasileira, mesa vazia, equipamento de raios X, vidro de proteção, espaço limpo, sem laudo na tela.</t>
+  </si>
+  <si>
+    <t>avental plumbífero, protetor de tireoide, comando do equipamento, suporte de receptor, ficha de exame em branco</t>
+  </si>
+  <si>
+    <t>Ajusta o comando atrás do vidro de proteção e confere o posicionamento da mesa vazia, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária clínica suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; laudo diagnóstico; tela com imagem clínica legível; cura; cirurgia; paciente exposto; hospital de luxo; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Tecnóloga em radiologia, mulher de pele negra, cerca de 26 anos, jaleco e avental plumbífero, ajustando o comando do equipamento atrás do vidro, mesa vazia. Objetos: avental, protetor de tireoide, comando, receptor e ficha em branco. Sem laudo, sem imagem clínica na tela, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>servicos-penais-ead-tecnologo</t>
   </si>
   <si>
@@ -2995,6 +3637,9 @@
   </si>
   <si>
     <t>servicos-penais</t>
+  </si>
+  <si>
+    <t>Desenvolva a gestão penitenciária, com legislação, integridade das pessoas privadas de liberdade e penas alternativas.</t>
   </si>
   <si>
     <t>O curso de Serviços Penais EAD, com duração de 4 semestres (2 anos), habilita profissionais que já fazem parte do mundo do Serviço de Segurança Pública, e os capacita para desempenhar a função de gestor de serviços penitenciários. Ao longo do curso, o aluno recebe conhecimentos e instruções necessários para que ele seja apto a preservar a integridade e o bem-estar dos encarcerados e internados, fomentando regras, saúde, qualidade de vida e retorno ao convívio social. Com toda a sua bagagem em legislação, o profissional planeja, apresenta e realiza ações governamentais voltadas para a mitigação dos desafios do encarceramento, incluindo a gestão de avaliações penais e medidas alternativas. Ao se formar, o aluno garante o título de tecnólogo em Serviços Penais.</t>
@@ -3031,6 +3676,27 @@
     <t>Aprenda sobre Serviços Penais a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Gestão de medidas alternativas e reintegração</t>
+  </si>
+  <si>
+    <t>Gestor de serviços penais de cerca de 33 anos, homem de pele morena, cabelo curto, camisa social e blazer simples, sem uniforme, postura de atendimento.</t>
+  </si>
+  <si>
+    <t>Sala administrativa de unidade de medidas alternativas brasileira, mesa, cadeiras iguais, mural institucional vazio, janela, espaço digno e organizado.</t>
+  </si>
+  <si>
+    <t>pastas de acompanhamento, código fechado, caneta, copo, calendário em branco</t>
+  </si>
+  <si>
+    <t>Orienta uma pessoa sentada à mesa e registra o plano de acompanhamento na pasta, sentado à direita, conversa respeitosa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; grades; algemas; arma; cela degradante; uniforme policial; violência; estereótipo de preso; ambiente precário ou de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestor de serviços penais, homem de pele morena, cerca de 33 anos, camisa e blazer, em sala administrativa digna, orientando e registrando o plano na pasta. Objetos: pastas, código fechado, caneta, copo e calendário em branco. Sem grades, sem algemas, sem arma, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>producao-cultural-ead-tecnologo</t>
   </si>
   <si>
@@ -3038,6 +3704,9 @@
   </si>
   <si>
     <t>producao-cultural</t>
+  </si>
+  <si>
+    <t>Organize projetos culturais da pesquisa à promoção, incluindo espetáculos, festivais, exposições e políticas culturais.</t>
   </si>
   <si>
     <t>O curso de Produção Cultural EAD da Cruzeiro do Sul Virtual desenvolve em seus alunos competências essenciais para todas as áreas e etapas da produção cultural. Desde a produção, organização, pesquisa até a promoção de eventos, os estudantes exploram disciplinas que incluem legislação e políticas culturais, cultura digital, cultura brasileira e gestão de políticas. O currículo proporciona uma base sólida em práticas contemporâneas, incentivando a criatividade, inovação e sustentabilidade nos projetos culturais desenvolvidos. Ao final do curso, os graduados estarão preparados para contribuir significativamente para o enriquecimento e a promoção da diversidade cultural em diversas comunidades. Com duração de 6 semestres (2 anos), o curso confere o título de tecnólogo.</t>
@@ -3074,6 +3743,27 @@
     <t>Aprenda sobre Produção Cultural a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem de exposição e promoção cultural</t>
+  </si>
+  <si>
+    <t>Produtora cultural de cerca de 28 anos, mulher de pele negra, cabelo crespo solto, macacão de algodão e camiseta, atenção à parede da mostra.</t>
+  </si>
+  <si>
+    <t>Galeria comunitária contemporânea brasileira, paredes brancas, obras encostadas, escada, janela, espaço acessível em montagem.</t>
+  </si>
+  <si>
+    <t>nível de bolha, fita métrica, cartaz em branco, martelo de borracha, pasta do projeto</t>
+  </si>
+  <si>
+    <t>Nivela a altura de uma obra na parede e confere a pasta do projeto, em pé à direita da galeria.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; câmera fotográfica como ação principal; claquete; planta de salão de eventos corporativos; museu de luxo; ambiente precário; cartazes com escritos.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Produtora cultural, mulher de pele negra, cerca de 28 anos, macacão, em galeria comunitária, nivelando uma obra e conferindo a pasta do projeto. Objetos: nível, fita métrica, cartaz em branco, martelo de borracha e pasta. Sem câmera em uso, sem escritos, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciencias-da-computacao-ead-bacharelado</t>
   </si>
   <si>
@@ -3081,6 +3771,9 @@
   </si>
   <si>
     <t>ciencias-da-computacao</t>
+  </si>
+  <si>
+    <t>Aprofunde algoritmos, estruturas de dados, sistemas operacionais e programação para criar e gerenciar sistemas.</t>
   </si>
   <si>
     <t>O curso de Ciências da Computação EAD da Cruzeiro do Sul Virtual oferece uma formação abrangente, preparando os profissionais para enfrentar os desafios da área. Os estudantes desenvolvem competências em programação, estrutura de dados, algoritmos, sistemas operacionais, inteligência artificial entre outros. Com versatilidade entre a teoria e a prática, o curso faz com que os alunos desenvolvam projetos e solucionem problemas reais, os preparando para o mercado de trabalho em diversos segmentos do mercado. Com duração de 8 semestres (4 anos) e certificação de bacharelado em Ciência da Computação, o curso aborda temas sobre ferramentas de programação, instruções para que as máquinas executem as tarefas necessárias para apresentar soluções cotidianas, entre outros.</t>
@@ -3116,6 +3809,27 @@
     <t>Desenvolva habilidades em Ciências da Computação com flexibilidade do EAD e baixo custo. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Desenho de algoritmo e estrutura de dados</t>
+  </si>
+  <si>
+    <t>Cientista da computação de cerca de 24 anos, homem de pele morena, cabelo cacheado, camiseta e cardigan, de pé diante do quadro de nós.</t>
+  </si>
+  <si>
+    <t>Laboratório de computação em instituição brasileira, computadores ao fundo desligados, quadro com círculos e setas, janela, espaço didático.</t>
+  </si>
+  <si>
+    <t>quadro com grafos, caneta para quadro, caderno de algoritmos, mouse, computador desligado</t>
+  </si>
+  <si>
+    <t>Desenha nós e setas de uma estrutura de dados no quadro e confere o caderno, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; código legível; fluxo de telas de app; smartphone em teste; flipchart de banco de dados empresarial; capuz de hacker; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Cientista da computação, homem de pele morena, cerca de 24 anos, cardigan, em laboratório, desenhando nós e setas no quadro e consultando o caderno de algoritmos. Quadro só com círculos e setas, sem escritos. Objetos: quadro, caneta, caderno, mouse e computador desligado. Sem smartphone, sem código, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-de-seguranca-privada-ead-tecnologo</t>
   </si>
   <si>
@@ -3123,6 +3837,9 @@
   </si>
   <si>
     <t>gestao-de-seguranca-privada</t>
+  </si>
+  <si>
+    <t>Planeje operações de proteção patrimonial, com análise de riscos, controle de operações e vigilância eletrônica.</t>
   </si>
   <si>
     <t>O curso de Gestão da Segurança Privada EAD da Cruzeiro do Sul Virtual capacita profissionais a identificar, diagnosticar e analisar os possíveis riscos que uma empresa ou uma situação correm. O curso tem o foco em planejamento, execução e controle das operações, a fim de formar profissionais capazes de gerenciar a segurança, transporte de valores, escolta armada e segurança pessoal. Com duração de 4 semestres (2 anos) e oferecendo o título de tecnólogo em Gestão da Segurança Privada, o curso possui certificação profissional (Carteira de Identidade Profissional) pelo Conselho Regional de Administração de São Paulo (CRA-SP), além de suporte dos professores, material didático digital e atividades interativas.</t>
@@ -3157,6 +3874,27 @@
     <t>Desenvolva habilidades em Gestão de Segurança Privada a distância EAD com flexibilidade e baixo custo. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Planejamento de proteção patrimonial e postos</t>
+  </si>
+  <si>
+    <t>Gestora de segurança privada de cerca de 32 anos, mulher de pele clara, cabelo liso preso, blazer grafite, apontando a planta do edifício.</t>
+  </si>
+  <si>
+    <t>Sala de briefing em empresa de segurança brasileira, mesa, planta de edifício, um monitor apagado, ambiente corporativo acessível, sem armas à vista.</t>
+  </si>
+  <si>
+    <t>planta baixa do prédio, rádios alinhados, crachás em branco, caneta, pasta de postos</t>
+  </si>
+  <si>
+    <t>Indica postos na planta do edifício e distribui rádios sobre a mesa, em pé à direita, sem arma.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; arma; colete tático ostensivo; escolta armada; cena policial; monitores de perseguição; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora de segurança privada, mulher de pele clara, cerca de 32 anos, blazer grafite, em sala de briefing, indicando postos na planta e alinhando rádios. Objetos: planta, rádios, crachás em branco, caneta e pasta. Sem arma, sem uniforme tático, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>comercio-exterior-ead-tecnologo</t>
   </si>
   <si>
@@ -3164,6 +3902,9 @@
   </si>
   <si>
     <t>comercio-exterior</t>
+  </si>
+  <si>
+    <t>Pratique negociações internacionais, logística de importação e exportação, cotação de fretes e operações cambiais.</t>
   </si>
   <si>
     <t>O curso de Comércio Exterior EAD da universidade Cruzeiro do Sul forma especialistas em técnicas comerciais a nível internacional, com altos conhecimentos em economia e tendências de consumo. O curso oferece aulas práticas em vendas, logística e mercado financeiro, visando formar profissionais para atuar na condução de negociações internacionais, planejar a logística internacional e manejar processos de operações cambiais. O graduado em Comércio Exterior tem o título de tecnólogo em Comércio Exterior, e será formado em um curso que possui conceito 5 no MEC.</t>
@@ -3198,6 +3939,30 @@
     <t>Estude Comércio Exterior a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Logística internacional e conferência de carga</t>
+  </si>
+  <si>
+    <t>Analista de comércio exterior de cerca de 30 anos, homem de pele negra, cabelo curto, camisa social e colete, prancheta, atenção ao pátio.</t>
+  </si>
+  <si>
+    <t>Escritório com vista para pátio de contêineres em porto ou centro logístico brasileiro, mesa, janela ampla, ambiente operacional organizado.</t>
+  </si>
+  <si>
+    <t>conhecimento de embarque fechado, calculadora, mini contêiner de mesa, caneta, pasta de frete</t>
+  </si>
+  <si>
+    <t>Confere o documento fechado e compara com o pátio visível na janela, em pé à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da janela, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; documentos com escritos; bandeiras como enfeite; escritório de luxo; porto precário; atividade de venda no varejo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de comércio exterior, homem de pele negra, cerca de 30 anos, camisa e colete, em escritório com vista a contêineres, conferindo documento fechado. Objetos: documento fechado, calculadora, mini contêiner, caneta e pasta. Sem escritos visíveis, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>design-de-produto-ead-tecnologo</t>
   </si>
   <si>
@@ -3205,6 +3970,9 @@
   </si>
   <si>
     <t>design-de-produto</t>
+  </si>
+  <si>
+    <t>Crie soluções em produto com pesquisa de uso, prototipagem, materiais, desenhos técnicos e testes de conceito.</t>
   </si>
   <si>
     <t>O curso de Design de Produto EAD na Cruzeiro do Sul forma profissionais competentes, capacitados a desenvolver e criar soluções inovadoras em forma de produto. Ao longo do curso, os alunos exploram a aplicação de princípios de design, técnicas de prototipagem e conhecimentos em materiais e processos de fabricação. Eles são treinados para identificar demandas de mercado, realizar pesquisa de usuário, conceber ideias criativas, elaborar desenhos técnicos, conduzir testes e validar conceitos. O curso, com conceito 4 na classificação do MEC e duração de 4 semestres (2 anos), resulta na obtenção do título de tecnólogo em Design de Produtos, integrando arte, técnica e tecnologia para formar profissionais qualificados e preparados para o mercado.</t>
@@ -3245,6 +4013,27 @@
     <t>Desenvolva habilidades em Design de Produto EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Prototipagem e desenho técnico de produto</t>
+  </si>
+  <si>
+    <t>Designer industrial de cerca de 28 anos, homem de pele clara, cabelo curto com topete, óculos de acetato, camisa xadrez de flanela, mãos no protótipo de utensílio.</t>
+  </si>
+  <si>
+    <t>Oficina de prototipagem contemporânea brasileira, bancada de madeira, ferramentas manuais, janela, espaço criativo acessível.</t>
+  </si>
+  <si>
+    <t>protótipo de utensílio, paquímetro, estilete, folhas de desenho técnico sem cotas, amostras de material</t>
+  </si>
+  <si>
+    <t>Ajusta o protótipo na bancada e confere a medida com o paquímetro, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; manequim de moda; maquete de edifício; cotas legíveis; joalheria de luxo; oficina precária.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Designer industrial, homem de pele clara, cerca de 28 anos, óculos de acetato, camisa xadrez, ajustando um protótipo de utensílio e medindo com paquímetro. Objetos: protótipo, paquímetro, estilete, folhas sem cotas e amostras. Sem manequim, sem maquete arquitetônica, sem avental de costura, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-de-tecnologia-da-informacao-ead-tecnologo</t>
   </si>
   <si>
@@ -3252,6 +4041,9 @@
   </si>
   <si>
     <t>gestao-de-tecnologia-da-informacao</t>
+  </si>
+  <si>
+    <t>Domine a administração da base tecnológica de sistemas de informática e comunicação, com decisão e gestão de equipes.</t>
   </si>
   <si>
     <t>O Tecnólogo de Gestão de Tecnologia da Informação EAD da Cruzeiro do Sul Virtual, oferece conhecimento robusto para os estudantes, abordando competências em implementação e administração de toda a base tecnológica dos sistemas de informática e comunicação empresarial, proporcionando qualificação de excelência, currículo atualizado e em sintonia com as melhores práticas do setor. O curso tem duração de 4 semestres (2 anos).</t>
@@ -3287,6 +4079,27 @@
     <t>Estude Gestão de Tecnologia da Informação a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Gestão de equipe e priorização de serviços de TI</t>
+  </si>
+  <si>
+    <t>Gestora de TI de cerca de 33 anos, mulher de pele clara, cabelo ondulado escuro, camisa social e cardigan, apontando o quadro de serviços.</t>
+  </si>
+  <si>
+    <t>Sala de gestão de TI em empresa brasileira, quadro kanban com cartões em branco, mesa de reunião, plantas, janela, sem bancada de programação.</t>
+  </si>
+  <si>
+    <t>quadro kanban, cartões em branco, caneta, notebook fechado, copo</t>
+  </si>
+  <si>
+    <t>Move um cartão no quadro de serviços e conversa com a equipe, em pé à direita, sem programar.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; código na tela; rack de servidores como cena principal; capuz; cartões com escritos; escritório de luxo; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora de TI, mulher de pele clara, cerca de 33 anos, camisa e cardigan, movendo cartão em branco no quadro kanban em sala de reunião. Objetos: quadro, cartões em branco, caneta, notebook fechado e copo. Sem código, sem rack em destaque, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>servico-social-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -3294,6 +4107,9 @@
   </si>
   <si>
     <t>servico-social</t>
+  </si>
+  <si>
+    <t>Elabore e acompanhe políticas sociais junto a órgãos, empresas e organizações, com orientação e encaminhamento.</t>
   </si>
   <si>
     <t>A graduação de Serviços Sociais semipresencial, desenvolve profissionais qualificados para elaborar, implementar e supervisionar políticas sociais em conjunto com setores governamentais, empresas privadas, ONGs e grupos comunitários. O curso é focado em oferecer competências para que o graduado seja capaz de fornecer assistência a famílias, indivíduos, grupos e pessoas em situação de vulnerabilidade social, inclusive os atingidos por discriminiação, negligência e violência doméstica, os orientando e encaminhando aos devidos procedimentos.Com o reconhecimento de Bacharel em Serviços Sociais, o estudante estará apto a compreender a realidade social, a fim de reduzir os efeitos das desigualdades sociais. O curso tem duração de 8 semestres (4 anos).</t>
@@ -3330,6 +4146,27 @@
     <t>Estude Serviço Social a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Elaboração de política social e fluxos de encaminhamento</t>
+  </si>
+  <si>
+    <t>Assistente social de cerca de 29 anos, mulher de pele morena, cabelo cacheado médio, camisa social e calça, postura de trabalho técnico.</t>
+  </si>
+  <si>
+    <t>Sala técnica de equipamento de política social brasileiro, mesa, estante de pastas, mural de fluxos em branco, janela, espaço digno e organizado, sem fila exposta.</t>
+  </si>
+  <si>
+    <t>pastas de casos fechadas, fluxograma em branco, caneta, copo, livro de legislação fechado</t>
+  </si>
+  <si>
+    <t>Monta um fluxograma de encaminhamento no mural e consulta a pasta fechada, em pé à direita, sem expor pessoas atendidas.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; pobreza como cenário; pessoas em vulnerabilidade como figurantes; barraco; fila humilhante; caridade espetacularizada; ambiente precário ou de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Assistente social, mulher de pele morena, cerca de 29 anos, camisa social, em sala técnica digna, montando fluxograma de encaminhamento no mural. Objetos: pastas fechadas, fluxograma em branco, caneta, copo e livro fechado. Sem fila, sem cena de miséria, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>secretariado-ead-tecnologo</t>
   </si>
   <si>
@@ -3337,6 +4174,9 @@
   </si>
   <si>
     <t>secretariado</t>
+  </si>
+  <si>
+    <t>Conheça assessoria a equipes, gestão de documentos, rotinas administrativas e organização de processos de escritório.</t>
   </si>
   <si>
     <t>O curso de Secretariado EAD forma profissionais para executar a realização de serviços utilizando conceitos e ferramentas tecnológicas de assessoria a executivos, diretores e suas equipes. O currículo do curso aborda temas como empreendedorismo, gestão de qualidade, plano de negócios, organização, assessoramento de eventos e idiomas estrangeiros. Os alunos desenvolvem habilidades essenciais para o suporte administrativo e gestão de escritórios, além de competências em tecnologia e comunicação. O curso tem duração de 4 semestres (2 anos) e confere o título de tecnologia, permitindo que o profissional de Secretariado desenvolva competências específicas, assessorando equipes, manuseando documentos, realizando a gestão de pessoas, entre outras demandas operacionais.</t>
@@ -3371,6 +4211,27 @@
     <t>Prepare-se para atuar na área de Secretariado a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Assessoria executiva e gestão de rotinas</t>
+  </si>
+  <si>
+    <t>Profissional de secretariado de cerca de 27 anos, homem de pele clara, cabelo curto, camisa social e colete, tablet na mão, postura de assessoria.</t>
+  </si>
+  <si>
+    <t>Antessala executiva contemporânea brasileira, mesa de apoio organizada, arquivo, planta, janela, espaço profissional acessível.</t>
+  </si>
+  <si>
+    <t>tablet, pasta de documentos, agenda fechada, grampeador, telefone fixo</t>
+  </si>
+  <si>
+    <t>Organiza a pasta de reunião e confere a agenda no tablet, em pé à direita da mesa de apoio, sem servir café.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; bandeja de café; estereótipo de assistente submissa; saia curta; pose servil; escritório de luxo; ambiente precário; papéis com escritos.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Profissional de secretariado, homem de pele clara, cerca de 27 anos, camisa e colete, organizando pasta de reunião e conferindo o tablet em antessala executiva. Objetos: tablet, pasta, agenda fechada, grampeador e telefone. Sem café, sem pose servil, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-ambiental-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -3378,6 +4239,9 @@
   </si>
   <si>
     <t>gestao-ambiental</t>
+  </si>
+  <si>
+    <t>Aplique certificação, educação ambiental e o uso racional da água e dos recursos naturais em projetos sustentáveis.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Gestão Ambiental semipresencial tem o objetivo de formar um profissional com visão holística das questões ambientais e seus impactos para atuar com planejamento, assessoria, educação e certificação, além do uso racional e eficiente de recursos ambientais, orientando-se pelo desenvolvimento sustentável e a responsabilidade socioambiental.
@@ -3412,6 +4276,27 @@
   </si>
   <si>
     <t>Estude Gestão Ambiental a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
+  </si>
+  <si>
+    <t>Monitoramento de recurso hídrico e gestão ambiental</t>
+  </si>
+  <si>
+    <t>Gestora ambiental de cerca de 30 anos, mulher de pele morena, cabelo cacheado preso, camisa de campo e colete, coletando amostra d'água.</t>
+  </si>
+  <si>
+    <t>Margem organizada de rio urbano brasileiro, vegetação, caminho, céu de manhã, estação de monitoramento simples, sem lavoura.</t>
+  </si>
+  <si>
+    <t>frasco de amostra, sonda de qualidade da água, prancheta, luvas, cooler pequeno</t>
+  </si>
+  <si>
+    <t>Mergulha o frasco no rio e anota a leitura da sonda na prancheta, agachada à direita da margem.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; trado de solo agrícola; talhão de lavoura; lixo como miséria espetacularizada; reserva de luxo; atividade agronômica de cultivo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional da manhã. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora ambiental, mulher de pele morena, cerca de 30 anos, colete, na margem de rio urbano, coletando amostra d'água e lendo a sonda. Objetos: frasco, sonda, prancheta, luvas e cooler. Sem lavoura, sem trado, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
   </si>
   <si>
     <t>design-de-animacao-ead-tecnologo</t>
@@ -9041,23 +9926,26 @@
       <c r="G27" t="s">
         <v>331</v>
       </c>
+      <c r="H27" t="s">
+        <v>585</v>
+      </c>
       <c r="I27" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="J27" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K27" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="L27" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M27" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N27" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P27" t="s">
         <v>46</v>
@@ -9069,27 +9957,54 @@
         <v>48</v>
       </c>
       <c r="T27" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="U27" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="V27" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="W27" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X27" t="s">
+        <v>595</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>596</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>597</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>598</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>599</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>600</v>
+      </c>
+      <c r="AD27" t="s">
+        <v>601</v>
+      </c>
+      <c r="AE27" t="s">
+        <v>602</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="B28" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="C28" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="D28" t="s">
         <v>65</v>
@@ -9103,23 +10018,26 @@
       <c r="G28" t="s">
         <v>331</v>
       </c>
+      <c r="H28" t="s">
+        <v>606</v>
+      </c>
       <c r="I28" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="J28" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="K28" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="L28" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="M28" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="N28" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="P28" t="s">
         <v>46</v>
@@ -9131,27 +10049,54 @@
         <v>48</v>
       </c>
       <c r="T28" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
       <c r="U28" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="V28" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="W28" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X28" t="s">
+        <v>616</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>617</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>618</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>619</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>620</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>622</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>623</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>606</v>
+        <v>624</v>
       </c>
       <c r="B29" t="s">
-        <v>607</v>
+        <v>625</v>
       </c>
       <c r="C29" t="s">
-        <v>608</v>
+        <v>626</v>
       </c>
       <c r="D29" t="s">
         <v>35</v>
@@ -9165,23 +10110,26 @@
       <c r="G29" t="s">
         <v>89</v>
       </c>
+      <c r="H29" t="s">
+        <v>627</v>
+      </c>
       <c r="I29" t="s">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="J29" t="s">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="K29" t="s">
-        <v>611</v>
+        <v>630</v>
       </c>
       <c r="L29" t="s">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="M29" t="s">
-        <v>613</v>
+        <v>632</v>
       </c>
       <c r="N29" t="s">
-        <v>614</v>
+        <v>633</v>
       </c>
       <c r="O29" t="s">
         <v>141</v>
@@ -9196,27 +10144,54 @@
         <v>48</v>
       </c>
       <c r="T29" t="s">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c r="U29" t="s">
-        <v>616</v>
+        <v>635</v>
       </c>
       <c r="V29" t="s">
-        <v>617</v>
+        <v>636</v>
       </c>
       <c r="W29" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X29" t="s">
+        <v>637</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>638</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>639</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>640</v>
+      </c>
+      <c r="AB29" t="s">
+        <v>641</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>642</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>643</v>
+      </c>
+      <c r="AE29" t="s">
+        <v>644</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>618</v>
+        <v>645</v>
       </c>
       <c r="B30" t="s">
-        <v>619</v>
+        <v>646</v>
       </c>
       <c r="C30" t="s">
-        <v>620</v>
+        <v>647</v>
       </c>
       <c r="D30" t="s">
         <v>35</v>
@@ -9230,23 +10205,26 @@
       <c r="G30" t="s">
         <v>158</v>
       </c>
+      <c r="H30" t="s">
+        <v>648</v>
+      </c>
       <c r="I30" t="s">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="J30" t="s">
-        <v>622</v>
+        <v>650</v>
       </c>
       <c r="K30" t="s">
-        <v>623</v>
+        <v>651</v>
       </c>
       <c r="L30" t="s">
-        <v>624</v>
+        <v>652</v>
       </c>
       <c r="M30" t="s">
-        <v>625</v>
+        <v>653</v>
       </c>
       <c r="N30" t="s">
-        <v>626</v>
+        <v>654</v>
       </c>
       <c r="P30" t="s">
         <v>166</v>
@@ -9261,27 +10239,54 @@
         <v>167</v>
       </c>
       <c r="T30" t="s">
-        <v>627</v>
+        <v>655</v>
       </c>
       <c r="U30" t="s">
-        <v>628</v>
+        <v>656</v>
       </c>
       <c r="V30" t="s">
-        <v>629</v>
+        <v>657</v>
       </c>
       <c r="W30" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X30" t="s">
+        <v>658</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>659</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>660</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>661</v>
+      </c>
+      <c r="AB30" t="s">
+        <v>662</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD30" t="s">
+        <v>663</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>664</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>630</v>
+        <v>665</v>
       </c>
       <c r="B31" t="s">
-        <v>631</v>
+        <v>666</v>
       </c>
       <c r="C31" t="s">
-        <v>632</v>
+        <v>667</v>
       </c>
       <c r="D31" t="s">
         <v>65</v>
@@ -9295,23 +10300,26 @@
       <c r="G31" t="s">
         <v>331</v>
       </c>
+      <c r="H31" t="s">
+        <v>668</v>
+      </c>
       <c r="I31" t="s">
-        <v>633</v>
+        <v>669</v>
       </c>
       <c r="J31" t="s">
-        <v>634</v>
+        <v>670</v>
       </c>
       <c r="K31" t="s">
-        <v>635</v>
+        <v>671</v>
       </c>
       <c r="L31" t="s">
-        <v>636</v>
+        <v>672</v>
       </c>
       <c r="M31" t="s">
-        <v>637</v>
+        <v>673</v>
       </c>
       <c r="N31" t="s">
-        <v>638</v>
+        <v>674</v>
       </c>
       <c r="P31" t="s">
         <v>46</v>
@@ -9323,27 +10331,54 @@
         <v>48</v>
       </c>
       <c r="T31" t="s">
-        <v>639</v>
+        <v>675</v>
       </c>
       <c r="U31" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="V31" t="s">
-        <v>641</v>
+        <v>677</v>
       </c>
       <c r="W31" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X31" t="s">
+        <v>678</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>679</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>680</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>681</v>
+      </c>
+      <c r="AB31" t="s">
+        <v>682</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD31" t="s">
+        <v>684</v>
+      </c>
+      <c r="AE31" t="s">
+        <v>685</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>642</v>
+        <v>686</v>
       </c>
       <c r="B32" t="s">
-        <v>643</v>
+        <v>687</v>
       </c>
       <c r="C32" t="s">
-        <v>644</v>
+        <v>688</v>
       </c>
       <c r="D32" t="s">
         <v>65</v>
@@ -9357,29 +10392,32 @@
       <c r="G32" t="s">
         <v>331</v>
       </c>
+      <c r="H32" t="s">
+        <v>689</v>
+      </c>
       <c r="I32" t="s">
-        <v>645</v>
+        <v>690</v>
       </c>
       <c r="J32" t="s">
-        <v>646</v>
+        <v>691</v>
       </c>
       <c r="K32" t="s">
-        <v>647</v>
+        <v>692</v>
       </c>
       <c r="L32" t="s">
-        <v>648</v>
+        <v>693</v>
       </c>
       <c r="M32" t="s">
-        <v>649</v>
+        <v>694</v>
       </c>
       <c r="N32" t="s">
-        <v>650</v>
+        <v>695</v>
       </c>
       <c r="O32" t="s">
         <v>141</v>
       </c>
       <c r="P32" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q32" t="s">
         <v>47</v>
@@ -9391,27 +10429,54 @@
         <v>167</v>
       </c>
       <c r="T32" t="s">
-        <v>652</v>
+        <v>697</v>
       </c>
       <c r="U32" t="s">
-        <v>653</v>
+        <v>698</v>
       </c>
       <c r="V32" t="s">
-        <v>654</v>
+        <v>699</v>
       </c>
       <c r="W32" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X32" t="s">
+        <v>700</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>701</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>702</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>703</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>704</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>705</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>706</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>655</v>
+        <v>707</v>
       </c>
       <c r="B33" t="s">
-        <v>656</v>
+        <v>708</v>
       </c>
       <c r="C33" t="s">
-        <v>657</v>
+        <v>709</v>
       </c>
       <c r="D33" t="s">
         <v>157</v>
@@ -9425,23 +10490,26 @@
       <c r="G33" t="s">
         <v>158</v>
       </c>
+      <c r="H33" t="s">
+        <v>710</v>
+      </c>
       <c r="I33" t="s">
-        <v>658</v>
+        <v>711</v>
       </c>
       <c r="J33" t="s">
-        <v>659</v>
+        <v>712</v>
       </c>
       <c r="K33" t="s">
-        <v>660</v>
+        <v>713</v>
       </c>
       <c r="L33" t="s">
-        <v>661</v>
+        <v>714</v>
       </c>
       <c r="M33" t="s">
-        <v>662</v>
+        <v>715</v>
       </c>
       <c r="N33" t="s">
-        <v>663</v>
+        <v>716</v>
       </c>
       <c r="O33" t="s">
         <v>141</v>
@@ -9456,27 +10524,54 @@
         <v>48</v>
       </c>
       <c r="T33" t="s">
-        <v>664</v>
+        <v>717</v>
       </c>
       <c r="U33" t="s">
-        <v>665</v>
+        <v>718</v>
       </c>
       <c r="V33" t="s">
-        <v>666</v>
+        <v>719</v>
       </c>
       <c r="W33" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X33" t="s">
+        <v>720</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>721</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>722</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>723</v>
+      </c>
+      <c r="AB33" t="s">
+        <v>724</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>725</v>
+      </c>
+      <c r="AD33" t="s">
+        <v>726</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>727</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>667</v>
+        <v>728</v>
       </c>
       <c r="B34" t="s">
-        <v>668</v>
+        <v>729</v>
       </c>
       <c r="C34" t="s">
-        <v>669</v>
+        <v>730</v>
       </c>
       <c r="D34" t="s">
         <v>35</v>
@@ -9490,23 +10585,26 @@
       <c r="G34" t="s">
         <v>309</v>
       </c>
+      <c r="H34" t="s">
+        <v>731</v>
+      </c>
       <c r="I34" t="s">
-        <v>670</v>
+        <v>732</v>
       </c>
       <c r="J34" t="s">
-        <v>671</v>
+        <v>733</v>
       </c>
       <c r="K34" t="s">
-        <v>672</v>
+        <v>734</v>
       </c>
       <c r="L34" t="s">
-        <v>673</v>
+        <v>735</v>
       </c>
       <c r="M34" t="s">
-        <v>674</v>
+        <v>736</v>
       </c>
       <c r="N34" t="s">
-        <v>675</v>
+        <v>737</v>
       </c>
       <c r="O34" t="s">
         <v>141</v>
@@ -9521,27 +10619,54 @@
         <v>48</v>
       </c>
       <c r="T34" t="s">
-        <v>676</v>
+        <v>738</v>
       </c>
       <c r="U34" t="s">
-        <v>677</v>
+        <v>739</v>
       </c>
       <c r="V34" t="s">
-        <v>678</v>
+        <v>740</v>
       </c>
       <c r="W34" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X34" t="s">
+        <v>741</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>742</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>743</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>744</v>
+      </c>
+      <c r="AB34" t="s">
+        <v>745</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>642</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>746</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>747</v>
+      </c>
+      <c r="AF34" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>679</v>
+        <v>748</v>
       </c>
       <c r="B35" t="s">
-        <v>680</v>
+        <v>749</v>
       </c>
       <c r="C35" t="s">
-        <v>681</v>
+        <v>750</v>
       </c>
       <c r="D35" t="s">
         <v>157</v>
@@ -9555,23 +10680,26 @@
       <c r="G35" t="s">
         <v>158</v>
       </c>
+      <c r="H35" t="s">
+        <v>751</v>
+      </c>
       <c r="I35" t="s">
-        <v>682</v>
+        <v>752</v>
       </c>
       <c r="J35" t="s">
-        <v>683</v>
+        <v>753</v>
       </c>
       <c r="K35" t="s">
-        <v>684</v>
+        <v>754</v>
       </c>
       <c r="L35" t="s">
-        <v>685</v>
+        <v>755</v>
       </c>
       <c r="M35" t="s">
-        <v>686</v>
+        <v>756</v>
       </c>
       <c r="N35" t="s">
-        <v>687</v>
+        <v>757</v>
       </c>
       <c r="P35" t="s">
         <v>166</v>
@@ -9586,27 +10714,54 @@
         <v>167</v>
       </c>
       <c r="T35" t="s">
-        <v>688</v>
+        <v>758</v>
       </c>
       <c r="U35" t="s">
-        <v>689</v>
+        <v>759</v>
       </c>
       <c r="V35" t="s">
-        <v>690</v>
+        <v>760</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X35" t="s">
+        <v>761</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>762</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>763</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>764</v>
+      </c>
+      <c r="AB35" t="s">
+        <v>765</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>766</v>
+      </c>
+      <c r="AD35" t="s">
+        <v>767</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>768</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>691</v>
+        <v>769</v>
       </c>
       <c r="B36" t="s">
-        <v>692</v>
+        <v>770</v>
       </c>
       <c r="C36" t="s">
-        <v>693</v>
+        <v>771</v>
       </c>
       <c r="D36" t="s">
         <v>157</v>
@@ -9620,23 +10775,26 @@
       <c r="G36" t="s">
         <v>158</v>
       </c>
+      <c r="H36" t="s">
+        <v>772</v>
+      </c>
       <c r="I36" t="s">
-        <v>694</v>
+        <v>773</v>
       </c>
       <c r="J36" t="s">
-        <v>695</v>
+        <v>774</v>
       </c>
       <c r="K36" t="s">
-        <v>696</v>
+        <v>775</v>
       </c>
       <c r="L36" t="s">
-        <v>697</v>
+        <v>776</v>
       </c>
       <c r="M36" t="s">
-        <v>698</v>
+        <v>777</v>
       </c>
       <c r="N36" t="s">
-        <v>699</v>
+        <v>778</v>
       </c>
       <c r="P36" t="s">
         <v>166</v>
@@ -9651,27 +10809,54 @@
         <v>167</v>
       </c>
       <c r="T36" t="s">
-        <v>700</v>
+        <v>779</v>
       </c>
       <c r="U36" t="s">
-        <v>701</v>
+        <v>780</v>
       </c>
       <c r="V36" t="s">
-        <v>702</v>
+        <v>781</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X36" t="s">
+        <v>782</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>783</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>784</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>785</v>
+      </c>
+      <c r="AB36" t="s">
+        <v>786</v>
+      </c>
+      <c r="AC36" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD36" t="s">
+        <v>788</v>
+      </c>
+      <c r="AE36" t="s">
+        <v>789</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>703</v>
+        <v>790</v>
       </c>
       <c r="B37" t="s">
-        <v>704</v>
+        <v>791</v>
       </c>
       <c r="C37" t="s">
-        <v>705</v>
+        <v>792</v>
       </c>
       <c r="D37" t="s">
         <v>65</v>
@@ -9685,23 +10870,26 @@
       <c r="G37" t="s">
         <v>331</v>
       </c>
+      <c r="H37" t="s">
+        <v>793</v>
+      </c>
       <c r="I37" t="s">
-        <v>706</v>
+        <v>794</v>
       </c>
       <c r="J37" t="s">
-        <v>707</v>
+        <v>795</v>
       </c>
       <c r="K37" t="s">
-        <v>708</v>
+        <v>796</v>
       </c>
       <c r="L37" t="s">
-        <v>709</v>
+        <v>797</v>
       </c>
       <c r="M37" t="s">
-        <v>710</v>
+        <v>798</v>
       </c>
       <c r="N37" t="s">
-        <v>711</v>
+        <v>799</v>
       </c>
       <c r="P37" t="s">
         <v>46</v>
@@ -9713,27 +10901,54 @@
         <v>48</v>
       </c>
       <c r="T37" t="s">
-        <v>712</v>
+        <v>800</v>
       </c>
       <c r="U37" t="s">
-        <v>713</v>
+        <v>801</v>
       </c>
       <c r="V37" t="s">
-        <v>714</v>
+        <v>802</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X37" t="s">
+        <v>803</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>804</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>805</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>806</v>
+      </c>
+      <c r="AB37" t="s">
+        <v>807</v>
+      </c>
+      <c r="AC37" t="s">
+        <v>347</v>
+      </c>
+      <c r="AD37" t="s">
+        <v>808</v>
+      </c>
+      <c r="AE37" t="s">
+        <v>809</v>
+      </c>
+      <c r="AF37" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="38" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>715</v>
+        <v>810</v>
       </c>
       <c r="B38" t="s">
-        <v>716</v>
+        <v>811</v>
       </c>
       <c r="C38" t="s">
-        <v>717</v>
+        <v>812</v>
       </c>
       <c r="D38" t="s">
         <v>65</v>
@@ -9747,23 +10962,26 @@
       <c r="G38" t="s">
         <v>203</v>
       </c>
+      <c r="H38" t="s">
+        <v>813</v>
+      </c>
       <c r="I38" t="s">
-        <v>718</v>
+        <v>814</v>
       </c>
       <c r="J38" t="s">
-        <v>719</v>
+        <v>815</v>
       </c>
       <c r="K38" t="s">
-        <v>720</v>
+        <v>816</v>
       </c>
       <c r="L38" t="s">
-        <v>721</v>
+        <v>817</v>
       </c>
       <c r="M38" t="s">
-        <v>722</v>
+        <v>818</v>
       </c>
       <c r="N38" t="s">
-        <v>723</v>
+        <v>819</v>
       </c>
       <c r="P38" t="s">
         <v>46</v>
@@ -9775,27 +10993,54 @@
         <v>48</v>
       </c>
       <c r="T38" t="s">
-        <v>724</v>
+        <v>820</v>
       </c>
       <c r="U38" t="s">
-        <v>725</v>
+        <v>821</v>
       </c>
       <c r="V38" t="s">
-        <v>726</v>
+        <v>822</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X38" t="s">
+        <v>823</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>824</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>825</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>826</v>
+      </c>
+      <c r="AB38" t="s">
+        <v>827</v>
+      </c>
+      <c r="AC38" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD38" t="s">
+        <v>828</v>
+      </c>
+      <c r="AE38" t="s">
+        <v>829</v>
+      </c>
+      <c r="AF38" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>727</v>
+        <v>830</v>
       </c>
       <c r="B39" t="s">
-        <v>728</v>
+        <v>831</v>
       </c>
       <c r="C39" t="s">
-        <v>729</v>
+        <v>832</v>
       </c>
       <c r="D39" t="s">
         <v>65</v>
@@ -9809,23 +11054,26 @@
       <c r="G39" t="s">
         <v>331</v>
       </c>
+      <c r="H39" t="s">
+        <v>833</v>
+      </c>
       <c r="I39" t="s">
-        <v>730</v>
+        <v>834</v>
       </c>
       <c r="J39" t="s">
-        <v>731</v>
+        <v>835</v>
       </c>
       <c r="K39" t="s">
-        <v>732</v>
+        <v>836</v>
       </c>
       <c r="L39" t="s">
-        <v>733</v>
+        <v>837</v>
       </c>
       <c r="M39" t="s">
-        <v>734</v>
+        <v>838</v>
       </c>
       <c r="N39" t="s">
-        <v>735</v>
+        <v>839</v>
       </c>
       <c r="P39" t="s">
         <v>46</v>
@@ -9837,27 +11085,54 @@
         <v>48</v>
       </c>
       <c r="T39" t="s">
-        <v>736</v>
+        <v>840</v>
       </c>
       <c r="U39" t="s">
-        <v>737</v>
+        <v>841</v>
       </c>
       <c r="V39" t="s">
-        <v>738</v>
+        <v>842</v>
       </c>
       <c r="W39" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X39" t="s">
+        <v>843</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>844</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>845</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>846</v>
+      </c>
+      <c r="AB39" t="s">
+        <v>847</v>
+      </c>
+      <c r="AC39" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD39" t="s">
+        <v>848</v>
+      </c>
+      <c r="AE39" t="s">
+        <v>849</v>
+      </c>
+      <c r="AF39" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>739</v>
+        <v>850</v>
       </c>
       <c r="B40" t="s">
-        <v>740</v>
+        <v>851</v>
       </c>
       <c r="C40" t="s">
-        <v>741</v>
+        <v>852</v>
       </c>
       <c r="D40" t="s">
         <v>65</v>
@@ -9871,23 +11146,26 @@
       <c r="G40" t="s">
         <v>331</v>
       </c>
+      <c r="H40" t="s">
+        <v>853</v>
+      </c>
       <c r="I40" t="s">
-        <v>742</v>
+        <v>854</v>
       </c>
       <c r="J40" t="s">
-        <v>743</v>
+        <v>855</v>
       </c>
       <c r="K40" t="s">
-        <v>744</v>
+        <v>856</v>
       </c>
       <c r="L40" t="s">
-        <v>745</v>
+        <v>857</v>
       </c>
       <c r="M40" t="s">
-        <v>746</v>
+        <v>858</v>
       </c>
       <c r="N40" t="s">
-        <v>747</v>
+        <v>859</v>
       </c>
       <c r="P40" t="s">
         <v>46</v>
@@ -9899,27 +11177,54 @@
         <v>48</v>
       </c>
       <c r="T40" t="s">
-        <v>748</v>
+        <v>860</v>
       </c>
       <c r="U40" t="s">
-        <v>749</v>
+        <v>861</v>
       </c>
       <c r="V40" t="s">
-        <v>750</v>
+        <v>862</v>
       </c>
       <c r="W40" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X40" t="s">
+        <v>863</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>864</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>865</v>
+      </c>
+      <c r="AA40" t="s">
+        <v>866</v>
+      </c>
+      <c r="AB40" t="s">
+        <v>867</v>
+      </c>
+      <c r="AC40" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD40" t="s">
+        <v>868</v>
+      </c>
+      <c r="AE40" t="s">
+        <v>869</v>
+      </c>
+      <c r="AF40" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>751</v>
+        <v>870</v>
       </c>
       <c r="B41" t="s">
-        <v>752</v>
+        <v>871</v>
       </c>
       <c r="C41" t="s">
-        <v>753</v>
+        <v>872</v>
       </c>
       <c r="D41" t="s">
         <v>65</v>
@@ -9933,23 +11238,26 @@
       <c r="G41" t="s">
         <v>89</v>
       </c>
+      <c r="H41" t="s">
+        <v>873</v>
+      </c>
       <c r="I41" t="s">
-        <v>754</v>
+        <v>874</v>
       </c>
       <c r="J41" t="s">
-        <v>755</v>
+        <v>875</v>
       </c>
       <c r="K41" t="s">
-        <v>756</v>
+        <v>876</v>
       </c>
       <c r="L41" t="s">
-        <v>757</v>
+        <v>877</v>
       </c>
       <c r="M41" t="s">
-        <v>758</v>
+        <v>878</v>
       </c>
       <c r="N41" t="s">
-        <v>759</v>
+        <v>879</v>
       </c>
       <c r="O41" t="s">
         <v>141</v>
@@ -9964,27 +11272,54 @@
         <v>48</v>
       </c>
       <c r="T41" t="s">
-        <v>760</v>
+        <v>880</v>
       </c>
       <c r="U41" t="s">
-        <v>761</v>
+        <v>881</v>
       </c>
       <c r="V41" t="s">
-        <v>762</v>
+        <v>882</v>
       </c>
       <c r="W41" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X41" t="s">
+        <v>883</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>884</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>885</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>886</v>
+      </c>
+      <c r="AB41" t="s">
+        <v>887</v>
+      </c>
+      <c r="AC41" t="s">
+        <v>888</v>
+      </c>
+      <c r="AD41" t="s">
+        <v>889</v>
+      </c>
+      <c r="AE41" t="s">
+        <v>890</v>
+      </c>
+      <c r="AF41" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>763</v>
+        <v>891</v>
       </c>
       <c r="B42" t="s">
-        <v>764</v>
+        <v>892</v>
       </c>
       <c r="C42" t="s">
-        <v>765</v>
+        <v>893</v>
       </c>
       <c r="D42" t="s">
         <v>65</v>
@@ -9998,23 +11333,26 @@
       <c r="G42" t="s">
         <v>38</v>
       </c>
+      <c r="H42" t="s">
+        <v>894</v>
+      </c>
       <c r="I42" t="s">
-        <v>766</v>
+        <v>895</v>
       </c>
       <c r="J42" t="s">
-        <v>767</v>
+        <v>896</v>
       </c>
       <c r="K42" t="s">
-        <v>768</v>
+        <v>897</v>
       </c>
       <c r="L42" t="s">
-        <v>769</v>
+        <v>898</v>
       </c>
       <c r="M42" t="s">
-        <v>770</v>
+        <v>899</v>
       </c>
       <c r="N42" t="s">
-        <v>771</v>
+        <v>900</v>
       </c>
       <c r="P42" t="s">
         <v>46</v>
@@ -10026,27 +11364,54 @@
         <v>48</v>
       </c>
       <c r="T42" t="s">
-        <v>772</v>
+        <v>901</v>
       </c>
       <c r="U42" t="s">
-        <v>773</v>
+        <v>902</v>
       </c>
       <c r="V42" t="s">
-        <v>774</v>
+        <v>903</v>
       </c>
       <c r="W42" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X42" t="s">
+        <v>904</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>905</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>906</v>
+      </c>
+      <c r="AA42" t="s">
+        <v>907</v>
+      </c>
+      <c r="AB42" t="s">
+        <v>908</v>
+      </c>
+      <c r="AC42" t="s">
+        <v>909</v>
+      </c>
+      <c r="AD42" t="s">
+        <v>910</v>
+      </c>
+      <c r="AE42" t="s">
+        <v>911</v>
+      </c>
+      <c r="AF42" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>775</v>
+        <v>912</v>
       </c>
       <c r="B43" t="s">
-        <v>776</v>
+        <v>913</v>
       </c>
       <c r="C43" t="s">
-        <v>777</v>
+        <v>914</v>
       </c>
       <c r="D43" t="s">
         <v>65</v>
@@ -10060,29 +11425,32 @@
       <c r="G43" t="s">
         <v>89</v>
       </c>
+      <c r="H43" t="s">
+        <v>915</v>
+      </c>
       <c r="I43" t="s">
-        <v>778</v>
+        <v>916</v>
       </c>
       <c r="J43" t="s">
-        <v>779</v>
+        <v>917</v>
       </c>
       <c r="K43" t="s">
-        <v>780</v>
+        <v>918</v>
       </c>
       <c r="L43" t="s">
-        <v>781</v>
+        <v>919</v>
       </c>
       <c r="M43" t="s">
-        <v>782</v>
+        <v>920</v>
       </c>
       <c r="N43" t="s">
-        <v>783</v>
+        <v>921</v>
       </c>
       <c r="O43" t="s">
         <v>141</v>
       </c>
       <c r="P43" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q43" t="s">
         <v>47</v>
@@ -10094,27 +11462,54 @@
         <v>167</v>
       </c>
       <c r="T43" t="s">
-        <v>784</v>
+        <v>922</v>
       </c>
       <c r="U43" t="s">
-        <v>785</v>
+        <v>923</v>
       </c>
       <c r="V43" t="s">
-        <v>786</v>
+        <v>924</v>
       </c>
       <c r="W43" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X43" t="s">
+        <v>925</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>926</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>927</v>
+      </c>
+      <c r="AA43" t="s">
+        <v>928</v>
+      </c>
+      <c r="AB43" t="s">
+        <v>929</v>
+      </c>
+      <c r="AC43" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD43" t="s">
+        <v>930</v>
+      </c>
+      <c r="AE43" t="s">
+        <v>931</v>
+      </c>
+      <c r="AF43" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>787</v>
+        <v>932</v>
       </c>
       <c r="B44" t="s">
-        <v>788</v>
+        <v>933</v>
       </c>
       <c r="C44" t="s">
-        <v>789</v>
+        <v>934</v>
       </c>
       <c r="D44" t="s">
         <v>65</v>
@@ -10128,23 +11523,26 @@
       <c r="G44" t="s">
         <v>203</v>
       </c>
+      <c r="H44" t="s">
+        <v>935</v>
+      </c>
       <c r="I44" t="s">
-        <v>790</v>
+        <v>936</v>
       </c>
       <c r="J44" t="s">
-        <v>791</v>
+        <v>937</v>
       </c>
       <c r="K44" t="s">
-        <v>792</v>
+        <v>938</v>
       </c>
       <c r="L44" t="s">
-        <v>793</v>
+        <v>939</v>
       </c>
       <c r="M44" t="s">
-        <v>794</v>
+        <v>940</v>
       </c>
       <c r="N44" t="s">
-        <v>795</v>
+        <v>941</v>
       </c>
       <c r="P44" t="s">
         <v>46</v>
@@ -10156,27 +11554,54 @@
         <v>48</v>
       </c>
       <c r="T44" t="s">
-        <v>796</v>
+        <v>942</v>
       </c>
       <c r="U44" t="s">
-        <v>797</v>
+        <v>943</v>
       </c>
       <c r="V44" t="s">
-        <v>798</v>
+        <v>944</v>
       </c>
       <c r="W44" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X44" t="s">
+        <v>945</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>946</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>947</v>
+      </c>
+      <c r="AA44" t="s">
+        <v>948</v>
+      </c>
+      <c r="AB44" t="s">
+        <v>949</v>
+      </c>
+      <c r="AC44" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD44" t="s">
+        <v>950</v>
+      </c>
+      <c r="AE44" t="s">
+        <v>951</v>
+      </c>
+      <c r="AF44" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>799</v>
+        <v>952</v>
       </c>
       <c r="B45" t="s">
-        <v>800</v>
+        <v>953</v>
       </c>
       <c r="C45" t="s">
-        <v>801</v>
+        <v>954</v>
       </c>
       <c r="D45" t="s">
         <v>65</v>
@@ -10190,23 +11615,26 @@
       <c r="G45" t="s">
         <v>331</v>
       </c>
+      <c r="H45" t="s">
+        <v>955</v>
+      </c>
       <c r="I45" t="s">
-        <v>802</v>
+        <v>956</v>
       </c>
       <c r="J45" t="s">
-        <v>803</v>
+        <v>957</v>
       </c>
       <c r="K45" t="s">
-        <v>804</v>
+        <v>958</v>
       </c>
       <c r="L45" t="s">
-        <v>805</v>
+        <v>959</v>
       </c>
       <c r="M45" t="s">
-        <v>806</v>
+        <v>960</v>
       </c>
       <c r="N45" t="s">
-        <v>807</v>
+        <v>961</v>
       </c>
       <c r="P45" t="s">
         <v>46</v>
@@ -10218,27 +11646,54 @@
         <v>48</v>
       </c>
       <c r="T45" t="s">
-        <v>808</v>
+        <v>962</v>
       </c>
       <c r="U45" t="s">
-        <v>809</v>
+        <v>963</v>
       </c>
       <c r="V45" t="s">
-        <v>810</v>
+        <v>964</v>
       </c>
       <c r="W45" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X45" t="s">
+        <v>965</v>
+      </c>
+      <c r="Y45" t="s">
+        <v>966</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>967</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>968</v>
+      </c>
+      <c r="AB45" t="s">
+        <v>969</v>
+      </c>
+      <c r="AC45" t="s">
+        <v>970</v>
+      </c>
+      <c r="AD45" t="s">
+        <v>971</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>972</v>
+      </c>
+      <c r="AF45" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>811</v>
+        <v>973</v>
       </c>
       <c r="B46" t="s">
-        <v>812</v>
+        <v>974</v>
       </c>
       <c r="C46" t="s">
-        <v>813</v>
+        <v>975</v>
       </c>
       <c r="D46" t="s">
         <v>65</v>
@@ -10252,23 +11707,26 @@
       <c r="G46" t="s">
         <v>331</v>
       </c>
+      <c r="H46" t="s">
+        <v>976</v>
+      </c>
       <c r="I46" t="s">
-        <v>814</v>
+        <v>977</v>
       </c>
       <c r="J46" t="s">
-        <v>815</v>
+        <v>978</v>
       </c>
       <c r="K46" t="s">
-        <v>816</v>
+        <v>979</v>
       </c>
       <c r="L46" t="s">
-        <v>817</v>
+        <v>980</v>
       </c>
       <c r="M46" t="s">
-        <v>818</v>
+        <v>981</v>
       </c>
       <c r="N46" t="s">
-        <v>819</v>
+        <v>982</v>
       </c>
       <c r="P46" t="s">
         <v>166</v>
@@ -10283,27 +11741,54 @@
         <v>167</v>
       </c>
       <c r="T46" t="s">
-        <v>820</v>
+        <v>983</v>
       </c>
       <c r="U46" t="s">
-        <v>821</v>
+        <v>984</v>
       </c>
       <c r="V46" t="s">
-        <v>822</v>
+        <v>985</v>
       </c>
       <c r="W46" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X46" t="s">
+        <v>986</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>987</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>988</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>989</v>
+      </c>
+      <c r="AB46" t="s">
+        <v>990</v>
+      </c>
+      <c r="AC46" t="s">
+        <v>991</v>
+      </c>
+      <c r="AD46" t="s">
+        <v>992</v>
+      </c>
+      <c r="AE46" t="s">
+        <v>993</v>
+      </c>
+      <c r="AF46" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>823</v>
+        <v>994</v>
       </c>
       <c r="B47" t="s">
-        <v>824</v>
+        <v>995</v>
       </c>
       <c r="C47" t="s">
-        <v>825</v>
+        <v>996</v>
       </c>
       <c r="D47" t="s">
         <v>65</v>
@@ -10317,23 +11802,26 @@
       <c r="G47" t="s">
         <v>203</v>
       </c>
+      <c r="H47" t="s">
+        <v>997</v>
+      </c>
       <c r="I47" t="s">
-        <v>826</v>
+        <v>998</v>
       </c>
       <c r="J47" t="s">
-        <v>827</v>
+        <v>999</v>
       </c>
       <c r="K47" t="s">
-        <v>828</v>
+        <v>1000</v>
       </c>
       <c r="L47" t="s">
-        <v>829</v>
+        <v>1001</v>
       </c>
       <c r="M47" t="s">
-        <v>830</v>
+        <v>1002</v>
       </c>
       <c r="N47" t="s">
-        <v>831</v>
+        <v>1003</v>
       </c>
       <c r="P47" t="s">
         <v>46</v>
@@ -10345,27 +11833,54 @@
         <v>48</v>
       </c>
       <c r="T47" t="s">
-        <v>832</v>
+        <v>1004</v>
       </c>
       <c r="U47" t="s">
-        <v>833</v>
+        <v>1005</v>
       </c>
       <c r="V47" t="s">
-        <v>834</v>
+        <v>1006</v>
       </c>
       <c r="W47" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X47" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>1008</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>1009</v>
+      </c>
+      <c r="AA47" t="s">
+        <v>1010</v>
+      </c>
+      <c r="AB47" t="s">
+        <v>1011</v>
+      </c>
+      <c r="AC47" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD47" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AE47" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AF47" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>835</v>
+        <v>1014</v>
       </c>
       <c r="B48" t="s">
-        <v>836</v>
+        <v>1015</v>
       </c>
       <c r="C48" t="s">
-        <v>837</v>
+        <v>1016</v>
       </c>
       <c r="D48" t="s">
         <v>35</v>
@@ -10379,23 +11894,26 @@
       <c r="G48" t="s">
         <v>158</v>
       </c>
+      <c r="H48" t="s">
+        <v>1017</v>
+      </c>
       <c r="I48" t="s">
-        <v>838</v>
+        <v>1018</v>
       </c>
       <c r="J48" t="s">
-        <v>839</v>
+        <v>1019</v>
       </c>
       <c r="K48" t="s">
-        <v>840</v>
+        <v>1020</v>
       </c>
       <c r="L48" t="s">
-        <v>841</v>
+        <v>1021</v>
       </c>
       <c r="M48" t="s">
-        <v>842</v>
+        <v>1022</v>
       </c>
       <c r="N48" t="s">
-        <v>843</v>
+        <v>1023</v>
       </c>
       <c r="P48" t="s">
         <v>46</v>
@@ -10407,27 +11925,54 @@
         <v>48</v>
       </c>
       <c r="T48" t="s">
-        <v>844</v>
+        <v>1024</v>
       </c>
       <c r="U48" t="s">
-        <v>845</v>
+        <v>1025</v>
       </c>
       <c r="V48" t="s">
-        <v>846</v>
+        <v>1026</v>
       </c>
       <c r="W48" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X48" t="s">
+        <v>1027</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>1028</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>1029</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AB48" t="s">
+        <v>1031</v>
+      </c>
+      <c r="AC48" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD48" t="s">
+        <v>1032</v>
+      </c>
+      <c r="AE48" t="s">
+        <v>1033</v>
+      </c>
+      <c r="AF48" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>847</v>
+        <v>1034</v>
       </c>
       <c r="B49" t="s">
-        <v>848</v>
+        <v>1035</v>
       </c>
       <c r="C49" t="s">
-        <v>849</v>
+        <v>1036</v>
       </c>
       <c r="D49" t="s">
         <v>35</v>
@@ -10441,29 +11986,32 @@
       <c r="G49" t="s">
         <v>203</v>
       </c>
+      <c r="H49" t="s">
+        <v>1037</v>
+      </c>
       <c r="I49" t="s">
-        <v>850</v>
+        <v>1038</v>
       </c>
       <c r="J49" t="s">
-        <v>851</v>
+        <v>1039</v>
       </c>
       <c r="K49" t="s">
-        <v>852</v>
+        <v>1040</v>
       </c>
       <c r="L49" t="s">
-        <v>853</v>
+        <v>1041</v>
       </c>
       <c r="M49" t="s">
-        <v>854</v>
+        <v>1042</v>
       </c>
       <c r="N49" t="s">
-        <v>855</v>
+        <v>1043</v>
       </c>
       <c r="O49" t="s">
         <v>141</v>
       </c>
       <c r="P49" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q49" t="s">
         <v>47</v>
@@ -10475,27 +12023,54 @@
         <v>167</v>
       </c>
       <c r="T49" t="s">
-        <v>856</v>
+        <v>1044</v>
       </c>
       <c r="U49" t="s">
-        <v>857</v>
+        <v>1045</v>
       </c>
       <c r="V49" t="s">
-        <v>858</v>
+        <v>1046</v>
       </c>
       <c r="W49" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X49" t="s">
+        <v>1047</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>1048</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>1049</v>
+      </c>
+      <c r="AA49" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AB49" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AC49" t="s">
+        <v>1052</v>
+      </c>
+      <c r="AD49" t="s">
+        <v>1053</v>
+      </c>
+      <c r="AE49" t="s">
+        <v>1054</v>
+      </c>
+      <c r="AF49" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>859</v>
+        <v>1055</v>
       </c>
       <c r="B50" t="s">
-        <v>860</v>
+        <v>1056</v>
       </c>
       <c r="C50" t="s">
-        <v>861</v>
+        <v>1057</v>
       </c>
       <c r="D50" t="s">
         <v>65</v>
@@ -10507,31 +12082,34 @@
         <v>66</v>
       </c>
       <c r="G50" t="s">
-        <v>860</v>
+        <v>1056</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1058</v>
       </c>
       <c r="I50" t="s">
-        <v>862</v>
+        <v>1059</v>
       </c>
       <c r="J50" t="s">
-        <v>863</v>
+        <v>1060</v>
       </c>
       <c r="K50" t="s">
-        <v>864</v>
+        <v>1061</v>
       </c>
       <c r="L50" t="s">
-        <v>865</v>
+        <v>1062</v>
       </c>
       <c r="M50" t="s">
-        <v>866</v>
+        <v>1063</v>
       </c>
       <c r="N50" t="s">
-        <v>867</v>
+        <v>1064</v>
       </c>
       <c r="O50" t="s">
         <v>141</v>
       </c>
       <c r="P50" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q50" t="s">
         <v>47</v>
@@ -10543,27 +12121,54 @@
         <v>167</v>
       </c>
       <c r="T50" t="s">
-        <v>868</v>
+        <v>1065</v>
       </c>
       <c r="U50" t="s">
-        <v>869</v>
+        <v>1066</v>
       </c>
       <c r="V50" t="s">
-        <v>870</v>
+        <v>1067</v>
       </c>
       <c r="W50" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X50" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Y50" t="s">
+        <v>1069</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>1070</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>1071</v>
+      </c>
+      <c r="AB50" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AC50" t="s">
+        <v>1073</v>
+      </c>
+      <c r="AD50" t="s">
+        <v>1074</v>
+      </c>
+      <c r="AE50" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AF50" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>871</v>
+        <v>1076</v>
       </c>
       <c r="B51" t="s">
-        <v>872</v>
+        <v>1077</v>
       </c>
       <c r="C51" t="s">
-        <v>873</v>
+        <v>1078</v>
       </c>
       <c r="D51" t="s">
         <v>65</v>
@@ -10577,23 +12182,26 @@
       <c r="G51" t="s">
         <v>89</v>
       </c>
+      <c r="H51" t="s">
+        <v>1079</v>
+      </c>
       <c r="I51" t="s">
-        <v>874</v>
+        <v>1080</v>
       </c>
       <c r="J51" t="s">
-        <v>875</v>
+        <v>1081</v>
       </c>
       <c r="K51" t="s">
-        <v>876</v>
+        <v>1082</v>
       </c>
       <c r="L51" t="s">
-        <v>877</v>
+        <v>1083</v>
       </c>
       <c r="M51" t="s">
-        <v>878</v>
+        <v>1084</v>
       </c>
       <c r="N51" t="s">
-        <v>879</v>
+        <v>1085</v>
       </c>
       <c r="O51" t="s">
         <v>141</v>
@@ -10608,27 +12216,54 @@
         <v>48</v>
       </c>
       <c r="T51" t="s">
-        <v>880</v>
+        <v>1086</v>
       </c>
       <c r="U51" t="s">
-        <v>881</v>
+        <v>1087</v>
       </c>
       <c r="V51" t="s">
-        <v>882</v>
+        <v>1088</v>
       </c>
       <c r="W51" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X51" t="s">
+        <v>1089</v>
+      </c>
+      <c r="Y51" t="s">
+        <v>1090</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AA51" t="s">
+        <v>1092</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>1093</v>
+      </c>
+      <c r="AC51" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AD51" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AE51" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AF51" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>883</v>
+        <v>1097</v>
       </c>
       <c r="B52" t="s">
-        <v>884</v>
+        <v>1098</v>
       </c>
       <c r="C52" t="s">
-        <v>885</v>
+        <v>1099</v>
       </c>
       <c r="D52" t="s">
         <v>65</v>
@@ -10642,23 +12277,26 @@
       <c r="G52" t="s">
         <v>500</v>
       </c>
+      <c r="H52" t="s">
+        <v>1100</v>
+      </c>
       <c r="I52" t="s">
-        <v>886</v>
+        <v>1101</v>
       </c>
       <c r="J52" t="s">
-        <v>887</v>
+        <v>1102</v>
       </c>
       <c r="K52" t="s">
-        <v>888</v>
+        <v>1103</v>
       </c>
       <c r="L52" t="s">
-        <v>889</v>
+        <v>1104</v>
       </c>
       <c r="M52" t="s">
-        <v>890</v>
+        <v>1105</v>
       </c>
       <c r="N52" t="s">
-        <v>891</v>
+        <v>1106</v>
       </c>
       <c r="P52" t="s">
         <v>46</v>
@@ -10670,27 +12308,54 @@
         <v>48</v>
       </c>
       <c r="T52" t="s">
-        <v>892</v>
+        <v>1107</v>
       </c>
       <c r="U52" t="s">
-        <v>893</v>
+        <v>1108</v>
       </c>
       <c r="V52" t="s">
-        <v>894</v>
+        <v>1109</v>
       </c>
       <c r="W52" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X52" t="s">
+        <v>1110</v>
+      </c>
+      <c r="Y52" t="s">
+        <v>1111</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>1112</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>1113</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AC52" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD52" t="s">
+        <v>1115</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>1116</v>
+      </c>
+      <c r="AF52" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>895</v>
+        <v>1117</v>
       </c>
       <c r="B53" t="s">
-        <v>896</v>
+        <v>1118</v>
       </c>
       <c r="C53" t="s">
-        <v>897</v>
+        <v>1119</v>
       </c>
       <c r="D53" t="s">
         <v>65</v>
@@ -10704,23 +12369,26 @@
       <c r="G53" t="s">
         <v>38</v>
       </c>
+      <c r="H53" t="s">
+        <v>1120</v>
+      </c>
       <c r="I53" t="s">
-        <v>898</v>
+        <v>1121</v>
       </c>
       <c r="J53" t="s">
-        <v>899</v>
+        <v>1122</v>
       </c>
       <c r="K53" t="s">
-        <v>900</v>
+        <v>1123</v>
       </c>
       <c r="L53" t="s">
-        <v>901</v>
+        <v>1124</v>
       </c>
       <c r="M53" t="s">
-        <v>902</v>
+        <v>1125</v>
       </c>
       <c r="N53" t="s">
-        <v>903</v>
+        <v>1126</v>
       </c>
       <c r="P53" t="s">
         <v>46</v>
@@ -10732,27 +12400,54 @@
         <v>48</v>
       </c>
       <c r="T53" t="s">
-        <v>904</v>
+        <v>1127</v>
       </c>
       <c r="U53" t="s">
-        <v>905</v>
+        <v>1128</v>
       </c>
       <c r="V53" t="s">
-        <v>906</v>
+        <v>1129</v>
       </c>
       <c r="W53" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X53" t="s">
+        <v>1130</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>1131</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>1132</v>
+      </c>
+      <c r="AA53" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AC53" t="s">
+        <v>725</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>1135</v>
+      </c>
+      <c r="AE53" t="s">
+        <v>1136</v>
+      </c>
+      <c r="AF53" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>907</v>
+        <v>1137</v>
       </c>
       <c r="B54" t="s">
-        <v>908</v>
+        <v>1138</v>
       </c>
       <c r="C54" t="s">
-        <v>909</v>
+        <v>1139</v>
       </c>
       <c r="D54" t="s">
         <v>35</v>
@@ -10766,23 +12461,26 @@
       <c r="G54" t="s">
         <v>203</v>
       </c>
+      <c r="H54" t="s">
+        <v>1140</v>
+      </c>
       <c r="I54" t="s">
-        <v>910</v>
+        <v>1141</v>
       </c>
       <c r="J54" t="s">
-        <v>911</v>
+        <v>1142</v>
       </c>
       <c r="K54" t="s">
-        <v>912</v>
+        <v>1143</v>
       </c>
       <c r="L54" t="s">
-        <v>913</v>
+        <v>1144</v>
       </c>
       <c r="M54" t="s">
-        <v>914</v>
+        <v>1145</v>
       </c>
       <c r="N54" t="s">
-        <v>915</v>
+        <v>1146</v>
       </c>
       <c r="P54" t="s">
         <v>46</v>
@@ -10794,27 +12492,54 @@
         <v>48</v>
       </c>
       <c r="T54" t="s">
-        <v>916</v>
+        <v>1147</v>
       </c>
       <c r="U54" t="s">
-        <v>917</v>
+        <v>1148</v>
       </c>
       <c r="V54" t="s">
-        <v>918</v>
+        <v>1149</v>
       </c>
       <c r="W54" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X54" t="s">
+        <v>1150</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>1151</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>1152</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>1153</v>
+      </c>
+      <c r="AB54" t="s">
+        <v>1154</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD54" t="s">
+        <v>1155</v>
+      </c>
+      <c r="AE54" t="s">
+        <v>1156</v>
+      </c>
+      <c r="AF54" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>919</v>
+        <v>1157</v>
       </c>
       <c r="B55" t="s">
-        <v>920</v>
+        <v>1158</v>
       </c>
       <c r="C55" t="s">
-        <v>921</v>
+        <v>1159</v>
       </c>
       <c r="D55" t="s">
         <v>65</v>
@@ -10828,23 +12553,26 @@
       <c r="G55" t="s">
         <v>331</v>
       </c>
+      <c r="H55" t="s">
+        <v>1160</v>
+      </c>
       <c r="I55" t="s">
-        <v>922</v>
+        <v>1161</v>
       </c>
       <c r="J55" t="s">
-        <v>923</v>
+        <v>1162</v>
       </c>
       <c r="K55" t="s">
-        <v>924</v>
+        <v>1163</v>
       </c>
       <c r="L55" t="s">
-        <v>925</v>
+        <v>1164</v>
       </c>
       <c r="M55" t="s">
-        <v>926</v>
+        <v>1165</v>
       </c>
       <c r="N55" t="s">
-        <v>927</v>
+        <v>1166</v>
       </c>
       <c r="P55" t="s">
         <v>46</v>
@@ -10856,27 +12584,54 @@
         <v>48</v>
       </c>
       <c r="T55" t="s">
-        <v>928</v>
+        <v>1167</v>
       </c>
       <c r="U55" t="s">
-        <v>929</v>
+        <v>1168</v>
       </c>
       <c r="V55" t="s">
-        <v>930</v>
+        <v>1169</v>
       </c>
       <c r="W55" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X55" t="s">
+        <v>1170</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>1171</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>1172</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>1173</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>1174</v>
+      </c>
+      <c r="AC55" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD55" t="s">
+        <v>1175</v>
+      </c>
+      <c r="AE55" t="s">
+        <v>1176</v>
+      </c>
+      <c r="AF55" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>931</v>
+        <v>1177</v>
       </c>
       <c r="B56" t="s">
-        <v>932</v>
+        <v>1178</v>
       </c>
       <c r="C56" t="s">
-        <v>933</v>
+        <v>1179</v>
       </c>
       <c r="D56" t="s">
         <v>65</v>
@@ -10890,23 +12645,26 @@
       <c r="G56" t="s">
         <v>331</v>
       </c>
+      <c r="H56" t="s">
+        <v>1180</v>
+      </c>
       <c r="I56" t="s">
-        <v>934</v>
+        <v>1181</v>
       </c>
       <c r="J56" t="s">
-        <v>935</v>
+        <v>1182</v>
       </c>
       <c r="K56" t="s">
-        <v>936</v>
+        <v>1183</v>
       </c>
       <c r="L56" t="s">
-        <v>937</v>
+        <v>1184</v>
       </c>
       <c r="M56" t="s">
-        <v>938</v>
+        <v>1185</v>
       </c>
       <c r="N56" t="s">
-        <v>939</v>
+        <v>1186</v>
       </c>
       <c r="P56" t="s">
         <v>46</v>
@@ -10918,27 +12676,54 @@
         <v>48</v>
       </c>
       <c r="T56" t="s">
-        <v>940</v>
+        <v>1187</v>
       </c>
       <c r="U56" t="s">
-        <v>941</v>
+        <v>1188</v>
       </c>
       <c r="V56" t="s">
-        <v>942</v>
+        <v>1189</v>
       </c>
       <c r="W56" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X56" t="s">
+        <v>1190</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>1191</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>1192</v>
+      </c>
+      <c r="AA56" t="s">
+        <v>1193</v>
+      </c>
+      <c r="AB56" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AC56" t="s">
+        <v>1195</v>
+      </c>
+      <c r="AD56" t="s">
+        <v>1196</v>
+      </c>
+      <c r="AE56" t="s">
+        <v>1197</v>
+      </c>
+      <c r="AF56" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>943</v>
+        <v>1198</v>
       </c>
       <c r="B57" t="s">
-        <v>944</v>
+        <v>1199</v>
       </c>
       <c r="C57" t="s">
-        <v>945</v>
+        <v>1200</v>
       </c>
       <c r="D57" t="s">
         <v>65</v>
@@ -10952,23 +12737,26 @@
       <c r="G57" t="s">
         <v>309</v>
       </c>
+      <c r="H57" t="s">
+        <v>1201</v>
+      </c>
       <c r="I57" t="s">
-        <v>946</v>
+        <v>1202</v>
       </c>
       <c r="J57" t="s">
-        <v>947</v>
+        <v>1203</v>
       </c>
       <c r="K57" t="s">
-        <v>948</v>
+        <v>1204</v>
       </c>
       <c r="L57" t="s">
-        <v>949</v>
+        <v>1205</v>
       </c>
       <c r="M57" t="s">
-        <v>950</v>
+        <v>1206</v>
       </c>
       <c r="N57" t="s">
-        <v>951</v>
+        <v>1207</v>
       </c>
       <c r="P57" t="s">
         <v>46</v>
@@ -10980,27 +12768,54 @@
         <v>48</v>
       </c>
       <c r="T57" t="s">
-        <v>952</v>
+        <v>1208</v>
       </c>
       <c r="U57" t="s">
-        <v>953</v>
+        <v>1209</v>
       </c>
       <c r="V57" t="s">
-        <v>954</v>
+        <v>1210</v>
       </c>
       <c r="W57" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X57" t="s">
+        <v>1211</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>1212</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>1213</v>
+      </c>
+      <c r="AA57" t="s">
+        <v>1214</v>
+      </c>
+      <c r="AB57" t="s">
+        <v>1215</v>
+      </c>
+      <c r="AC57" t="s">
+        <v>642</v>
+      </c>
+      <c r="AD57" t="s">
+        <v>1216</v>
+      </c>
+      <c r="AE57" t="s">
+        <v>1217</v>
+      </c>
+      <c r="AF57" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>955</v>
+        <v>1218</v>
       </c>
       <c r="B58" t="s">
-        <v>956</v>
+        <v>1219</v>
       </c>
       <c r="C58" t="s">
-        <v>957</v>
+        <v>1220</v>
       </c>
       <c r="D58" t="s">
         <v>65</v>
@@ -11014,23 +12829,26 @@
       <c r="G58" t="s">
         <v>203</v>
       </c>
+      <c r="H58" t="s">
+        <v>1221</v>
+      </c>
       <c r="I58" t="s">
-        <v>958</v>
+        <v>1222</v>
       </c>
       <c r="J58" t="s">
-        <v>959</v>
+        <v>1223</v>
       </c>
       <c r="K58" t="s">
-        <v>960</v>
+        <v>1224</v>
       </c>
       <c r="L58" t="s">
-        <v>961</v>
+        <v>1225</v>
       </c>
       <c r="M58" t="s">
-        <v>962</v>
+        <v>1226</v>
       </c>
       <c r="N58" t="s">
-        <v>963</v>
+        <v>1227</v>
       </c>
       <c r="P58" t="s">
         <v>46</v>
@@ -11042,27 +12860,54 @@
         <v>48</v>
       </c>
       <c r="T58" t="s">
-        <v>964</v>
+        <v>1228</v>
       </c>
       <c r="U58" t="s">
-        <v>965</v>
+        <v>1229</v>
       </c>
       <c r="V58" t="s">
-        <v>966</v>
+        <v>1230</v>
       </c>
       <c r="W58" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X58" t="s">
+        <v>1231</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>1232</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>1233</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>1234</v>
+      </c>
+      <c r="AB58" t="s">
+        <v>1235</v>
+      </c>
+      <c r="AC58" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD58" t="s">
+        <v>1236</v>
+      </c>
+      <c r="AE58" t="s">
+        <v>1237</v>
+      </c>
+      <c r="AF58" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>967</v>
+        <v>1238</v>
       </c>
       <c r="B59" t="s">
-        <v>968</v>
+        <v>1239</v>
       </c>
       <c r="C59" t="s">
-        <v>969</v>
+        <v>1240</v>
       </c>
       <c r="D59" t="s">
         <v>35</v>
@@ -11076,23 +12921,26 @@
       <c r="G59" t="s">
         <v>89</v>
       </c>
+      <c r="H59" t="s">
+        <v>1241</v>
+      </c>
       <c r="I59" t="s">
-        <v>970</v>
+        <v>1242</v>
       </c>
       <c r="J59" t="s">
-        <v>971</v>
+        <v>1243</v>
       </c>
       <c r="K59" t="s">
-        <v>972</v>
+        <v>1244</v>
       </c>
       <c r="L59" t="s">
-        <v>973</v>
+        <v>1245</v>
       </c>
       <c r="M59" t="s">
-        <v>974</v>
+        <v>1246</v>
       </c>
       <c r="N59" t="s">
-        <v>975</v>
+        <v>1247</v>
       </c>
       <c r="P59" t="s">
         <v>166</v>
@@ -11107,27 +12955,54 @@
         <v>167</v>
       </c>
       <c r="T59" t="s">
-        <v>976</v>
+        <v>1248</v>
       </c>
       <c r="U59" t="s">
-        <v>977</v>
+        <v>1249</v>
       </c>
       <c r="V59" t="s">
-        <v>978</v>
+        <v>1250</v>
       </c>
       <c r="W59" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X59" t="s">
+        <v>1251</v>
+      </c>
+      <c r="Y59" t="s">
+        <v>1252</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AA59" t="s">
+        <v>1254</v>
+      </c>
+      <c r="AB59" t="s">
+        <v>1255</v>
+      </c>
+      <c r="AC59" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD59" t="s">
+        <v>1256</v>
+      </c>
+      <c r="AE59" t="s">
+        <v>1257</v>
+      </c>
+      <c r="AF59" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>979</v>
+        <v>1258</v>
       </c>
       <c r="B60" t="s">
-        <v>980</v>
+        <v>1259</v>
       </c>
       <c r="C60" t="s">
-        <v>981</v>
+        <v>1260</v>
       </c>
       <c r="D60" t="s">
         <v>65</v>
@@ -11141,23 +13016,26 @@
       <c r="G60" t="s">
         <v>331</v>
       </c>
+      <c r="H60" t="s">
+        <v>1261</v>
+      </c>
       <c r="I60" t="s">
-        <v>982</v>
+        <v>1262</v>
       </c>
       <c r="J60" t="s">
-        <v>983</v>
+        <v>1263</v>
       </c>
       <c r="K60" t="s">
-        <v>984</v>
+        <v>1264</v>
       </c>
       <c r="L60" t="s">
-        <v>985</v>
+        <v>1265</v>
       </c>
       <c r="M60" t="s">
-        <v>986</v>
+        <v>1266</v>
       </c>
       <c r="N60" t="s">
-        <v>987</v>
+        <v>1267</v>
       </c>
       <c r="P60" t="s">
         <v>46</v>
@@ -11169,27 +13047,54 @@
         <v>48</v>
       </c>
       <c r="T60" t="s">
-        <v>988</v>
+        <v>1268</v>
       </c>
       <c r="U60" t="s">
-        <v>989</v>
+        <v>1269</v>
       </c>
       <c r="V60" t="s">
-        <v>990</v>
+        <v>1270</v>
       </c>
       <c r="W60" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X60" t="s">
+        <v>1271</v>
+      </c>
+      <c r="Y60" t="s">
+        <v>1272</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>1273</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>1274</v>
+      </c>
+      <c r="AB60" t="s">
+        <v>1275</v>
+      </c>
+      <c r="AC60" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD60" t="s">
+        <v>1276</v>
+      </c>
+      <c r="AE60" t="s">
+        <v>1277</v>
+      </c>
+      <c r="AF60" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>991</v>
+        <v>1278</v>
       </c>
       <c r="B61" t="s">
-        <v>992</v>
+        <v>1279</v>
       </c>
       <c r="C61" t="s">
-        <v>993</v>
+        <v>1280</v>
       </c>
       <c r="D61" t="s">
         <v>65</v>
@@ -11203,23 +13108,26 @@
       <c r="G61" t="s">
         <v>331</v>
       </c>
+      <c r="H61" t="s">
+        <v>1281</v>
+      </c>
       <c r="I61" t="s">
-        <v>994</v>
+        <v>1282</v>
       </c>
       <c r="J61" t="s">
-        <v>995</v>
+        <v>1283</v>
       </c>
       <c r="K61" t="s">
-        <v>996</v>
+        <v>1284</v>
       </c>
       <c r="L61" t="s">
-        <v>997</v>
+        <v>1285</v>
       </c>
       <c r="M61" t="s">
-        <v>998</v>
+        <v>1286</v>
       </c>
       <c r="N61" t="s">
-        <v>999</v>
+        <v>1287</v>
       </c>
       <c r="P61" t="s">
         <v>166</v>
@@ -11234,27 +13142,54 @@
         <v>167</v>
       </c>
       <c r="T61" t="s">
-        <v>1000</v>
+        <v>1288</v>
       </c>
       <c r="U61" t="s">
-        <v>1001</v>
+        <v>1289</v>
       </c>
       <c r="V61" t="s">
-        <v>1002</v>
+        <v>1290</v>
       </c>
       <c r="W61" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X61" t="s">
+        <v>1291</v>
+      </c>
+      <c r="Y61" t="s">
+        <v>1292</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>1293</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>1294</v>
+      </c>
+      <c r="AB61" t="s">
+        <v>1295</v>
+      </c>
+      <c r="AC61" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD61" t="s">
+        <v>1296</v>
+      </c>
+      <c r="AE61" t="s">
+        <v>1297</v>
+      </c>
+      <c r="AF61" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>1003</v>
+        <v>1298</v>
       </c>
       <c r="B62" t="s">
-        <v>1004</v>
+        <v>1299</v>
       </c>
       <c r="C62" t="s">
-        <v>1005</v>
+        <v>1300</v>
       </c>
       <c r="D62" t="s">
         <v>65</v>
@@ -11269,22 +13204,22 @@
         <v>203</v>
       </c>
       <c r="I62" t="s">
-        <v>1006</v>
+        <v>1301</v>
       </c>
       <c r="J62" t="s">
-        <v>1007</v>
+        <v>1302</v>
       </c>
       <c r="K62" t="s">
-        <v>1008</v>
+        <v>1303</v>
       </c>
       <c r="L62" t="s">
-        <v>1009</v>
+        <v>1304</v>
       </c>
       <c r="M62" t="s">
-        <v>1010</v>
+        <v>1305</v>
       </c>
       <c r="N62" t="s">
-        <v>1011</v>
+        <v>1306</v>
       </c>
       <c r="P62" t="s">
         <v>46</v>
@@ -11296,13 +13231,13 @@
         <v>48</v>
       </c>
       <c r="T62" t="s">
-        <v>1012</v>
+        <v>1307</v>
       </c>
       <c r="U62" t="s">
-        <v>1013</v>
+        <v>1308</v>
       </c>
       <c r="V62" t="s">
-        <v>1014</v>
+        <v>1309</v>
       </c>
       <c r="W62" s="1" t="s">
         <v>52</v>
@@ -11310,13 +13245,13 @@
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1015</v>
+        <v>1310</v>
       </c>
       <c r="B63" t="s">
-        <v>1016</v>
+        <v>1311</v>
       </c>
       <c r="C63" t="s">
-        <v>1017</v>
+        <v>1312</v>
       </c>
       <c r="D63" t="s">
         <v>35</v>
@@ -11331,22 +13266,22 @@
         <v>38</v>
       </c>
       <c r="I63" t="s">
-        <v>1018</v>
+        <v>1313</v>
       </c>
       <c r="J63" t="s">
-        <v>1019</v>
+        <v>1314</v>
       </c>
       <c r="K63" t="s">
-        <v>1020</v>
+        <v>1315</v>
       </c>
       <c r="L63" t="s">
-        <v>1021</v>
+        <v>1316</v>
       </c>
       <c r="M63" t="s">
-        <v>1022</v>
+        <v>1317</v>
       </c>
       <c r="N63" t="s">
-        <v>1023</v>
+        <v>1318</v>
       </c>
       <c r="P63" t="s">
         <v>46</v>
@@ -11358,13 +13293,13 @@
         <v>48</v>
       </c>
       <c r="T63" t="s">
-        <v>1024</v>
+        <v>1319</v>
       </c>
       <c r="U63" t="s">
-        <v>1025</v>
+        <v>1320</v>
       </c>
       <c r="V63" t="s">
-        <v>1026</v>
+        <v>1321</v>
       </c>
       <c r="W63" s="1" t="s">
         <v>52</v>
@@ -11372,13 +13307,13 @@
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1027</v>
+        <v>1322</v>
       </c>
       <c r="B64" t="s">
-        <v>1028</v>
+        <v>1323</v>
       </c>
       <c r="C64" t="s">
-        <v>1029</v>
+        <v>1324</v>
       </c>
       <c r="D64" t="s">
         <v>65</v>
@@ -11393,22 +13328,22 @@
         <v>38</v>
       </c>
       <c r="I64" t="s">
-        <v>1030</v>
+        <v>1325</v>
       </c>
       <c r="J64" t="s">
-        <v>1031</v>
+        <v>1326</v>
       </c>
       <c r="K64" t="s">
-        <v>1032</v>
+        <v>1327</v>
       </c>
       <c r="L64" t="s">
-        <v>1033</v>
+        <v>1328</v>
       </c>
       <c r="M64" t="s">
-        <v>1034</v>
+        <v>1329</v>
       </c>
       <c r="N64" t="s">
-        <v>1035</v>
+        <v>1330</v>
       </c>
       <c r="P64" t="s">
         <v>46</v>
@@ -11420,13 +13355,13 @@
         <v>48</v>
       </c>
       <c r="T64" t="s">
-        <v>1036</v>
+        <v>1331</v>
       </c>
       <c r="U64" t="s">
-        <v>1037</v>
+        <v>1332</v>
       </c>
       <c r="V64" t="s">
-        <v>1038</v>
+        <v>1333</v>
       </c>
       <c r="W64" s="1" t="s">
         <v>52</v>
@@ -11434,13 +13369,13 @@
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1039</v>
+        <v>1334</v>
       </c>
       <c r="B65" t="s">
-        <v>1040</v>
+        <v>1335</v>
       </c>
       <c r="C65" t="s">
-        <v>1041</v>
+        <v>1336</v>
       </c>
       <c r="D65" t="s">
         <v>157</v>
@@ -11455,22 +13390,22 @@
         <v>158</v>
       </c>
       <c r="I65" t="s">
-        <v>1042</v>
+        <v>1337</v>
       </c>
       <c r="J65" t="s">
-        <v>1043</v>
+        <v>1338</v>
       </c>
       <c r="K65" t="s">
-        <v>1044</v>
+        <v>1339</v>
       </c>
       <c r="L65" t="s">
-        <v>1045</v>
+        <v>1340</v>
       </c>
       <c r="M65" t="s">
-        <v>1046</v>
+        <v>1341</v>
       </c>
       <c r="N65" t="s">
-        <v>1047</v>
+        <v>1342</v>
       </c>
       <c r="P65" t="s">
         <v>166</v>
@@ -11485,13 +13420,13 @@
         <v>167</v>
       </c>
       <c r="T65" t="s">
-        <v>1048</v>
+        <v>1343</v>
       </c>
       <c r="U65" t="s">
-        <v>1049</v>
+        <v>1344</v>
       </c>
       <c r="V65" t="s">
-        <v>1050</v>
+        <v>1345</v>
       </c>
       <c r="W65" s="1" t="s">
         <v>52</v>
@@ -11499,13 +13434,13 @@
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1051</v>
+        <v>1346</v>
       </c>
       <c r="B66" t="s">
-        <v>1052</v>
+        <v>1347</v>
       </c>
       <c r="C66" t="s">
-        <v>1053</v>
+        <v>1348</v>
       </c>
       <c r="D66" t="s">
         <v>35</v>
@@ -11520,28 +13455,28 @@
         <v>331</v>
       </c>
       <c r="I66" t="s">
-        <v>1054</v>
+        <v>1349</v>
       </c>
       <c r="J66" t="s">
-        <v>1055</v>
+        <v>1350</v>
       </c>
       <c r="K66" t="s">
-        <v>1056</v>
+        <v>1351</v>
       </c>
       <c r="L66" t="s">
-        <v>1057</v>
+        <v>1352</v>
       </c>
       <c r="M66" t="s">
-        <v>1058</v>
+        <v>1353</v>
       </c>
       <c r="N66" t="s">
-        <v>1059</v>
+        <v>1354</v>
       </c>
       <c r="O66" t="s">
         <v>141</v>
       </c>
       <c r="P66" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q66" t="s">
         <v>47</v>
@@ -11553,13 +13488,13 @@
         <v>167</v>
       </c>
       <c r="T66" t="s">
-        <v>1060</v>
+        <v>1355</v>
       </c>
       <c r="U66" t="s">
-        <v>1061</v>
+        <v>1356</v>
       </c>
       <c r="V66" t="s">
-        <v>1062</v>
+        <v>1357</v>
       </c>
       <c r="W66" s="1" t="s">
         <v>52</v>
@@ -11567,13 +13502,13 @@
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1063</v>
+        <v>1358</v>
       </c>
       <c r="B67" t="s">
-        <v>1064</v>
+        <v>1359</v>
       </c>
       <c r="C67" t="s">
-        <v>1065</v>
+        <v>1360</v>
       </c>
       <c r="D67" t="s">
         <v>35</v>
@@ -11588,22 +13523,22 @@
         <v>89</v>
       </c>
       <c r="I67" t="s">
-        <v>1066</v>
+        <v>1361</v>
       </c>
       <c r="J67" t="s">
-        <v>1067</v>
+        <v>1362</v>
       </c>
       <c r="K67" t="s">
-        <v>1068</v>
+        <v>1363</v>
       </c>
       <c r="L67" t="s">
-        <v>1069</v>
+        <v>1364</v>
       </c>
       <c r="M67" t="s">
-        <v>1070</v>
+        <v>1365</v>
       </c>
       <c r="N67" t="s">
-        <v>1071</v>
+        <v>1366</v>
       </c>
       <c r="O67" t="s">
         <v>141</v>
@@ -11618,13 +13553,13 @@
         <v>48</v>
       </c>
       <c r="T67" t="s">
-        <v>1072</v>
+        <v>1367</v>
       </c>
       <c r="U67" t="s">
-        <v>1073</v>
+        <v>1368</v>
       </c>
       <c r="V67" t="s">
-        <v>1074</v>
+        <v>1369</v>
       </c>
       <c r="W67" s="1" t="s">
         <v>52</v>
@@ -11632,13 +13567,13 @@
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1075</v>
+        <v>1370</v>
       </c>
       <c r="B68" t="s">
-        <v>1076</v>
+        <v>1371</v>
       </c>
       <c r="C68" t="s">
-        <v>1077</v>
+        <v>1372</v>
       </c>
       <c r="D68" t="s">
         <v>157</v>
@@ -11653,22 +13588,22 @@
         <v>158</v>
       </c>
       <c r="I68" t="s">
-        <v>1078</v>
+        <v>1373</v>
       </c>
       <c r="J68" t="s">
-        <v>1079</v>
+        <v>1374</v>
       </c>
       <c r="K68" t="s">
-        <v>1080</v>
+        <v>1375</v>
       </c>
       <c r="L68" t="s">
-        <v>1081</v>
+        <v>1376</v>
       </c>
       <c r="M68" t="s">
-        <v>1082</v>
+        <v>1377</v>
       </c>
       <c r="N68" t="s">
-        <v>1083</v>
+        <v>1378</v>
       </c>
       <c r="P68" t="s">
         <v>46</v>
@@ -11680,13 +13615,13 @@
         <v>48</v>
       </c>
       <c r="T68" t="s">
-        <v>1084</v>
+        <v>1379</v>
       </c>
       <c r="U68" t="s">
-        <v>1085</v>
+        <v>1380</v>
       </c>
       <c r="V68" t="s">
-        <v>1086</v>
+        <v>1381</v>
       </c>
       <c r="W68" s="1" t="s">
         <v>52</v>
@@ -11694,13 +13629,13 @@
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1087</v>
+        <v>1382</v>
       </c>
       <c r="B69" t="s">
-        <v>1088</v>
+        <v>1383</v>
       </c>
       <c r="C69" t="s">
-        <v>1089</v>
+        <v>1384</v>
       </c>
       <c r="D69" t="s">
         <v>35</v>
@@ -11715,22 +13650,22 @@
         <v>89</v>
       </c>
       <c r="I69" t="s">
-        <v>1090</v>
+        <v>1385</v>
       </c>
       <c r="J69" t="s">
-        <v>1091</v>
+        <v>1386</v>
       </c>
       <c r="K69" t="s">
-        <v>1092</v>
+        <v>1387</v>
       </c>
       <c r="L69" t="s">
-        <v>1093</v>
+        <v>1388</v>
       </c>
       <c r="M69" t="s">
-        <v>1094</v>
+        <v>1389</v>
       </c>
       <c r="N69" t="s">
-        <v>1095</v>
+        <v>1390</v>
       </c>
       <c r="O69" t="s">
         <v>141</v>
@@ -11745,13 +13680,13 @@
         <v>48</v>
       </c>
       <c r="T69" t="s">
-        <v>1096</v>
+        <v>1391</v>
       </c>
       <c r="U69" t="s">
-        <v>1097</v>
+        <v>1392</v>
       </c>
       <c r="V69" t="s">
-        <v>1098</v>
+        <v>1393</v>
       </c>
       <c r="W69" s="1" t="s">
         <v>52</v>
@@ -11759,13 +13694,13 @@
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1099</v>
+        <v>1394</v>
       </c>
       <c r="B70" t="s">
-        <v>1100</v>
+        <v>1395</v>
       </c>
       <c r="C70" t="s">
-        <v>1101</v>
+        <v>1396</v>
       </c>
       <c r="D70" t="s">
         <v>35</v>
@@ -11780,22 +13715,22 @@
         <v>89</v>
       </c>
       <c r="I70" t="s">
-        <v>1102</v>
+        <v>1397</v>
       </c>
       <c r="J70" t="s">
-        <v>1103</v>
+        <v>1398</v>
       </c>
       <c r="K70" t="s">
-        <v>1104</v>
+        <v>1399</v>
       </c>
       <c r="L70" t="s">
-        <v>1105</v>
+        <v>1400</v>
       </c>
       <c r="M70" t="s">
-        <v>1106</v>
+        <v>1401</v>
       </c>
       <c r="N70" t="s">
-        <v>1107</v>
+        <v>1402</v>
       </c>
       <c r="O70" t="s">
         <v>141</v>
@@ -11810,13 +13745,13 @@
         <v>48</v>
       </c>
       <c r="T70" t="s">
-        <v>1108</v>
+        <v>1403</v>
       </c>
       <c r="U70" t="s">
-        <v>1109</v>
+        <v>1404</v>
       </c>
       <c r="V70" t="s">
-        <v>1110</v>
+        <v>1405</v>
       </c>
       <c r="W70" s="1" t="s">
         <v>52</v>
@@ -11824,13 +13759,13 @@
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1111</v>
+        <v>1406</v>
       </c>
       <c r="B71" t="s">
-        <v>1112</v>
+        <v>1407</v>
       </c>
       <c r="C71" t="s">
-        <v>1113</v>
+        <v>1408</v>
       </c>
       <c r="D71" t="s">
         <v>35</v>
@@ -11845,22 +13780,22 @@
         <v>158</v>
       </c>
       <c r="I71" t="s">
-        <v>1114</v>
+        <v>1409</v>
       </c>
       <c r="J71" t="s">
-        <v>1115</v>
+        <v>1410</v>
       </c>
       <c r="K71" t="s">
-        <v>1116</v>
+        <v>1411</v>
       </c>
       <c r="L71" t="s">
-        <v>1117</v>
+        <v>1412</v>
       </c>
       <c r="M71" t="s">
-        <v>1118</v>
+        <v>1413</v>
       </c>
       <c r="N71" t="s">
-        <v>1119</v>
+        <v>1414</v>
       </c>
       <c r="P71" t="s">
         <v>166</v>
@@ -11875,13 +13810,13 @@
         <v>167</v>
       </c>
       <c r="T71" t="s">
-        <v>1120</v>
+        <v>1415</v>
       </c>
       <c r="U71" t="s">
-        <v>1121</v>
+        <v>1416</v>
       </c>
       <c r="V71" t="s">
-        <v>1122</v>
+        <v>1417</v>
       </c>
       <c r="W71" s="1" t="s">
         <v>52</v>
@@ -11889,16 +13824,16 @@
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1123</v>
+        <v>1418</v>
       </c>
       <c r="B72" t="s">
-        <v>1124</v>
+        <v>1419</v>
       </c>
       <c r="C72" t="s">
-        <v>1125</v>
+        <v>1420</v>
       </c>
       <c r="D72" t="s">
-        <v>1126</v>
+        <v>1421</v>
       </c>
       <c r="E72" t="s">
         <v>132</v>
@@ -11910,22 +13845,22 @@
         <v>158</v>
       </c>
       <c r="I72" t="s">
-        <v>1127</v>
+        <v>1422</v>
       </c>
       <c r="J72" t="s">
-        <v>1128</v>
+        <v>1423</v>
       </c>
       <c r="K72" t="s">
-        <v>1129</v>
+        <v>1424</v>
       </c>
       <c r="L72" t="s">
-        <v>1130</v>
+        <v>1425</v>
       </c>
       <c r="M72" t="s">
-        <v>1131</v>
+        <v>1426</v>
       </c>
       <c r="N72" t="s">
-        <v>1132</v>
+        <v>1427</v>
       </c>
       <c r="P72" t="s">
         <v>166</v>
@@ -11937,16 +13872,16 @@
         <v>48</v>
       </c>
       <c r="S72" t="s">
-        <v>1133</v>
+        <v>1428</v>
       </c>
       <c r="T72" t="s">
-        <v>1134</v>
+        <v>1429</v>
       </c>
       <c r="U72" t="s">
-        <v>1135</v>
+        <v>1430</v>
       </c>
       <c r="V72" t="s">
-        <v>1136</v>
+        <v>1431</v>
       </c>
       <c r="W72" s="1" t="s">
         <v>52</v>
@@ -11954,13 +13889,13 @@
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1137</v>
+        <v>1432</v>
       </c>
       <c r="B73" t="s">
-        <v>1138</v>
+        <v>1433</v>
       </c>
       <c r="C73" t="s">
-        <v>1139</v>
+        <v>1434</v>
       </c>
       <c r="D73" t="s">
         <v>157</v>
@@ -11969,25 +13904,25 @@
         <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>1140</v>
+        <v>1435</v>
       </c>
       <c r="G73" t="s">
         <v>158</v>
       </c>
       <c r="I73" t="s">
-        <v>1141</v>
+        <v>1436</v>
       </c>
       <c r="J73" t="s">
-        <v>1142</v>
+        <v>1437</v>
       </c>
       <c r="K73" t="s">
-        <v>1143</v>
+        <v>1438</v>
       </c>
       <c r="M73" t="s">
-        <v>1144</v>
+        <v>1439</v>
       </c>
       <c r="N73" t="s">
-        <v>1145</v>
+        <v>1440</v>
       </c>
       <c r="O73" t="s">
         <v>141</v>
@@ -12002,30 +13937,30 @@
         <v>48</v>
       </c>
       <c r="S73" t="s">
-        <v>1146</v>
+        <v>1441</v>
       </c>
       <c r="T73" t="s">
-        <v>1147</v>
+        <v>1442</v>
       </c>
       <c r="U73" t="s">
-        <v>1148</v>
+        <v>1443</v>
       </c>
       <c r="V73" t="s">
-        <v>1149</v>
+        <v>1444</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>1150</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1151</v>
+        <v>1446</v>
       </c>
       <c r="B74" t="s">
-        <v>1152</v>
+        <v>1447</v>
       </c>
       <c r="C74" t="s">
-        <v>1153</v>
+        <v>1448</v>
       </c>
       <c r="D74" t="s">
         <v>65</v>
@@ -12040,22 +13975,22 @@
         <v>500</v>
       </c>
       <c r="I74" t="s">
-        <v>1154</v>
+        <v>1449</v>
       </c>
       <c r="J74" t="s">
-        <v>1155</v>
+        <v>1450</v>
       </c>
       <c r="K74" t="s">
-        <v>1156</v>
+        <v>1451</v>
       </c>
       <c r="L74" t="s">
-        <v>1157</v>
+        <v>1452</v>
       </c>
       <c r="M74" t="s">
-        <v>1158</v>
+        <v>1453</v>
       </c>
       <c r="N74" t="s">
-        <v>1159</v>
+        <v>1454</v>
       </c>
       <c r="P74" t="s">
         <v>46</v>
@@ -12067,13 +14002,13 @@
         <v>48</v>
       </c>
       <c r="T74" t="s">
-        <v>1160</v>
+        <v>1455</v>
       </c>
       <c r="U74" t="s">
-        <v>1161</v>
+        <v>1456</v>
       </c>
       <c r="V74" t="s">
-        <v>1162</v>
+        <v>1457</v>
       </c>
       <c r="W74" s="1" t="s">
         <v>52</v>
@@ -12081,13 +14016,13 @@
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1163</v>
+        <v>1458</v>
       </c>
       <c r="B75" t="s">
-        <v>1164</v>
+        <v>1459</v>
       </c>
       <c r="C75" t="s">
-        <v>1165</v>
+        <v>1460</v>
       </c>
       <c r="D75" t="s">
         <v>65</v>
@@ -12102,22 +14037,22 @@
         <v>203</v>
       </c>
       <c r="I75" t="s">
-        <v>1166</v>
+        <v>1461</v>
       </c>
       <c r="J75" t="s">
-        <v>1167</v>
+        <v>1462</v>
       </c>
       <c r="K75" t="s">
-        <v>1168</v>
+        <v>1463</v>
       </c>
       <c r="L75" t="s">
-        <v>1169</v>
+        <v>1464</v>
       </c>
       <c r="M75" t="s">
-        <v>1170</v>
+        <v>1465</v>
       </c>
       <c r="N75" t="s">
-        <v>1171</v>
+        <v>1466</v>
       </c>
       <c r="P75" t="s">
         <v>46</v>
@@ -12129,13 +14064,13 @@
         <v>48</v>
       </c>
       <c r="T75" t="s">
-        <v>1172</v>
+        <v>1467</v>
       </c>
       <c r="U75" t="s">
-        <v>1173</v>
+        <v>1468</v>
       </c>
       <c r="V75" t="s">
-        <v>1174</v>
+        <v>1469</v>
       </c>
       <c r="W75" s="1" t="s">
         <v>52</v>
@@ -12143,13 +14078,13 @@
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1175</v>
+        <v>1470</v>
       </c>
       <c r="B76" t="s">
-        <v>1176</v>
+        <v>1471</v>
       </c>
       <c r="C76" t="s">
-        <v>1177</v>
+        <v>1472</v>
       </c>
       <c r="D76" t="s">
         <v>65</v>
@@ -12164,22 +14099,22 @@
         <v>38</v>
       </c>
       <c r="I76" t="s">
-        <v>1178</v>
+        <v>1473</v>
       </c>
       <c r="J76" t="s">
-        <v>1179</v>
+        <v>1474</v>
       </c>
       <c r="K76" t="s">
-        <v>1180</v>
+        <v>1475</v>
       </c>
       <c r="L76" t="s">
-        <v>1181</v>
+        <v>1476</v>
       </c>
       <c r="M76" t="s">
-        <v>1182</v>
+        <v>1477</v>
       </c>
       <c r="N76" t="s">
-        <v>1183</v>
+        <v>1478</v>
       </c>
       <c r="P76" t="s">
         <v>46</v>
@@ -12191,13 +14126,13 @@
         <v>48</v>
       </c>
       <c r="T76" t="s">
-        <v>1184</v>
+        <v>1479</v>
       </c>
       <c r="U76" t="s">
-        <v>1185</v>
+        <v>1480</v>
       </c>
       <c r="V76" t="s">
-        <v>1186</v>
+        <v>1481</v>
       </c>
       <c r="W76" s="1" t="s">
         <v>52</v>
@@ -12205,13 +14140,13 @@
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1187</v>
+        <v>1482</v>
       </c>
       <c r="B77" t="s">
-        <v>1188</v>
+        <v>1483</v>
       </c>
       <c r="C77" t="s">
-        <v>1189</v>
+        <v>1484</v>
       </c>
       <c r="D77" t="s">
         <v>35</v>
@@ -12226,22 +14161,22 @@
         <v>203</v>
       </c>
       <c r="I77" t="s">
-        <v>1190</v>
+        <v>1485</v>
       </c>
       <c r="J77" t="s">
-        <v>1191</v>
+        <v>1486</v>
       </c>
       <c r="K77" t="s">
-        <v>1192</v>
+        <v>1487</v>
       </c>
       <c r="L77" t="s">
-        <v>1193</v>
+        <v>1488</v>
       </c>
       <c r="M77" t="s">
-        <v>1194</v>
+        <v>1489</v>
       </c>
       <c r="N77" t="s">
-        <v>1195</v>
+        <v>1490</v>
       </c>
       <c r="P77" t="s">
         <v>46</v>
@@ -12253,13 +14188,13 @@
         <v>48</v>
       </c>
       <c r="T77" t="s">
-        <v>1196</v>
+        <v>1491</v>
       </c>
       <c r="U77" t="s">
-        <v>1197</v>
+        <v>1492</v>
       </c>
       <c r="V77" t="s">
-        <v>1198</v>
+        <v>1493</v>
       </c>
       <c r="W77" s="1" t="s">
         <v>52</v>
@@ -12267,13 +14202,13 @@
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1199</v>
+        <v>1494</v>
       </c>
       <c r="B78" t="s">
-        <v>1200</v>
+        <v>1495</v>
       </c>
       <c r="C78" t="s">
-        <v>1201</v>
+        <v>1496</v>
       </c>
       <c r="D78" t="s">
         <v>35</v>
@@ -12288,22 +14223,22 @@
         <v>89</v>
       </c>
       <c r="I78" t="s">
-        <v>1202</v>
+        <v>1497</v>
       </c>
       <c r="J78" t="s">
-        <v>1203</v>
+        <v>1498</v>
       </c>
       <c r="K78" t="s">
-        <v>1204</v>
+        <v>1499</v>
       </c>
       <c r="L78" t="s">
-        <v>1205</v>
+        <v>1500</v>
       </c>
       <c r="M78" t="s">
-        <v>1206</v>
+        <v>1501</v>
       </c>
       <c r="N78" t="s">
-        <v>1207</v>
+        <v>1502</v>
       </c>
       <c r="O78" t="s">
         <v>141</v>
@@ -12318,13 +14253,13 @@
         <v>48</v>
       </c>
       <c r="T78" t="s">
-        <v>1208</v>
+        <v>1503</v>
       </c>
       <c r="U78" t="s">
-        <v>1209</v>
+        <v>1504</v>
       </c>
       <c r="V78" t="s">
-        <v>1210</v>
+        <v>1505</v>
       </c>
       <c r="W78" s="1" t="s">
         <v>52</v>
@@ -12332,13 +14267,13 @@
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1211</v>
+        <v>1506</v>
       </c>
       <c r="B79" t="s">
-        <v>1212</v>
+        <v>1507</v>
       </c>
       <c r="C79" t="s">
-        <v>1213</v>
+        <v>1508</v>
       </c>
       <c r="D79" t="s">
         <v>35</v>
@@ -12353,28 +14288,28 @@
         <v>331</v>
       </c>
       <c r="I79" t="s">
-        <v>1214</v>
+        <v>1509</v>
       </c>
       <c r="J79" t="s">
-        <v>1215</v>
+        <v>1510</v>
       </c>
       <c r="K79" t="s">
-        <v>1216</v>
+        <v>1511</v>
       </c>
       <c r="L79" t="s">
-        <v>1217</v>
+        <v>1512</v>
       </c>
       <c r="M79" t="s">
-        <v>1218</v>
+        <v>1513</v>
       </c>
       <c r="N79" t="s">
-        <v>1219</v>
+        <v>1514</v>
       </c>
       <c r="O79" t="s">
         <v>141</v>
       </c>
       <c r="P79" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q79" t="s">
         <v>47</v>
@@ -12386,13 +14321,13 @@
         <v>167</v>
       </c>
       <c r="T79" t="s">
-        <v>1220</v>
+        <v>1515</v>
       </c>
       <c r="U79" t="s">
-        <v>1221</v>
+        <v>1516</v>
       </c>
       <c r="V79" t="s">
-        <v>1222</v>
+        <v>1517</v>
       </c>
       <c r="W79" s="1" t="s">
         <v>52</v>
@@ -12400,13 +14335,13 @@
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1223</v>
+        <v>1518</v>
       </c>
       <c r="B80" t="s">
-        <v>1224</v>
+        <v>1519</v>
       </c>
       <c r="C80" t="s">
-        <v>1225</v>
+        <v>1520</v>
       </c>
       <c r="D80" t="s">
         <v>35</v>
@@ -12421,22 +14356,22 @@
         <v>500</v>
       </c>
       <c r="I80" t="s">
-        <v>1226</v>
+        <v>1521</v>
       </c>
       <c r="J80" t="s">
-        <v>1227</v>
+        <v>1522</v>
       </c>
       <c r="K80" t="s">
-        <v>1228</v>
+        <v>1523</v>
       </c>
       <c r="L80" t="s">
-        <v>1229</v>
+        <v>1524</v>
       </c>
       <c r="M80" t="s">
-        <v>1230</v>
+        <v>1525</v>
       </c>
       <c r="N80" t="s">
-        <v>1231</v>
+        <v>1526</v>
       </c>
       <c r="P80" t="s">
         <v>46</v>
@@ -12448,13 +14383,13 @@
         <v>48</v>
       </c>
       <c r="T80" t="s">
-        <v>1232</v>
+        <v>1527</v>
       </c>
       <c r="U80" t="s">
-        <v>1233</v>
+        <v>1528</v>
       </c>
       <c r="V80" t="s">
-        <v>1234</v>
+        <v>1529</v>
       </c>
       <c r="W80" s="1" t="s">
         <v>52</v>
@@ -12462,13 +14397,13 @@
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1235</v>
+        <v>1530</v>
       </c>
       <c r="B81" t="s">
-        <v>1236</v>
+        <v>1531</v>
       </c>
       <c r="C81" t="s">
-        <v>1237</v>
+        <v>1532</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
@@ -12483,22 +14418,22 @@
         <v>203</v>
       </c>
       <c r="I81" t="s">
-        <v>1238</v>
+        <v>1533</v>
       </c>
       <c r="J81" t="s">
-        <v>1239</v>
+        <v>1534</v>
       </c>
       <c r="K81" t="s">
-        <v>1240</v>
+        <v>1535</v>
       </c>
       <c r="L81" t="s">
-        <v>1241</v>
+        <v>1536</v>
       </c>
       <c r="M81" t="s">
-        <v>1242</v>
+        <v>1537</v>
       </c>
       <c r="N81" t="s">
-        <v>1243</v>
+        <v>1538</v>
       </c>
       <c r="P81" t="s">
         <v>46</v>
@@ -12510,13 +14445,13 @@
         <v>48</v>
       </c>
       <c r="T81" t="s">
-        <v>1244</v>
+        <v>1539</v>
       </c>
       <c r="U81" t="s">
-        <v>1245</v>
+        <v>1540</v>
       </c>
       <c r="V81" t="s">
-        <v>1246</v>
+        <v>1541</v>
       </c>
       <c r="W81" s="1" t="s">
         <v>52</v>
@@ -12524,13 +14459,13 @@
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1247</v>
+        <v>1542</v>
       </c>
       <c r="B82" t="s">
-        <v>1248</v>
+        <v>1543</v>
       </c>
       <c r="C82" t="s">
-        <v>1249</v>
+        <v>1544</v>
       </c>
       <c r="D82" t="s">
         <v>157</v>
@@ -12545,22 +14480,22 @@
         <v>158</v>
       </c>
       <c r="I82" t="s">
-        <v>1250</v>
+        <v>1545</v>
       </c>
       <c r="J82" t="s">
-        <v>1251</v>
+        <v>1546</v>
       </c>
       <c r="K82" t="s">
-        <v>1252</v>
+        <v>1547</v>
       </c>
       <c r="L82" t="s">
-        <v>1253</v>
+        <v>1548</v>
       </c>
       <c r="M82" t="s">
-        <v>1254</v>
+        <v>1549</v>
       </c>
       <c r="N82" t="s">
-        <v>1255</v>
+        <v>1550</v>
       </c>
       <c r="P82" t="s">
         <v>166</v>
@@ -12575,13 +14510,13 @@
         <v>167</v>
       </c>
       <c r="T82" t="s">
-        <v>1256</v>
+        <v>1551</v>
       </c>
       <c r="U82" t="s">
-        <v>1257</v>
+        <v>1552</v>
       </c>
       <c r="V82" t="s">
-        <v>1258</v>
+        <v>1553</v>
       </c>
       <c r="W82" s="1" t="s">
         <v>52</v>
@@ -12589,13 +14524,13 @@
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1259</v>
+        <v>1554</v>
       </c>
       <c r="B83" t="s">
-        <v>1260</v>
+        <v>1555</v>
       </c>
       <c r="C83" t="s">
-        <v>1261</v>
+        <v>1556</v>
       </c>
       <c r="D83" t="s">
         <v>35</v>
@@ -12610,22 +14545,22 @@
         <v>203</v>
       </c>
       <c r="I83" t="s">
-        <v>1262</v>
+        <v>1557</v>
       </c>
       <c r="J83" t="s">
-        <v>1263</v>
+        <v>1558</v>
       </c>
       <c r="K83" t="s">
-        <v>1264</v>
+        <v>1559</v>
       </c>
       <c r="L83" t="s">
-        <v>1265</v>
+        <v>1560</v>
       </c>
       <c r="M83" t="s">
-        <v>1266</v>
+        <v>1561</v>
       </c>
       <c r="N83" t="s">
-        <v>1267</v>
+        <v>1562</v>
       </c>
       <c r="O83" t="s">
         <v>141</v>
@@ -12640,13 +14575,13 @@
         <v>48</v>
       </c>
       <c r="T83" t="s">
-        <v>1268</v>
+        <v>1563</v>
       </c>
       <c r="U83" t="s">
-        <v>1269</v>
+        <v>1564</v>
       </c>
       <c r="V83" t="s">
-        <v>1270</v>
+        <v>1565</v>
       </c>
       <c r="W83" s="1" t="s">
         <v>52</v>
@@ -12654,13 +14589,13 @@
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1271</v>
+        <v>1566</v>
       </c>
       <c r="B84" t="s">
-        <v>1272</v>
+        <v>1567</v>
       </c>
       <c r="C84" t="s">
-        <v>1273</v>
+        <v>1568</v>
       </c>
       <c r="D84" t="s">
         <v>65</v>
@@ -12675,22 +14610,22 @@
         <v>203</v>
       </c>
       <c r="I84" t="s">
-        <v>1274</v>
+        <v>1569</v>
       </c>
       <c r="J84" t="s">
-        <v>1275</v>
+        <v>1570</v>
       </c>
       <c r="K84" t="s">
-        <v>1276</v>
+        <v>1571</v>
       </c>
       <c r="L84" t="s">
-        <v>1277</v>
+        <v>1572</v>
       </c>
       <c r="M84" t="s">
-        <v>1278</v>
+        <v>1573</v>
       </c>
       <c r="N84" t="s">
-        <v>1279</v>
+        <v>1574</v>
       </c>
       <c r="P84" t="s">
         <v>46</v>
@@ -12702,13 +14637,13 @@
         <v>48</v>
       </c>
       <c r="T84" t="s">
-        <v>1280</v>
+        <v>1575</v>
       </c>
       <c r="U84" t="s">
-        <v>1281</v>
+        <v>1576</v>
       </c>
       <c r="V84" t="s">
-        <v>1282</v>
+        <v>1577</v>
       </c>
       <c r="W84" s="1" t="s">
         <v>52</v>
@@ -12716,13 +14651,13 @@
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1283</v>
+        <v>1578</v>
       </c>
       <c r="B85" t="s">
-        <v>1284</v>
+        <v>1579</v>
       </c>
       <c r="C85" t="s">
-        <v>1285</v>
+        <v>1580</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -12737,22 +14672,22 @@
         <v>331</v>
       </c>
       <c r="I85" t="s">
-        <v>1286</v>
+        <v>1581</v>
       </c>
       <c r="J85" t="s">
-        <v>1287</v>
+        <v>1582</v>
       </c>
       <c r="K85" t="s">
-        <v>1288</v>
+        <v>1583</v>
       </c>
       <c r="L85" t="s">
-        <v>1289</v>
+        <v>1584</v>
       </c>
       <c r="M85" t="s">
-        <v>1290</v>
+        <v>1585</v>
       </c>
       <c r="N85" t="s">
-        <v>1291</v>
+        <v>1586</v>
       </c>
       <c r="P85" t="s">
         <v>46</v>
@@ -12764,13 +14699,13 @@
         <v>48</v>
       </c>
       <c r="T85" t="s">
-        <v>1292</v>
+        <v>1587</v>
       </c>
       <c r="U85" t="s">
-        <v>1293</v>
+        <v>1588</v>
       </c>
       <c r="V85" t="s">
-        <v>1294</v>
+        <v>1589</v>
       </c>
       <c r="W85" s="1" t="s">
         <v>52</v>
@@ -12778,13 +14713,13 @@
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1295</v>
+        <v>1590</v>
       </c>
       <c r="B86" t="s">
-        <v>1296</v>
+        <v>1591</v>
       </c>
       <c r="C86" t="s">
-        <v>1297</v>
+        <v>1592</v>
       </c>
       <c r="D86" t="s">
         <v>65</v>
@@ -12799,22 +14734,22 @@
         <v>500</v>
       </c>
       <c r="I86" t="s">
-        <v>1298</v>
+        <v>1593</v>
       </c>
       <c r="J86" t="s">
-        <v>1299</v>
+        <v>1594</v>
       </c>
       <c r="K86" t="s">
-        <v>1300</v>
+        <v>1595</v>
       </c>
       <c r="L86" t="s">
-        <v>1301</v>
+        <v>1596</v>
       </c>
       <c r="M86" t="s">
-        <v>1302</v>
+        <v>1597</v>
       </c>
       <c r="N86" t="s">
-        <v>1303</v>
+        <v>1598</v>
       </c>
       <c r="P86" t="s">
         <v>46</v>
@@ -12826,13 +14761,13 @@
         <v>48</v>
       </c>
       <c r="T86" t="s">
-        <v>1304</v>
+        <v>1599</v>
       </c>
       <c r="U86" t="s">
-        <v>1305</v>
+        <v>1600</v>
       </c>
       <c r="V86" t="s">
-        <v>1306</v>
+        <v>1601</v>
       </c>
       <c r="W86" s="1" t="s">
         <v>52</v>
@@ -12840,13 +14775,13 @@
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1307</v>
+        <v>1602</v>
       </c>
       <c r="B87" t="s">
-        <v>1308</v>
+        <v>1603</v>
       </c>
       <c r="C87" t="s">
-        <v>1309</v>
+        <v>1604</v>
       </c>
       <c r="D87" t="s">
         <v>35</v>
@@ -12861,22 +14796,22 @@
         <v>89</v>
       </c>
       <c r="I87" t="s">
-        <v>1310</v>
+        <v>1605</v>
       </c>
       <c r="J87" t="s">
-        <v>1311</v>
+        <v>1606</v>
       </c>
       <c r="K87" t="s">
-        <v>1312</v>
+        <v>1607</v>
       </c>
       <c r="L87" t="s">
-        <v>1313</v>
+        <v>1608</v>
       </c>
       <c r="M87" t="s">
-        <v>1314</v>
+        <v>1609</v>
       </c>
       <c r="N87" t="s">
-        <v>1315</v>
+        <v>1610</v>
       </c>
       <c r="O87" t="s">
         <v>141</v>
@@ -12891,13 +14826,13 @@
         <v>48</v>
       </c>
       <c r="T87" t="s">
-        <v>1316</v>
+        <v>1611</v>
       </c>
       <c r="U87" t="s">
-        <v>1317</v>
+        <v>1612</v>
       </c>
       <c r="V87" t="s">
-        <v>1318</v>
+        <v>1613</v>
       </c>
       <c r="W87" s="1" t="s">
         <v>52</v>
@@ -12905,13 +14840,13 @@
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1319</v>
+        <v>1614</v>
       </c>
       <c r="B88" t="s">
-        <v>1320</v>
+        <v>1615</v>
       </c>
       <c r="C88" t="s">
-        <v>1321</v>
+        <v>1616</v>
       </c>
       <c r="D88" t="s">
         <v>157</v>
@@ -12926,22 +14861,22 @@
         <v>158</v>
       </c>
       <c r="I88" t="s">
-        <v>1322</v>
+        <v>1617</v>
       </c>
       <c r="J88" t="s">
-        <v>1323</v>
+        <v>1618</v>
       </c>
       <c r="K88" t="s">
-        <v>1324</v>
+        <v>1619</v>
       </c>
       <c r="L88" t="s">
-        <v>1325</v>
+        <v>1620</v>
       </c>
       <c r="M88" t="s">
-        <v>1326</v>
+        <v>1621</v>
       </c>
       <c r="N88" t="s">
-        <v>1327</v>
+        <v>1622</v>
       </c>
       <c r="P88" t="s">
         <v>166</v>
@@ -12956,13 +14891,13 @@
         <v>167</v>
       </c>
       <c r="T88" t="s">
-        <v>1328</v>
+        <v>1623</v>
       </c>
       <c r="U88" t="s">
-        <v>1329</v>
+        <v>1624</v>
       </c>
       <c r="V88" t="s">
-        <v>1330</v>
+        <v>1625</v>
       </c>
       <c r="W88" s="1" t="s">
         <v>52</v>
@@ -12970,13 +14905,13 @@
     </row>
     <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1331</v>
+        <v>1626</v>
       </c>
       <c r="B89" t="s">
-        <v>1332</v>
+        <v>1627</v>
       </c>
       <c r="C89" t="s">
-        <v>1333</v>
+        <v>1628</v>
       </c>
       <c r="D89" t="s">
         <v>65</v>
@@ -12991,22 +14926,22 @@
         <v>309</v>
       </c>
       <c r="I89" t="s">
-        <v>1334</v>
+        <v>1629</v>
       </c>
       <c r="J89" t="s">
-        <v>1335</v>
+        <v>1630</v>
       </c>
       <c r="K89" t="s">
-        <v>1336</v>
+        <v>1631</v>
       </c>
       <c r="L89" t="s">
-        <v>1337</v>
+        <v>1632</v>
       </c>
       <c r="M89" t="s">
-        <v>1338</v>
+        <v>1633</v>
       </c>
       <c r="N89" t="s">
-        <v>1339</v>
+        <v>1634</v>
       </c>
       <c r="P89" t="s">
         <v>46</v>
@@ -13018,13 +14953,13 @@
         <v>48</v>
       </c>
       <c r="T89" t="s">
-        <v>1340</v>
+        <v>1635</v>
       </c>
       <c r="U89" t="s">
-        <v>1341</v>
+        <v>1636</v>
       </c>
       <c r="V89" t="s">
-        <v>1342</v>
+        <v>1637</v>
       </c>
       <c r="W89" s="1" t="s">
         <v>52</v>
@@ -13032,13 +14967,13 @@
     </row>
     <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1343</v>
+        <v>1638</v>
       </c>
       <c r="B90" t="s">
-        <v>1344</v>
+        <v>1639</v>
       </c>
       <c r="C90" t="s">
-        <v>1345</v>
+        <v>1640</v>
       </c>
       <c r="D90" t="s">
         <v>65</v>
@@ -13053,22 +14988,22 @@
         <v>331</v>
       </c>
       <c r="I90" t="s">
-        <v>1346</v>
+        <v>1641</v>
       </c>
       <c r="J90" t="s">
-        <v>1347</v>
+        <v>1642</v>
       </c>
       <c r="K90" t="s">
-        <v>1348</v>
+        <v>1643</v>
       </c>
       <c r="L90" t="s">
-        <v>1349</v>
+        <v>1644</v>
       </c>
       <c r="M90" t="s">
-        <v>1350</v>
+        <v>1645</v>
       </c>
       <c r="N90" t="s">
-        <v>1351</v>
+        <v>1646</v>
       </c>
       <c r="P90" t="s">
         <v>46</v>
@@ -13080,13 +15015,13 @@
         <v>48</v>
       </c>
       <c r="T90" t="s">
-        <v>1352</v>
+        <v>1647</v>
       </c>
       <c r="U90" t="s">
-        <v>1353</v>
+        <v>1648</v>
       </c>
       <c r="V90" t="s">
-        <v>1354</v>
+        <v>1649</v>
       </c>
       <c r="W90" s="1" t="s">
         <v>52</v>
@@ -13094,13 +15029,13 @@
     </row>
     <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1355</v>
+        <v>1650</v>
       </c>
       <c r="B91" t="s">
-        <v>1356</v>
+        <v>1651</v>
       </c>
       <c r="C91" t="s">
-        <v>1357</v>
+        <v>1652</v>
       </c>
       <c r="D91" t="s">
         <v>65</v>
@@ -13115,22 +15050,22 @@
         <v>500</v>
       </c>
       <c r="I91" t="s">
-        <v>1358</v>
+        <v>1653</v>
       </c>
       <c r="J91" t="s">
-        <v>1359</v>
+        <v>1654</v>
       </c>
       <c r="K91" t="s">
-        <v>1360</v>
+        <v>1655</v>
       </c>
       <c r="L91" t="s">
-        <v>1361</v>
+        <v>1656</v>
       </c>
       <c r="M91" t="s">
-        <v>1362</v>
+        <v>1657</v>
       </c>
       <c r="N91" t="s">
-        <v>1363</v>
+        <v>1658</v>
       </c>
       <c r="P91" t="s">
         <v>46</v>
@@ -13142,13 +15077,13 @@
         <v>48</v>
       </c>
       <c r="T91" t="s">
-        <v>1364</v>
+        <v>1659</v>
       </c>
       <c r="U91" t="s">
-        <v>1365</v>
+        <v>1660</v>
       </c>
       <c r="V91" t="s">
-        <v>1366</v>
+        <v>1661</v>
       </c>
       <c r="W91" s="1" t="s">
         <v>52</v>
@@ -13156,13 +15091,13 @@
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1367</v>
+        <v>1662</v>
       </c>
       <c r="B92" t="s">
-        <v>1368</v>
+        <v>1663</v>
       </c>
       <c r="C92" t="s">
-        <v>1369</v>
+        <v>1664</v>
       </c>
       <c r="D92" t="s">
         <v>157</v>
@@ -13177,22 +15112,22 @@
         <v>158</v>
       </c>
       <c r="I92" t="s">
-        <v>1370</v>
+        <v>1665</v>
       </c>
       <c r="J92" t="s">
-        <v>1371</v>
+        <v>1666</v>
       </c>
       <c r="K92" t="s">
-        <v>1372</v>
+        <v>1667</v>
       </c>
       <c r="L92" t="s">
-        <v>1373</v>
+        <v>1668</v>
       </c>
       <c r="M92" t="s">
-        <v>1374</v>
+        <v>1669</v>
       </c>
       <c r="N92" t="s">
-        <v>1375</v>
+        <v>1670</v>
       </c>
       <c r="P92" t="s">
         <v>166</v>
@@ -13207,13 +15142,13 @@
         <v>167</v>
       </c>
       <c r="T92" t="s">
-        <v>1376</v>
+        <v>1671</v>
       </c>
       <c r="U92" t="s">
-        <v>1377</v>
+        <v>1672</v>
       </c>
       <c r="V92" t="s">
-        <v>1378</v>
+        <v>1673</v>
       </c>
       <c r="W92" s="1" t="s">
         <v>52</v>
@@ -13221,13 +15156,13 @@
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1379</v>
+        <v>1674</v>
       </c>
       <c r="B93" t="s">
-        <v>1380</v>
+        <v>1675</v>
       </c>
       <c r="C93" t="s">
-        <v>1381</v>
+        <v>1676</v>
       </c>
       <c r="D93" t="s">
         <v>35</v>
@@ -13242,28 +15177,28 @@
         <v>500</v>
       </c>
       <c r="I93" t="s">
-        <v>1382</v>
+        <v>1677</v>
       </c>
       <c r="J93" t="s">
-        <v>1383</v>
+        <v>1678</v>
       </c>
       <c r="K93" t="s">
-        <v>1384</v>
+        <v>1679</v>
       </c>
       <c r="L93" t="s">
-        <v>1385</v>
+        <v>1680</v>
       </c>
       <c r="M93" t="s">
-        <v>1386</v>
+        <v>1681</v>
       </c>
       <c r="N93" t="s">
-        <v>1387</v>
+        <v>1682</v>
       </c>
       <c r="O93" t="s">
         <v>141</v>
       </c>
       <c r="P93" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q93" t="s">
         <v>47</v>
@@ -13275,13 +15210,13 @@
         <v>167</v>
       </c>
       <c r="T93" t="s">
-        <v>1388</v>
+        <v>1683</v>
       </c>
       <c r="U93" t="s">
-        <v>1389</v>
+        <v>1684</v>
       </c>
       <c r="V93" t="s">
-        <v>1390</v>
+        <v>1685</v>
       </c>
       <c r="W93" s="1" t="s">
         <v>52</v>
@@ -13289,13 +15224,13 @@
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1391</v>
+        <v>1686</v>
       </c>
       <c r="B94" t="s">
-        <v>1392</v>
+        <v>1687</v>
       </c>
       <c r="C94" t="s">
-        <v>1393</v>
+        <v>1688</v>
       </c>
       <c r="D94" t="s">
         <v>65</v>
@@ -13310,22 +15245,22 @@
         <v>309</v>
       </c>
       <c r="I94" t="s">
-        <v>1394</v>
+        <v>1689</v>
       </c>
       <c r="J94" t="s">
-        <v>1395</v>
+        <v>1690</v>
       </c>
       <c r="K94" t="s">
-        <v>1396</v>
+        <v>1691</v>
       </c>
       <c r="L94" t="s">
-        <v>1397</v>
+        <v>1692</v>
       </c>
       <c r="M94" t="s">
-        <v>1398</v>
+        <v>1693</v>
       </c>
       <c r="N94" t="s">
-        <v>1399</v>
+        <v>1694</v>
       </c>
       <c r="P94" t="s">
         <v>46</v>
@@ -13337,13 +15272,13 @@
         <v>48</v>
       </c>
       <c r="T94" t="s">
-        <v>1400</v>
+        <v>1695</v>
       </c>
       <c r="U94" t="s">
-        <v>1401</v>
+        <v>1696</v>
       </c>
       <c r="V94" t="s">
-        <v>1402</v>
+        <v>1697</v>
       </c>
       <c r="W94" s="1" t="s">
         <v>52</v>
@@ -13351,13 +15286,13 @@
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1403</v>
+        <v>1698</v>
       </c>
       <c r="B95" t="s">
-        <v>1404</v>
+        <v>1699</v>
       </c>
       <c r="C95" t="s">
-        <v>1405</v>
+        <v>1700</v>
       </c>
       <c r="D95" t="s">
         <v>35</v>
@@ -13372,22 +15307,22 @@
         <v>158</v>
       </c>
       <c r="I95" t="s">
-        <v>1406</v>
+        <v>1701</v>
       </c>
       <c r="J95" t="s">
-        <v>1407</v>
+        <v>1702</v>
       </c>
       <c r="K95" t="s">
-        <v>1408</v>
+        <v>1703</v>
       </c>
       <c r="L95" t="s">
-        <v>1409</v>
+        <v>1704</v>
       </c>
       <c r="M95" t="s">
-        <v>1410</v>
+        <v>1705</v>
       </c>
       <c r="N95" t="s">
-        <v>1411</v>
+        <v>1706</v>
       </c>
       <c r="P95" t="s">
         <v>46</v>
@@ -13399,13 +15334,13 @@
         <v>48</v>
       </c>
       <c r="T95" t="s">
-        <v>1412</v>
+        <v>1707</v>
       </c>
       <c r="U95" t="s">
-        <v>1413</v>
+        <v>1708</v>
       </c>
       <c r="V95" t="s">
-        <v>1414</v>
+        <v>1709</v>
       </c>
       <c r="W95" s="1" t="s">
         <v>52</v>
@@ -13413,13 +15348,13 @@
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1415</v>
+        <v>1710</v>
       </c>
       <c r="B96" t="s">
-        <v>1416</v>
+        <v>1711</v>
       </c>
       <c r="C96" t="s">
-        <v>1417</v>
+        <v>1712</v>
       </c>
       <c r="D96" t="s">
         <v>35</v>
@@ -13434,22 +15369,22 @@
         <v>158</v>
       </c>
       <c r="I96" t="s">
-        <v>1418</v>
+        <v>1713</v>
       </c>
       <c r="J96" t="s">
-        <v>1419</v>
+        <v>1714</v>
       </c>
       <c r="K96" t="s">
-        <v>1420</v>
+        <v>1715</v>
       </c>
       <c r="L96" t="s">
-        <v>1421</v>
+        <v>1716</v>
       </c>
       <c r="M96" t="s">
-        <v>1422</v>
+        <v>1717</v>
       </c>
       <c r="N96" t="s">
-        <v>1423</v>
+        <v>1718</v>
       </c>
       <c r="P96" t="s">
         <v>46</v>
@@ -13461,13 +15396,13 @@
         <v>48</v>
       </c>
       <c r="T96" t="s">
-        <v>1424</v>
+        <v>1719</v>
       </c>
       <c r="U96" t="s">
-        <v>1425</v>
+        <v>1720</v>
       </c>
       <c r="V96" t="s">
-        <v>1426</v>
+        <v>1721</v>
       </c>
       <c r="W96" s="1" t="s">
         <v>52</v>
@@ -13475,13 +15410,13 @@
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1427</v>
+        <v>1722</v>
       </c>
       <c r="B97" t="s">
-        <v>1428</v>
+        <v>1723</v>
       </c>
       <c r="C97" t="s">
-        <v>1429</v>
+        <v>1724</v>
       </c>
       <c r="D97" t="s">
         <v>35</v>
@@ -13496,22 +15431,22 @@
         <v>158</v>
       </c>
       <c r="I97" t="s">
-        <v>1430</v>
+        <v>1725</v>
       </c>
       <c r="J97" t="s">
-        <v>1431</v>
+        <v>1726</v>
       </c>
       <c r="K97" t="s">
-        <v>1432</v>
+        <v>1727</v>
       </c>
       <c r="L97" t="s">
-        <v>1433</v>
+        <v>1728</v>
       </c>
       <c r="M97" t="s">
-        <v>1434</v>
+        <v>1729</v>
       </c>
       <c r="N97" t="s">
-        <v>1435</v>
+        <v>1730</v>
       </c>
       <c r="P97" t="s">
         <v>166</v>
@@ -13526,13 +15461,13 @@
         <v>167</v>
       </c>
       <c r="T97" t="s">
-        <v>1436</v>
+        <v>1731</v>
       </c>
       <c r="U97" t="s">
-        <v>1437</v>
+        <v>1732</v>
       </c>
       <c r="V97" t="s">
-        <v>1438</v>
+        <v>1733</v>
       </c>
       <c r="W97" s="1" t="s">
         <v>52</v>
@@ -13540,13 +15475,13 @@
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1439</v>
+        <v>1734</v>
       </c>
       <c r="B98" t="s">
-        <v>1440</v>
+        <v>1735</v>
       </c>
       <c r="C98" t="s">
-        <v>1441</v>
+        <v>1736</v>
       </c>
       <c r="D98" t="s">
         <v>157</v>
@@ -13555,25 +15490,25 @@
         <v>132</v>
       </c>
       <c r="F98" t="s">
-        <v>1140</v>
+        <v>1435</v>
       </c>
       <c r="G98" t="s">
         <v>158</v>
       </c>
       <c r="I98" t="s">
-        <v>1442</v>
+        <v>1737</v>
       </c>
       <c r="J98" t="s">
-        <v>1443</v>
+        <v>1738</v>
       </c>
       <c r="K98" t="s">
-        <v>1444</v>
+        <v>1739</v>
       </c>
       <c r="M98" t="s">
-        <v>1445</v>
+        <v>1740</v>
       </c>
       <c r="N98" t="s">
-        <v>1446</v>
+        <v>1741</v>
       </c>
       <c r="O98" t="s">
         <v>141</v>
@@ -13588,30 +15523,30 @@
         <v>48</v>
       </c>
       <c r="S98" t="s">
-        <v>1146</v>
+        <v>1441</v>
       </c>
       <c r="T98" t="s">
-        <v>1447</v>
+        <v>1742</v>
       </c>
       <c r="U98" t="s">
-        <v>1448</v>
+        <v>1743</v>
       </c>
       <c r="V98" t="s">
-        <v>1449</v>
+        <v>1744</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>1150</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1450</v>
+        <v>1745</v>
       </c>
       <c r="B99" t="s">
-        <v>1451</v>
+        <v>1746</v>
       </c>
       <c r="C99" t="s">
-        <v>1452</v>
+        <v>1747</v>
       </c>
       <c r="D99" t="s">
         <v>35</v>
@@ -13626,22 +15561,22 @@
         <v>89</v>
       </c>
       <c r="I99" t="s">
-        <v>1453</v>
+        <v>1748</v>
       </c>
       <c r="J99" t="s">
-        <v>1454</v>
+        <v>1749</v>
       </c>
       <c r="K99" t="s">
-        <v>1455</v>
+        <v>1750</v>
       </c>
       <c r="L99" t="s">
-        <v>1456</v>
+        <v>1751</v>
       </c>
       <c r="M99" t="s">
-        <v>1457</v>
+        <v>1752</v>
       </c>
       <c r="N99" t="s">
-        <v>1458</v>
+        <v>1753</v>
       </c>
       <c r="O99" t="s">
         <v>141</v>
@@ -13656,13 +15591,13 @@
         <v>48</v>
       </c>
       <c r="T99" t="s">
-        <v>1459</v>
+        <v>1754</v>
       </c>
       <c r="U99" t="s">
-        <v>1460</v>
+        <v>1755</v>
       </c>
       <c r="V99" t="s">
-        <v>1461</v>
+        <v>1756</v>
       </c>
       <c r="W99" s="1" t="s">
         <v>52</v>
@@ -13670,13 +15605,13 @@
     </row>
     <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1462</v>
+        <v>1757</v>
       </c>
       <c r="B100" t="s">
-        <v>1463</v>
+        <v>1758</v>
       </c>
       <c r="C100" t="s">
-        <v>1464</v>
+        <v>1759</v>
       </c>
       <c r="D100" t="s">
         <v>35</v>
@@ -13691,22 +15626,22 @@
         <v>203</v>
       </c>
       <c r="I100" t="s">
-        <v>1465</v>
+        <v>1760</v>
       </c>
       <c r="J100" t="s">
-        <v>1466</v>
+        <v>1761</v>
       </c>
       <c r="K100" t="s">
-        <v>1467</v>
+        <v>1762</v>
       </c>
       <c r="L100" t="s">
-        <v>1468</v>
+        <v>1763</v>
       </c>
       <c r="M100" t="s">
-        <v>1469</v>
+        <v>1764</v>
       </c>
       <c r="N100" t="s">
-        <v>1470</v>
+        <v>1765</v>
       </c>
       <c r="O100" t="s">
         <v>141</v>
@@ -13721,13 +15656,13 @@
         <v>48</v>
       </c>
       <c r="T100" t="s">
-        <v>1471</v>
+        <v>1766</v>
       </c>
       <c r="U100" t="s">
-        <v>1472</v>
+        <v>1767</v>
       </c>
       <c r="V100" t="s">
-        <v>1473</v>
+        <v>1768</v>
       </c>
       <c r="W100" s="1" t="s">
         <v>52</v>
@@ -13735,13 +15670,13 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1474</v>
+        <v>1769</v>
       </c>
       <c r="B101" t="s">
-        <v>1475</v>
+        <v>1770</v>
       </c>
       <c r="C101" t="s">
-        <v>1476</v>
+        <v>1771</v>
       </c>
       <c r="D101" t="s">
         <v>35</v>
@@ -13756,28 +15691,28 @@
         <v>89</v>
       </c>
       <c r="I101" t="s">
-        <v>1477</v>
+        <v>1772</v>
       </c>
       <c r="J101" t="s">
-        <v>1478</v>
+        <v>1773</v>
       </c>
       <c r="K101" t="s">
-        <v>1479</v>
+        <v>1774</v>
       </c>
       <c r="L101" t="s">
-        <v>1480</v>
+        <v>1775</v>
       </c>
       <c r="M101" t="s">
-        <v>1481</v>
+        <v>1776</v>
       </c>
       <c r="N101" t="s">
-        <v>1482</v>
+        <v>1777</v>
       </c>
       <c r="O101" t="s">
         <v>141</v>
       </c>
       <c r="P101" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q101" t="s">
         <v>47</v>
@@ -13789,13 +15724,13 @@
         <v>167</v>
       </c>
       <c r="T101" t="s">
-        <v>1483</v>
+        <v>1778</v>
       </c>
       <c r="U101" t="s">
-        <v>1484</v>
+        <v>1779</v>
       </c>
       <c r="V101" t="s">
-        <v>1485</v>
+        <v>1780</v>
       </c>
       <c r="W101" s="1" t="s">
         <v>52</v>
@@ -13803,13 +15738,13 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1486</v>
+        <v>1781</v>
       </c>
       <c r="B102" t="s">
-        <v>1487</v>
+        <v>1782</v>
       </c>
       <c r="C102" t="s">
-        <v>1488</v>
+        <v>1783</v>
       </c>
       <c r="D102" t="s">
         <v>35</v>
@@ -13824,22 +15759,22 @@
         <v>203</v>
       </c>
       <c r="I102" t="s">
-        <v>1489</v>
+        <v>1784</v>
       </c>
       <c r="J102" t="s">
-        <v>1490</v>
+        <v>1785</v>
       </c>
       <c r="K102" t="s">
-        <v>1491</v>
+        <v>1786</v>
       </c>
       <c r="L102" t="s">
-        <v>1492</v>
+        <v>1787</v>
       </c>
       <c r="M102" t="s">
-        <v>1493</v>
+        <v>1788</v>
       </c>
       <c r="N102" t="s">
-        <v>1494</v>
+        <v>1789</v>
       </c>
       <c r="O102" t="s">
         <v>141</v>
@@ -13854,13 +15789,13 @@
         <v>48</v>
       </c>
       <c r="T102" t="s">
-        <v>1495</v>
+        <v>1790</v>
       </c>
       <c r="U102" t="s">
-        <v>1496</v>
+        <v>1791</v>
       </c>
       <c r="V102" t="s">
-        <v>1497</v>
+        <v>1792</v>
       </c>
       <c r="W102" s="1" t="s">
         <v>52</v>
@@ -13868,13 +15803,13 @@
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1498</v>
+        <v>1793</v>
       </c>
       <c r="B103" t="s">
-        <v>1499</v>
+        <v>1794</v>
       </c>
       <c r="C103" t="s">
-        <v>1500</v>
+        <v>1795</v>
       </c>
       <c r="D103" t="s">
         <v>35</v>
@@ -13889,22 +15824,22 @@
         <v>203</v>
       </c>
       <c r="I103" t="s">
-        <v>1501</v>
+        <v>1796</v>
       </c>
       <c r="J103" t="s">
-        <v>1502</v>
+        <v>1797</v>
       </c>
       <c r="K103" t="s">
-        <v>1503</v>
+        <v>1798</v>
       </c>
       <c r="L103" t="s">
-        <v>1504</v>
+        <v>1799</v>
       </c>
       <c r="M103" t="s">
-        <v>1505</v>
+        <v>1800</v>
       </c>
       <c r="N103" t="s">
-        <v>1506</v>
+        <v>1801</v>
       </c>
       <c r="O103" t="s">
         <v>141</v>
@@ -13919,13 +15854,13 @@
         <v>48</v>
       </c>
       <c r="T103" t="s">
-        <v>1507</v>
+        <v>1802</v>
       </c>
       <c r="U103" t="s">
-        <v>1508</v>
+        <v>1803</v>
       </c>
       <c r="V103" t="s">
-        <v>1509</v>
+        <v>1804</v>
       </c>
       <c r="W103" s="1" t="s">
         <v>52</v>
@@ -13933,13 +15868,13 @@
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1510</v>
+        <v>1805</v>
       </c>
       <c r="B104" t="s">
-        <v>1511</v>
+        <v>1806</v>
       </c>
       <c r="C104" t="s">
-        <v>1512</v>
+        <v>1807</v>
       </c>
       <c r="D104" t="s">
         <v>157</v>
@@ -13954,22 +15889,22 @@
         <v>158</v>
       </c>
       <c r="I104" t="s">
-        <v>1513</v>
+        <v>1808</v>
       </c>
       <c r="J104" t="s">
-        <v>1514</v>
+        <v>1809</v>
       </c>
       <c r="K104" t="s">
-        <v>1515</v>
+        <v>1810</v>
       </c>
       <c r="L104" t="s">
-        <v>1516</v>
+        <v>1811</v>
       </c>
       <c r="M104" t="s">
-        <v>1517</v>
+        <v>1812</v>
       </c>
       <c r="N104" t="s">
-        <v>1518</v>
+        <v>1813</v>
       </c>
       <c r="P104" t="s">
         <v>166</v>
@@ -13984,13 +15919,13 @@
         <v>167</v>
       </c>
       <c r="T104" t="s">
-        <v>1519</v>
+        <v>1814</v>
       </c>
       <c r="U104" t="s">
-        <v>1520</v>
+        <v>1815</v>
       </c>
       <c r="V104" t="s">
-        <v>1521</v>
+        <v>1816</v>
       </c>
       <c r="W104" s="1" t="s">
         <v>52</v>
@@ -13998,13 +15933,13 @@
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1522</v>
+        <v>1817</v>
       </c>
       <c r="B105" t="s">
-        <v>1523</v>
+        <v>1818</v>
       </c>
       <c r="C105" t="s">
-        <v>1524</v>
+        <v>1819</v>
       </c>
       <c r="D105" t="s">
         <v>157</v>
@@ -14019,22 +15954,22 @@
         <v>158</v>
       </c>
       <c r="I105" t="s">
-        <v>1525</v>
+        <v>1820</v>
       </c>
       <c r="J105" t="s">
-        <v>1526</v>
+        <v>1821</v>
       </c>
       <c r="K105" t="s">
-        <v>1527</v>
+        <v>1822</v>
       </c>
       <c r="L105" t="s">
-        <v>1528</v>
+        <v>1823</v>
       </c>
       <c r="M105" t="s">
-        <v>1529</v>
+        <v>1824</v>
       </c>
       <c r="N105" t="s">
-        <v>1530</v>
+        <v>1825</v>
       </c>
       <c r="P105" t="s">
         <v>166</v>
@@ -14049,13 +15984,13 @@
         <v>167</v>
       </c>
       <c r="T105" t="s">
-        <v>1531</v>
+        <v>1826</v>
       </c>
       <c r="U105" t="s">
-        <v>1532</v>
+        <v>1827</v>
       </c>
       <c r="V105" t="s">
-        <v>1533</v>
+        <v>1828</v>
       </c>
       <c r="W105" s="1" t="s">
         <v>52</v>
@@ -14063,13 +15998,13 @@
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1534</v>
+        <v>1829</v>
       </c>
       <c r="B106" t="s">
-        <v>1535</v>
+        <v>1830</v>
       </c>
       <c r="C106" t="s">
-        <v>1536</v>
+        <v>1831</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -14084,22 +16019,22 @@
         <v>203</v>
       </c>
       <c r="I106" t="s">
-        <v>1537</v>
+        <v>1832</v>
       </c>
       <c r="J106" t="s">
-        <v>1538</v>
+        <v>1833</v>
       </c>
       <c r="K106" t="s">
-        <v>1539</v>
+        <v>1834</v>
       </c>
       <c r="L106" t="s">
-        <v>1540</v>
+        <v>1835</v>
       </c>
       <c r="M106" t="s">
-        <v>1541</v>
+        <v>1836</v>
       </c>
       <c r="N106" t="s">
-        <v>1542</v>
+        <v>1837</v>
       </c>
       <c r="P106" t="s">
         <v>46</v>
@@ -14111,13 +16046,13 @@
         <v>48</v>
       </c>
       <c r="T106" t="s">
-        <v>1543</v>
+        <v>1838</v>
       </c>
       <c r="U106" t="s">
-        <v>1544</v>
+        <v>1839</v>
       </c>
       <c r="V106" t="s">
-        <v>1545</v>
+        <v>1840</v>
       </c>
       <c r="W106" s="1" t="s">
         <v>52</v>
@@ -14125,13 +16060,13 @@
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1546</v>
+        <v>1841</v>
       </c>
       <c r="B107" t="s">
-        <v>1547</v>
+        <v>1842</v>
       </c>
       <c r="C107" t="s">
-        <v>1548</v>
+        <v>1843</v>
       </c>
       <c r="D107" t="s">
         <v>35</v>
@@ -14146,22 +16081,22 @@
         <v>158</v>
       </c>
       <c r="I107" t="s">
-        <v>1549</v>
+        <v>1844</v>
       </c>
       <c r="J107" t="s">
-        <v>1550</v>
+        <v>1845</v>
       </c>
       <c r="K107" t="s">
-        <v>1551</v>
+        <v>1846</v>
       </c>
       <c r="L107" t="s">
-        <v>1552</v>
+        <v>1847</v>
       </c>
       <c r="M107" t="s">
-        <v>1553</v>
+        <v>1848</v>
       </c>
       <c r="N107" t="s">
-        <v>1554</v>
+        <v>1849</v>
       </c>
       <c r="P107" t="s">
         <v>46</v>
@@ -14173,13 +16108,13 @@
         <v>48</v>
       </c>
       <c r="T107" t="s">
-        <v>1555</v>
+        <v>1850</v>
       </c>
       <c r="U107" t="s">
-        <v>1556</v>
+        <v>1851</v>
       </c>
       <c r="V107" t="s">
-        <v>1557</v>
+        <v>1852</v>
       </c>
       <c r="W107" s="1" t="s">
         <v>52</v>
@@ -14187,13 +16122,13 @@
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1558</v>
+        <v>1853</v>
       </c>
       <c r="B108" t="s">
-        <v>1559</v>
+        <v>1854</v>
       </c>
       <c r="C108" t="s">
-        <v>1560</v>
+        <v>1855</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
@@ -14208,22 +16143,22 @@
         <v>331</v>
       </c>
       <c r="I108" t="s">
-        <v>1561</v>
+        <v>1856</v>
       </c>
       <c r="J108" t="s">
-        <v>1562</v>
+        <v>1857</v>
       </c>
       <c r="K108" t="s">
-        <v>1563</v>
+        <v>1858</v>
       </c>
       <c r="L108" t="s">
-        <v>1564</v>
+        <v>1859</v>
       </c>
       <c r="M108" t="s">
-        <v>1565</v>
+        <v>1860</v>
       </c>
       <c r="N108" t="s">
-        <v>1566</v>
+        <v>1861</v>
       </c>
       <c r="P108" t="s">
         <v>46</v>
@@ -14235,13 +16170,13 @@
         <v>48</v>
       </c>
       <c r="T108" t="s">
-        <v>1567</v>
+        <v>1862</v>
       </c>
       <c r="U108" t="s">
-        <v>1568</v>
+        <v>1863</v>
       </c>
       <c r="V108" t="s">
-        <v>1569</v>
+        <v>1864</v>
       </c>
       <c r="W108" s="1" t="s">
         <v>52</v>
@@ -14249,13 +16184,13 @@
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1570</v>
+        <v>1865</v>
       </c>
       <c r="B109" t="s">
-        <v>1571</v>
+        <v>1866</v>
       </c>
       <c r="C109" t="s">
-        <v>1572</v>
+        <v>1867</v>
       </c>
       <c r="D109" t="s">
         <v>157</v>
@@ -14270,22 +16205,22 @@
         <v>158</v>
       </c>
       <c r="I109" t="s">
-        <v>1573</v>
+        <v>1868</v>
       </c>
       <c r="J109" t="s">
-        <v>1574</v>
+        <v>1869</v>
       </c>
       <c r="K109" t="s">
-        <v>1575</v>
+        <v>1870</v>
       </c>
       <c r="L109" t="s">
-        <v>1576</v>
+        <v>1871</v>
       </c>
       <c r="M109" t="s">
-        <v>1577</v>
+        <v>1872</v>
       </c>
       <c r="N109" t="s">
-        <v>1578</v>
+        <v>1873</v>
       </c>
       <c r="P109" t="s">
         <v>166</v>
@@ -14300,13 +16235,13 @@
         <v>167</v>
       </c>
       <c r="T109" t="s">
-        <v>1579</v>
+        <v>1874</v>
       </c>
       <c r="U109" t="s">
-        <v>1580</v>
+        <v>1875</v>
       </c>
       <c r="V109" t="s">
-        <v>1581</v>
+        <v>1876</v>
       </c>
       <c r="W109" s="1" t="s">
         <v>52</v>
@@ -14314,13 +16249,13 @@
     </row>
     <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1582</v>
+        <v>1877</v>
       </c>
       <c r="B110" t="s">
-        <v>1583</v>
+        <v>1878</v>
       </c>
       <c r="C110" t="s">
-        <v>1584</v>
+        <v>1879</v>
       </c>
       <c r="D110" t="s">
         <v>157</v>
@@ -14335,22 +16270,22 @@
         <v>158</v>
       </c>
       <c r="I110" t="s">
-        <v>1585</v>
+        <v>1880</v>
       </c>
       <c r="J110" t="s">
-        <v>1586</v>
+        <v>1881</v>
       </c>
       <c r="K110" t="s">
-        <v>1587</v>
+        <v>1882</v>
       </c>
       <c r="L110" t="s">
-        <v>1588</v>
+        <v>1883</v>
       </c>
       <c r="M110" t="s">
-        <v>1589</v>
+        <v>1884</v>
       </c>
       <c r="N110" t="s">
-        <v>1590</v>
+        <v>1885</v>
       </c>
       <c r="P110" t="s">
         <v>166</v>
@@ -14365,13 +16300,13 @@
         <v>167</v>
       </c>
       <c r="T110" t="s">
-        <v>1591</v>
+        <v>1886</v>
       </c>
       <c r="U110" t="s">
-        <v>1592</v>
+        <v>1887</v>
       </c>
       <c r="V110" t="s">
-        <v>1593</v>
+        <v>1888</v>
       </c>
       <c r="W110" s="1" t="s">
         <v>52</v>
@@ -14379,13 +16314,13 @@
     </row>
     <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1594</v>
+        <v>1889</v>
       </c>
       <c r="B111" t="s">
-        <v>1595</v>
+        <v>1890</v>
       </c>
       <c r="C111" t="s">
-        <v>1596</v>
+        <v>1891</v>
       </c>
       <c r="D111" t="s">
         <v>65</v>
@@ -14400,22 +16335,22 @@
         <v>89</v>
       </c>
       <c r="I111" t="s">
-        <v>1597</v>
+        <v>1892</v>
       </c>
       <c r="J111" t="s">
-        <v>1598</v>
+        <v>1893</v>
       </c>
       <c r="K111" t="s">
-        <v>1599</v>
+        <v>1894</v>
       </c>
       <c r="L111" t="s">
-        <v>1600</v>
+        <v>1895</v>
       </c>
       <c r="M111" t="s">
-        <v>1601</v>
+        <v>1896</v>
       </c>
       <c r="N111" t="s">
-        <v>1602</v>
+        <v>1897</v>
       </c>
       <c r="P111" t="s">
         <v>166</v>
@@ -14430,13 +16365,13 @@
         <v>167</v>
       </c>
       <c r="T111" t="s">
-        <v>1603</v>
+        <v>1898</v>
       </c>
       <c r="U111" t="s">
-        <v>1604</v>
+        <v>1899</v>
       </c>
       <c r="V111" t="s">
-        <v>1605</v>
+        <v>1900</v>
       </c>
       <c r="W111" s="1" t="s">
         <v>52</v>
@@ -14444,13 +16379,13 @@
     </row>
     <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1606</v>
+        <v>1901</v>
       </c>
       <c r="B112" t="s">
-        <v>1607</v>
+        <v>1902</v>
       </c>
       <c r="C112" t="s">
-        <v>1608</v>
+        <v>1903</v>
       </c>
       <c r="D112" t="s">
         <v>65</v>
@@ -14465,28 +16400,28 @@
         <v>203</v>
       </c>
       <c r="I112" t="s">
-        <v>1609</v>
+        <v>1904</v>
       </c>
       <c r="J112" t="s">
-        <v>1610</v>
+        <v>1905</v>
       </c>
       <c r="K112" t="s">
-        <v>1611</v>
+        <v>1906</v>
       </c>
       <c r="L112" t="s">
-        <v>1612</v>
+        <v>1907</v>
       </c>
       <c r="M112" t="s">
-        <v>1613</v>
+        <v>1908</v>
       </c>
       <c r="N112" t="s">
-        <v>1614</v>
+        <v>1909</v>
       </c>
       <c r="O112" t="s">
         <v>141</v>
       </c>
       <c r="P112" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q112" t="s">
         <v>47</v>
@@ -14498,13 +16433,13 @@
         <v>167</v>
       </c>
       <c r="T112" t="s">
-        <v>1615</v>
+        <v>1910</v>
       </c>
       <c r="U112" t="s">
-        <v>1616</v>
+        <v>1911</v>
       </c>
       <c r="V112" t="s">
-        <v>1617</v>
+        <v>1912</v>
       </c>
       <c r="W112" s="1" t="s">
         <v>52</v>
@@ -14512,13 +16447,13 @@
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1618</v>
+        <v>1913</v>
       </c>
       <c r="B113" t="s">
-        <v>1619</v>
+        <v>1914</v>
       </c>
       <c r="C113" t="s">
-        <v>1620</v>
+        <v>1915</v>
       </c>
       <c r="D113" t="s">
         <v>65</v>
@@ -14533,28 +16468,28 @@
         <v>203</v>
       </c>
       <c r="I113" t="s">
-        <v>1621</v>
+        <v>1916</v>
       </c>
       <c r="J113" t="s">
-        <v>1622</v>
+        <v>1917</v>
       </c>
       <c r="K113" t="s">
-        <v>1623</v>
+        <v>1918</v>
       </c>
       <c r="L113" t="s">
-        <v>1624</v>
+        <v>1919</v>
       </c>
       <c r="M113" t="s">
-        <v>1625</v>
+        <v>1920</v>
       </c>
       <c r="N113" t="s">
-        <v>1626</v>
+        <v>1921</v>
       </c>
       <c r="O113" t="s">
         <v>141</v>
       </c>
       <c r="P113" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q113" t="s">
         <v>47</v>
@@ -14566,13 +16501,13 @@
         <v>167</v>
       </c>
       <c r="T113" t="s">
-        <v>1627</v>
+        <v>1922</v>
       </c>
       <c r="U113" t="s">
-        <v>1628</v>
+        <v>1923</v>
       </c>
       <c r="V113" t="s">
-        <v>1629</v>
+        <v>1924</v>
       </c>
       <c r="W113" s="1" t="s">
         <v>52</v>
@@ -14580,13 +16515,13 @@
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1630</v>
+        <v>1925</v>
       </c>
       <c r="B114" t="s">
-        <v>1631</v>
+        <v>1926</v>
       </c>
       <c r="C114" t="s">
-        <v>1632</v>
+        <v>1927</v>
       </c>
       <c r="D114" t="s">
         <v>35</v>
@@ -14601,22 +16536,22 @@
         <v>331</v>
       </c>
       <c r="I114" t="s">
-        <v>1633</v>
+        <v>1928</v>
       </c>
       <c r="J114" t="s">
-        <v>1634</v>
+        <v>1929</v>
       </c>
       <c r="K114" t="s">
-        <v>1635</v>
+        <v>1930</v>
       </c>
       <c r="L114" t="s">
-        <v>1636</v>
+        <v>1931</v>
       </c>
       <c r="M114" t="s">
-        <v>1637</v>
+        <v>1932</v>
       </c>
       <c r="N114" t="s">
-        <v>1638</v>
+        <v>1933</v>
       </c>
       <c r="P114" t="s">
         <v>46</v>
@@ -14628,13 +16563,13 @@
         <v>48</v>
       </c>
       <c r="T114" t="s">
-        <v>1639</v>
+        <v>1934</v>
       </c>
       <c r="U114" t="s">
-        <v>1640</v>
+        <v>1935</v>
       </c>
       <c r="V114" t="s">
-        <v>1641</v>
+        <v>1936</v>
       </c>
       <c r="W114" s="1" t="s">
         <v>52</v>
@@ -14642,13 +16577,13 @@
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1642</v>
+        <v>1937</v>
       </c>
       <c r="B115" t="s">
-        <v>1643</v>
+        <v>1938</v>
       </c>
       <c r="C115" t="s">
-        <v>1644</v>
+        <v>1939</v>
       </c>
       <c r="D115" t="s">
         <v>65</v>
@@ -14663,22 +16598,22 @@
         <v>331</v>
       </c>
       <c r="I115" t="s">
-        <v>1645</v>
+        <v>1940</v>
       </c>
       <c r="J115" t="s">
-        <v>1646</v>
+        <v>1941</v>
       </c>
       <c r="K115" t="s">
-        <v>1647</v>
+        <v>1942</v>
       </c>
       <c r="L115" t="s">
-        <v>1648</v>
+        <v>1943</v>
       </c>
       <c r="M115" t="s">
-        <v>1649</v>
+        <v>1944</v>
       </c>
       <c r="N115" t="s">
-        <v>1650</v>
+        <v>1945</v>
       </c>
       <c r="P115" t="s">
         <v>46</v>
@@ -14690,13 +16625,13 @@
         <v>48</v>
       </c>
       <c r="T115" t="s">
-        <v>1651</v>
+        <v>1946</v>
       </c>
       <c r="U115" t="s">
-        <v>1652</v>
+        <v>1947</v>
       </c>
       <c r="V115" t="s">
-        <v>1653</v>
+        <v>1948</v>
       </c>
       <c r="W115" s="1" t="s">
         <v>52</v>
@@ -14704,13 +16639,13 @@
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1654</v>
+        <v>1949</v>
       </c>
       <c r="B116" t="s">
-        <v>1655</v>
+        <v>1950</v>
       </c>
       <c r="C116" t="s">
-        <v>1656</v>
+        <v>1951</v>
       </c>
       <c r="D116" t="s">
         <v>65</v>
@@ -14725,22 +16660,22 @@
         <v>203</v>
       </c>
       <c r="I116" t="s">
-        <v>1657</v>
+        <v>1952</v>
       </c>
       <c r="J116" t="s">
-        <v>1658</v>
+        <v>1953</v>
       </c>
       <c r="K116" t="s">
-        <v>1659</v>
+        <v>1954</v>
       </c>
       <c r="L116" t="s">
-        <v>1660</v>
+        <v>1955</v>
       </c>
       <c r="M116" t="s">
-        <v>1661</v>
+        <v>1956</v>
       </c>
       <c r="N116" t="s">
-        <v>1662</v>
+        <v>1957</v>
       </c>
       <c r="P116" t="s">
         <v>46</v>
@@ -14752,13 +16687,13 @@
         <v>48</v>
       </c>
       <c r="T116" t="s">
-        <v>1663</v>
+        <v>1958</v>
       </c>
       <c r="U116" t="s">
-        <v>1664</v>
+        <v>1959</v>
       </c>
       <c r="V116" t="s">
-        <v>1665</v>
+        <v>1960</v>
       </c>
       <c r="W116" s="1" t="s">
         <v>52</v>
@@ -14766,13 +16701,13 @@
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1666</v>
+        <v>1961</v>
       </c>
       <c r="B117" t="s">
-        <v>1667</v>
+        <v>1962</v>
       </c>
       <c r="C117" t="s">
-        <v>1668</v>
+        <v>1963</v>
       </c>
       <c r="D117" t="s">
         <v>35</v>
@@ -14787,28 +16722,28 @@
         <v>331</v>
       </c>
       <c r="I117" t="s">
-        <v>1669</v>
+        <v>1964</v>
       </c>
       <c r="J117" t="s">
-        <v>1670</v>
+        <v>1965</v>
       </c>
       <c r="K117" t="s">
-        <v>1671</v>
+        <v>1966</v>
       </c>
       <c r="L117" t="s">
-        <v>1672</v>
+        <v>1967</v>
       </c>
       <c r="M117" t="s">
-        <v>1673</v>
+        <v>1968</v>
       </c>
       <c r="N117" t="s">
-        <v>1674</v>
+        <v>1969</v>
       </c>
       <c r="O117" t="s">
         <v>141</v>
       </c>
       <c r="P117" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q117" t="s">
         <v>47</v>
@@ -14820,13 +16755,13 @@
         <v>167</v>
       </c>
       <c r="T117" t="s">
-        <v>1675</v>
+        <v>1970</v>
       </c>
       <c r="U117" t="s">
-        <v>1676</v>
+        <v>1971</v>
       </c>
       <c r="V117" t="s">
-        <v>1677</v>
+        <v>1972</v>
       </c>
       <c r="W117" s="1" t="s">
         <v>52</v>
@@ -14834,13 +16769,13 @@
     </row>
     <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1678</v>
+        <v>1973</v>
       </c>
       <c r="B118" t="s">
-        <v>1679</v>
+        <v>1974</v>
       </c>
       <c r="C118" t="s">
-        <v>1680</v>
+        <v>1975</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -14855,22 +16790,22 @@
         <v>158</v>
       </c>
       <c r="I118" t="s">
-        <v>1681</v>
+        <v>1976</v>
       </c>
       <c r="J118" t="s">
-        <v>1682</v>
+        <v>1977</v>
       </c>
       <c r="K118" t="s">
-        <v>1683</v>
+        <v>1978</v>
       </c>
       <c r="L118" t="s">
-        <v>1684</v>
+        <v>1979</v>
       </c>
       <c r="M118" t="s">
-        <v>1685</v>
+        <v>1980</v>
       </c>
       <c r="N118" t="s">
-        <v>1686</v>
+        <v>1981</v>
       </c>
       <c r="P118" t="s">
         <v>166</v>
@@ -14885,13 +16820,13 @@
         <v>167</v>
       </c>
       <c r="T118" t="s">
-        <v>1687</v>
+        <v>1982</v>
       </c>
       <c r="U118" t="s">
-        <v>1688</v>
+        <v>1983</v>
       </c>
       <c r="V118" t="s">
-        <v>1689</v>
+        <v>1984</v>
       </c>
       <c r="W118" s="1" t="s">
         <v>52</v>
@@ -14899,13 +16834,13 @@
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1690</v>
+        <v>1985</v>
       </c>
       <c r="B119" t="s">
-        <v>1691</v>
+        <v>1986</v>
       </c>
       <c r="C119" t="s">
-        <v>1692</v>
+        <v>1987</v>
       </c>
       <c r="D119" t="s">
         <v>35</v>
@@ -14920,22 +16855,22 @@
         <v>203</v>
       </c>
       <c r="I119" t="s">
-        <v>1693</v>
+        <v>1988</v>
       </c>
       <c r="J119" t="s">
-        <v>1694</v>
+        <v>1989</v>
       </c>
       <c r="K119" t="s">
-        <v>1695</v>
+        <v>1990</v>
       </c>
       <c r="L119" t="s">
-        <v>1696</v>
+        <v>1991</v>
       </c>
       <c r="M119" t="s">
-        <v>1697</v>
+        <v>1992</v>
       </c>
       <c r="N119" t="s">
-        <v>1698</v>
+        <v>1993</v>
       </c>
       <c r="O119" t="s">
         <v>141</v>
@@ -14950,13 +16885,13 @@
         <v>48</v>
       </c>
       <c r="T119" t="s">
-        <v>1699</v>
+        <v>1994</v>
       </c>
       <c r="U119" t="s">
-        <v>1700</v>
+        <v>1995</v>
       </c>
       <c r="V119" t="s">
-        <v>1701</v>
+        <v>1996</v>
       </c>
       <c r="W119" s="1" t="s">
         <v>52</v>
@@ -14964,13 +16899,13 @@
     </row>
     <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1702</v>
+        <v>1997</v>
       </c>
       <c r="B120" t="s">
-        <v>1703</v>
+        <v>1998</v>
       </c>
       <c r="C120" t="s">
-        <v>1704</v>
+        <v>1999</v>
       </c>
       <c r="D120" t="s">
         <v>65</v>
@@ -14985,22 +16920,22 @@
         <v>203</v>
       </c>
       <c r="I120" t="s">
-        <v>1705</v>
+        <v>2000</v>
       </c>
       <c r="J120" t="s">
-        <v>1706</v>
+        <v>2001</v>
       </c>
       <c r="K120" t="s">
-        <v>1707</v>
+        <v>2002</v>
       </c>
       <c r="L120" t="s">
-        <v>1708</v>
+        <v>2003</v>
       </c>
       <c r="M120" t="s">
-        <v>1709</v>
+        <v>2004</v>
       </c>
       <c r="N120" t="s">
-        <v>1710</v>
+        <v>2005</v>
       </c>
       <c r="P120" t="s">
         <v>46</v>
@@ -15012,13 +16947,13 @@
         <v>48</v>
       </c>
       <c r="T120" t="s">
-        <v>1711</v>
+        <v>2006</v>
       </c>
       <c r="U120" t="s">
-        <v>1712</v>
+        <v>2007</v>
       </c>
       <c r="V120" t="s">
-        <v>1713</v>
+        <v>2008</v>
       </c>
       <c r="W120" s="1" t="s">
         <v>52</v>
@@ -15026,13 +16961,13 @@
     </row>
     <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1714</v>
+        <v>2009</v>
       </c>
       <c r="B121" t="s">
-        <v>1715</v>
+        <v>2010</v>
       </c>
       <c r="C121" t="s">
-        <v>1716</v>
+        <v>2011</v>
       </c>
       <c r="D121" t="s">
         <v>35</v>
@@ -15047,22 +16982,22 @@
         <v>89</v>
       </c>
       <c r="I121" t="s">
-        <v>1717</v>
+        <v>2012</v>
       </c>
       <c r="J121" t="s">
-        <v>1718</v>
+        <v>2013</v>
       </c>
       <c r="K121" t="s">
-        <v>1719</v>
+        <v>2014</v>
       </c>
       <c r="L121" t="s">
-        <v>1720</v>
+        <v>2015</v>
       </c>
       <c r="M121" t="s">
-        <v>1721</v>
+        <v>2016</v>
       </c>
       <c r="N121" t="s">
-        <v>1722</v>
+        <v>2017</v>
       </c>
       <c r="O121" t="s">
         <v>141</v>
@@ -15077,13 +17012,13 @@
         <v>48</v>
       </c>
       <c r="T121" t="s">
-        <v>1723</v>
+        <v>2018</v>
       </c>
       <c r="U121" t="s">
-        <v>1724</v>
+        <v>2019</v>
       </c>
       <c r="V121" t="s">
-        <v>1725</v>
+        <v>2020</v>
       </c>
       <c r="W121" s="1" t="s">
         <v>52</v>
@@ -15091,13 +17026,13 @@
     </row>
     <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1726</v>
+        <v>2021</v>
       </c>
       <c r="B122" t="s">
-        <v>1727</v>
+        <v>2022</v>
       </c>
       <c r="C122" t="s">
-        <v>1728</v>
+        <v>2023</v>
       </c>
       <c r="D122" t="s">
         <v>65</v>
@@ -15112,22 +17047,22 @@
         <v>331</v>
       </c>
       <c r="I122" t="s">
-        <v>1729</v>
+        <v>2024</v>
       </c>
       <c r="J122" t="s">
-        <v>1730</v>
+        <v>2025</v>
       </c>
       <c r="K122" t="s">
-        <v>1731</v>
+        <v>2026</v>
       </c>
       <c r="L122" t="s">
-        <v>1732</v>
+        <v>2027</v>
       </c>
       <c r="M122" t="s">
-        <v>1733</v>
+        <v>2028</v>
       </c>
       <c r="N122" t="s">
-        <v>1734</v>
+        <v>2029</v>
       </c>
       <c r="P122" t="s">
         <v>46</v>
@@ -15139,13 +17074,13 @@
         <v>48</v>
       </c>
       <c r="T122" t="s">
-        <v>1735</v>
+        <v>2030</v>
       </c>
       <c r="U122" t="s">
-        <v>1736</v>
+        <v>2031</v>
       </c>
       <c r="V122" t="s">
-        <v>1737</v>
+        <v>2032</v>
       </c>
       <c r="W122" s="1" t="s">
         <v>52</v>
@@ -15153,13 +17088,13 @@
     </row>
     <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1738</v>
+        <v>2033</v>
       </c>
       <c r="B123" t="s">
-        <v>1739</v>
+        <v>2034</v>
       </c>
       <c r="C123" t="s">
-        <v>1740</v>
+        <v>2035</v>
       </c>
       <c r="D123" t="s">
         <v>65</v>
@@ -15174,22 +17109,22 @@
         <v>203</v>
       </c>
       <c r="I123" t="s">
-        <v>1741</v>
+        <v>2036</v>
       </c>
       <c r="J123" t="s">
-        <v>1742</v>
+        <v>2037</v>
       </c>
       <c r="K123" t="s">
-        <v>1743</v>
+        <v>2038</v>
       </c>
       <c r="L123" t="s">
-        <v>1744</v>
+        <v>2039</v>
       </c>
       <c r="M123" t="s">
-        <v>1745</v>
+        <v>2040</v>
       </c>
       <c r="N123" t="s">
-        <v>1746</v>
+        <v>2041</v>
       </c>
       <c r="P123" t="s">
         <v>46</v>
@@ -15201,13 +17136,13 @@
         <v>48</v>
       </c>
       <c r="T123" t="s">
-        <v>1747</v>
+        <v>2042</v>
       </c>
       <c r="U123" t="s">
-        <v>1748</v>
+        <v>2043</v>
       </c>
       <c r="V123" t="s">
-        <v>1749</v>
+        <v>2044</v>
       </c>
       <c r="W123" s="1" t="s">
         <v>52</v>
@@ -15215,13 +17150,13 @@
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>1750</v>
+        <v>2045</v>
       </c>
       <c r="B124" t="s">
-        <v>1751</v>
+        <v>2046</v>
       </c>
       <c r="C124" t="s">
-        <v>1752</v>
+        <v>2047</v>
       </c>
       <c r="D124" t="s">
         <v>65</v>
@@ -15236,22 +17171,22 @@
         <v>331</v>
       </c>
       <c r="I124" t="s">
-        <v>1753</v>
+        <v>2048</v>
       </c>
       <c r="J124" t="s">
-        <v>1754</v>
+        <v>2049</v>
       </c>
       <c r="K124" t="s">
-        <v>1755</v>
+        <v>2050</v>
       </c>
       <c r="L124" t="s">
-        <v>1756</v>
+        <v>2051</v>
       </c>
       <c r="M124" t="s">
-        <v>1757</v>
+        <v>2052</v>
       </c>
       <c r="N124" t="s">
-        <v>1758</v>
+        <v>2053</v>
       </c>
       <c r="P124" t="s">
         <v>46</v>
@@ -15263,13 +17198,13 @@
         <v>48</v>
       </c>
       <c r="T124" t="s">
-        <v>1759</v>
+        <v>2054</v>
       </c>
       <c r="U124" t="s">
-        <v>1760</v>
+        <v>2055</v>
       </c>
       <c r="V124" t="s">
-        <v>1761</v>
+        <v>2056</v>
       </c>
       <c r="W124" s="1" t="s">
         <v>52</v>
@@ -15277,13 +17212,13 @@
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>1762</v>
+        <v>2057</v>
       </c>
       <c r="B125" t="s">
-        <v>1763</v>
+        <v>2058</v>
       </c>
       <c r="C125" t="s">
-        <v>1764</v>
+        <v>2059</v>
       </c>
       <c r="D125" t="s">
         <v>35</v>
@@ -15298,22 +17233,22 @@
         <v>203</v>
       </c>
       <c r="I125" t="s">
-        <v>1765</v>
+        <v>2060</v>
       </c>
       <c r="J125" t="s">
-        <v>1766</v>
+        <v>2061</v>
       </c>
       <c r="K125" t="s">
-        <v>1767</v>
+        <v>2062</v>
       </c>
       <c r="L125" t="s">
-        <v>1768</v>
+        <v>2063</v>
       </c>
       <c r="M125" t="s">
-        <v>1769</v>
+        <v>2064</v>
       </c>
       <c r="N125" t="s">
-        <v>1770</v>
+        <v>2065</v>
       </c>
       <c r="O125" t="s">
         <v>141</v>
@@ -15328,13 +17263,13 @@
         <v>48</v>
       </c>
       <c r="T125" t="s">
-        <v>1771</v>
+        <v>2066</v>
       </c>
       <c r="U125" t="s">
-        <v>1772</v>
+        <v>2067</v>
       </c>
       <c r="V125" t="s">
-        <v>1773</v>
+        <v>2068</v>
       </c>
       <c r="W125" s="1" t="s">
         <v>52</v>
@@ -15342,13 +17277,13 @@
     </row>
     <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1774</v>
+        <v>2069</v>
       </c>
       <c r="B126" t="s">
-        <v>1775</v>
+        <v>2070</v>
       </c>
       <c r="C126" t="s">
-        <v>1776</v>
+        <v>2071</v>
       </c>
       <c r="D126" t="s">
         <v>65</v>
@@ -15363,28 +17298,28 @@
         <v>38</v>
       </c>
       <c r="I126" t="s">
-        <v>1777</v>
+        <v>2072</v>
       </c>
       <c r="J126" t="s">
-        <v>1778</v>
+        <v>2073</v>
       </c>
       <c r="K126" t="s">
-        <v>1779</v>
+        <v>2074</v>
       </c>
       <c r="L126" t="s">
-        <v>1780</v>
+        <v>2075</v>
       </c>
       <c r="M126" t="s">
-        <v>1781</v>
+        <v>2076</v>
       </c>
       <c r="N126" t="s">
-        <v>1782</v>
+        <v>2077</v>
       </c>
       <c r="O126" t="s">
         <v>141</v>
       </c>
       <c r="P126" t="s">
-        <v>651</v>
+        <v>696</v>
       </c>
       <c r="Q126" t="s">
         <v>47</v>
@@ -15396,13 +17331,13 @@
         <v>167</v>
       </c>
       <c r="T126" t="s">
-        <v>1783</v>
+        <v>2078</v>
       </c>
       <c r="U126" t="s">
-        <v>1784</v>
+        <v>2079</v>
       </c>
       <c r="V126" t="s">
-        <v>1785</v>
+        <v>2080</v>
       </c>
       <c r="W126" s="1" t="s">
         <v>52</v>
@@ -15410,13 +17345,13 @@
     </row>
     <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>1786</v>
+        <v>2081</v>
       </c>
       <c r="B127" t="s">
-        <v>1787</v>
+        <v>2082</v>
       </c>
       <c r="C127" t="s">
-        <v>1788</v>
+        <v>2083</v>
       </c>
       <c r="D127" t="s">
         <v>157</v>
@@ -15425,25 +17360,25 @@
         <v>132</v>
       </c>
       <c r="F127" t="s">
-        <v>1140</v>
+        <v>1435</v>
       </c>
       <c r="G127" t="s">
         <v>158</v>
       </c>
       <c r="I127" t="s">
-        <v>1789</v>
+        <v>2084</v>
       </c>
       <c r="J127" t="s">
-        <v>1790</v>
+        <v>2085</v>
       </c>
       <c r="K127" t="s">
-        <v>1791</v>
+        <v>2086</v>
       </c>
       <c r="M127" t="s">
-        <v>1792</v>
+        <v>2087</v>
       </c>
       <c r="N127" t="s">
-        <v>1793</v>
+        <v>2088</v>
       </c>
       <c r="O127" t="s">
         <v>141</v>
@@ -15458,30 +17393,30 @@
         <v>48</v>
       </c>
       <c r="S127" t="s">
-        <v>1146</v>
+        <v>1441</v>
       </c>
       <c r="T127" t="s">
-        <v>1794</v>
+        <v>2089</v>
       </c>
       <c r="U127" t="s">
-        <v>1795</v>
+        <v>2090</v>
       </c>
       <c r="V127" t="s">
-        <v>1796</v>
+        <v>2091</v>
       </c>
       <c r="W127" s="1" t="s">
-        <v>1150</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>1797</v>
+        <v>2092</v>
       </c>
       <c r="B128" t="s">
-        <v>1798</v>
+        <v>2093</v>
       </c>
       <c r="C128" t="s">
-        <v>1799</v>
+        <v>2094</v>
       </c>
       <c r="D128" t="s">
         <v>65</v>
@@ -15496,22 +17431,22 @@
         <v>203</v>
       </c>
       <c r="I128" t="s">
-        <v>1800</v>
+        <v>2095</v>
       </c>
       <c r="J128" t="s">
-        <v>1801</v>
+        <v>2096</v>
       </c>
       <c r="K128" t="s">
-        <v>1802</v>
+        <v>2097</v>
       </c>
       <c r="L128" t="s">
-        <v>1803</v>
+        <v>2098</v>
       </c>
       <c r="M128" t="s">
-        <v>1804</v>
+        <v>2099</v>
       </c>
       <c r="N128" t="s">
-        <v>1805</v>
+        <v>2100</v>
       </c>
       <c r="P128" t="s">
         <v>46</v>
@@ -15523,13 +17458,13 @@
         <v>48</v>
       </c>
       <c r="T128" t="s">
-        <v>1806</v>
+        <v>2101</v>
       </c>
       <c r="U128" t="s">
-        <v>1807</v>
+        <v>2102</v>
       </c>
       <c r="V128" t="s">
-        <v>1808</v>
+        <v>2103</v>
       </c>
       <c r="W128" s="1" t="s">
         <v>52</v>
@@ -15537,13 +17472,13 @@
     </row>
     <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>1809</v>
+        <v>2104</v>
       </c>
       <c r="B129" t="s">
-        <v>1810</v>
+        <v>2105</v>
       </c>
       <c r="C129" t="s">
-        <v>1811</v>
+        <v>2106</v>
       </c>
       <c r="D129" t="s">
         <v>35</v>
@@ -15558,22 +17493,22 @@
         <v>203</v>
       </c>
       <c r="I129" t="s">
-        <v>1812</v>
+        <v>2107</v>
       </c>
       <c r="J129" t="s">
-        <v>1813</v>
+        <v>2108</v>
       </c>
       <c r="K129" t="s">
-        <v>1814</v>
+        <v>2109</v>
       </c>
       <c r="L129" t="s">
-        <v>1815</v>
+        <v>2110</v>
       </c>
       <c r="M129" t="s">
-        <v>1816</v>
+        <v>2111</v>
       </c>
       <c r="N129" t="s">
-        <v>1817</v>
+        <v>2112</v>
       </c>
       <c r="P129" t="s">
         <v>46</v>
@@ -15585,13 +17520,13 @@
         <v>48</v>
       </c>
       <c r="T129" t="s">
-        <v>1818</v>
+        <v>2113</v>
       </c>
       <c r="U129" t="s">
-        <v>1819</v>
+        <v>2114</v>
       </c>
       <c r="V129" t="s">
-        <v>1820</v>
+        <v>2115</v>
       </c>
       <c r="W129" s="1" t="s">
         <v>52</v>

--- a/input/cursos.xlsx
+++ b/input/cursos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3264" uniqueCount="2116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3614" uniqueCount="2406">
   <si>
     <t>course_id</t>
   </si>
@@ -4308,6 +4308,9 @@
     <t>design-de-animacao</t>
   </si>
   <si>
+    <t>Crie animações digitais com modelagem, edição de vídeo, efeitos visuais, roteiros e narrativas para TV, cinema e games.</t>
+  </si>
+  <si>
     <t>O curso de Design de Animação EAD da Cruzeiro do Sul Virtual, prepara os estudantes para atuarem na criação e produção de animações digitais. Ao longo do curso, os alunos desenvolvem habilidades em áreas como modelagem 3D, animação tradicional e digital, edição de vídeo, efeitos visuais, roteiros e narrativas. Com um currículo alinhado às demandas do mercado, o programa combina teoria e prática, utilizando tecnologias avançadas e metodologias que permitem aos estudantes explorar criativamente o universo da animação, com materiais de ensino multimídia e interativos. Ao finalizar os 4 semestres (2 anos), os alunos receberão o diploma de tecnologia em Design de animação, estando aptos para o mercado do segmento.</t>
   </si>
   <si>
@@ -4338,6 +4341,27 @@
     <t>Explore sua criatividade em Design de Animação EAD com flexibilidade e baixo custo. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Pose de marionete e desenho da pose animada</t>
+  </si>
+  <si>
+    <t>Animadora de cerca de 24 anos, mulher de pele morena, cabelo black com topete, camisa oversized lilás e calça jeans, atenção ao braço articulado.</t>
+  </si>
+  <si>
+    <t>Sala escura de animação 2D brasileira, mesa inclinada, caixa de luz, prateleira de bonequinhos, luz pontual, sem papelaria de corte.</t>
+  </si>
+  <si>
+    <t>braço articulado, tablet gráfico, caneta digital, folhas de pose em branco, luminária</t>
+  </si>
+  <si>
+    <t>Ajusta a pose do braço articulado e desenha a pose no tablet, sentada à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; controle de videogame; layout editorial impresso; protótipo de utensílio; câmera de cinema em uso; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação pontual profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Animadora, mulher de pele morena, cerca de 24 anos, cabelo black com topete, camisa lilás, em sala escura de animação 2D, ajustando o braço articulado e desenhando a pose no tablet sobre mesa inclinada. Objetos: braço articulado, tablet gráfico, caneta digital, folhas em branco e luminária. Sem controle de videogame, sem layout impresso, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>publicidade-e-propaganda-ead-bacharelado</t>
   </si>
   <si>
@@ -4345,6 +4369,9 @@
   </si>
   <si>
     <t>publicidade-e-propaganda</t>
+  </si>
+  <si>
+    <t>Elabore campanhas e peças publicitárias, com pesquisa de mercado, mídias tradicionais e digitais e comportamento do consumidor.</t>
   </si>
   <si>
     <t>O curso de Publicidade e Propaganda EAD na Cruzeiro do Sul Virtual prepara os alunos para atuarem na criação, planejamento e execução de campanhas publicitárias. Os estudantes aprendem a desenvolver estratégias de comunicação, utilizar mídias tradicionais e digitais, criar peças publicitárias, realizar pesquisas de mercado e entender o comportamento do consumidor. O curso é contemplado com laboratórios de rádio e TV, estúdio de fotografia e outros equipamentos para que a experiência de aprendizado seja completa, integrando teoria e prática. Com duração de 8 semestres (4 anos) e conceito 4 na classificação do MEC, o curso proporciona uma formação abrangente que prepara os profissionais para o mercado de trabalho.</t>
@@ -4379,6 +4406,30 @@
     <t>Prepare-se para atuar na área de Publicidade e Propaganda a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem de peças de campanha na mesa de luz</t>
+  </si>
+  <si>
+    <t>Diretora de arte de cerca de 27 anos, mulher de pele negra, cabelo crespo com lenço estampado, camisa listrada e calça, atenção às provas.</t>
+  </si>
+  <si>
+    <t>Sala criativa de agência contemporânea brasileira, mesa de luz, prateleira de papéis, janela, espaço organizado e acessível, sem set de filmagem.</t>
+  </si>
+  <si>
+    <t>mesa de luz, provas de peça em branco, lápis, recortes de cor, régua</t>
+  </si>
+  <si>
+    <t>Alinha provas iluminadas na mesa de luz e testa um recorte de cor, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária da mesa de luz, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; câmera em operação; microfone de coletiva; gôndola de varejo; pauta de rádio; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Diretora de arte, mulher de pele negra, cerca de 27 anos, lenço e camisa listrada, em agência, alinhando provas em branco na mesa de luz. Objetos: mesa de luz, provas em branco, lápis, recortes de cor e régua. Sem câmera em uso, sem microfone, sem gôndola, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>producao-audiovisual-ead-tecnologo</t>
   </si>
   <si>
@@ -4386,6 +4437,9 @@
   </si>
   <si>
     <t>producao-audiovisual</t>
+  </si>
+  <si>
+    <t>Dirija a criação audiovisual, da ideia ao produto final, com roteiro, captação, direção e linguagem para cinema, TV e comerciais.</t>
   </si>
   <si>
     <t>O curso de Produção Audiovisual EAD da Universidade Cruzeiro do Sul visa tornar os estudantes aptos para compreenderem todo o processo de criação por trás de conteúdos audiovisuais, desde a criação da ideia até a implementação em produtos finais, como filmes, documentários, comerciais, entre outros. Durante o curso, os alunos estudam disciplinas que envolvem as diversas etapas do processo de produção, fornecendo bases essenciais para a criação de narrativas criativas e interessantes, como Estética e linguagem audiovisual, Narrativa transmídia e storytelling, Roteiro e narrativa, Criação e produção publicitária para Rádio, TV e cinema e Mobile Filmmaking. Com duração de 4 semestres (2 anos), o curso confere a titulação de tecnólogo.</t>
@@ -4423,6 +4477,27 @@
     <t>Estude Produção Audiovisual a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Direção e captação em set audiovisual</t>
+  </si>
+  <si>
+    <t>Diretor audiovisual de cerca de 26 anos, homem de pele morena clara, cabelo crespo curto, camisa preta e calça, fone no pescoço, olho no visor.</t>
+  </si>
+  <si>
+    <t>Set interno contemporâneo brasileiro, fundo neutro, câmera no tripé, boom ao lado, luz de janela, espaço funcional sem estúdio de still.</t>
+  </si>
+  <si>
+    <t>câmera no tripé, claquete, boom, monitor de campo apagado, fita gaffer</t>
+  </si>
+  <si>
+    <t>Olha pelo visor da câmera no tripé e levanta a claquete, em pé à direita do set, dirigindo a captação.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; still de objeto em fundo infinito; câmera compacta pousada sem uso; mesa de pauta multiplataforma; ring light de influenciador; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Diretor audiovisual, homem de pele morena clara, cerca de 26 anos, camisa preta, em set interno, olhando pelo visor e levantando a claquete. Objetos: câmera no tripé, claquete, boom, monitor apagado e fita gaffer. Sem still de produto, sem fundo infinito, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>geografia-licenciatura-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -4430,6 +4505,9 @@
   </si>
   <si>
     <t>geografia-licenciatura</t>
+  </si>
+  <si>
+    <t>Pratique o ensino de geografia no fundamental e no médio, com espaço geográfico, paisagens e metodologias educativas.</t>
   </si>
   <si>
     <t>O curso de Geografia semipresencial da Universidade Cruzeiro do Sul Virtual tem duração de 8 semestres (4 anos). O curso prepara os futuros professores para ensinar Geografia no ensino fundamental e médio, abordando tanto aspectos físicos e humanos da Geografia quanto técnicas pedagógicas modernas. Os estudantes desenvolvem competências para criar estratégias educativas eficazes, utilizando recursos tecnológicos e metodologias inovadoras. Ao concluir, os alunos recebem o título de Licenciado em Geografia, aptos a lecionar e contribuir para a formação de uma sociedade mais consciente e informada sobre questões ambientais, sociais e econômicas.</t>
@@ -4464,6 +4542,27 @@
     <t>Prepare-se para lecionar Geografia a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Aula de relevo e paisagem com mapa tátil</t>
+  </si>
+  <si>
+    <t>Professora de geografia de cerca de 25 anos, mulher de pele negra, cabelo em box braids médias, camisa amarela e calça, apontando o relevo.</t>
+  </si>
+  <si>
+    <t>Sala de aula de educação básica brasileira contemporânea, carteiras, globo, janelas, espaço claro e organizado, sem laboratório de geoprocessamento.</t>
+  </si>
+  <si>
+    <t>globo terrestre, mapa em relevo sem nomes, giz, apagador, bacia de areia</t>
+  </si>
+  <si>
+    <t>Percorre o relevo do mapa com a mão e aponta o globo para a turma, em pé à direita, quadro apagado.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; GPS de campo; monitor de satélite; drone; nomes de cidades no mapa; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de geografia, mulher de pele negra, cerca de 25 anos, camisa amarela, em sala de aula, percorrendo o mapa em relevo sem nomes e apontando o globo. Objetos: globo, mapa em relevo, giz, apagador e bacia de areia. Sem GPS, sem tela de satélite, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciencias-economicas-ead-bacharelado</t>
   </si>
   <si>
@@ -4471,6 +4570,9 @@
   </si>
   <si>
     <t>ciencias-economicas</t>
+  </si>
+  <si>
+    <t>Analise a criação e o consumo de bens e serviços com teorias econômicas, evolução temporal e técnicas quantitativas.</t>
   </si>
   <si>
     <t>O Bacharelado em Ciências Econômicas EAD, com aulas gravadas e transmissões ao vivo tem como objetivo fornecer conhecimento profundos acerca dos processos relacionados à criação e consumo de bens e serviços, concedendo noções que preparam os futuros profissionais para examinar o panorama econômico a partir de três abordagens principais: teorias econômicas, evolução temporal e técnicas quantitativas, com ênfase em cálculos e dados estatísticos. A duração do curso é de 4 semestres (8 semestres).</t>
@@ -4507,6 +4609,27 @@
     <t>Estude Ciências Econômicas a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Análise de curvas e séries econômicas</t>
+  </si>
+  <si>
+    <t>Economista de cerca de 28 anos, homem de pele clara, cabelo curto loiro escuro, camisa azul-clara e óculos retangulares, atenção à lousa.</t>
+  </si>
+  <si>
+    <t>Sala de estudos econômicos em prédio comercial brasileiro, lousa, mesa com impressos, janela, espaço sóbrio e acessível, sem tesouraria.</t>
+  </si>
+  <si>
+    <t>lousa com curvas vazias, tabelas impressas sem números legíveis, régua, caneta, caderno</t>
+  </si>
+  <si>
+    <t>Traça uma curva na lousa e compara com a tabela impressa, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; calculadora financeira como cena principal; livro-razão; gôndola; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Economista, homem de pele clara, cerca de 28 anos, camisa azul-clara, traçando uma curva na lousa e comparando com a tabela impressa. Objetos: lousa com curvas, tabelas sem números legíveis, régua, caneta e caderno. Sem calculadora financeira em destaque, sem livro-razão, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>nutricao-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -4514,6 +4637,9 @@
   </si>
   <si>
     <t>nutricao</t>
+  </si>
+  <si>
+    <t>Oriente a promoção da alimentação e da segurança nutricional, considerando a realidade social de indivíduos e coletividades.</t>
   </si>
   <si>
     <t>O Bacharelado de Nutrição semipresencial da Cruzeiro do Sul Virtual, tem como objetivo capacitar futuros nutricionistas com perspectiva ampla, capacitados para expandir-se em diversos setores com foco na segurança alimentar e nutricional. O curso prepara alunos para atuar na promoção, preservação e reabilitação da saúde de seus pacientes, além de prevenir doenças, agindo de forma a considerar a realidade social, econômica e política de seus pacientes. A duração da graduação é de 8 semestres (4 anos).</t>
@@ -4551,6 +4677,30 @@
     <t>Estude Nutrição a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem de cardápio coletivo com réplicas de alimentos</t>
+  </si>
+  <si>
+    <t>Nutricionista de cerca de 29 anos, mulher de pele negra, cabelo crespo em coque alto, avental listrado sobre camisa, atenção à bandeja.</t>
+  </si>
+  <si>
+    <t>Cozinha de unidade de alimentação coletiva brasileira contemporânea, bancada inox, prateleira de utensílios, iluminação clara, sem consultório clínico.</t>
+  </si>
+  <si>
+    <t>réplicas de alimentos, ficha de cardápio em branco, balança de alimentos, bandeja, caneta</t>
+  </si>
+  <si>
+    <t>Compõe a bandeja com réplicas e anota a combinação na ficha em branco, em pé à direita da bancada, sem examinar paciente.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária de cozinha, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico; cura; tratamento; balança corporal; estetoscópio; spa; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Nutricionista, mulher de pele negra, cerca de 29 anos, avental listrado e coque alto, em cozinha coletiva, compondo a bandeja com réplicas de alimentos e anotando na ficha em branco. Objetos: réplicas, ficha em branco, balança de alimentos, bandeja e caneta. Sem consultório, sem exame clínico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciencias-sociais-ead-licenciatura</t>
   </si>
   <si>
@@ -4558,6 +4708,9 @@
   </si>
   <si>
     <t>ciencias-sociais</t>
+  </si>
+  <si>
+    <t>Estude estruturas, interações e dinâmicas sociais, com teorias sociológicas, antropológicas e políticas aplicadas a questões atuais.</t>
   </si>
   <si>
     <t>A graduação em Ciências Sociais EAD da Cruzeiro do Sul Virtual, tem como base o estudo de comportamentos e práticas humanas, com enfoque nas análises de estruturas, interações e dinâmicas sociais. Ao longo do curso, os estudantes encaram debates e temas relacionados a teorias sociológicas, antropológicas e políticas, com o objetivo de torná-los aptos a refletir e interpretar culturas, relações sociais, e instituições e sua influência nas práticas individuais e coletivas. Ao longo dos 8 semestres (4 anos) de curso, os licenciados em Ciências Sociais são desafiados a avaliar questões atuais e políticas, como desigualdades sociais, globalização, movimentos de protesto e sustentabilidade,o que torna os futuros profissionais aptos a examinar detalhadamente a sociedade e seus processos como um todo.</t>
@@ -4593,6 +4746,27 @@
     <t>Desenvolva-se em Ciências Sociais a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Mediação de debate sobre dinâmicas sociais</t>
+  </si>
+  <si>
+    <t>Professora de ciências sociais de cerca de 32 anos, mulher de pele clara, cabelo pixie castanho, blazer terracota sobre blusa, postura de mediação.</t>
+  </si>
+  <si>
+    <t>Sala de aula com cadeiras em círculo em escola brasileira contemporânea, mural com fotos sem legendas, janela, espaço democrático e organizado.</t>
+  </si>
+  <si>
+    <t>fotos de imprensa sem escritos, livro fechado, giz, cadeiras em círculo, caneta</t>
+  </si>
+  <si>
+    <t>Mostra uma foto sem escritos e conduz o debate em círculo, em pé à direita, sem púlpito.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; palanque; bandeiras; fila de vulnerabilidade; biblioteca interdisciplinar com lupa; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de ciências sociais, mulher de pele clara, cerca de 32 anos, blazer terracota, em sala com cadeiras em círculo, mostrando uma foto sem escritos. Objetos: fotos sem escritos, livro fechado, giz, cadeiras e caneta. Sem palanque, sem bandeiras, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>farmacia-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -4600,6 +4774,9 @@
   </si>
   <si>
     <t>farmacia</t>
+  </si>
+  <si>
+    <t>Formule medicamentos, cosméticos e produtos de higiene, com análise de substâncias e controle de qualidade.</t>
   </si>
   <si>
     <t>O curso de Farmácia semipresencial da Cruzeiro do Sul Virtual visa formar futuros profissionais capazes de se tornarem responsáveis pelo desenvolvimento de medicamentos destinados a restaurar a saúde humana. Durante o curso, os alunos aprendem a pesquisar e formular medicamentos, cosméticos e produtos de higiene pessoal. Além disso, estudará métodos de investigação, análise e testagem de substâncias e ingredientes ativos, observando suas interações no organismo. Com duração de 8 semestres (4 anos) e certificação de bacharelado, a universidade oferece laboratórios educacionais do curso de Farmácia semipresencial, a fim de que o aluno realize análises clínicas e toxicológicas, além de seguir protocolos sanitários e de controle de qualidade para identificar adulterações e falsificações.</t>
@@ -4642,6 +4819,30 @@
     <t>Estude Farmácia a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Manipulação e pesagem de fórmula magistral</t>
+  </si>
+  <si>
+    <t>Farmacêutica de cerca de 31 anos, mulher de pele clara, cabelo castanho preso visível sob a touca, jaleco e óculos de proteção, atenção à balança.</t>
+  </si>
+  <si>
+    <t>Sala de manipulação com armários de madeira e frascos âmbar, pia de inox, azulejo branco, luz de bancada, sem laboratório industrial.</t>
+  </si>
+  <si>
+    <t>gral e pistilo, cápsulas vazias, balança de precisão, espátula, frascos âmbar sem rótulo</t>
+  </si>
+  <si>
+    <t>Pesa o pó na balança e transfere para as cápsulas com a espátula, em pé à direita da bancada.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária clínica, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; microscópio; diagnóstico; cura; atendimento de balcão; pipeta de titulação colorida; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Farmacêutica, mulher de pele clara, cerca de 31 anos, jaleco, touca e óculos de proteção, pesando pó na balança e preenchendo cápsulas em sala com armários de madeira. Objetos: gral, cápsulas vazias, balança de precisão, espátula e frascos âmbar sem rótulo. Sem microscópio, sem balcão de drogaria, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>terapia-ocupacional-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -4649,6 +4850,9 @@
   </si>
   <si>
     <t>terapia-ocupacional</t>
+  </si>
+  <si>
+    <t>Apoie a autonomia em atividades cotidianas, com foco na funcionalidade e na qualidade de vida nas rotinas diárias.</t>
   </si>
   <si>
     <t>O curso de Terapia Ocupacional semipresencial da Cruzeiro do Sul Virtual, capacita profissionais para atuar em diversas áreas da saúde, abrangendo desde a prevenção de doenças até a promoção abrangente da saúde, com foco na funcionalidade humana e na harmonização das interações nos contextos de vida, saúde e social, tanto individualmente quanto em comunidade. Com duração de 8 semestres (4 anos), o curso é voltado para profissionais que buscam ajudar pessoas a superar limitações físicas, emocionais, cognitivas e psicológicas para obter qualidade de vida e oferece a certificação de Bacharelado.</t>
@@ -4685,6 +4889,27 @@
     <t>Aprenda sobre Terapia Ocupacional a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Adaptação de utensílio para atividade cotidiana</t>
+  </si>
+  <si>
+    <t>Terapeuta ocupacional de cerca de 31 anos, mulher de pele morena clara, cabelo ondulado preso, polo clínico e calça, postura de orientação.</t>
+  </si>
+  <si>
+    <t>Cozinha terapêutica simulada em clínica acessível brasileira, bancada baixa, cadeira, janela, espaço digno, sem maca de fisioterapia.</t>
+  </si>
+  <si>
+    <t>tábua com ventosas, utensílio de cabo engrossado, copo com alça, cronômetro de atividade, cadeira</t>
+  </si>
+  <si>
+    <t>Orienta uma pessoa adulta a fatiar fruta com o utensílio adaptado, em pé à direita da bancada, sem alongar articulações.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; maca de fisioterapia; elásticos de reabilitação; diagnóstico; cura; infantilização; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Terapeuta ocupacional, mulher de pele morena clara, cerca de 31 anos, polo clínico, em cozinha simulada, orientando o uso do utensílio de cabo engrossado. Objetos: tábua com ventosas, utensílio adaptado, copo com alça, cronômetro e cadeira. Sem maca, sem elásticos, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>fisica-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -4692,6 +4917,9 @@
   </si>
   <si>
     <t>fisica</t>
+  </si>
+  <si>
+    <t>Investigue fenômenos da física moderna, dinâmica, calor, luz e ondas, com aplicação prática e pesquisa.</t>
   </si>
   <si>
     <t>A graduação de Física da Cruzeiro do Sul Virtual é oferecida na modalidade semipresencial, e contempla os estudos da Física de forma abrangente, desde os conceitos fundamentais até as suas aplicações mais avançadas no campo prático. Ao longo do curso de bacharelado, os estudantes são instigados a investigar áreas como física moderna, dinâmica, calor e temperatura, luz, fenômenos ondulatórios, e ramos especializados como astrofísica.</t>
@@ -4728,6 +4956,30 @@
     <t>Estude Física a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Alinhamento de bancada óptica de pesquisa</t>
+  </si>
+  <si>
+    <t>Pesquisador em física de cerca de 27 anos, homem de pele negra, cabelo curto, jaleco, óculos de proteção, atenção às lentes.</t>
+  </si>
+  <si>
+    <t>Laboratório de pesquisa óptica em instituição brasileira contemporânea, trilho óptico, cortinas, iluminação controlada, sem carteiras escolares.</t>
+  </si>
+  <si>
+    <t>trilho óptico, laser de laboratório desligado, lentes montadas, caderno de medidas, óculos de proteção</t>
+  </si>
+  <si>
+    <t>Alinha uma lente no trilho óptico e anota a posição no caderno, em pé à direita da bancada.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária de laboratório, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; carrinho didático; giz; quadro escolar; experimento de ensino fundamental; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Pesquisador em física, homem de pele negra, cerca de 27 anos, jaleco e óculos de proteção, alinhando uma lente no trilho óptico. Objetos: trilho óptico, laser desligado, lentes, caderno e óculos. Sem carrinhos didáticos, sem quadro escolar, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>educacao-fisica-semipresencial-bacharelado-licenciatura</t>
   </si>
   <si>
@@ -4738,6 +4990,9 @@
   </si>
   <si>
     <t>Bach / Licenc</t>
+  </si>
+  <si>
+    <t>Conduza práticas de atividade física, esporte, lazer e saúde, com planejamento voltado ao bem-estar da população.</t>
   </si>
   <si>
     <t>A Graduação de Educação Física semipresencial da Cruzeiro do Sul Virtual, se dispõe a formar futuros profissionais de alto nível, os tornando aptos a fomentar o equilíbrio físico e mental com práticas sistemáticas de atividades físicas. Ao longo do curso, os estudantes são imersos em conhecimentos referentes à inúmeras áreas da Educação Física, o que abrange práticas de ensino, treinamento esportivo, lazer e saúde, com o objetivo principal de promover o bem-estar físico da população. Através do aprendizado que o curso fornece, em 8 semestres (4 anos), os futuros profissionais recebem instruções e conhecimentos para conduzir e desenvolver o planejamento, organização e execução de múltiplas práticas físicas, como esportes, exercícios de resistência e ginástica, entre outros.</t>
@@ -4784,6 +5039,27 @@
     <t>Estude Educação Física EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Condução de prática física em quadra pública</t>
+  </si>
+  <si>
+    <t>Educadora física de cerca de 28 anos, mulher de pele morena, cabelo preso em rabo alto, camiseta esportiva e shorts, tênis, gesto de demonstração.</t>
+  </si>
+  <si>
+    <t>Quadra poliesportiva pública brasileira ao ar livre, piso pintado, alambrado ao fundo, céu de manhã, grupo misto desfocado, sem sala de aula e sem academia de musculação.</t>
+  </si>
+  <si>
+    <t>cones, bola, cronômetro, apito, colchonetes</t>
+  </si>
+  <si>
+    <t>Demonstra um alongamento no colchonete e indica o próximo cone para o grupo, em pé à direita da quadra.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; sala de aula com giz; aparelhos de musculação; palanque de evento esportivo; pasta de orçamento; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional da manhã. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Educadora física, mulher de pele morena, cerca de 28 anos, camiseta esportiva, em quadra pública, demonstrando alongamento e indicando cones. Objetos: cones, bola, cronômetro, apito e colchonetes. Sem giz, sem academia, sem palanque, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>formacao-pedagogica-filosofia-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -4794,6 +5070,9 @@
   </si>
   <si>
     <t>2 Semestres</t>
+  </si>
+  <si>
+    <t>Prepare-se para a docência em filosofia, com projetos pedagógicos, materiais didáticos e coordenação de ensino.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Formação Pedagógica em Filosofia da Cruzeiro do Sul Virtual está disponível no formato Semipresencial e é destinado especificamente a alunos que já possuem uma graduação prévia. Ao longo da formação, os estudantes mergulharão diversas áreas da filosofia abordando temas como história da filosofia, ética, lógica, filosofia política, estética e entre outros, desenvolvendo uma capacidade analítica, crítica e reflexiva em relação ao mundo contemporâneo. 
@@ -4831,6 +5110,27 @@
     <t>indisponivel</t>
   </si>
   <si>
+    <t>Sequência didática de aula de filosofia</t>
+  </si>
+  <si>
+    <t>Formadora pedagógica de cerca de 34 anos, mulher de pele clara, cabelo castanho em coque baixo, camisa e saia midi, atenção aos cartões de aula.</t>
+  </si>
+  <si>
+    <t>Sala de coordenação pedagógica brasileira contemporânea, mesa, estante, janela, espaço de planejamento, sem seminário acadêmico e sem turma em círculo.</t>
+  </si>
+  <si>
+    <t>cartões de aula em branco, caderno de sequência didática, livros fechados, caneta, pastas</t>
+  </si>
+  <si>
+    <t>Ordena os cartões de aula em uma sequência e confere o caderno pedagógico, sentada à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; púlpito; debate de seminário; giz no quadro de turma; toga; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Formadora pedagógica, mulher de pele clara, cerca de 34 anos, camisa e saia, ordenando cartões de aula em branco e conferindo o caderno de sequência. Objetos: cartões em branco, caderno, livros fechados, caneta e pastas. Sem seminário, sem púlpito, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>pericia-judicial-e-extrajudicial-ead-tecnologo</t>
   </si>
   <si>
@@ -4838,6 +5138,9 @@
   </si>
   <si>
     <t>pericia-judicial-e-extrajudicial</t>
+  </si>
+  <si>
+    <t>Examine evidências técnicas para apoiar decisões jurídicas, com ética, análise de fatos e relatórios periciais.</t>
   </si>
   <si>
     <t>A graduação em Perícia Judicial e Extrajudicial EAD, visa entregar uma formação focada na ética e na constante atualização dos princípios da profissão, essenciais para manter a qualidade e a relevância do ofício, a fim de contribuir para a justiça, assim como a resolução dos casos. Com o compromisso de capacitar futuros profissionais preparados para a atuação como peritos técnicos em diferentes áreas, o curso fornece a expertise necessária para enfrentar os desafios do mercado e contribuir com soluções eficazes e a evolução do ramo.</t>
@@ -4873,6 +5176,27 @@
     <t>Aprenda sobre Perícia Judicial e Extrajudicial a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Medição técnica de vício construtivo para laudo</t>
+  </si>
+  <si>
+    <t>Perito técnico de cerca de 33 anos, homem de pele clara, cabelo curto com entradas, camisa e colete de trabalho, trena na mão.</t>
+  </si>
+  <si>
+    <t>Sala técnica clara em prédio brasileiro, mesa com fotos de fissura, amostra de parede, janela, espaço sóbrio, sem cena de crime e sem cartório.</t>
+  </si>
+  <si>
+    <t>trena, fotos de fissura, nível de bolha, laudo em branco, fragmento de reboco</t>
+  </si>
+  <si>
+    <t>Mede a fissura na foto e confere o nível no fragmento de reboco, em pé à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; fita de isolamento; impressão digital; arma; uniforme policial; laboratório forense teatral; carimbo cartorial; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Perito técnico, homem de pele clara, cerca de 33 anos, colete de trabalho, medindo a fissura na foto e conferindo o nível no fragmento de reboco. Objetos: trena, fotos, nível, laudo em branco e fragmento. Sem fita de isolamento, sem arma, sem carimbo, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>analise-de-dados-de-alta-performance-ead-tecnologo</t>
   </si>
   <si>
@@ -4880,6 +5204,9 @@
   </si>
   <si>
     <t>analise-de-dados-de-alta-performance</t>
+  </si>
+  <si>
+    <t>Extraia leituras de grandes volumes de dados, com mineração, visualização e apoio à decisão em diferentes setores.</t>
   </si>
   <si>
     <t>O curso de Análise de Dados de Alta Performance EAD, prepara profissionais para lidar com grandes volumes de dados complexos, utilizando ferramentas e técnicas avançadas para extrair insights valiosos. Com uma abordagem prática e teórica, o currículo inclui disciplinas como tópicos de big data, análise de dados, mineração de dados, machine learning, inteligência artificial, e visualização de informação. Os alunos desenvolvem habilidades em coleta, armazenamento, análise, revisão, mapeamento e consolidação de dados de diversas áreas do mercado, interpretando resultados, e contribuindo significativamente em áreas como marketing, finanças, saúde, e outras indústrias que dependem de análise de dados para tomada de decisão estratégica. O curso tem duração de 4 semestres (2 anos), certificação de tecnólogo e capacita os graduandos para enfrentar desafios contemporâneos na era da informação.</t>
@@ -4913,6 +5240,30 @@
     <t>Aprenda Big Data Analytics com qualidade e flexibilidade. Vestibular On-line em EAD reconhecida. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Consolidação de painéis e mineração visual</t>
+  </si>
+  <si>
+    <t>Analista de dados de cerca de 27 anos, mulher de pele negra, box braids longas, camisa verde e calça, em pé diante das telas.</t>
+  </si>
+  <si>
+    <t>Sala de visualização em empresa brasileira contemporânea, três monitores com mapas de calor abstratos, persiana, sem lousa de algoritmos.</t>
+  </si>
+  <si>
+    <t>três monitores, mouse, caderno, impressão de painel sem legendas, caneca</t>
+  </si>
+  <si>
+    <t>Compara os mapas de calor nos três monitores e recorta um trecho na impressão, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; treino de modelo preditivo com tablet; cilindros de banco; código fonte; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de dados, mulher de pele negra, cerca de 27 anos, camisa verde, em pé diante de três monitores com mapas de calor abstratos. Objetos: três monitores, mouse, caderno, impressão sem legendas e caneca. Sem tablet de modelo preditivo, sem cilindros de dados, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>marketing-ead-tecnologo</t>
   </si>
   <si>
@@ -4920,6 +5271,9 @@
   </si>
   <si>
     <t>marketing</t>
+  </si>
+  <si>
+    <t>Monte testes de varejo e desenvolvimento de produtos e serviços, com análise de mercado e fidelização de clientes.</t>
   </si>
   <si>
     <t>O curso de Marketing EAD da Cruzeiro do Sul Virtual tem duração de 4 semestres (2 anos) e confere o título de tecnólogo em Marketing. A graduação oferece uma formação abrangente, combinando uma base humanística com uma visão específica da área de marketing e vendas, tendo nota 5 de conceito no MEC. Dentre os conhecimentos abordados, estão temas como marketing de varejo, supply chain, estratégias e definição de preços, sustentabilidade empresarial, e desenvolvimento de produtos e serviços. A metodologia online permite flexibilidade nos estudos, com acesso a videoaulas, materiais interativos e suporte de tutores, preparando os graduados para atuarem em diversas áreas do mercado.</t>
@@ -4955,6 +5309,27 @@
     <t>Aprenda sobre Marketing a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Teste de gôndola e posicionamento de produto no varejo</t>
+  </si>
+  <si>
+    <t>Analista de marketing de cerca de 30 anos, mulher de pele morena, cabelo liso longo, blazer rosa queimado, atenção à gôndola de teste.</t>
+  </si>
+  <si>
+    <t>Sala de teste de varejo em empresa brasileira, gôndola baixa, mesa lateral, janela, espaço contemporâneo acessível, sem agência criativa.</t>
+  </si>
+  <si>
+    <t>gôndola de teste, etiquetas em branco, embalagens genéricas, caderno, caneta</t>
+  </si>
+  <si>
+    <t>Reposiciona embalagens na gôndola e coloca etiquetas em branco, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; mesa de luz de peças publicitárias; câmera; pauta de mídias; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de marketing, mulher de pele morena, cerca de 30 anos, blazer rosa queimado, reposicionando embalagens genéricas na gôndola e colocando etiquetas em branco. Objetos: gôndola, etiquetas em branco, embalagens genéricas, caderno e caneta. Sem mesa de luz, sem câmera, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-de-software-ead-bacharelado</t>
   </si>
   <si>
@@ -4962,6 +5337,9 @@
   </si>
   <si>
     <t>engenharia-de-software</t>
+  </si>
+  <si>
+    <t>Projete e mantenha sistemas de software de forma sistemática, controlada e mensurável, com qualidade e gestão.</t>
   </si>
   <si>
     <t>O curso de Engenharia de Software EAD tem como objetivo capacitar profissionais aptos a desenvolver software de alta qualidade para diversos setores. Prepara os alunos para projetar e manter sistemas de software de forma sistemática, controlada, mensurável e eficaz, abordando questões tecnológicas, éticas, legais e econômicas. O curso tem 8 semestres de duração (4 anos), e confere ao formando o título de bacharel em Engenharia de Software.</t>
@@ -4995,6 +5373,27 @@
     <t>Estude Engenharia de Software a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Arquitetura em camadas de um sistema de software</t>
+  </si>
+  <si>
+    <t>Engenheiro de software de cerca de 29 anos, homem de pele morena, cabelo baixo, polo cinza e calça, de pé diante do quadro.</t>
+  </si>
+  <si>
+    <t>Sala de arquitetura de software em empresa brasileira, quadro branco amplo, mesa, persiana, sem rack e sem flipchart de entidades.</t>
+  </si>
+  <si>
+    <t>quadro branco, canetão, notas adesivas em branco, notebook fechado, copo</t>
+  </si>
+  <si>
+    <t>Desenha camadas empilhadas no quadro e reposiciona uma nota adesiva, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; código na tela; smartphone em teste; flipchart de entidades; kanban de gestão; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheiro de software, homem de pele morena, cerca de 29 anos, polo cinza, desenhando camadas empilhadas no quadro branco. Objetos: quadro, canetão, notas adesivas em branco, notebook fechado e copo. Sem código, sem smartphone, sem flipchart, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>psicopedagogia-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -5002,6 +5401,9 @@
   </si>
   <si>
     <t>psicopedagogia</t>
+  </si>
+  <si>
+    <t>Acompanhe processos de aprendizagem de crianças e adultos, com recursos educativos e apoio ao desenvolvimento cognitivo.</t>
   </si>
   <si>
     <t>O curso de Psicopedagogia semipresencial, com conceito 4 na classificação do MEC, capacita profissionais para avaliar e ajudar crianças e adultos com dificuldades de aprendizagem, utilizando recursos e atividades inovadoras para transformar vidas. Esses profissionais identificam possíveis problemas que crianças e adolescentes enfrentam no ambiente familiar e escolar.O curso proporciona uma formação completa e atualizada, preparando os futuros psicopedagogos para auxiliar nos processos de aprendizagem e promover o desenvolvimento cognitivo e emocional. Com duração de 6 semestres (3 anos) e certificação de bacharelado, os alunos estarão aptos a diagnosticar problemas de aprendizagem, planejar intervenções educativas e promover o bem-estar educacional.</t>
@@ -5035,6 +5437,27 @@
     <t>Desenvolva habilidades em Psicopedagogia a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Mediação de aprendizagem com material concreto</t>
+  </si>
+  <si>
+    <t>Psicopedagoga de cerca de 28 anos, mulher de pele negra, cabelo crespo solto, blusa azul e calça, atenção ao tabuleiro.</t>
+  </si>
+  <si>
+    <t>Sala de apoio pedagógico contemporânea brasileira, mesa baixa, estante de jogos, janela, espaço acolhedor, sem alfabeto móvel de anos iniciais.</t>
+  </si>
+  <si>
+    <t>tangram, relógio de areia, tabuleiro de sequência, lápis, caderno</t>
+  </si>
+  <si>
+    <t>Observa um adolescente montar o tangram e anota a estratégia no caderno, sentada à direita, sem aplicar teste clínico.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico; cura; alfabeto móvel; mesa regulável de inclusão; jaleco clínico; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Psicopedagoga, mulher de pele negra, cerca de 28 anos, blusa azul, observando o tangram e anotando no caderno. Objetos: tangram, relógio de areia, tabuleiro, lápis e caderno. Sem alfabeto móvel, sem jaleco, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciencias-contabeis-ead-bacharelado</t>
   </si>
   <si>
@@ -5042,6 +5465,9 @@
   </si>
   <si>
     <t>ciencias-contabeis</t>
+  </si>
+  <si>
+    <t>Aplique princípios contábeis, auditoria, planejamento tributário e análise de demonstrativos na gestão das empresas.</t>
   </si>
   <si>
     <t>O curso de Ciências Contábeis EAD da Cruzeiro do Sul Virtual promove uma formação pautada na gestão estratégica, atualizada com as transformações na legislação e os desafios da internacionalização, impactando diretamente as empresas no Brasil. O curso oferece uma formação abrangente e flexível para profissionais que desejam se destacar no ramo da contabilidade. Com foco na aplicação prática dos princípios contábeis e nas competências gerenciais, o plano de aulas aborda temas essenciais como auditoria, controle financeiro, planejamento tributário e análise de demonstrativos contábeis. Com duração de 8 semestres (4 anos), o curso oferece a certificação de bacharel em Ciências Contábeis.</t>
@@ -5080,6 +5506,27 @@
     <t>Estude Ciências Contábeis a distância com a mesma qualidade do presencial. Vestibular On-line em EAD reconhecida. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Conferência de livro-razão e pastas fiscais</t>
+  </si>
+  <si>
+    <t>Contador de cerca de 32 anos, homem de pele negra, cabelo curto, camisa branca, óculos, atenção ao carimbo.</t>
+  </si>
+  <si>
+    <t>Escritório contábil contemporâneo brasileiro, mesa com pastas, arquivo, janela, espaço funcional, sem gráficos de investimento.</t>
+  </si>
+  <si>
+    <t>livro-razão fechado, carimbo, pastas fiscais, calculadora simples, caneta</t>
+  </si>
+  <si>
+    <t>Carimba a pasta fiscal e confere o livro-razão fechado, sentado à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; gráfico de linhas de investimento; gôndola; curvas na lousa; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Contador, homem de pele negra, cerca de 32 anos, camisa branca, carimbando a pasta fiscal e conferindo o livro-razão. Objetos: livro-razão, carimbo, pastas fiscais, calculadora simples e caneta. Sem gráficos de investimento, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciencia-politica-ead-bacharelado</t>
   </si>
   <si>
@@ -5087,6 +5534,9 @@
   </si>
   <si>
     <t>ciencia-politica</t>
+  </si>
+  <si>
+    <t>Interprete teorias políticas, sistemas de governo, políticas públicas e relações de poder em diferentes conjunturas.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Ciência Política EAD na Cruzeiro do Sul Virtual forma profissionais capazes de analisar conjunturas, compreender a dinâmica de movimentos sociais e apresentar soluções para problemas do presente ou futuro. Os alunos exploram teorias políticas, sistemas governamentais, políticas públicas e relação de poder no âmbito de diferentes contextos históricos e contemporâneos.
@@ -5123,6 +5573,27 @@
     <t>Aprenda Ciências Políticas a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Estudo de organograma institucional e opinião pública</t>
+  </si>
+  <si>
+    <t>Cientista política de cerca de 26 anos, mulher de pele morena, cabelo cacheado curto, camisa social areia, atenção ao organograma.</t>
+  </si>
+  <si>
+    <t>Sala de pesquisa institucional brasileira, mural, mesa, estante, persiana, espaço sóbrio, sem plenário, sem fila de atendimento e sem palanque.</t>
+  </si>
+  <si>
+    <t>organograma de parede em caixas vazias, livro, fita adesiva, caneta, notebook fechado</t>
+  </si>
+  <si>
+    <t>Fixa caixas vazias no organograma de parede e consulta o livro, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; palanque; campanha; político; bandeiras; tribuna; fita de fila; mapa-múndi; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Cientista política, mulher de pele morena, cerca de 26 anos, camisa areia, em pé fixando caixas vazias no organograma de parede e consultando o livro. Objetos: organograma de parede, livro, fita adesiva, caneta e notebook fechado. Sem palanque, sem bandeiras, sem fila, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>banco-de-dados-ead-tecnologo</t>
   </si>
   <si>
@@ -5130,6 +5601,9 @@
   </si>
   <si>
     <t>banco-de-dados</t>
+  </si>
+  <si>
+    <t>Estruture e preserve bases empresariais, com integridade, desempenho, programação e supervisão das informações.</t>
   </si>
   <si>
     <t>O curso Tecnólogo de Banco de Dados EAD, tem seu aprendizado focado em programação, gerenciamento de informações e sistemas de apoio à tomada de decisão, capacitando os futuros profissionais para o desenvolvimento de sistemas que contenham performance estratégica, indicadores precisos, métodos organizados e dados sistematizados. Além disso, os estudantes são formados e instruídos para implementar, supervisionar, estruturar e garantir a integridade das bases de dados empresariais, capacitando-os para enfrentar desafios práticos e táticos no âmbito da tecnologia da informação.</t>
@@ -5165,6 +5639,30 @@
     <t>Desenvolva sua carreira em Banco de Dados de forma flexível e acessível. Vestibular On-line em EAD líder. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Modelagem física e backup de base de dados</t>
+  </si>
+  <si>
+    <t>Administrador de banco de cerca de 25 anos, homem de pele clara, cabelo ondulado, polo marinho, atenção ao monitor.</t>
+  </si>
+  <si>
+    <t>Sala técnica anexa a servidores em empresa brasileira, um monitor, rack ao fundo desligado, iluminação fria suave, sem reunião com flipchart.</t>
+  </si>
+  <si>
+    <t>monitor com cilindros abstratos, HD externo, caderno de índices, teclado, patch cord</t>
+  </si>
+  <si>
+    <t>Confere os cilindros no monitor e conecta o HD externo para backup, sentado à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentado à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária de sala técnica, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; flipchart de entidades; camadas de arquitetura; mapas de calor; código fonte legível; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Administrador de banco, homem de pele clara, cerca de 25 anos, polo marinho, conferindo cilindros abstratos no monitor e conectando o HD externo. Objetos: monitor, HD externo, caderno, teclado e cabo. Sem flipchart, sem mapa de calor, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>educacao-especial-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -5172,6 +5670,9 @@
   </si>
   <si>
     <t>educacao-especial</t>
+  </si>
+  <si>
+    <t>Promova a inclusão escolar com estratégias pedagógicas acessíveis e compreensão das particularidades do alunado.</t>
   </si>
   <si>
     <t>O curso de Educação Especial semipresencial, visa formar profissionais capacitados para promover a inclusão de alunos com necessidades especiais no ambiente escolar. Durante o curso, os alunos irão adquirir conhecimentos e habilidades essenciais para tornar as escolas mais acessíveis e inclusivas. As disciplinas do curso abordam a compreensão das particularidades da educação especial e a elaboração de estratégias pedagógicas eficientes. Com duração de 8 semestres (4 anos), o curso confere o título de Licenciatura em Educação Especial, explorando temas como Pensamento, linguagem e desenvolvimento humano, Superdotação e altas habilidades, Psicopedagogia aplicada a pessoas com deficiência, entre outras.</t>
@@ -5208,6 +5709,27 @@
     <t>Prepare-se para atuar na Educação Especial EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Preparação de estação escolar acessível</t>
+  </si>
+  <si>
+    <t>Professora de educação especial de cerca de 30 anos, mulher de pele clara, cabelo ruivo curto, camisa e calça, ajustando a mesa.</t>
+  </si>
+  <si>
+    <t>Sala de aula inclusiva contemporânea brasileira, mesa regulável, rampa portátil, janela, espaço digno e organizado, sem berçário.</t>
+  </si>
+  <si>
+    <t>mesa regulável, letras táteis, cartões pictográficos em branco, rampa portátil, caderno</t>
+  </si>
+  <si>
+    <t>Ajusta a altura da mesa regulável e dispõe as letras táteis, em pé à direita, sem expor aluno.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; infantilização; caridade espetacularizada; tangram clínico; alfabeto móvel de anos iniciais; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora, mulher de pele clara, cerca de 30 anos, cabelo ruivo curto, ajustando mesa regulável e dispondo letras táteis em sala inclusiva vazia. Objetos: mesa regulável, letras táteis, cartões em branco, rampa portátil e caderno. Sem infantilização, sem tangram, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-ambiental-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -5215,6 +5737,9 @@
   </si>
   <si>
     <t>engenharia-ambiental</t>
+  </si>
+  <si>
+    <t>Desenvolva projetos de saneamento, controle de poluição e gestão de recursos naturais para equilíbrio ambiental.</t>
   </si>
   <si>
     <t>O curso de Engenharia Ambiental semipresencial da Cruzeiro do Sul Virtual busca formar profissionais comprometidos a entender e solucionar desafios complexos relacionados à preservação do meio ambiente, que tenham habilidades para desenvolver projetos e implementar tecnologias que promovam o equilíbrio entre atividades humanas e a sustentabilidade ambiental, gestão de recursos naturais, controle de poluição e preservação da biodiversidade, tendo disciplinas como Tópicos de ciências exatas; Física geral e experimental; Geologia e pedologia; Direito ambiental e Sustentabilidade e produção limpa. Com duração de 10 semestres (5 anos), o curso fornece o título de bacharel em Engenharia Ambiental.</t>
@@ -5253,6 +5778,30 @@
     <t>Desenvolva soluções sustentáveis em Engenharia Ambiental EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Inspeção de estação de tratamento de água</t>
+  </si>
+  <si>
+    <t>Engenheira ambiental de cerca de 27 anos, mulher de pele negra, cabelo em tranças, capacete branco e colete, atenção à válvula.</t>
+  </si>
+  <si>
+    <t>Passarela de estação de tratamento de água contemporânea brasileira, tanques organizados, céu claro, instalação limpa, sem margem de rio e sem lavoura.</t>
+  </si>
+  <si>
+    <t>capacete, sonda de efluente, prancheta, luvas, volante de válvula</t>
+  </si>
+  <si>
+    <t>Lê a sonda no tanque e anota na prancheta junto à válvula, em pé à direita da passarela.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem à direita em primeiro plano, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; trado de solo; talhão agrícola; frasco de rio urbano; lixo espetacularizado; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheira ambiental, mulher de pele negra, cerca de 27 anos, capacete e colete, na passarela da estação, lendo a sonda no tanque. Objetos: capacete, sonda, prancheta, luvas e válvula. Sem lavoura, sem margem de rio, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-de-producao-industrial-ead-tecnologo</t>
   </si>
   <si>
@@ -5260,6 +5809,9 @@
   </si>
   <si>
     <t>gestao-de-producao-industrial</t>
+  </si>
+  <si>
+    <t>Coordene processos industriais, com gestão estratégica de produção, qualidade, logística industrial e sustentabilidade.</t>
   </si>
   <si>
     <t>O curso de Gestão de Produção Industrial EAD da Cruzeiro do Sul Virtual, com duração de 6 semestres (3 anos) e conceito 4 na classificação do MEC, prepara profissionais para liderar e otimizar processos industriais com eficiência. O programa é focado no desenvolvimento de habilidades essenciais em áreas cruciais como gestão estratégica de produção, controle de qualidade, logística industrial e sustentabilidade. Ao longo do curso, os alunos estudam disciplinas fundamentais como Gestão Estratégica de Negócios, Controle de Qualidade e Logística. Com esse conhecimento abrangente, os graduados estão preparados para enfrentar os desafios complexos do setor industrial e contribuir para o crescimento sustentável das empresas.</t>
@@ -5297,6 +5849,30 @@
     <t>Desenvolva habilidades em Gestão de Produção Industrial a distância EAD com flexibilidade e baixo custo. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Planejamento semanal da produção no mezanino</t>
+  </si>
+  <si>
+    <t>Gestor de produção de cerca de 34 anos, homem de pele morena, cabelo curto, camisa social sem capacete, atenção ao quadro de ímãs.</t>
+  </si>
+  <si>
+    <t>Escritório de mezanino com vista para o chão de fábrica brasileiro, quadro de planejamento, janela industrial, espaço de gestão, sem laboratório de medição.</t>
+  </si>
+  <si>
+    <t>quadro de planejamento, ímãs coloridos, tablet, caneta, fone</t>
+  </si>
+  <si>
+    <t>Move ímãs no quadro semanal e confere o tablet, em pé à direita, fábrica ao fundo desfocada.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária industrial suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; cronômetro de estação; paquímetro; paleteira; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestor de produção, homem de pele morena, cerca de 34 anos, camisa social, movendo ímãs coloridos no quadro de planejamento no mezanino. Objetos: quadro, ímãs, tablet, caneta e fone. Sem capacete, sem cronômetro, sem paquímetro, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>logistica-ead-tecnologo</t>
   </si>
   <si>
@@ -5304,6 +5880,9 @@
   </si>
   <si>
     <t>logistica</t>
+  </si>
+  <si>
+    <t>Organize transporte, armazenagem e distribuição na cadeia de suprimentos, do ponto de origem ao consumo.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Logística EAD na Cruzeiro do Sul Virtual é repleto de inovação e feito com base nas exigências do mercado da área para que os alunos saibam administrar em todas as perspectivas: desde o ponto de origem até o ponto de consumo, os capacitando para a gestão eficiente de operações logísticas, envolvendo planejamento, controle e execução de atividades relacionadas à cadeia de suprimentos, transporte, armazenagem e distribuição de produtos.
@@ -5343,6 +5922,30 @@
     <t>Desenvolva habilidades em Logística a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Movimentação de paletes e conferência de romaneio</t>
+  </si>
+  <si>
+    <t>Supervisor de logística de cerca de 28 anos, homem de pele negra, cabelo raspado, polo e colete refletivo, rádio na mão.</t>
+  </si>
+  <si>
+    <t>Doca de centro de distribuição brasileiro contemporâneo, paletes alinhados, porta de carga aberta, iluminação industrial, espaço organizado, sem sala de mapeamento de processos.</t>
+  </si>
+  <si>
+    <t>paleteira, palete, prancheta de romaneio em branco, rádio, etiquetas em branco</t>
+  </si>
+  <si>
+    <t>Dirige a paleteira até a doca e confere o romaneio na prancheta, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem à direita em primeiro plano, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária industrial, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; papel pardo de fluxograma; ímãs de planejamento; paquímetro; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Supervisor de logística, homem de pele negra, cerca de 28 anos, colete refletivo, conduzindo a paleteira na doca e conferindo o romaneio em branco. Objetos: paleteira, palete, prancheta, rádio e etiquetas em branco. Sem fluxograma, sem ímãs de planejamento, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>servicos-juridicos-e-notariais-ead-tecnologo</t>
   </si>
   <si>
@@ -5350,6 +5953,9 @@
   </si>
   <si>
     <t>servicos-juridicos-e-notariais</t>
+  </si>
+  <si>
+    <t>Registre atos cartorários e rotinas jurídicas, com sistema notarial, trabalhista e estrutura do Judiciário.</t>
   </si>
   <si>
     <t>O curso de Serviços Jurídicos e Notariais EAD visa formar profissionais capacitados para lidar diretamente com questões jurídicas, policiais e cartoriais, tendo duração de 4 semestres (2 anos). Durante o curso, você desenvolverá habilidades em diversas disciplinas essenciais, como Economia, Direito do Consumidor, Sistema Notarial e Registral, Direito Trabalhista e Previdenciário, entre outras. Com um sólido embasamento teórico e prático, o profissional estará preparado para realizar atividades relacionadas à estrutura organizacional do sistema judiciário com excelência, com o título de tecnólogo em Serviços Jurídicos e Notariais.</t>
@@ -5385,6 +5991,27 @@
     <t>Desenvolva habilidades em Serviços Jurídicos e Notariais a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Registro cartorial e autenticação de documentos</t>
+  </si>
+  <si>
+    <t>Agente notarial de cerca de 29 anos, mulher de pele morena, cabelo liso preso, camisa e colete, atenção ao livro de registro.</t>
+  </si>
+  <si>
+    <t>Cartório contemporâneo brasileiro, balcão de atendimento, estante de livros iguais, janela, espaço formal acessível, sem mesa redonda de mediação.</t>
+  </si>
+  <si>
+    <t>livro de registro, carimbo, selo em branco, caneta, documento fechado</t>
+  </si>
+  <si>
+    <t>Carimba o documento fechado e vira a página do livro de registro, em pé à direita do balcão.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; trena de perícia; mesa redonda de acordo; fita de isolamento; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Agente notarial, mulher de pele morena, cerca de 29 anos, colete, carimbando o documento fechado e virando o livro de registro. Objetos: livro de registro, carimbo, selo em branco, caneta e documento fechado. Sem trena, sem mesa redonda, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>biomedicina-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -5392,6 +6019,9 @@
   </si>
   <si>
     <t>biomedicina</t>
+  </si>
+  <si>
+    <t>Realize análises laboratoriais e pesquisa em saúde, com ética e rigor técnico em exames e estudos científicos.</t>
   </si>
   <si>
     <t>O curso de Biomedicina semipresencial da Universidade Cruzeiro do Sul Virtual, visa capacitar profissionais técnico-generalistas altamente qualificados e capazes de atuar em diversas áreas da saúde e da pesquisa científica, fornecendo aulas práticas em laboratórios avançados, e, ao mesmo tempo, formando profissionais com visão humanista, pautada por altos padrões de qualidade e princípios éticos. O biomédico formado na Cruzeiro do sul estará apto a pesquisar, estudar e descobrir como neutralizar as doenças que afetam as pessoas o tempo todo.Com duração de 8 semestres (4 anos), o curso confere o título de bacharel em Biomedicina.</t>
@@ -5436,6 +6066,27 @@
     <t>Estude Biomedicina a distância com qualidade e reconhecimento. Vestibular On-line. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Microscopia e preparo de lâminas laboratoriais</t>
+  </si>
+  <si>
+    <t>Biomédica de cerca de 24 anos, mulher de pele clara, cabelo preto longo preso, jaleco, luvas, olho no microscópio.</t>
+  </si>
+  <si>
+    <t>Laboratório de análises clínicas contemporâneo brasileiro, bancada, microscópio, estante de tubos, iluminação clara, sem farmácia de manipulação.</t>
+  </si>
+  <si>
+    <t>microscópio, lâminas, tubos de amostra, pipeta, caderno</t>
+  </si>
+  <si>
+    <t>Prepara a lâmina e observa no microscópio, em pé à direita da bancada, sem emitir laudo na tela.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico; cura; cápsulas magistrais; equipamento de raios X; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Biomédica, mulher de pele clara, cerca de 24 anos, jaleco, preparando a lâmina e olhando no microscópio. Objetos: microscópio, lâminas, tubos, pipeta e caderno. Sem cápsulas, sem laudo na tela, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>quimica-licenciatura-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -5443,6 +6094,9 @@
   </si>
   <si>
     <t>quimica-licenciatura</t>
+  </si>
+  <si>
+    <t>Ensine química na educação básica, com didática, experimentos e materiais para química geral, orgânica e analítica.</t>
   </si>
   <si>
     <t>O curso de Química semipresencial da Cruzeiro do Sul Virtual prepara profissionais para atuar na educação básica, especialmente no ensino médio, assim como em outras áreas, como laboratórios de pesquisa, empresas de produtos químicos, etc. Com uma grade curricular abrangente, o curso inclui disciplinas de química geral, orgânica, inorgânica, analítica e físico-química, além de matérias pedagógicas e de didática específicas para a formação de professores.Os alunos desenvolvem habilidades para planejar e conduzir atividades de ensino, utilizando metodologias inovadoras e recursos tecnológicos. O curso também promove o desenvolvimento de competências para a realização de pesquisas educacionais e para a elaboração de materiais didáticos, preparando os futuros professores para contribuir de forma significativa na formação de seus alunos. Com duração de 8 semestres (4 anos) e conceito 4 na avaliação do MEC, o curso confere o título de licenciatura em química.</t>
@@ -5481,6 +6135,27 @@
     <t>Prepare-se para lecionar Química a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Aula com modelo molecular e vidraria didática</t>
+  </si>
+  <si>
+    <t>Professora de química de cerca de 32 anos, mulher de pele negra, cabelo black curto, jaleco fechado sobre camisa xadrez, mostrando o modelo.</t>
+  </si>
+  <si>
+    <t>Sala de química do ensino médio brasileira, mesas com kits de modelos, pia ao fundo, quadro de giz, janelas, espaço de aula, sem capela industrial.</t>
+  </si>
+  <si>
+    <t>modelo molecular, béquer vazio, giz, quadro, óculos de proteção</t>
+  </si>
+  <si>
+    <t>Mostra o modelo molecular para a turma e aponta o béquer vazio, em pé à direita, quadro sem escritos.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; pipeta de titulação como ação principal; capela industrial; microscópio clínico; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de química, mulher de pele negra, cerca de 32 anos, jaleco fechado sobre camisa xadrez, mostrando o modelo molecular à turma em sala com kits sobre as mesas. Objetos: modelo molecular, béquer vazio, giz, quadro e óculos. Sem pipetagem, sem capela, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>design-de-interiores-ead-tecnologo</t>
   </si>
   <si>
@@ -5488,6 +6163,9 @@
   </si>
   <si>
     <t>design-de-interiores</t>
+  </si>
+  <si>
+    <t>Combine cores, texturas e mobiliário em projetos residenciais e comerciais, com ergonomia, organização e segurança.</t>
   </si>
   <si>
     <t>O curso de Design de Interiores EAD da Cruzeiro do Sul Virtual busca promover o conhecimento e qualificação para que os formados tenham a expertise de como combinar cores, texturas, mobiliários e itens de decoração para transformar o ambiente de seus clientes. O curso visa ensinar sobre a criação, desenvolvimento e execução de projetos residenciais, comerciais e institucionais, seguindo os critérios de ergonomia, sustentabilidade, organização e segurança. Com 4 semestres (2 anos) de duração e conceito 4 no MEC, o curso confere o título de tecnólogo em Design de Interiores.</t>
@@ -5523,6 +6201,30 @@
     <t>Explore sua criatividade em Design de Interiores EAD com flexibilidade e baixo custo. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Layout de mobiliário e amostras de revestimento no cômodo</t>
+  </si>
+  <si>
+    <t>Designer de interiores de cerca de 31 anos, mulher de pele negra, cabelo crespo em puff alto, camisa e calça, atenção à fita no piso.</t>
+  </si>
+  <si>
+    <t>Sala residencial vazia contemporânea brasileira, piso claro, janela, parede neutra, espaço em obra limpa, sem maquete de edifício e sem bancada de protótipo.</t>
+  </si>
+  <si>
+    <t>fita no piso, amostras de tecido, moodboard sem escritos, luminária de piso, vaso</t>
+  </si>
+  <si>
+    <t>Delimita o contorno do sofá com fita no piso e compara as amostras de tecido, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio-aberto, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural da janela, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; maquete de edifício; protótipo de utensílio; prancha de arquitetura urbana; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Designer de interiores, mulher de pele negra, cerca de 31 anos, puff alto, delimitando o sofá com fita no piso e comparando amostras de tecido. Objetos: fita no piso, amostras, moodboard sem escritos, luminária e vaso. Sem maquete de prédio, sem protótipo industrial, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-desportiva-e-de-lazer-ead-tecnologo</t>
   </si>
   <si>
@@ -5530,6 +6232,9 @@
   </si>
   <si>
     <t>gestao-desportiva-e-de-lazer</t>
+  </si>
+  <si>
+    <t>Administre clubes, eventos esportivos e programas de lazer, com equipes, finanças e sustentabilidade das iniciativas.</t>
   </si>
   <si>
     <t>O curso de Gestão Desportiva e de Lazer EAD da Cruzeiro do Sul Virtual capacita profissionais para elaborar e implementar projetos bem-sucedidos nas áreas de lazer, arte, cultura e desporto. Os estudantes aprendem a gerenciar equipes e recursos humanos, financeiros e tecnológicos de maneira eficaz, desenvolvendo competências para tomar decisões estratégicas que garantam o sucesso e a sustentabilidade dessas iniciativas. O curso tem conceito 4 na classificação do MEC, duração de 4 semestres (2 anos) e confere o título de tecnólogo em Gestão Desportiva e de Lazer.</t>
@@ -5564,6 +6269,27 @@
     <t>Desenvolva habilidades em Gestão Desportiva e de Lazer a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Gestão de operação e cronograma de arena</t>
+  </si>
+  <si>
+    <t>Gestora desportiva de cerca de 33 anos, mulher de pele clara, cabelo castanho liso, blazer e crachá virado, atenção ao cronograma.</t>
+  </si>
+  <si>
+    <t>Sala administrativa com vista para quadra coberta brasileira, mesa, mural vazio, janela para o ginásio, espaço de gestão, sem demonstração de exercício.</t>
+  </si>
+  <si>
+    <t>cronograma em branco, pasta de custos, rádios, crachás em branco, planta da arena</t>
+  </si>
+  <si>
+    <t>Alinha os rádios na mesa e cruza o cronograma com a planta, em pé à direita, quadra ao fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; alongamento; cones de treino; apito em uso; palanque; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora desportiva, mulher de pele clara, cerca de 33 anos, blazer, alinhando rádios e conferindo cronograma em branco com a planta da arena. Objetos: cronograma em branco, pasta, rádios, crachás e planta. Sem alongamento, sem cones, sem apito, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>conciliacao-mediacao-e-arbitragem-ead-tecnologo</t>
   </si>
   <si>
@@ -5571,6 +6297,9 @@
   </si>
   <si>
     <t>conciliacao-mediacao-e-arbitragem</t>
+  </si>
+  <si>
+    <t>Facilite acordos por conciliação, mediação e arbitragem, reduzindo litígios em disputas empresariais e de consumo.</t>
   </si>
   <si>
     <t>O curso de Conciliação, Mediação e Arbitragem EAD da Cruzeiro do Sul Virtual, com duração de 4 semestres (2 anos), confere o título de Tecnólogo e possui conceito 4 na classificação do MEC. Este curso oferece uma sólida formação em métodos alternativos de resolução de conflitos, proporcionando diferenciais formativos que capacitam os alunos a atuar com sucesso no mercado de trabalho. O conteúdo abrange as competências necessárias para mediar, arbitrar e conciliar disputas, preparando os estudantes para enfrentar desafios em diversas áreas de atuação.</t>
@@ -5606,6 +6335,27 @@
     <t>Prepare-se para atuar em Conciliação, Mediação e Arbitragem a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Preparação de mesa igualitária de mediação</t>
+  </si>
+  <si>
+    <t>Mediador de cerca de 35 anos, homem de pele morena, cabelo curto com fios grisalhos, camisa sem gravata, postura de acolhimento.</t>
+  </si>
+  <si>
+    <t>Sala de mediação contemporânea brasileira, mesa redonda, três cadeiras iguais, planta, janela, espaço neutro, sem balcão de cartório e sem tribuna.</t>
+  </si>
+  <si>
+    <t>mesa redonda, jarra de água, dois blocos iguais, duas canetas, relógio de mesa</t>
+  </si>
+  <si>
+    <t>Alinha os dois blocos iguais e a jarra no centro da mesa, sentado à direita, sem martelo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; martelo de juiz; carimbo; trena; fita de isolamento; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Mediador, homem de pele morena, cerca de 35 anos, camisa sem gravata, alinhando dois blocos iguais e a jarra no centro da mesa redonda. Objetos: mesa redonda, jarra, dois blocos, duas canetas e relógio. Sem martelo, sem carimbo, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>filosofia-licenciatura-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -5613,6 +6363,9 @@
   </si>
   <si>
     <t>filosofia-licenciatura</t>
+  </si>
+  <si>
+    <t>Debata ética, lógica e filosofia política em sala, formando reflexão crítica para o ensino na educação básica.</t>
   </si>
   <si>
     <t>O curso de Filosofia semipresencial da Cruzeiro do Sul promove uma reflexão profunda e rigorosa sobre ética, lógica, metafísica e outras áreas essenciais da Filosofia. Com conceito 4 no MEC, oferece uma sólida formação abrangendo diversas disciplinas filosóficas, incluindo ética, lógica e filosofia política.Na modalidade semipresencial, os alunos têm a flexibilidade de estudar com material didático de qualidade, videoaulas, fóruns de discussão e suporte online dos tutores. Ao longo dos 8 semestres, os estudantes desenvolvem habilidades de análise crítica, reflexão teórica e contribuições intelectuais significativas em diversas áreas do conhecimento e da sociedade, o que os deixará aptos à profissão de um licenciado em Filosofia.</t>
@@ -5649,6 +6402,27 @@
     <t>Prepare-se para lecionar Filosofia a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Roda de discussão filosófica no ensino básico</t>
+  </si>
+  <si>
+    <t>Professora de filosofia de cerca de 25 anos, mulher de pele negra, cabelo trançado médio, camisa branca e calça, em pé no círculo.</t>
+  </si>
+  <si>
+    <t>Sala de ensino médio brasileira contemporânea, cadeiras em círculo, quadro apagado, janelas, espaço claro, sem mesa de seminário acadêmico.</t>
+  </si>
+  <si>
+    <t>cartões de pergunta em branco, giz, livros fechados, apagador, cadeiras em círculo</t>
+  </si>
+  <si>
+    <t>Distribui cartões em branco no círculo e inicia o debate, em pé à direita, quadro sem escritos.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; mesa comprida de seminário; cartões de sequência didática de coordenação; púlpito; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de filosofia, mulher de pele negra, cerca de 25 anos, camisa branca, distribuindo cartões em branco na roda de cadeiras. Objetos: cartões em branco, giz, livros fechados, apagador e cadeiras. Sem mesa de seminário, sem púlpito, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>relacoes-internacionais-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -5656,6 +6430,9 @@
   </si>
   <si>
     <t>relacoes-internacionais</t>
+  </si>
+  <si>
+    <t>Negocie dinâmicas políticas, econômicas e culturais entre países e organizações, com direito internacional e cenários globais.</t>
   </si>
   <si>
     <t>O curso de Relações Internacionais EAD da Cruzeiro do Sul Virtual tem duração de 6 semestres (3 anos) e confere o título de bacharel em Relações Internacionais. Este curso oferece uma formação abrangente e atualizada, preparando os alunos para entender e analisar as dinâmicas políticas, econômicas, sociais e culturais entre países e organizações internacionais. Com disponibilidade das modalidades com aulas gravadas e aulas ao vivo, os estudantes têm flexibilidade para acompanhar as disciplinas de acordo com sua disponibilidade. O currículo inclui estudos sobre direito internacional, economia global, segurança internacional, políticas internacionais, entre outros temas relevantes para a atuação profissional em um mundo cada vez mais globalizado.</t>
@@ -5692,6 +6469,27 @@
     <t>Estude Relações Internacionais a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Análise de cenário internacional em mapa-múndi</t>
+  </si>
+  <si>
+    <t>Analista internacional de cerca de 30 anos, homem de pele clara, cabelo curto, camisa e pulôver, alfinete na mão.</t>
+  </si>
+  <si>
+    <t>Escritório funcional de análise internacional no Brasil, mapa-múndi sem nomes, mesa, janela, espaço sóbrio, sem embaixada de luxo e sem fileira de bandeiras.</t>
+  </si>
+  <si>
+    <t>mapa-múndi sem nomes, dossiês fechados, alfinetes, caneta, notebook fechado</t>
+  </si>
+  <si>
+    <t>Fixa um alfinete no mapa-múndi e cruza com o dossiê fechado, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; bandeiras em excesso; palanque; organograma de governo local; contêineres; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista internacional, homem de pele clara, cerca de 30 anos, pulôver, fixando um alfinete no mapa-múndi sem nomes. Objetos: mapa-múndi, dossiês fechados, alfinetes, caneta e notebook fechado. Sem fileira de bandeiras, sem palanque, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>design-grafico-ead-tecnologo</t>
   </si>
   <si>
@@ -5699,6 +6497,9 @@
   </si>
   <si>
     <t>design-grafico</t>
+  </si>
+  <si>
+    <t>Componha layouts, ilustrações e materiais gráficos com tipografia, cor, composição e princípios de design.</t>
   </si>
   <si>
     <t>O curso de Design Gráfico EAD da Cruzeiro do Sul Virtual prepara os alunos para dominarem habilidades na criação visual, combinando arte e tecnologia. Os estudantes aprendem a desenvolver layouts, logos, ilustrações e diversos materiais gráficos. Com duração de 4 semestres (2 anos), e conceito de avaliação 5 no MEC, o curso está disponível nas modalidades com aulas gravadas e aulas ao vivo. Os alunos exploram princípios de design, tipografia, cores e composição, preparando-se para carreiras em agências de publicidade, editoras, estúdios de design, como profissionais autônomos no mercado criativo, entre outros.</t>
@@ -5735,6 +6536,27 @@
     <t>Aprenda Design Gráfico EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Corte e diagramação de prova gráfica</t>
+  </si>
+  <si>
+    <t>Designer gráfica de cerca de 23 anos, mulher de pele morena clara, cabelo curto ondulado, camisa estampada, atenção ao tapete de corte.</t>
+  </si>
+  <si>
+    <t>Oficina de produção gráfica contemporânea brasileira, mesa de corte, pilhas de papel, prensa de prova ao fundo, janela, espaço de impressão.</t>
+  </si>
+  <si>
+    <t>tapete de corte, provas de página em branco, tesoura, guia de cor, peso de papel</t>
+  </si>
+  <si>
+    <t>Recorta a prova no tapete e alinha a página no grid, em pé à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; braço articulado; gôndola; mesa de luz de campanha; protótipo de produto; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Designer gráfica, mulher de pele morena clara, cerca de 23 anos, camisa estampada, recortando prova em branco no tapete de corte em oficina com prensa ao fundo. Objetos: tapete de corte, provas em branco, tesoura, guia de cor e peso de papel. Sem braço articulado, sem gôndola, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>interdisciplinar-em-humanidades-ead-bacharelado</t>
   </si>
   <si>
@@ -5742,6 +6564,9 @@
   </si>
   <si>
     <t>interdisciplinar-em-humanidades</t>
+  </si>
+  <si>
+    <t>Integre saberes humanísticos, artísticos e científicos para atuar em pesquisa, cultura e organizações sociais.</t>
   </si>
   <si>
     <t>A graduação Interdisciplinar em Humanidades EAD da Cruzeiro do Sul Virtual, prepara futuros profissionais nos âmbitos de áreas humanísticas, artísticas e científicas, os fornecendo os conhecimentos necessários para que sejam integrados na vida social e profissional, através de uma formação abrangente e multifacetada. A duração do curso é de 6 semestres (3 anos), e após a formação, o estudante garante o diploma de bacharel em Interdisciplinar em Humanidades.</t>
@@ -5775,6 +6600,27 @@
     <t>Explore diversas áreas das Humanidades a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Cruza de fontes artísticas, históricas e científicas</t>
+  </si>
+  <si>
+    <t>Pesquisadora em humanidades de cerca de 32 anos, mulher de pele morena, cabelo cacheado longo, vestido midi e cardigan, lupa na mão.</t>
+  </si>
+  <si>
+    <t>Sala de acervo cultural contemporânea brasileira, mesa larga, estante mista, janela, espaço de pesquisa acessível, sem círculo de aula de sociologia.</t>
+  </si>
+  <si>
+    <t>livros de áreas distintas, reprodução de obra, mapa antigo sem nomes, caderno, lupa</t>
+  </si>
+  <si>
+    <t>Compara a reprodução da obra com o mapa antigo sob a lupa e anota no caderno, sentada à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; foto de imprensa em círculo de aula; fluxograma de política social; palanque; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Pesquisadora em humanidades, mulher de pele morena, cerca de 32 anos, cardigan, comparando reprodução de obra e mapa antigo sob a lupa. Objetos: livros, reprodução, mapa sem nomes, caderno e lupa. Sem círculo de aula, sem palanque, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>geografia-ead-bacharelado</t>
   </si>
   <si>
@@ -5782,6 +6628,9 @@
   </si>
   <si>
     <t>geografia</t>
+  </si>
+  <si>
+    <t>Mapeie o espaço com geografia física, humana, geoprocessamento e análise ambiental de fenômenos territoriais.</t>
   </si>
   <si>
     <t>A graduação em Geografia - Bacharelado da Cruzeiro do Sul Virtual, na modalidade EAD fornece amplo conhecimento em geografia física, humana, técnicas de geoprocessamento e análise ambiental. Ao longo do curso, os estudantes são capacitados para a compreensão sobre fenômenos sociais, econômicos e ambientais, usufruindo de tecnologias inovadores de aprendizado. O curso tem duração de 6 semestres (3 anos).</t>
@@ -5816,6 +6665,27 @@
   </si>
   <si>
     <t>Aprofunde-se em Geografia a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
+  </si>
+  <si>
+    <t>Geoprocessamento e conferência de rastreio em campo urbano</t>
+  </si>
+  <si>
+    <t>Geógrafo de cerca de 27 anos, homem de pele morena, cabelo crespo, camisa de campo e calça, GPS na mão.</t>
+  </si>
+  <si>
+    <t>Mirante urbano brasileiro contemporâneo, cidade ao fundo, mesa dobrável com notebook, céu claro, espaço de campo, sem sala de aula com globo.</t>
+  </si>
+  <si>
+    <t>GPS, notebook com imagem de satélite desfocada, prancheta, binóculo, caneta</t>
+  </si>
+  <si>
+    <t>Compara o ponto no GPS com a imagem de satélite no notebook, em pé à direita do mirante.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; globo escolar; mapa em relevo de sala; giz; nomes de bairros na tela; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Geógrafo, homem de pele morena, cerca de 27 anos, camisa de campo, no mirante urbano, comparando o GPS com a imagem de satélite desfocada. Objetos: GPS, notebook, prancheta, binóculo e caneta. Sem globo, sem giz, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
   </si>
   <si>
     <t>ciencias-biologicas-semipresencial-bacharelado</t>
@@ -13203,23 +14073,26 @@
       <c r="G62" t="s">
         <v>203</v>
       </c>
+      <c r="H62" t="s">
+        <v>1301</v>
+      </c>
       <c r="I62" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="J62" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="K62" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="L62" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="M62" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N62" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="P62" t="s">
         <v>46</v>
@@ -13231,27 +14104,54 @@
         <v>48</v>
       </c>
       <c r="T62" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="U62" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="V62" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="W62" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X62" t="s">
+        <v>1311</v>
+      </c>
+      <c r="Y62" t="s">
+        <v>1312</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>1313</v>
+      </c>
+      <c r="AA62" t="s">
+        <v>1314</v>
+      </c>
+      <c r="AB62" t="s">
+        <v>1315</v>
+      </c>
+      <c r="AC62" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD62" t="s">
+        <v>1316</v>
+      </c>
+      <c r="AE62" t="s">
+        <v>1317</v>
+      </c>
+      <c r="AF62" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1310</v>
+        <v>1318</v>
       </c>
       <c r="B63" t="s">
-        <v>1311</v>
+        <v>1319</v>
       </c>
       <c r="C63" t="s">
-        <v>1312</v>
+        <v>1320</v>
       </c>
       <c r="D63" t="s">
         <v>35</v>
@@ -13265,23 +14165,26 @@
       <c r="G63" t="s">
         <v>38</v>
       </c>
+      <c r="H63" t="s">
+        <v>1321</v>
+      </c>
       <c r="I63" t="s">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="J63" t="s">
-        <v>1314</v>
+        <v>1323</v>
       </c>
       <c r="K63" t="s">
-        <v>1315</v>
+        <v>1324</v>
       </c>
       <c r="L63" t="s">
-        <v>1316</v>
+        <v>1325</v>
       </c>
       <c r="M63" t="s">
-        <v>1317</v>
+        <v>1326</v>
       </c>
       <c r="N63" t="s">
-        <v>1318</v>
+        <v>1327</v>
       </c>
       <c r="P63" t="s">
         <v>46</v>
@@ -13293,27 +14196,54 @@
         <v>48</v>
       </c>
       <c r="T63" t="s">
-        <v>1319</v>
+        <v>1328</v>
       </c>
       <c r="U63" t="s">
-        <v>1320</v>
+        <v>1329</v>
       </c>
       <c r="V63" t="s">
-        <v>1321</v>
+        <v>1330</v>
       </c>
       <c r="W63" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X63" t="s">
+        <v>1331</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>1332</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>1333</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>1334</v>
+      </c>
+      <c r="AB63" t="s">
+        <v>1335</v>
+      </c>
+      <c r="AC63" t="s">
+        <v>1336</v>
+      </c>
+      <c r="AD63" t="s">
+        <v>1337</v>
+      </c>
+      <c r="AE63" t="s">
+        <v>1338</v>
+      </c>
+      <c r="AF63" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>1322</v>
+        <v>1339</v>
       </c>
       <c r="B64" t="s">
-        <v>1323</v>
+        <v>1340</v>
       </c>
       <c r="C64" t="s">
-        <v>1324</v>
+        <v>1341</v>
       </c>
       <c r="D64" t="s">
         <v>65</v>
@@ -13327,23 +14257,26 @@
       <c r="G64" t="s">
         <v>38</v>
       </c>
+      <c r="H64" t="s">
+        <v>1342</v>
+      </c>
       <c r="I64" t="s">
-        <v>1325</v>
+        <v>1343</v>
       </c>
       <c r="J64" t="s">
-        <v>1326</v>
+        <v>1344</v>
       </c>
       <c r="K64" t="s">
-        <v>1327</v>
+        <v>1345</v>
       </c>
       <c r="L64" t="s">
-        <v>1328</v>
+        <v>1346</v>
       </c>
       <c r="M64" t="s">
-        <v>1329</v>
+        <v>1347</v>
       </c>
       <c r="N64" t="s">
-        <v>1330</v>
+        <v>1348</v>
       </c>
       <c r="P64" t="s">
         <v>46</v>
@@ -13355,27 +14288,54 @@
         <v>48</v>
       </c>
       <c r="T64" t="s">
-        <v>1331</v>
+        <v>1349</v>
       </c>
       <c r="U64" t="s">
-        <v>1332</v>
+        <v>1350</v>
       </c>
       <c r="V64" t="s">
-        <v>1333</v>
+        <v>1351</v>
       </c>
       <c r="W64" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X64" t="s">
+        <v>1352</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>1353</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>1354</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AB64" t="s">
+        <v>1356</v>
+      </c>
+      <c r="AC64" t="s">
+        <v>600</v>
+      </c>
+      <c r="AD64" t="s">
+        <v>1357</v>
+      </c>
+      <c r="AE64" t="s">
+        <v>1358</v>
+      </c>
+      <c r="AF64" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="65" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>1334</v>
+        <v>1359</v>
       </c>
       <c r="B65" t="s">
-        <v>1335</v>
+        <v>1360</v>
       </c>
       <c r="C65" t="s">
-        <v>1336</v>
+        <v>1361</v>
       </c>
       <c r="D65" t="s">
         <v>157</v>
@@ -13389,23 +14349,26 @@
       <c r="G65" t="s">
         <v>158</v>
       </c>
+      <c r="H65" t="s">
+        <v>1362</v>
+      </c>
       <c r="I65" t="s">
-        <v>1337</v>
+        <v>1363</v>
       </c>
       <c r="J65" t="s">
-        <v>1338</v>
+        <v>1364</v>
       </c>
       <c r="K65" t="s">
-        <v>1339</v>
+        <v>1365</v>
       </c>
       <c r="L65" t="s">
-        <v>1340</v>
+        <v>1366</v>
       </c>
       <c r="M65" t="s">
-        <v>1341</v>
+        <v>1367</v>
       </c>
       <c r="N65" t="s">
-        <v>1342</v>
+        <v>1368</v>
       </c>
       <c r="P65" t="s">
         <v>166</v>
@@ -13420,27 +14383,54 @@
         <v>167</v>
       </c>
       <c r="T65" t="s">
-        <v>1343</v>
+        <v>1369</v>
       </c>
       <c r="U65" t="s">
-        <v>1344</v>
+        <v>1370</v>
       </c>
       <c r="V65" t="s">
-        <v>1345</v>
+        <v>1371</v>
       </c>
       <c r="W65" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X65" t="s">
+        <v>1372</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>1373</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AB65" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AC65" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD65" t="s">
+        <v>1377</v>
+      </c>
+      <c r="AE65" t="s">
+        <v>1378</v>
+      </c>
+      <c r="AF65" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="66" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>1346</v>
+        <v>1379</v>
       </c>
       <c r="B66" t="s">
-        <v>1347</v>
+        <v>1380</v>
       </c>
       <c r="C66" t="s">
-        <v>1348</v>
+        <v>1381</v>
       </c>
       <c r="D66" t="s">
         <v>35</v>
@@ -13454,23 +14444,26 @@
       <c r="G66" t="s">
         <v>331</v>
       </c>
+      <c r="H66" t="s">
+        <v>1382</v>
+      </c>
       <c r="I66" t="s">
-        <v>1349</v>
+        <v>1383</v>
       </c>
       <c r="J66" t="s">
-        <v>1350</v>
+        <v>1384</v>
       </c>
       <c r="K66" t="s">
-        <v>1351</v>
+        <v>1385</v>
       </c>
       <c r="L66" t="s">
-        <v>1352</v>
+        <v>1386</v>
       </c>
       <c r="M66" t="s">
-        <v>1353</v>
+        <v>1387</v>
       </c>
       <c r="N66" t="s">
-        <v>1354</v>
+        <v>1388</v>
       </c>
       <c r="O66" t="s">
         <v>141</v>
@@ -13488,27 +14481,54 @@
         <v>167</v>
       </c>
       <c r="T66" t="s">
-        <v>1355</v>
+        <v>1389</v>
       </c>
       <c r="U66" t="s">
-        <v>1356</v>
+        <v>1390</v>
       </c>
       <c r="V66" t="s">
-        <v>1357</v>
+        <v>1391</v>
       </c>
       <c r="W66" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X66" t="s">
+        <v>1392</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>1393</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>1394</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>1395</v>
+      </c>
+      <c r="AB66" t="s">
+        <v>1396</v>
+      </c>
+      <c r="AC66" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD66" t="s">
+        <v>1397</v>
+      </c>
+      <c r="AE66" t="s">
+        <v>1398</v>
+      </c>
+      <c r="AF66" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="67" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>1358</v>
+        <v>1399</v>
       </c>
       <c r="B67" t="s">
-        <v>1359</v>
+        <v>1400</v>
       </c>
       <c r="C67" t="s">
-        <v>1360</v>
+        <v>1401</v>
       </c>
       <c r="D67" t="s">
         <v>35</v>
@@ -13522,23 +14542,26 @@
       <c r="G67" t="s">
         <v>89</v>
       </c>
+      <c r="H67" t="s">
+        <v>1402</v>
+      </c>
       <c r="I67" t="s">
-        <v>1361</v>
+        <v>1403</v>
       </c>
       <c r="J67" t="s">
-        <v>1362</v>
+        <v>1404</v>
       </c>
       <c r="K67" t="s">
-        <v>1363</v>
+        <v>1405</v>
       </c>
       <c r="L67" t="s">
-        <v>1364</v>
+        <v>1406</v>
       </c>
       <c r="M67" t="s">
-        <v>1365</v>
+        <v>1407</v>
       </c>
       <c r="N67" t="s">
-        <v>1366</v>
+        <v>1408</v>
       </c>
       <c r="O67" t="s">
         <v>141</v>
@@ -13553,27 +14576,54 @@
         <v>48</v>
       </c>
       <c r="T67" t="s">
-        <v>1367</v>
+        <v>1409</v>
       </c>
       <c r="U67" t="s">
-        <v>1368</v>
+        <v>1410</v>
       </c>
       <c r="V67" t="s">
-        <v>1369</v>
+        <v>1411</v>
       </c>
       <c r="W67" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X67" t="s">
+        <v>1412</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>1413</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>1414</v>
+      </c>
+      <c r="AA67" t="s">
+        <v>1415</v>
+      </c>
+      <c r="AB67" t="s">
+        <v>1416</v>
+      </c>
+      <c r="AC67" t="s">
+        <v>1417</v>
+      </c>
+      <c r="AD67" t="s">
+        <v>1418</v>
+      </c>
+      <c r="AE67" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AF67" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="68" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1370</v>
+        <v>1420</v>
       </c>
       <c r="B68" t="s">
-        <v>1371</v>
+        <v>1421</v>
       </c>
       <c r="C68" t="s">
-        <v>1372</v>
+        <v>1422</v>
       </c>
       <c r="D68" t="s">
         <v>157</v>
@@ -13587,23 +14637,26 @@
       <c r="G68" t="s">
         <v>158</v>
       </c>
+      <c r="H68" t="s">
+        <v>1423</v>
+      </c>
       <c r="I68" t="s">
-        <v>1373</v>
+        <v>1424</v>
       </c>
       <c r="J68" t="s">
-        <v>1374</v>
+        <v>1425</v>
       </c>
       <c r="K68" t="s">
-        <v>1375</v>
+        <v>1426</v>
       </c>
       <c r="L68" t="s">
-        <v>1376</v>
+        <v>1427</v>
       </c>
       <c r="M68" t="s">
-        <v>1377</v>
+        <v>1428</v>
       </c>
       <c r="N68" t="s">
-        <v>1378</v>
+        <v>1429</v>
       </c>
       <c r="P68" t="s">
         <v>46</v>
@@ -13615,27 +14668,54 @@
         <v>48</v>
       </c>
       <c r="T68" t="s">
-        <v>1379</v>
+        <v>1430</v>
       </c>
       <c r="U68" t="s">
-        <v>1380</v>
+        <v>1431</v>
       </c>
       <c r="V68" t="s">
-        <v>1381</v>
+        <v>1432</v>
       </c>
       <c r="W68" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X68" t="s">
+        <v>1433</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>1434</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AA68" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AB68" t="s">
+        <v>1437</v>
+      </c>
+      <c r="AC68" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD68" t="s">
+        <v>1438</v>
+      </c>
+      <c r="AE68" t="s">
+        <v>1439</v>
+      </c>
+      <c r="AF68" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="69" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>1382</v>
+        <v>1440</v>
       </c>
       <c r="B69" t="s">
-        <v>1383</v>
+        <v>1441</v>
       </c>
       <c r="C69" t="s">
-        <v>1384</v>
+        <v>1442</v>
       </c>
       <c r="D69" t="s">
         <v>35</v>
@@ -13649,23 +14729,26 @@
       <c r="G69" t="s">
         <v>89</v>
       </c>
+      <c r="H69" t="s">
+        <v>1443</v>
+      </c>
       <c r="I69" t="s">
-        <v>1385</v>
+        <v>1444</v>
       </c>
       <c r="J69" t="s">
-        <v>1386</v>
+        <v>1445</v>
       </c>
       <c r="K69" t="s">
-        <v>1387</v>
+        <v>1446</v>
       </c>
       <c r="L69" t="s">
-        <v>1388</v>
+        <v>1447</v>
       </c>
       <c r="M69" t="s">
-        <v>1389</v>
+        <v>1448</v>
       </c>
       <c r="N69" t="s">
-        <v>1390</v>
+        <v>1449</v>
       </c>
       <c r="O69" t="s">
         <v>141</v>
@@ -13680,27 +14763,54 @@
         <v>48</v>
       </c>
       <c r="T69" t="s">
-        <v>1391</v>
+        <v>1450</v>
       </c>
       <c r="U69" t="s">
-        <v>1392</v>
+        <v>1451</v>
       </c>
       <c r="V69" t="s">
-        <v>1393</v>
+        <v>1452</v>
       </c>
       <c r="W69" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X69" t="s">
+        <v>1453</v>
+      </c>
+      <c r="Y69" t="s">
+        <v>1454</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>1455</v>
+      </c>
+      <c r="AA69" t="s">
+        <v>1456</v>
+      </c>
+      <c r="AB69" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AC69" t="s">
+        <v>1458</v>
+      </c>
+      <c r="AD69" t="s">
+        <v>1459</v>
+      </c>
+      <c r="AE69" t="s">
+        <v>1460</v>
+      </c>
+      <c r="AF69" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>1394</v>
+        <v>1461</v>
       </c>
       <c r="B70" t="s">
-        <v>1395</v>
+        <v>1462</v>
       </c>
       <c r="C70" t="s">
-        <v>1396</v>
+        <v>1463</v>
       </c>
       <c r="D70" t="s">
         <v>35</v>
@@ -13714,23 +14824,26 @@
       <c r="G70" t="s">
         <v>89</v>
       </c>
+      <c r="H70" t="s">
+        <v>1464</v>
+      </c>
       <c r="I70" t="s">
-        <v>1397</v>
+        <v>1465</v>
       </c>
       <c r="J70" t="s">
-        <v>1398</v>
+        <v>1466</v>
       </c>
       <c r="K70" t="s">
-        <v>1399</v>
+        <v>1467</v>
       </c>
       <c r="L70" t="s">
-        <v>1400</v>
+        <v>1468</v>
       </c>
       <c r="M70" t="s">
-        <v>1401</v>
+        <v>1469</v>
       </c>
       <c r="N70" t="s">
-        <v>1402</v>
+        <v>1470</v>
       </c>
       <c r="O70" t="s">
         <v>141</v>
@@ -13745,27 +14858,54 @@
         <v>48</v>
       </c>
       <c r="T70" t="s">
-        <v>1403</v>
+        <v>1471</v>
       </c>
       <c r="U70" t="s">
-        <v>1404</v>
+        <v>1472</v>
       </c>
       <c r="V70" t="s">
-        <v>1405</v>
+        <v>1473</v>
       </c>
       <c r="W70" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X70" t="s">
+        <v>1474</v>
+      </c>
+      <c r="Y70" t="s">
+        <v>1475</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>1476</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>1477</v>
+      </c>
+      <c r="AB70" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AC70" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD70" t="s">
+        <v>1479</v>
+      </c>
+      <c r="AE70" t="s">
+        <v>1480</v>
+      </c>
+      <c r="AF70" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="71" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>1406</v>
+        <v>1481</v>
       </c>
       <c r="B71" t="s">
-        <v>1407</v>
+        <v>1482</v>
       </c>
       <c r="C71" t="s">
-        <v>1408</v>
+        <v>1483</v>
       </c>
       <c r="D71" t="s">
         <v>35</v>
@@ -13779,23 +14919,26 @@
       <c r="G71" t="s">
         <v>158</v>
       </c>
+      <c r="H71" t="s">
+        <v>1484</v>
+      </c>
       <c r="I71" t="s">
-        <v>1409</v>
+        <v>1485</v>
       </c>
       <c r="J71" t="s">
-        <v>1410</v>
+        <v>1486</v>
       </c>
       <c r="K71" t="s">
-        <v>1411</v>
+        <v>1487</v>
       </c>
       <c r="L71" t="s">
-        <v>1412</v>
+        <v>1488</v>
       </c>
       <c r="M71" t="s">
-        <v>1413</v>
+        <v>1489</v>
       </c>
       <c r="N71" t="s">
-        <v>1414</v>
+        <v>1490</v>
       </c>
       <c r="P71" t="s">
         <v>166</v>
@@ -13810,30 +14953,57 @@
         <v>167</v>
       </c>
       <c r="T71" t="s">
-        <v>1415</v>
+        <v>1491</v>
       </c>
       <c r="U71" t="s">
-        <v>1416</v>
+        <v>1492</v>
       </c>
       <c r="V71" t="s">
-        <v>1417</v>
+        <v>1493</v>
       </c>
       <c r="W71" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X71" t="s">
+        <v>1494</v>
+      </c>
+      <c r="Y71" t="s">
+        <v>1495</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>1496</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>1497</v>
+      </c>
+      <c r="AB71" t="s">
+        <v>1498</v>
+      </c>
+      <c r="AC71" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AD71" t="s">
+        <v>1500</v>
+      </c>
+      <c r="AE71" t="s">
+        <v>1501</v>
+      </c>
+      <c r="AF71" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="72" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1418</v>
+        <v>1502</v>
       </c>
       <c r="B72" t="s">
-        <v>1419</v>
+        <v>1503</v>
       </c>
       <c r="C72" t="s">
-        <v>1420</v>
+        <v>1504</v>
       </c>
       <c r="D72" t="s">
-        <v>1421</v>
+        <v>1505</v>
       </c>
       <c r="E72" t="s">
         <v>132</v>
@@ -13844,23 +15014,26 @@
       <c r="G72" t="s">
         <v>158</v>
       </c>
+      <c r="H72" t="s">
+        <v>1506</v>
+      </c>
       <c r="I72" t="s">
-        <v>1422</v>
+        <v>1507</v>
       </c>
       <c r="J72" t="s">
-        <v>1423</v>
+        <v>1508</v>
       </c>
       <c r="K72" t="s">
-        <v>1424</v>
+        <v>1509</v>
       </c>
       <c r="L72" t="s">
-        <v>1425</v>
+        <v>1510</v>
       </c>
       <c r="M72" t="s">
-        <v>1426</v>
+        <v>1511</v>
       </c>
       <c r="N72" t="s">
-        <v>1427</v>
+        <v>1512</v>
       </c>
       <c r="P72" t="s">
         <v>166</v>
@@ -13872,30 +15045,57 @@
         <v>48</v>
       </c>
       <c r="S72" t="s">
-        <v>1428</v>
+        <v>1513</v>
       </c>
       <c r="T72" t="s">
-        <v>1429</v>
+        <v>1514</v>
       </c>
       <c r="U72" t="s">
-        <v>1430</v>
+        <v>1515</v>
       </c>
       <c r="V72" t="s">
-        <v>1431</v>
+        <v>1516</v>
       </c>
       <c r="W72" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X72" t="s">
+        <v>1517</v>
+      </c>
+      <c r="Y72" t="s">
+        <v>1518</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>1520</v>
+      </c>
+      <c r="AB72" t="s">
+        <v>1521</v>
+      </c>
+      <c r="AC72" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD72" t="s">
+        <v>1522</v>
+      </c>
+      <c r="AE72" t="s">
+        <v>1523</v>
+      </c>
+      <c r="AF72" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="73" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>1432</v>
+        <v>1524</v>
       </c>
       <c r="B73" t="s">
-        <v>1433</v>
+        <v>1525</v>
       </c>
       <c r="C73" t="s">
-        <v>1434</v>
+        <v>1526</v>
       </c>
       <c r="D73" t="s">
         <v>157</v>
@@ -13904,25 +15104,28 @@
         <v>132</v>
       </c>
       <c r="F73" t="s">
-        <v>1435</v>
+        <v>1527</v>
       </c>
       <c r="G73" t="s">
         <v>158</v>
       </c>
+      <c r="H73" t="s">
+        <v>1528</v>
+      </c>
       <c r="I73" t="s">
-        <v>1436</v>
+        <v>1529</v>
       </c>
       <c r="J73" t="s">
-        <v>1437</v>
+        <v>1530</v>
       </c>
       <c r="K73" t="s">
-        <v>1438</v>
+        <v>1531</v>
       </c>
       <c r="M73" t="s">
-        <v>1439</v>
+        <v>1532</v>
       </c>
       <c r="N73" t="s">
-        <v>1440</v>
+        <v>1533</v>
       </c>
       <c r="O73" t="s">
         <v>141</v>
@@ -13937,30 +15140,57 @@
         <v>48</v>
       </c>
       <c r="S73" t="s">
-        <v>1441</v>
+        <v>1534</v>
       </c>
       <c r="T73" t="s">
-        <v>1442</v>
+        <v>1535</v>
       </c>
       <c r="U73" t="s">
-        <v>1443</v>
+        <v>1536</v>
       </c>
       <c r="V73" t="s">
-        <v>1444</v>
+        <v>1537</v>
       </c>
       <c r="W73" s="1" t="s">
-        <v>1445</v>
+        <v>1538</v>
+      </c>
+      <c r="X73" t="s">
+        <v>1539</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>1540</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>1541</v>
+      </c>
+      <c r="AA73" t="s">
+        <v>1542</v>
+      </c>
+      <c r="AB73" t="s">
+        <v>1543</v>
+      </c>
+      <c r="AC73" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD73" t="s">
+        <v>1544</v>
+      </c>
+      <c r="AE73" t="s">
+        <v>1545</v>
+      </c>
+      <c r="AF73" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="74" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1446</v>
+        <v>1546</v>
       </c>
       <c r="B74" t="s">
-        <v>1447</v>
+        <v>1547</v>
       </c>
       <c r="C74" t="s">
-        <v>1448</v>
+        <v>1548</v>
       </c>
       <c r="D74" t="s">
         <v>65</v>
@@ -13974,23 +15204,26 @@
       <c r="G74" t="s">
         <v>500</v>
       </c>
+      <c r="H74" t="s">
+        <v>1549</v>
+      </c>
       <c r="I74" t="s">
-        <v>1449</v>
+        <v>1550</v>
       </c>
       <c r="J74" t="s">
-        <v>1450</v>
+        <v>1551</v>
       </c>
       <c r="K74" t="s">
-        <v>1451</v>
+        <v>1552</v>
       </c>
       <c r="L74" t="s">
-        <v>1452</v>
+        <v>1553</v>
       </c>
       <c r="M74" t="s">
-        <v>1453</v>
+        <v>1554</v>
       </c>
       <c r="N74" t="s">
-        <v>1454</v>
+        <v>1555</v>
       </c>
       <c r="P74" t="s">
         <v>46</v>
@@ -14002,27 +15235,54 @@
         <v>48</v>
       </c>
       <c r="T74" t="s">
-        <v>1455</v>
+        <v>1556</v>
       </c>
       <c r="U74" t="s">
-        <v>1456</v>
+        <v>1557</v>
       </c>
       <c r="V74" t="s">
-        <v>1457</v>
+        <v>1558</v>
       </c>
       <c r="W74" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X74" t="s">
+        <v>1559</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>1560</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>1561</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>1562</v>
+      </c>
+      <c r="AB74" t="s">
+        <v>1563</v>
+      </c>
+      <c r="AC74" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD74" t="s">
+        <v>1564</v>
+      </c>
+      <c r="AE74" t="s">
+        <v>1565</v>
+      </c>
+      <c r="AF74" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>1458</v>
+        <v>1566</v>
       </c>
       <c r="B75" t="s">
-        <v>1459</v>
+        <v>1567</v>
       </c>
       <c r="C75" t="s">
-        <v>1460</v>
+        <v>1568</v>
       </c>
       <c r="D75" t="s">
         <v>65</v>
@@ -14036,23 +15296,26 @@
       <c r="G75" t="s">
         <v>203</v>
       </c>
+      <c r="H75" t="s">
+        <v>1569</v>
+      </c>
       <c r="I75" t="s">
-        <v>1461</v>
+        <v>1570</v>
       </c>
       <c r="J75" t="s">
-        <v>1462</v>
+        <v>1571</v>
       </c>
       <c r="K75" t="s">
-        <v>1463</v>
+        <v>1572</v>
       </c>
       <c r="L75" t="s">
-        <v>1464</v>
+        <v>1573</v>
       </c>
       <c r="M75" t="s">
-        <v>1465</v>
+        <v>1574</v>
       </c>
       <c r="N75" t="s">
-        <v>1466</v>
+        <v>1575</v>
       </c>
       <c r="P75" t="s">
         <v>46</v>
@@ -14064,27 +15327,54 @@
         <v>48</v>
       </c>
       <c r="T75" t="s">
-        <v>1467</v>
+        <v>1576</v>
       </c>
       <c r="U75" t="s">
-        <v>1468</v>
+        <v>1577</v>
       </c>
       <c r="V75" t="s">
-        <v>1469</v>
+        <v>1578</v>
       </c>
       <c r="W75" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X75" t="s">
+        <v>1579</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>1580</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>1581</v>
+      </c>
+      <c r="AA75" t="s">
+        <v>1582</v>
+      </c>
+      <c r="AB75" t="s">
+        <v>1583</v>
+      </c>
+      <c r="AC75" t="s">
+        <v>1584</v>
+      </c>
+      <c r="AD75" t="s">
+        <v>1585</v>
+      </c>
+      <c r="AE75" t="s">
+        <v>1586</v>
+      </c>
+      <c r="AF75" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1470</v>
+        <v>1587</v>
       </c>
       <c r="B76" t="s">
-        <v>1471</v>
+        <v>1588</v>
       </c>
       <c r="C76" t="s">
-        <v>1472</v>
+        <v>1589</v>
       </c>
       <c r="D76" t="s">
         <v>65</v>
@@ -14098,23 +15388,26 @@
       <c r="G76" t="s">
         <v>38</v>
       </c>
+      <c r="H76" t="s">
+        <v>1590</v>
+      </c>
       <c r="I76" t="s">
-        <v>1473</v>
+        <v>1591</v>
       </c>
       <c r="J76" t="s">
-        <v>1474</v>
+        <v>1592</v>
       </c>
       <c r="K76" t="s">
-        <v>1475</v>
+        <v>1593</v>
       </c>
       <c r="L76" t="s">
-        <v>1476</v>
+        <v>1594</v>
       </c>
       <c r="M76" t="s">
-        <v>1477</v>
+        <v>1595</v>
       </c>
       <c r="N76" t="s">
-        <v>1478</v>
+        <v>1596</v>
       </c>
       <c r="P76" t="s">
         <v>46</v>
@@ -14126,27 +15419,54 @@
         <v>48</v>
       </c>
       <c r="T76" t="s">
-        <v>1479</v>
+        <v>1597</v>
       </c>
       <c r="U76" t="s">
-        <v>1480</v>
+        <v>1598</v>
       </c>
       <c r="V76" t="s">
-        <v>1481</v>
+        <v>1599</v>
       </c>
       <c r="W76" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X76" t="s">
+        <v>1600</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>1601</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>1602</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>1603</v>
+      </c>
+      <c r="AB76" t="s">
+        <v>1604</v>
+      </c>
+      <c r="AC76" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD76" t="s">
+        <v>1605</v>
+      </c>
+      <c r="AE76" t="s">
+        <v>1606</v>
+      </c>
+      <c r="AF76" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1482</v>
+        <v>1607</v>
       </c>
       <c r="B77" t="s">
-        <v>1483</v>
+        <v>1608</v>
       </c>
       <c r="C77" t="s">
-        <v>1484</v>
+        <v>1609</v>
       </c>
       <c r="D77" t="s">
         <v>35</v>
@@ -14160,23 +15480,26 @@
       <c r="G77" t="s">
         <v>203</v>
       </c>
+      <c r="H77" t="s">
+        <v>1610</v>
+      </c>
       <c r="I77" t="s">
-        <v>1485</v>
+        <v>1611</v>
       </c>
       <c r="J77" t="s">
-        <v>1486</v>
+        <v>1612</v>
       </c>
       <c r="K77" t="s">
-        <v>1487</v>
+        <v>1613</v>
       </c>
       <c r="L77" t="s">
-        <v>1488</v>
+        <v>1614</v>
       </c>
       <c r="M77" t="s">
-        <v>1489</v>
+        <v>1615</v>
       </c>
       <c r="N77" t="s">
-        <v>1490</v>
+        <v>1616</v>
       </c>
       <c r="P77" t="s">
         <v>46</v>
@@ -14188,27 +15511,54 @@
         <v>48</v>
       </c>
       <c r="T77" t="s">
-        <v>1491</v>
+        <v>1617</v>
       </c>
       <c r="U77" t="s">
-        <v>1492</v>
+        <v>1618</v>
       </c>
       <c r="V77" t="s">
-        <v>1493</v>
+        <v>1619</v>
       </c>
       <c r="W77" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X77" t="s">
+        <v>1620</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>1621</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>1622</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>1623</v>
+      </c>
+      <c r="AB77" t="s">
+        <v>1624</v>
+      </c>
+      <c r="AC77" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD77" t="s">
+        <v>1625</v>
+      </c>
+      <c r="AE77" t="s">
+        <v>1626</v>
+      </c>
+      <c r="AF77" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1494</v>
+        <v>1627</v>
       </c>
       <c r="B78" t="s">
-        <v>1495</v>
+        <v>1628</v>
       </c>
       <c r="C78" t="s">
-        <v>1496</v>
+        <v>1629</v>
       </c>
       <c r="D78" t="s">
         <v>35</v>
@@ -14222,23 +15572,26 @@
       <c r="G78" t="s">
         <v>89</v>
       </c>
+      <c r="H78" t="s">
+        <v>1630</v>
+      </c>
       <c r="I78" t="s">
-        <v>1497</v>
+        <v>1631</v>
       </c>
       <c r="J78" t="s">
-        <v>1498</v>
+        <v>1632</v>
       </c>
       <c r="K78" t="s">
-        <v>1499</v>
+        <v>1633</v>
       </c>
       <c r="L78" t="s">
-        <v>1500</v>
+        <v>1634</v>
       </c>
       <c r="M78" t="s">
-        <v>1501</v>
+        <v>1635</v>
       </c>
       <c r="N78" t="s">
-        <v>1502</v>
+        <v>1636</v>
       </c>
       <c r="O78" t="s">
         <v>141</v>
@@ -14253,27 +15606,54 @@
         <v>48</v>
       </c>
       <c r="T78" t="s">
-        <v>1503</v>
+        <v>1637</v>
       </c>
       <c r="U78" t="s">
-        <v>1504</v>
+        <v>1638</v>
       </c>
       <c r="V78" t="s">
-        <v>1505</v>
+        <v>1639</v>
       </c>
       <c r="W78" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X78" t="s">
+        <v>1640</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>1641</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>1642</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>1643</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>1644</v>
+      </c>
+      <c r="AC78" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD78" t="s">
+        <v>1645</v>
+      </c>
+      <c r="AE78" t="s">
+        <v>1646</v>
+      </c>
+      <c r="AF78" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="79" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>1506</v>
+        <v>1647</v>
       </c>
       <c r="B79" t="s">
-        <v>1507</v>
+        <v>1648</v>
       </c>
       <c r="C79" t="s">
-        <v>1508</v>
+        <v>1649</v>
       </c>
       <c r="D79" t="s">
         <v>35</v>
@@ -14287,23 +15667,26 @@
       <c r="G79" t="s">
         <v>331</v>
       </c>
+      <c r="H79" t="s">
+        <v>1650</v>
+      </c>
       <c r="I79" t="s">
-        <v>1509</v>
+        <v>1651</v>
       </c>
       <c r="J79" t="s">
-        <v>1510</v>
+        <v>1652</v>
       </c>
       <c r="K79" t="s">
-        <v>1511</v>
+        <v>1653</v>
       </c>
       <c r="L79" t="s">
-        <v>1512</v>
+        <v>1654</v>
       </c>
       <c r="M79" t="s">
-        <v>1513</v>
+        <v>1655</v>
       </c>
       <c r="N79" t="s">
-        <v>1514</v>
+        <v>1656</v>
       </c>
       <c r="O79" t="s">
         <v>141</v>
@@ -14321,27 +15704,54 @@
         <v>167</v>
       </c>
       <c r="T79" t="s">
-        <v>1515</v>
+        <v>1657</v>
       </c>
       <c r="U79" t="s">
-        <v>1516</v>
+        <v>1658</v>
       </c>
       <c r="V79" t="s">
-        <v>1517</v>
+        <v>1659</v>
       </c>
       <c r="W79" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X79" t="s">
+        <v>1660</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>1661</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>1662</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>1663</v>
+      </c>
+      <c r="AB79" t="s">
+        <v>1664</v>
+      </c>
+      <c r="AC79" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD79" t="s">
+        <v>1665</v>
+      </c>
+      <c r="AE79" t="s">
+        <v>1666</v>
+      </c>
+      <c r="AF79" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="80" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>1518</v>
+        <v>1667</v>
       </c>
       <c r="B80" t="s">
-        <v>1519</v>
+        <v>1668</v>
       </c>
       <c r="C80" t="s">
-        <v>1520</v>
+        <v>1669</v>
       </c>
       <c r="D80" t="s">
         <v>35</v>
@@ -14355,23 +15765,26 @@
       <c r="G80" t="s">
         <v>500</v>
       </c>
+      <c r="H80" t="s">
+        <v>1670</v>
+      </c>
       <c r="I80" t="s">
-        <v>1521</v>
+        <v>1671</v>
       </c>
       <c r="J80" t="s">
-        <v>1522</v>
+        <v>1672</v>
       </c>
       <c r="K80" t="s">
-        <v>1523</v>
+        <v>1673</v>
       </c>
       <c r="L80" t="s">
-        <v>1524</v>
+        <v>1674</v>
       </c>
       <c r="M80" t="s">
-        <v>1525</v>
+        <v>1675</v>
       </c>
       <c r="N80" t="s">
-        <v>1526</v>
+        <v>1676</v>
       </c>
       <c r="P80" t="s">
         <v>46</v>
@@ -14383,27 +15796,54 @@
         <v>48</v>
       </c>
       <c r="T80" t="s">
-        <v>1527</v>
+        <v>1677</v>
       </c>
       <c r="U80" t="s">
-        <v>1528</v>
+        <v>1678</v>
       </c>
       <c r="V80" t="s">
-        <v>1529</v>
+        <v>1679</v>
       </c>
       <c r="W80" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X80" t="s">
+        <v>1680</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>1681</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>1682</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>1683</v>
+      </c>
+      <c r="AB80" t="s">
+        <v>1684</v>
+      </c>
+      <c r="AC80" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD80" t="s">
+        <v>1685</v>
+      </c>
+      <c r="AE80" t="s">
+        <v>1686</v>
+      </c>
+      <c r="AF80" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="81" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>1530</v>
+        <v>1687</v>
       </c>
       <c r="B81" t="s">
-        <v>1531</v>
+        <v>1688</v>
       </c>
       <c r="C81" t="s">
-        <v>1532</v>
+        <v>1689</v>
       </c>
       <c r="D81" t="s">
         <v>65</v>
@@ -14417,23 +15857,26 @@
       <c r="G81" t="s">
         <v>203</v>
       </c>
+      <c r="H81" t="s">
+        <v>1690</v>
+      </c>
       <c r="I81" t="s">
-        <v>1533</v>
+        <v>1691</v>
       </c>
       <c r="J81" t="s">
-        <v>1534</v>
+        <v>1692</v>
       </c>
       <c r="K81" t="s">
-        <v>1535</v>
+        <v>1693</v>
       </c>
       <c r="L81" t="s">
-        <v>1536</v>
+        <v>1694</v>
       </c>
       <c r="M81" t="s">
-        <v>1537</v>
+        <v>1695</v>
       </c>
       <c r="N81" t="s">
-        <v>1538</v>
+        <v>1696</v>
       </c>
       <c r="P81" t="s">
         <v>46</v>
@@ -14445,27 +15888,54 @@
         <v>48</v>
       </c>
       <c r="T81" t="s">
-        <v>1539</v>
+        <v>1697</v>
       </c>
       <c r="U81" t="s">
-        <v>1540</v>
+        <v>1698</v>
       </c>
       <c r="V81" t="s">
-        <v>1541</v>
+        <v>1699</v>
       </c>
       <c r="W81" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X81" t="s">
+        <v>1700</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>1701</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>1702</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>1703</v>
+      </c>
+      <c r="AB81" t="s">
+        <v>1704</v>
+      </c>
+      <c r="AC81" t="s">
+        <v>1705</v>
+      </c>
+      <c r="AD81" t="s">
+        <v>1706</v>
+      </c>
+      <c r="AE81" t="s">
+        <v>1707</v>
+      </c>
+      <c r="AF81" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1542</v>
+        <v>1708</v>
       </c>
       <c r="B82" t="s">
-        <v>1543</v>
+        <v>1709</v>
       </c>
       <c r="C82" t="s">
-        <v>1544</v>
+        <v>1710</v>
       </c>
       <c r="D82" t="s">
         <v>157</v>
@@ -14479,23 +15949,26 @@
       <c r="G82" t="s">
         <v>158</v>
       </c>
+      <c r="H82" t="s">
+        <v>1711</v>
+      </c>
       <c r="I82" t="s">
-        <v>1545</v>
+        <v>1712</v>
       </c>
       <c r="J82" t="s">
-        <v>1546</v>
+        <v>1713</v>
       </c>
       <c r="K82" t="s">
-        <v>1547</v>
+        <v>1714</v>
       </c>
       <c r="L82" t="s">
-        <v>1548</v>
+        <v>1715</v>
       </c>
       <c r="M82" t="s">
-        <v>1549</v>
+        <v>1716</v>
       </c>
       <c r="N82" t="s">
-        <v>1550</v>
+        <v>1717</v>
       </c>
       <c r="P82" t="s">
         <v>166</v>
@@ -14510,27 +15983,54 @@
         <v>167</v>
       </c>
       <c r="T82" t="s">
-        <v>1551</v>
+        <v>1718</v>
       </c>
       <c r="U82" t="s">
-        <v>1552</v>
+        <v>1719</v>
       </c>
       <c r="V82" t="s">
-        <v>1553</v>
+        <v>1720</v>
       </c>
       <c r="W82" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X82" t="s">
+        <v>1721</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>1722</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>1723</v>
+      </c>
+      <c r="AA82" t="s">
+        <v>1724</v>
+      </c>
+      <c r="AB82" t="s">
+        <v>1725</v>
+      </c>
+      <c r="AC82" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD82" t="s">
+        <v>1726</v>
+      </c>
+      <c r="AE82" t="s">
+        <v>1727</v>
+      </c>
+      <c r="AF82" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="83" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1554</v>
+        <v>1728</v>
       </c>
       <c r="B83" t="s">
-        <v>1555</v>
+        <v>1729</v>
       </c>
       <c r="C83" t="s">
-        <v>1556</v>
+        <v>1730</v>
       </c>
       <c r="D83" t="s">
         <v>35</v>
@@ -14544,23 +16044,26 @@
       <c r="G83" t="s">
         <v>203</v>
       </c>
+      <c r="H83" t="s">
+        <v>1731</v>
+      </c>
       <c r="I83" t="s">
-        <v>1557</v>
+        <v>1732</v>
       </c>
       <c r="J83" t="s">
-        <v>1558</v>
+        <v>1733</v>
       </c>
       <c r="K83" t="s">
-        <v>1559</v>
+        <v>1734</v>
       </c>
       <c r="L83" t="s">
-        <v>1560</v>
+        <v>1735</v>
       </c>
       <c r="M83" t="s">
-        <v>1561</v>
+        <v>1736</v>
       </c>
       <c r="N83" t="s">
-        <v>1562</v>
+        <v>1737</v>
       </c>
       <c r="O83" t="s">
         <v>141</v>
@@ -14575,27 +16078,54 @@
         <v>48</v>
       </c>
       <c r="T83" t="s">
-        <v>1563</v>
+        <v>1738</v>
       </c>
       <c r="U83" t="s">
-        <v>1564</v>
+        <v>1739</v>
       </c>
       <c r="V83" t="s">
-        <v>1565</v>
+        <v>1740</v>
       </c>
       <c r="W83" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X83" t="s">
+        <v>1741</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>1742</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>1743</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>1744</v>
+      </c>
+      <c r="AB83" t="s">
+        <v>1745</v>
+      </c>
+      <c r="AC83" t="s">
+        <v>1746</v>
+      </c>
+      <c r="AD83" t="s">
+        <v>1747</v>
+      </c>
+      <c r="AE83" t="s">
+        <v>1748</v>
+      </c>
+      <c r="AF83" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="84" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1566</v>
+        <v>1749</v>
       </c>
       <c r="B84" t="s">
-        <v>1567</v>
+        <v>1750</v>
       </c>
       <c r="C84" t="s">
-        <v>1568</v>
+        <v>1751</v>
       </c>
       <c r="D84" t="s">
         <v>65</v>
@@ -14609,23 +16139,26 @@
       <c r="G84" t="s">
         <v>203</v>
       </c>
+      <c r="H84" t="s">
+        <v>1752</v>
+      </c>
       <c r="I84" t="s">
-        <v>1569</v>
+        <v>1753</v>
       </c>
       <c r="J84" t="s">
-        <v>1570</v>
+        <v>1754</v>
       </c>
       <c r="K84" t="s">
-        <v>1571</v>
+        <v>1755</v>
       </c>
       <c r="L84" t="s">
-        <v>1572</v>
+        <v>1756</v>
       </c>
       <c r="M84" t="s">
-        <v>1573</v>
+        <v>1757</v>
       </c>
       <c r="N84" t="s">
-        <v>1574</v>
+        <v>1758</v>
       </c>
       <c r="P84" t="s">
         <v>46</v>
@@ -14637,27 +16170,54 @@
         <v>48</v>
       </c>
       <c r="T84" t="s">
-        <v>1575</v>
+        <v>1759</v>
       </c>
       <c r="U84" t="s">
-        <v>1576</v>
+        <v>1760</v>
       </c>
       <c r="V84" t="s">
-        <v>1577</v>
+        <v>1761</v>
       </c>
       <c r="W84" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X84" t="s">
+        <v>1762</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>1763</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>1764</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>1765</v>
+      </c>
+      <c r="AB84" t="s">
+        <v>1766</v>
+      </c>
+      <c r="AC84" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AD84" t="s">
+        <v>1768</v>
+      </c>
+      <c r="AE84" t="s">
+        <v>1769</v>
+      </c>
+      <c r="AF84" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="85" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1578</v>
+        <v>1770</v>
       </c>
       <c r="B85" t="s">
-        <v>1579</v>
+        <v>1771</v>
       </c>
       <c r="C85" t="s">
-        <v>1580</v>
+        <v>1772</v>
       </c>
       <c r="D85" t="s">
         <v>65</v>
@@ -14671,23 +16231,26 @@
       <c r="G85" t="s">
         <v>331</v>
       </c>
+      <c r="H85" t="s">
+        <v>1773</v>
+      </c>
       <c r="I85" t="s">
-        <v>1581</v>
+        <v>1774</v>
       </c>
       <c r="J85" t="s">
-        <v>1582</v>
+        <v>1775</v>
       </c>
       <c r="K85" t="s">
-        <v>1583</v>
+        <v>1776</v>
       </c>
       <c r="L85" t="s">
-        <v>1584</v>
+        <v>1777</v>
       </c>
       <c r="M85" t="s">
-        <v>1585</v>
+        <v>1778</v>
       </c>
       <c r="N85" t="s">
-        <v>1586</v>
+        <v>1779</v>
       </c>
       <c r="P85" t="s">
         <v>46</v>
@@ -14699,27 +16262,54 @@
         <v>48</v>
       </c>
       <c r="T85" t="s">
-        <v>1587</v>
+        <v>1780</v>
       </c>
       <c r="U85" t="s">
-        <v>1588</v>
+        <v>1781</v>
       </c>
       <c r="V85" t="s">
-        <v>1589</v>
+        <v>1782</v>
       </c>
       <c r="W85" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X85" t="s">
+        <v>1783</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>1784</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>1785</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>1786</v>
+      </c>
+      <c r="AB85" t="s">
+        <v>1787</v>
+      </c>
+      <c r="AC85" t="s">
+        <v>1788</v>
+      </c>
+      <c r="AD85" t="s">
+        <v>1789</v>
+      </c>
+      <c r="AE85" t="s">
+        <v>1790</v>
+      </c>
+      <c r="AF85" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="86" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1590</v>
+        <v>1791</v>
       </c>
       <c r="B86" t="s">
-        <v>1591</v>
+        <v>1792</v>
       </c>
       <c r="C86" t="s">
-        <v>1592</v>
+        <v>1793</v>
       </c>
       <c r="D86" t="s">
         <v>65</v>
@@ -14733,23 +16323,26 @@
       <c r="G86" t="s">
         <v>500</v>
       </c>
+      <c r="H86" t="s">
+        <v>1794</v>
+      </c>
       <c r="I86" t="s">
-        <v>1593</v>
+        <v>1795</v>
       </c>
       <c r="J86" t="s">
-        <v>1594</v>
+        <v>1796</v>
       </c>
       <c r="K86" t="s">
-        <v>1595</v>
+        <v>1797</v>
       </c>
       <c r="L86" t="s">
-        <v>1596</v>
+        <v>1798</v>
       </c>
       <c r="M86" t="s">
-        <v>1597</v>
+        <v>1799</v>
       </c>
       <c r="N86" t="s">
-        <v>1598</v>
+        <v>1800</v>
       </c>
       <c r="P86" t="s">
         <v>46</v>
@@ -14761,27 +16354,54 @@
         <v>48</v>
       </c>
       <c r="T86" t="s">
-        <v>1599</v>
+        <v>1801</v>
       </c>
       <c r="U86" t="s">
-        <v>1600</v>
+        <v>1802</v>
       </c>
       <c r="V86" t="s">
-        <v>1601</v>
+        <v>1803</v>
       </c>
       <c r="W86" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X86" t="s">
+        <v>1804</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>1805</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>1806</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>1807</v>
+      </c>
+      <c r="AB86" t="s">
+        <v>1808</v>
+      </c>
+      <c r="AC86" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD86" t="s">
+        <v>1809</v>
+      </c>
+      <c r="AE86" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AF86" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1602</v>
+        <v>1811</v>
       </c>
       <c r="B87" t="s">
-        <v>1603</v>
+        <v>1812</v>
       </c>
       <c r="C87" t="s">
-        <v>1604</v>
+        <v>1813</v>
       </c>
       <c r="D87" t="s">
         <v>35</v>
@@ -14795,23 +16415,26 @@
       <c r="G87" t="s">
         <v>89</v>
       </c>
+      <c r="H87" t="s">
+        <v>1814</v>
+      </c>
       <c r="I87" t="s">
-        <v>1605</v>
+        <v>1815</v>
       </c>
       <c r="J87" t="s">
-        <v>1606</v>
+        <v>1816</v>
       </c>
       <c r="K87" t="s">
-        <v>1607</v>
+        <v>1817</v>
       </c>
       <c r="L87" t="s">
-        <v>1608</v>
+        <v>1818</v>
       </c>
       <c r="M87" t="s">
-        <v>1609</v>
+        <v>1819</v>
       </c>
       <c r="N87" t="s">
-        <v>1610</v>
+        <v>1820</v>
       </c>
       <c r="O87" t="s">
         <v>141</v>
@@ -14826,27 +16449,54 @@
         <v>48</v>
       </c>
       <c r="T87" t="s">
-        <v>1611</v>
+        <v>1821</v>
       </c>
       <c r="U87" t="s">
-        <v>1612</v>
+        <v>1822</v>
       </c>
       <c r="V87" t="s">
-        <v>1613</v>
+        <v>1823</v>
       </c>
       <c r="W87" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X87" t="s">
+        <v>1824</v>
+      </c>
+      <c r="Y87" t="s">
+        <v>1825</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>1826</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>1827</v>
+      </c>
+      <c r="AB87" t="s">
+        <v>1828</v>
+      </c>
+      <c r="AC87" t="s">
+        <v>1499</v>
+      </c>
+      <c r="AD87" t="s">
+        <v>1829</v>
+      </c>
+      <c r="AE87" t="s">
+        <v>1830</v>
+      </c>
+      <c r="AF87" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="88" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1614</v>
+        <v>1831</v>
       </c>
       <c r="B88" t="s">
-        <v>1615</v>
+        <v>1832</v>
       </c>
       <c r="C88" t="s">
-        <v>1616</v>
+        <v>1833</v>
       </c>
       <c r="D88" t="s">
         <v>157</v>
@@ -14860,23 +16510,26 @@
       <c r="G88" t="s">
         <v>158</v>
       </c>
+      <c r="H88" t="s">
+        <v>1834</v>
+      </c>
       <c r="I88" t="s">
-        <v>1617</v>
+        <v>1835</v>
       </c>
       <c r="J88" t="s">
-        <v>1618</v>
+        <v>1836</v>
       </c>
       <c r="K88" t="s">
-        <v>1619</v>
+        <v>1837</v>
       </c>
       <c r="L88" t="s">
-        <v>1620</v>
+        <v>1838</v>
       </c>
       <c r="M88" t="s">
-        <v>1621</v>
+        <v>1839</v>
       </c>
       <c r="N88" t="s">
-        <v>1622</v>
+        <v>1840</v>
       </c>
       <c r="P88" t="s">
         <v>166</v>
@@ -14891,27 +16544,54 @@
         <v>167</v>
       </c>
       <c r="T88" t="s">
-        <v>1623</v>
+        <v>1841</v>
       </c>
       <c r="U88" t="s">
-        <v>1624</v>
+        <v>1842</v>
       </c>
       <c r="V88" t="s">
-        <v>1625</v>
+        <v>1843</v>
       </c>
       <c r="W88" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X88" t="s">
+        <v>1844</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>1845</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>1846</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>1847</v>
+      </c>
+      <c r="AB88" t="s">
+        <v>1848</v>
+      </c>
+      <c r="AC88" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD88" t="s">
+        <v>1849</v>
+      </c>
+      <c r="AE88" t="s">
+        <v>1850</v>
+      </c>
+      <c r="AF88" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1626</v>
+        <v>1851</v>
       </c>
       <c r="B89" t="s">
-        <v>1627</v>
+        <v>1852</v>
       </c>
       <c r="C89" t="s">
-        <v>1628</v>
+        <v>1853</v>
       </c>
       <c r="D89" t="s">
         <v>65</v>
@@ -14925,23 +16605,26 @@
       <c r="G89" t="s">
         <v>309</v>
       </c>
+      <c r="H89" t="s">
+        <v>1854</v>
+      </c>
       <c r="I89" t="s">
-        <v>1629</v>
+        <v>1855</v>
       </c>
       <c r="J89" t="s">
-        <v>1630</v>
+        <v>1856</v>
       </c>
       <c r="K89" t="s">
-        <v>1631</v>
+        <v>1857</v>
       </c>
       <c r="L89" t="s">
-        <v>1632</v>
+        <v>1858</v>
       </c>
       <c r="M89" t="s">
-        <v>1633</v>
+        <v>1859</v>
       </c>
       <c r="N89" t="s">
-        <v>1634</v>
+        <v>1860</v>
       </c>
       <c r="P89" t="s">
         <v>46</v>
@@ -14953,27 +16636,54 @@
         <v>48</v>
       </c>
       <c r="T89" t="s">
-        <v>1635</v>
+        <v>1861</v>
       </c>
       <c r="U89" t="s">
-        <v>1636</v>
+        <v>1862</v>
       </c>
       <c r="V89" t="s">
-        <v>1637</v>
+        <v>1863</v>
       </c>
       <c r="W89" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X89" t="s">
+        <v>1864</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>1865</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>1866</v>
+      </c>
+      <c r="AA89" t="s">
+        <v>1867</v>
+      </c>
+      <c r="AB89" t="s">
+        <v>1868</v>
+      </c>
+      <c r="AC89" t="s">
+        <v>1869</v>
+      </c>
+      <c r="AD89" t="s">
+        <v>1870</v>
+      </c>
+      <c r="AE89" t="s">
+        <v>1871</v>
+      </c>
+      <c r="AF89" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1638</v>
+        <v>1872</v>
       </c>
       <c r="B90" t="s">
-        <v>1639</v>
+        <v>1873</v>
       </c>
       <c r="C90" t="s">
-        <v>1640</v>
+        <v>1874</v>
       </c>
       <c r="D90" t="s">
         <v>65</v>
@@ -14987,23 +16697,26 @@
       <c r="G90" t="s">
         <v>331</v>
       </c>
+      <c r="H90" t="s">
+        <v>1875</v>
+      </c>
       <c r="I90" t="s">
-        <v>1641</v>
+        <v>1876</v>
       </c>
       <c r="J90" t="s">
-        <v>1642</v>
+        <v>1877</v>
       </c>
       <c r="K90" t="s">
-        <v>1643</v>
+        <v>1878</v>
       </c>
       <c r="L90" t="s">
-        <v>1644</v>
+        <v>1879</v>
       </c>
       <c r="M90" t="s">
-        <v>1645</v>
+        <v>1880</v>
       </c>
       <c r="N90" t="s">
-        <v>1646</v>
+        <v>1881</v>
       </c>
       <c r="P90" t="s">
         <v>46</v>
@@ -15015,27 +16728,54 @@
         <v>48</v>
       </c>
       <c r="T90" t="s">
-        <v>1647</v>
+        <v>1882</v>
       </c>
       <c r="U90" t="s">
-        <v>1648</v>
+        <v>1883</v>
       </c>
       <c r="V90" t="s">
-        <v>1649</v>
+        <v>1884</v>
       </c>
       <c r="W90" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X90" t="s">
+        <v>1885</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>1886</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>1887</v>
+      </c>
+      <c r="AA90" t="s">
+        <v>1888</v>
+      </c>
+      <c r="AB90" t="s">
+        <v>1889</v>
+      </c>
+      <c r="AC90" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD90" t="s">
+        <v>1890</v>
+      </c>
+      <c r="AE90" t="s">
+        <v>1891</v>
+      </c>
+      <c r="AF90" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1650</v>
+        <v>1892</v>
       </c>
       <c r="B91" t="s">
-        <v>1651</v>
+        <v>1893</v>
       </c>
       <c r="C91" t="s">
-        <v>1652</v>
+        <v>1894</v>
       </c>
       <c r="D91" t="s">
         <v>65</v>
@@ -15049,23 +16789,26 @@
       <c r="G91" t="s">
         <v>500</v>
       </c>
+      <c r="H91" t="s">
+        <v>1895</v>
+      </c>
       <c r="I91" t="s">
-        <v>1653</v>
+        <v>1896</v>
       </c>
       <c r="J91" t="s">
-        <v>1654</v>
+        <v>1897</v>
       </c>
       <c r="K91" t="s">
-        <v>1655</v>
+        <v>1898</v>
       </c>
       <c r="L91" t="s">
-        <v>1656</v>
+        <v>1899</v>
       </c>
       <c r="M91" t="s">
-        <v>1657</v>
+        <v>1900</v>
       </c>
       <c r="N91" t="s">
-        <v>1658</v>
+        <v>1901</v>
       </c>
       <c r="P91" t="s">
         <v>46</v>
@@ -15077,27 +16820,54 @@
         <v>48</v>
       </c>
       <c r="T91" t="s">
-        <v>1659</v>
+        <v>1902</v>
       </c>
       <c r="U91" t="s">
-        <v>1660</v>
+        <v>1903</v>
       </c>
       <c r="V91" t="s">
-        <v>1661</v>
+        <v>1904</v>
       </c>
       <c r="W91" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X91" t="s">
+        <v>1905</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>1906</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>1907</v>
+      </c>
+      <c r="AA91" t="s">
+        <v>1908</v>
+      </c>
+      <c r="AB91" t="s">
+        <v>1909</v>
+      </c>
+      <c r="AC91" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD91" t="s">
+        <v>1910</v>
+      </c>
+      <c r="AE91" t="s">
+        <v>1911</v>
+      </c>
+      <c r="AF91" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="92" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1662</v>
+        <v>1912</v>
       </c>
       <c r="B92" t="s">
-        <v>1663</v>
+        <v>1913</v>
       </c>
       <c r="C92" t="s">
-        <v>1664</v>
+        <v>1914</v>
       </c>
       <c r="D92" t="s">
         <v>157</v>
@@ -15111,23 +16881,26 @@
       <c r="G92" t="s">
         <v>158</v>
       </c>
+      <c r="H92" t="s">
+        <v>1915</v>
+      </c>
       <c r="I92" t="s">
-        <v>1665</v>
+        <v>1916</v>
       </c>
       <c r="J92" t="s">
-        <v>1666</v>
+        <v>1917</v>
       </c>
       <c r="K92" t="s">
-        <v>1667</v>
+        <v>1918</v>
       </c>
       <c r="L92" t="s">
-        <v>1668</v>
+        <v>1919</v>
       </c>
       <c r="M92" t="s">
-        <v>1669</v>
+        <v>1920</v>
       </c>
       <c r="N92" t="s">
-        <v>1670</v>
+        <v>1921</v>
       </c>
       <c r="P92" t="s">
         <v>166</v>
@@ -15142,27 +16915,54 @@
         <v>167</v>
       </c>
       <c r="T92" t="s">
-        <v>1671</v>
+        <v>1922</v>
       </c>
       <c r="U92" t="s">
-        <v>1672</v>
+        <v>1923</v>
       </c>
       <c r="V92" t="s">
-        <v>1673</v>
+        <v>1924</v>
       </c>
       <c r="W92" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X92" t="s">
+        <v>1925</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>1926</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>1927</v>
+      </c>
+      <c r="AA92" t="s">
+        <v>1928</v>
+      </c>
+      <c r="AB92" t="s">
+        <v>1929</v>
+      </c>
+      <c r="AC92" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD92" t="s">
+        <v>1930</v>
+      </c>
+      <c r="AE92" t="s">
+        <v>1931</v>
+      </c>
+      <c r="AF92" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="93" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1674</v>
+        <v>1932</v>
       </c>
       <c r="B93" t="s">
-        <v>1675</v>
+        <v>1933</v>
       </c>
       <c r="C93" t="s">
-        <v>1676</v>
+        <v>1934</v>
       </c>
       <c r="D93" t="s">
         <v>35</v>
@@ -15176,23 +16976,26 @@
       <c r="G93" t="s">
         <v>500</v>
       </c>
+      <c r="H93" t="s">
+        <v>1935</v>
+      </c>
       <c r="I93" t="s">
-        <v>1677</v>
+        <v>1936</v>
       </c>
       <c r="J93" t="s">
-        <v>1678</v>
+        <v>1937</v>
       </c>
       <c r="K93" t="s">
-        <v>1679</v>
+        <v>1938</v>
       </c>
       <c r="L93" t="s">
-        <v>1680</v>
+        <v>1939</v>
       </c>
       <c r="M93" t="s">
-        <v>1681</v>
+        <v>1940</v>
       </c>
       <c r="N93" t="s">
-        <v>1682</v>
+        <v>1941</v>
       </c>
       <c r="O93" t="s">
         <v>141</v>
@@ -15210,27 +17013,54 @@
         <v>167</v>
       </c>
       <c r="T93" t="s">
-        <v>1683</v>
+        <v>1942</v>
       </c>
       <c r="U93" t="s">
-        <v>1684</v>
+        <v>1943</v>
       </c>
       <c r="V93" t="s">
-        <v>1685</v>
+        <v>1944</v>
       </c>
       <c r="W93" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X93" t="s">
+        <v>1945</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>1946</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>1947</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>1948</v>
+      </c>
+      <c r="AB93" t="s">
+        <v>1949</v>
+      </c>
+      <c r="AC93" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD93" t="s">
+        <v>1950</v>
+      </c>
+      <c r="AE93" t="s">
+        <v>1951</v>
+      </c>
+      <c r="AF93" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="94" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1686</v>
+        <v>1952</v>
       </c>
       <c r="B94" t="s">
-        <v>1687</v>
+        <v>1953</v>
       </c>
       <c r="C94" t="s">
-        <v>1688</v>
+        <v>1954</v>
       </c>
       <c r="D94" t="s">
         <v>65</v>
@@ -15244,23 +17074,26 @@
       <c r="G94" t="s">
         <v>309</v>
       </c>
+      <c r="H94" t="s">
+        <v>1955</v>
+      </c>
       <c r="I94" t="s">
-        <v>1689</v>
+        <v>1956</v>
       </c>
       <c r="J94" t="s">
-        <v>1690</v>
+        <v>1957</v>
       </c>
       <c r="K94" t="s">
-        <v>1691</v>
+        <v>1958</v>
       </c>
       <c r="L94" t="s">
-        <v>1692</v>
+        <v>1959</v>
       </c>
       <c r="M94" t="s">
-        <v>1693</v>
+        <v>1960</v>
       </c>
       <c r="N94" t="s">
-        <v>1694</v>
+        <v>1961</v>
       </c>
       <c r="P94" t="s">
         <v>46</v>
@@ -15272,27 +17105,54 @@
         <v>48</v>
       </c>
       <c r="T94" t="s">
-        <v>1695</v>
+        <v>1962</v>
       </c>
       <c r="U94" t="s">
-        <v>1696</v>
+        <v>1963</v>
       </c>
       <c r="V94" t="s">
-        <v>1697</v>
+        <v>1964</v>
       </c>
       <c r="W94" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X94" t="s">
+        <v>1965</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>1966</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>1967</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>1968</v>
+      </c>
+      <c r="AB94" t="s">
+        <v>1969</v>
+      </c>
+      <c r="AC94" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD94" t="s">
+        <v>1970</v>
+      </c>
+      <c r="AE94" t="s">
+        <v>1971</v>
+      </c>
+      <c r="AF94" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="95" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1698</v>
+        <v>1972</v>
       </c>
       <c r="B95" t="s">
-        <v>1699</v>
+        <v>1973</v>
       </c>
       <c r="C95" t="s">
-        <v>1700</v>
+        <v>1974</v>
       </c>
       <c r="D95" t="s">
         <v>35</v>
@@ -15306,23 +17166,26 @@
       <c r="G95" t="s">
         <v>158</v>
       </c>
+      <c r="H95" t="s">
+        <v>1975</v>
+      </c>
       <c r="I95" t="s">
-        <v>1701</v>
+        <v>1976</v>
       </c>
       <c r="J95" t="s">
-        <v>1702</v>
+        <v>1977</v>
       </c>
       <c r="K95" t="s">
-        <v>1703</v>
+        <v>1978</v>
       </c>
       <c r="L95" t="s">
-        <v>1704</v>
+        <v>1979</v>
       </c>
       <c r="M95" t="s">
-        <v>1705</v>
+        <v>1980</v>
       </c>
       <c r="N95" t="s">
-        <v>1706</v>
+        <v>1981</v>
       </c>
       <c r="P95" t="s">
         <v>46</v>
@@ -15334,27 +17197,54 @@
         <v>48</v>
       </c>
       <c r="T95" t="s">
-        <v>1707</v>
+        <v>1982</v>
       </c>
       <c r="U95" t="s">
-        <v>1708</v>
+        <v>1983</v>
       </c>
       <c r="V95" t="s">
-        <v>1709</v>
+        <v>1984</v>
       </c>
       <c r="W95" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X95" t="s">
+        <v>1985</v>
+      </c>
+      <c r="Y95" t="s">
+        <v>1986</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>1987</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>1988</v>
+      </c>
+      <c r="AB95" t="s">
+        <v>1989</v>
+      </c>
+      <c r="AC95" t="s">
+        <v>282</v>
+      </c>
+      <c r="AD95" t="s">
+        <v>1990</v>
+      </c>
+      <c r="AE95" t="s">
+        <v>1991</v>
+      </c>
+      <c r="AF95" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="96" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1710</v>
+        <v>1992</v>
       </c>
       <c r="B96" t="s">
-        <v>1711</v>
+        <v>1993</v>
       </c>
       <c r="C96" t="s">
-        <v>1712</v>
+        <v>1994</v>
       </c>
       <c r="D96" t="s">
         <v>35</v>
@@ -15368,23 +17258,26 @@
       <c r="G96" t="s">
         <v>158</v>
       </c>
+      <c r="H96" t="s">
+        <v>1995</v>
+      </c>
       <c r="I96" t="s">
-        <v>1713</v>
+        <v>1996</v>
       </c>
       <c r="J96" t="s">
-        <v>1714</v>
+        <v>1997</v>
       </c>
       <c r="K96" t="s">
-        <v>1715</v>
+        <v>1998</v>
       </c>
       <c r="L96" t="s">
-        <v>1716</v>
+        <v>1999</v>
       </c>
       <c r="M96" t="s">
-        <v>1717</v>
+        <v>2000</v>
       </c>
       <c r="N96" t="s">
-        <v>1718</v>
+        <v>2001</v>
       </c>
       <c r="P96" t="s">
         <v>46</v>
@@ -15396,27 +17289,54 @@
         <v>48</v>
       </c>
       <c r="T96" t="s">
-        <v>1719</v>
+        <v>2002</v>
       </c>
       <c r="U96" t="s">
-        <v>1720</v>
+        <v>2003</v>
       </c>
       <c r="V96" t="s">
-        <v>1721</v>
+        <v>2004</v>
       </c>
       <c r="W96" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X96" t="s">
+        <v>2005</v>
+      </c>
+      <c r="Y96" t="s">
+        <v>2006</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>2007</v>
+      </c>
+      <c r="AA96" t="s">
+        <v>2008</v>
+      </c>
+      <c r="AB96" t="s">
+        <v>2009</v>
+      </c>
+      <c r="AC96" t="s">
+        <v>1746</v>
+      </c>
+      <c r="AD96" t="s">
+        <v>2010</v>
+      </c>
+      <c r="AE96" t="s">
+        <v>2011</v>
+      </c>
+      <c r="AF96" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="97" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1722</v>
+        <v>2012</v>
       </c>
       <c r="B97" t="s">
-        <v>1723</v>
+        <v>2013</v>
       </c>
       <c r="C97" t="s">
-        <v>1724</v>
+        <v>2014</v>
       </c>
       <c r="D97" t="s">
         <v>35</v>
@@ -15431,22 +17351,22 @@
         <v>158</v>
       </c>
       <c r="I97" t="s">
-        <v>1725</v>
+        <v>2015</v>
       </c>
       <c r="J97" t="s">
-        <v>1726</v>
+        <v>2016</v>
       </c>
       <c r="K97" t="s">
-        <v>1727</v>
+        <v>2017</v>
       </c>
       <c r="L97" t="s">
-        <v>1728</v>
+        <v>2018</v>
       </c>
       <c r="M97" t="s">
-        <v>1729</v>
+        <v>2019</v>
       </c>
       <c r="N97" t="s">
-        <v>1730</v>
+        <v>2020</v>
       </c>
       <c r="P97" t="s">
         <v>166</v>
@@ -15461,13 +17381,13 @@
         <v>167</v>
       </c>
       <c r="T97" t="s">
-        <v>1731</v>
+        <v>2021</v>
       </c>
       <c r="U97" t="s">
-        <v>1732</v>
+        <v>2022</v>
       </c>
       <c r="V97" t="s">
-        <v>1733</v>
+        <v>2023</v>
       </c>
       <c r="W97" s="1" t="s">
         <v>52</v>
@@ -15475,13 +17395,13 @@
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1734</v>
+        <v>2024</v>
       </c>
       <c r="B98" t="s">
-        <v>1735</v>
+        <v>2025</v>
       </c>
       <c r="C98" t="s">
-        <v>1736</v>
+        <v>2026</v>
       </c>
       <c r="D98" t="s">
         <v>157</v>
@@ -15490,25 +17410,25 @@
         <v>132</v>
       </c>
       <c r="F98" t="s">
-        <v>1435</v>
+        <v>1527</v>
       </c>
       <c r="G98" t="s">
         <v>158</v>
       </c>
       <c r="I98" t="s">
-        <v>1737</v>
+        <v>2027</v>
       </c>
       <c r="J98" t="s">
-        <v>1738</v>
+        <v>2028</v>
       </c>
       <c r="K98" t="s">
-        <v>1739</v>
+        <v>2029</v>
       </c>
       <c r="M98" t="s">
-        <v>1740</v>
+        <v>2030</v>
       </c>
       <c r="N98" t="s">
-        <v>1741</v>
+        <v>2031</v>
       </c>
       <c r="O98" t="s">
         <v>141</v>
@@ -15523,30 +17443,30 @@
         <v>48</v>
       </c>
       <c r="S98" t="s">
-        <v>1441</v>
+        <v>1534</v>
       </c>
       <c r="T98" t="s">
-        <v>1742</v>
+        <v>2032</v>
       </c>
       <c r="U98" t="s">
-        <v>1743</v>
+        <v>2033</v>
       </c>
       <c r="V98" t="s">
-        <v>1744</v>
+        <v>2034</v>
       </c>
       <c r="W98" s="1" t="s">
-        <v>1445</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1745</v>
+        <v>2035</v>
       </c>
       <c r="B99" t="s">
-        <v>1746</v>
+        <v>2036</v>
       </c>
       <c r="C99" t="s">
-        <v>1747</v>
+        <v>2037</v>
       </c>
       <c r="D99" t="s">
         <v>35</v>
@@ -15561,22 +17481,22 @@
         <v>89</v>
       </c>
       <c r="I99" t="s">
-        <v>1748</v>
+        <v>2038</v>
       </c>
       <c r="J99" t="s">
-        <v>1749</v>
+        <v>2039</v>
       </c>
       <c r="K99" t="s">
-        <v>1750</v>
+        <v>2040</v>
       </c>
       <c r="L99" t="s">
-        <v>1751</v>
+        <v>2041</v>
       </c>
       <c r="M99" t="s">
-        <v>1752</v>
+        <v>2042</v>
       </c>
       <c r="N99" t="s">
-        <v>1753</v>
+        <v>2043</v>
       </c>
       <c r="O99" t="s">
         <v>141</v>
@@ -15591,13 +17511,13 @@
         <v>48</v>
       </c>
       <c r="T99" t="s">
-        <v>1754</v>
+        <v>2044</v>
       </c>
       <c r="U99" t="s">
-        <v>1755</v>
+        <v>2045</v>
       </c>
       <c r="V99" t="s">
-        <v>1756</v>
+        <v>2046</v>
       </c>
       <c r="W99" s="1" t="s">
         <v>52</v>
@@ -15605,13 +17525,13 @@
     </row>
     <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1757</v>
+        <v>2047</v>
       </c>
       <c r="B100" t="s">
-        <v>1758</v>
+        <v>2048</v>
       </c>
       <c r="C100" t="s">
-        <v>1759</v>
+        <v>2049</v>
       </c>
       <c r="D100" t="s">
         <v>35</v>
@@ -15626,22 +17546,22 @@
         <v>203</v>
       </c>
       <c r="I100" t="s">
-        <v>1760</v>
+        <v>2050</v>
       </c>
       <c r="J100" t="s">
-        <v>1761</v>
+        <v>2051</v>
       </c>
       <c r="K100" t="s">
-        <v>1762</v>
+        <v>2052</v>
       </c>
       <c r="L100" t="s">
-        <v>1763</v>
+        <v>2053</v>
       </c>
       <c r="M100" t="s">
-        <v>1764</v>
+        <v>2054</v>
       </c>
       <c r="N100" t="s">
-        <v>1765</v>
+        <v>2055</v>
       </c>
       <c r="O100" t="s">
         <v>141</v>
@@ -15656,13 +17576,13 @@
         <v>48</v>
       </c>
       <c r="T100" t="s">
-        <v>1766</v>
+        <v>2056</v>
       </c>
       <c r="U100" t="s">
-        <v>1767</v>
+        <v>2057</v>
       </c>
       <c r="V100" t="s">
-        <v>1768</v>
+        <v>2058</v>
       </c>
       <c r="W100" s="1" t="s">
         <v>52</v>
@@ -15670,13 +17590,13 @@
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1769</v>
+        <v>2059</v>
       </c>
       <c r="B101" t="s">
-        <v>1770</v>
+        <v>2060</v>
       </c>
       <c r="C101" t="s">
-        <v>1771</v>
+        <v>2061</v>
       </c>
       <c r="D101" t="s">
         <v>35</v>
@@ -15691,22 +17611,22 @@
         <v>89</v>
       </c>
       <c r="I101" t="s">
-        <v>1772</v>
+        <v>2062</v>
       </c>
       <c r="J101" t="s">
-        <v>1773</v>
+        <v>2063</v>
       </c>
       <c r="K101" t="s">
-        <v>1774</v>
+        <v>2064</v>
       </c>
       <c r="L101" t="s">
-        <v>1775</v>
+        <v>2065</v>
       </c>
       <c r="M101" t="s">
-        <v>1776</v>
+        <v>2066</v>
       </c>
       <c r="N101" t="s">
-        <v>1777</v>
+        <v>2067</v>
       </c>
       <c r="O101" t="s">
         <v>141</v>
@@ -15724,13 +17644,13 @@
         <v>167</v>
       </c>
       <c r="T101" t="s">
-        <v>1778</v>
+        <v>2068</v>
       </c>
       <c r="U101" t="s">
-        <v>1779</v>
+        <v>2069</v>
       </c>
       <c r="V101" t="s">
-        <v>1780</v>
+        <v>2070</v>
       </c>
       <c r="W101" s="1" t="s">
         <v>52</v>
@@ -15738,13 +17658,13 @@
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1781</v>
+        <v>2071</v>
       </c>
       <c r="B102" t="s">
-        <v>1782</v>
+        <v>2072</v>
       </c>
       <c r="C102" t="s">
-        <v>1783</v>
+        <v>2073</v>
       </c>
       <c r="D102" t="s">
         <v>35</v>
@@ -15759,22 +17679,22 @@
         <v>203</v>
       </c>
       <c r="I102" t="s">
-        <v>1784</v>
+        <v>2074</v>
       </c>
       <c r="J102" t="s">
-        <v>1785</v>
+        <v>2075</v>
       </c>
       <c r="K102" t="s">
-        <v>1786</v>
+        <v>2076</v>
       </c>
       <c r="L102" t="s">
-        <v>1787</v>
+        <v>2077</v>
       </c>
       <c r="M102" t="s">
-        <v>1788</v>
+        <v>2078</v>
       </c>
       <c r="N102" t="s">
-        <v>1789</v>
+        <v>2079</v>
       </c>
       <c r="O102" t="s">
         <v>141</v>
@@ -15789,13 +17709,13 @@
         <v>48</v>
       </c>
       <c r="T102" t="s">
-        <v>1790</v>
+        <v>2080</v>
       </c>
       <c r="U102" t="s">
-        <v>1791</v>
+        <v>2081</v>
       </c>
       <c r="V102" t="s">
-        <v>1792</v>
+        <v>2082</v>
       </c>
       <c r="W102" s="1" t="s">
         <v>52</v>
@@ -15803,13 +17723,13 @@
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1793</v>
+        <v>2083</v>
       </c>
       <c r="B103" t="s">
-        <v>1794</v>
+        <v>2084</v>
       </c>
       <c r="C103" t="s">
-        <v>1795</v>
+        <v>2085</v>
       </c>
       <c r="D103" t="s">
         <v>35</v>
@@ -15824,22 +17744,22 @@
         <v>203</v>
       </c>
       <c r="I103" t="s">
-        <v>1796</v>
+        <v>2086</v>
       </c>
       <c r="J103" t="s">
-        <v>1797</v>
+        <v>2087</v>
       </c>
       <c r="K103" t="s">
-        <v>1798</v>
+        <v>2088</v>
       </c>
       <c r="L103" t="s">
-        <v>1799</v>
+        <v>2089</v>
       </c>
       <c r="M103" t="s">
-        <v>1800</v>
+        <v>2090</v>
       </c>
       <c r="N103" t="s">
-        <v>1801</v>
+        <v>2091</v>
       </c>
       <c r="O103" t="s">
         <v>141</v>
@@ -15854,13 +17774,13 @@
         <v>48</v>
       </c>
       <c r="T103" t="s">
-        <v>1802</v>
+        <v>2092</v>
       </c>
       <c r="U103" t="s">
-        <v>1803</v>
+        <v>2093</v>
       </c>
       <c r="V103" t="s">
-        <v>1804</v>
+        <v>2094</v>
       </c>
       <c r="W103" s="1" t="s">
         <v>52</v>
@@ -15868,13 +17788,13 @@
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1805</v>
+        <v>2095</v>
       </c>
       <c r="B104" t="s">
-        <v>1806</v>
+        <v>2096</v>
       </c>
       <c r="C104" t="s">
-        <v>1807</v>
+        <v>2097</v>
       </c>
       <c r="D104" t="s">
         <v>157</v>
@@ -15889,22 +17809,22 @@
         <v>158</v>
       </c>
       <c r="I104" t="s">
-        <v>1808</v>
+        <v>2098</v>
       </c>
       <c r="J104" t="s">
-        <v>1809</v>
+        <v>2099</v>
       </c>
       <c r="K104" t="s">
-        <v>1810</v>
+        <v>2100</v>
       </c>
       <c r="L104" t="s">
-        <v>1811</v>
+        <v>2101</v>
       </c>
       <c r="M104" t="s">
-        <v>1812</v>
+        <v>2102</v>
       </c>
       <c r="N104" t="s">
-        <v>1813</v>
+        <v>2103</v>
       </c>
       <c r="P104" t="s">
         <v>166</v>
@@ -15919,13 +17839,13 @@
         <v>167</v>
       </c>
       <c r="T104" t="s">
-        <v>1814</v>
+        <v>2104</v>
       </c>
       <c r="U104" t="s">
-        <v>1815</v>
+        <v>2105</v>
       </c>
       <c r="V104" t="s">
-        <v>1816</v>
+        <v>2106</v>
       </c>
       <c r="W104" s="1" t="s">
         <v>52</v>
@@ -15933,13 +17853,13 @@
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1817</v>
+        <v>2107</v>
       </c>
       <c r="B105" t="s">
-        <v>1818</v>
+        <v>2108</v>
       </c>
       <c r="C105" t="s">
-        <v>1819</v>
+        <v>2109</v>
       </c>
       <c r="D105" t="s">
         <v>157</v>
@@ -15954,22 +17874,22 @@
         <v>158</v>
       </c>
       <c r="I105" t="s">
-        <v>1820</v>
+        <v>2110</v>
       </c>
       <c r="J105" t="s">
-        <v>1821</v>
+        <v>2111</v>
       </c>
       <c r="K105" t="s">
-        <v>1822</v>
+        <v>2112</v>
       </c>
       <c r="L105" t="s">
-        <v>1823</v>
+        <v>2113</v>
       </c>
       <c r="M105" t="s">
-        <v>1824</v>
+        <v>2114</v>
       </c>
       <c r="N105" t="s">
-        <v>1825</v>
+        <v>2115</v>
       </c>
       <c r="P105" t="s">
         <v>166</v>
@@ -15984,13 +17904,13 @@
         <v>167</v>
       </c>
       <c r="T105" t="s">
-        <v>1826</v>
+        <v>2116</v>
       </c>
       <c r="U105" t="s">
-        <v>1827</v>
+        <v>2117</v>
       </c>
       <c r="V105" t="s">
-        <v>1828</v>
+        <v>2118</v>
       </c>
       <c r="W105" s="1" t="s">
         <v>52</v>
@@ -15998,13 +17918,13 @@
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1829</v>
+        <v>2119</v>
       </c>
       <c r="B106" t="s">
-        <v>1830</v>
+        <v>2120</v>
       </c>
       <c r="C106" t="s">
-        <v>1831</v>
+        <v>2121</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -16019,22 +17939,22 @@
         <v>203</v>
       </c>
       <c r="I106" t="s">
-        <v>1832</v>
+        <v>2122</v>
       </c>
       <c r="J106" t="s">
-        <v>1833</v>
+        <v>2123</v>
       </c>
       <c r="K106" t="s">
-        <v>1834</v>
+        <v>2124</v>
       </c>
       <c r="L106" t="s">
-        <v>1835</v>
+        <v>2125</v>
       </c>
       <c r="M106" t="s">
-        <v>1836</v>
+        <v>2126</v>
       </c>
       <c r="N106" t="s">
-        <v>1837</v>
+        <v>2127</v>
       </c>
       <c r="P106" t="s">
         <v>46</v>
@@ -16046,13 +17966,13 @@
         <v>48</v>
       </c>
       <c r="T106" t="s">
-        <v>1838</v>
+        <v>2128</v>
       </c>
       <c r="U106" t="s">
-        <v>1839</v>
+        <v>2129</v>
       </c>
       <c r="V106" t="s">
-        <v>1840</v>
+        <v>2130</v>
       </c>
       <c r="W106" s="1" t="s">
         <v>52</v>
@@ -16060,13 +17980,13 @@
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1841</v>
+        <v>2131</v>
       </c>
       <c r="B107" t="s">
-        <v>1842</v>
+        <v>2132</v>
       </c>
       <c r="C107" t="s">
-        <v>1843</v>
+        <v>2133</v>
       </c>
       <c r="D107" t="s">
         <v>35</v>
@@ -16081,22 +18001,22 @@
         <v>158</v>
       </c>
       <c r="I107" t="s">
-        <v>1844</v>
+        <v>2134</v>
       </c>
       <c r="J107" t="s">
-        <v>1845</v>
+        <v>2135</v>
       </c>
       <c r="K107" t="s">
-        <v>1846</v>
+        <v>2136</v>
       </c>
       <c r="L107" t="s">
-        <v>1847</v>
+        <v>2137</v>
       </c>
       <c r="M107" t="s">
-        <v>1848</v>
+        <v>2138</v>
       </c>
       <c r="N107" t="s">
-        <v>1849</v>
+        <v>2139</v>
       </c>
       <c r="P107" t="s">
         <v>46</v>
@@ -16108,13 +18028,13 @@
         <v>48</v>
       </c>
       <c r="T107" t="s">
-        <v>1850</v>
+        <v>2140</v>
       </c>
       <c r="U107" t="s">
-        <v>1851</v>
+        <v>2141</v>
       </c>
       <c r="V107" t="s">
-        <v>1852</v>
+        <v>2142</v>
       </c>
       <c r="W107" s="1" t="s">
         <v>52</v>
@@ -16122,13 +18042,13 @@
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1853</v>
+        <v>2143</v>
       </c>
       <c r="B108" t="s">
-        <v>1854</v>
+        <v>2144</v>
       </c>
       <c r="C108" t="s">
-        <v>1855</v>
+        <v>2145</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
@@ -16143,22 +18063,22 @@
         <v>331</v>
       </c>
       <c r="I108" t="s">
-        <v>1856</v>
+        <v>2146</v>
       </c>
       <c r="J108" t="s">
-        <v>1857</v>
+        <v>2147</v>
       </c>
       <c r="K108" t="s">
-        <v>1858</v>
+        <v>2148</v>
       </c>
       <c r="L108" t="s">
-        <v>1859</v>
+        <v>2149</v>
       </c>
       <c r="M108" t="s">
-        <v>1860</v>
+        <v>2150</v>
       </c>
       <c r="N108" t="s">
-        <v>1861</v>
+        <v>2151</v>
       </c>
       <c r="P108" t="s">
         <v>46</v>
@@ -16170,13 +18090,13 @@
         <v>48</v>
       </c>
       <c r="T108" t="s">
-        <v>1862</v>
+        <v>2152</v>
       </c>
       <c r="U108" t="s">
-        <v>1863</v>
+        <v>2153</v>
       </c>
       <c r="V108" t="s">
-        <v>1864</v>
+        <v>2154</v>
       </c>
       <c r="W108" s="1" t="s">
         <v>52</v>
@@ -16184,13 +18104,13 @@
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1865</v>
+        <v>2155</v>
       </c>
       <c r="B109" t="s">
-        <v>1866</v>
+        <v>2156</v>
       </c>
       <c r="C109" t="s">
-        <v>1867</v>
+        <v>2157</v>
       </c>
       <c r="D109" t="s">
         <v>157</v>
@@ -16205,22 +18125,22 @@
         <v>158</v>
       </c>
       <c r="I109" t="s">
-        <v>1868</v>
+        <v>2158</v>
       </c>
       <c r="J109" t="s">
-        <v>1869</v>
+        <v>2159</v>
       </c>
       <c r="K109" t="s">
-        <v>1870</v>
+        <v>2160</v>
       </c>
       <c r="L109" t="s">
-        <v>1871</v>
+        <v>2161</v>
       </c>
       <c r="M109" t="s">
-        <v>1872</v>
+        <v>2162</v>
       </c>
       <c r="N109" t="s">
-        <v>1873</v>
+        <v>2163</v>
       </c>
       <c r="P109" t="s">
         <v>166</v>
@@ -16235,13 +18155,13 @@
         <v>167</v>
       </c>
       <c r="T109" t="s">
-        <v>1874</v>
+        <v>2164</v>
       </c>
       <c r="U109" t="s">
-        <v>1875</v>
+        <v>2165</v>
       </c>
       <c r="V109" t="s">
-        <v>1876</v>
+        <v>2166</v>
       </c>
       <c r="W109" s="1" t="s">
         <v>52</v>
@@ -16249,13 +18169,13 @@
     </row>
     <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1877</v>
+        <v>2167</v>
       </c>
       <c r="B110" t="s">
-        <v>1878</v>
+        <v>2168</v>
       </c>
       <c r="C110" t="s">
-        <v>1879</v>
+        <v>2169</v>
       </c>
       <c r="D110" t="s">
         <v>157</v>
@@ -16270,22 +18190,22 @@
         <v>158</v>
       </c>
       <c r="I110" t="s">
-        <v>1880</v>
+        <v>2170</v>
       </c>
       <c r="J110" t="s">
-        <v>1881</v>
+        <v>2171</v>
       </c>
       <c r="K110" t="s">
-        <v>1882</v>
+        <v>2172</v>
       </c>
       <c r="L110" t="s">
-        <v>1883</v>
+        <v>2173</v>
       </c>
       <c r="M110" t="s">
-        <v>1884</v>
+        <v>2174</v>
       </c>
       <c r="N110" t="s">
-        <v>1885</v>
+        <v>2175</v>
       </c>
       <c r="P110" t="s">
         <v>166</v>
@@ -16300,13 +18220,13 @@
         <v>167</v>
       </c>
       <c r="T110" t="s">
-        <v>1886</v>
+        <v>2176</v>
       </c>
       <c r="U110" t="s">
-        <v>1887</v>
+        <v>2177</v>
       </c>
       <c r="V110" t="s">
-        <v>1888</v>
+        <v>2178</v>
       </c>
       <c r="W110" s="1" t="s">
         <v>52</v>
@@ -16314,13 +18234,13 @@
     </row>
     <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1889</v>
+        <v>2179</v>
       </c>
       <c r="B111" t="s">
-        <v>1890</v>
+        <v>2180</v>
       </c>
       <c r="C111" t="s">
-        <v>1891</v>
+        <v>2181</v>
       </c>
       <c r="D111" t="s">
         <v>65</v>
@@ -16335,22 +18255,22 @@
         <v>89</v>
       </c>
       <c r="I111" t="s">
-        <v>1892</v>
+        <v>2182</v>
       </c>
       <c r="J111" t="s">
-        <v>1893</v>
+        <v>2183</v>
       </c>
       <c r="K111" t="s">
-        <v>1894</v>
+        <v>2184</v>
       </c>
       <c r="L111" t="s">
-        <v>1895</v>
+        <v>2185</v>
       </c>
       <c r="M111" t="s">
-        <v>1896</v>
+        <v>2186</v>
       </c>
       <c r="N111" t="s">
-        <v>1897</v>
+        <v>2187</v>
       </c>
       <c r="P111" t="s">
         <v>166</v>
@@ -16365,13 +18285,13 @@
         <v>167</v>
       </c>
       <c r="T111" t="s">
-        <v>1898</v>
+        <v>2188</v>
       </c>
       <c r="U111" t="s">
-        <v>1899</v>
+        <v>2189</v>
       </c>
       <c r="V111" t="s">
-        <v>1900</v>
+        <v>2190</v>
       </c>
       <c r="W111" s="1" t="s">
         <v>52</v>
@@ -16379,13 +18299,13 @@
     </row>
     <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1901</v>
+        <v>2191</v>
       </c>
       <c r="B112" t="s">
-        <v>1902</v>
+        <v>2192</v>
       </c>
       <c r="C112" t="s">
-        <v>1903</v>
+        <v>2193</v>
       </c>
       <c r="D112" t="s">
         <v>65</v>
@@ -16400,22 +18320,22 @@
         <v>203</v>
       </c>
       <c r="I112" t="s">
-        <v>1904</v>
+        <v>2194</v>
       </c>
       <c r="J112" t="s">
-        <v>1905</v>
+        <v>2195</v>
       </c>
       <c r="K112" t="s">
-        <v>1906</v>
+        <v>2196</v>
       </c>
       <c r="L112" t="s">
-        <v>1907</v>
+        <v>2197</v>
       </c>
       <c r="M112" t="s">
-        <v>1908</v>
+        <v>2198</v>
       </c>
       <c r="N112" t="s">
-        <v>1909</v>
+        <v>2199</v>
       </c>
       <c r="O112" t="s">
         <v>141</v>
@@ -16433,13 +18353,13 @@
         <v>167</v>
       </c>
       <c r="T112" t="s">
-        <v>1910</v>
+        <v>2200</v>
       </c>
       <c r="U112" t="s">
-        <v>1911</v>
+        <v>2201</v>
       </c>
       <c r="V112" t="s">
-        <v>1912</v>
+        <v>2202</v>
       </c>
       <c r="W112" s="1" t="s">
         <v>52</v>
@@ -16447,13 +18367,13 @@
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1913</v>
+        <v>2203</v>
       </c>
       <c r="B113" t="s">
-        <v>1914</v>
+        <v>2204</v>
       </c>
       <c r="C113" t="s">
-        <v>1915</v>
+        <v>2205</v>
       </c>
       <c r="D113" t="s">
         <v>65</v>
@@ -16468,22 +18388,22 @@
         <v>203</v>
       </c>
       <c r="I113" t="s">
-        <v>1916</v>
+        <v>2206</v>
       </c>
       <c r="J113" t="s">
-        <v>1917</v>
+        <v>2207</v>
       </c>
       <c r="K113" t="s">
-        <v>1918</v>
+        <v>2208</v>
       </c>
       <c r="L113" t="s">
-        <v>1919</v>
+        <v>2209</v>
       </c>
       <c r="M113" t="s">
-        <v>1920</v>
+        <v>2210</v>
       </c>
       <c r="N113" t="s">
-        <v>1921</v>
+        <v>2211</v>
       </c>
       <c r="O113" t="s">
         <v>141</v>
@@ -16501,13 +18421,13 @@
         <v>167</v>
       </c>
       <c r="T113" t="s">
-        <v>1922</v>
+        <v>2212</v>
       </c>
       <c r="U113" t="s">
-        <v>1923</v>
+        <v>2213</v>
       </c>
       <c r="V113" t="s">
-        <v>1924</v>
+        <v>2214</v>
       </c>
       <c r="W113" s="1" t="s">
         <v>52</v>
@@ -16515,13 +18435,13 @@
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1925</v>
+        <v>2215</v>
       </c>
       <c r="B114" t="s">
-        <v>1926</v>
+        <v>2216</v>
       </c>
       <c r="C114" t="s">
-        <v>1927</v>
+        <v>2217</v>
       </c>
       <c r="D114" t="s">
         <v>35</v>
@@ -16536,22 +18456,22 @@
         <v>331</v>
       </c>
       <c r="I114" t="s">
-        <v>1928</v>
+        <v>2218</v>
       </c>
       <c r="J114" t="s">
-        <v>1929</v>
+        <v>2219</v>
       </c>
       <c r="K114" t="s">
-        <v>1930</v>
+        <v>2220</v>
       </c>
       <c r="L114" t="s">
-        <v>1931</v>
+        <v>2221</v>
       </c>
       <c r="M114" t="s">
-        <v>1932</v>
+        <v>2222</v>
       </c>
       <c r="N114" t="s">
-        <v>1933</v>
+        <v>2223</v>
       </c>
       <c r="P114" t="s">
         <v>46</v>
@@ -16563,13 +18483,13 @@
         <v>48</v>
       </c>
       <c r="T114" t="s">
-        <v>1934</v>
+        <v>2224</v>
       </c>
       <c r="U114" t="s">
-        <v>1935</v>
+        <v>2225</v>
       </c>
       <c r="V114" t="s">
-        <v>1936</v>
+        <v>2226</v>
       </c>
       <c r="W114" s="1" t="s">
         <v>52</v>
@@ -16577,13 +18497,13 @@
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1937</v>
+        <v>2227</v>
       </c>
       <c r="B115" t="s">
-        <v>1938</v>
+        <v>2228</v>
       </c>
       <c r="C115" t="s">
-        <v>1939</v>
+        <v>2229</v>
       </c>
       <c r="D115" t="s">
         <v>65</v>
@@ -16598,22 +18518,22 @@
         <v>331</v>
       </c>
       <c r="I115" t="s">
-        <v>1940</v>
+        <v>2230</v>
       </c>
       <c r="J115" t="s">
-        <v>1941</v>
+        <v>2231</v>
       </c>
       <c r="K115" t="s">
-        <v>1942</v>
+        <v>2232</v>
       </c>
       <c r="L115" t="s">
-        <v>1943</v>
+        <v>2233</v>
       </c>
       <c r="M115" t="s">
-        <v>1944</v>
+        <v>2234</v>
       </c>
       <c r="N115" t="s">
-        <v>1945</v>
+        <v>2235</v>
       </c>
       <c r="P115" t="s">
         <v>46</v>
@@ -16625,13 +18545,13 @@
         <v>48</v>
       </c>
       <c r="T115" t="s">
-        <v>1946</v>
+        <v>2236</v>
       </c>
       <c r="U115" t="s">
-        <v>1947</v>
+        <v>2237</v>
       </c>
       <c r="V115" t="s">
-        <v>1948</v>
+        <v>2238</v>
       </c>
       <c r="W115" s="1" t="s">
         <v>52</v>
@@ -16639,13 +18559,13 @@
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1949</v>
+        <v>2239</v>
       </c>
       <c r="B116" t="s">
-        <v>1950</v>
+        <v>2240</v>
       </c>
       <c r="C116" t="s">
-        <v>1951</v>
+        <v>2241</v>
       </c>
       <c r="D116" t="s">
         <v>65</v>
@@ -16660,22 +18580,22 @@
         <v>203</v>
       </c>
       <c r="I116" t="s">
-        <v>1952</v>
+        <v>2242</v>
       </c>
       <c r="J116" t="s">
-        <v>1953</v>
+        <v>2243</v>
       </c>
       <c r="K116" t="s">
-        <v>1954</v>
+        <v>2244</v>
       </c>
       <c r="L116" t="s">
-        <v>1955</v>
+        <v>2245</v>
       </c>
       <c r="M116" t="s">
-        <v>1956</v>
+        <v>2246</v>
       </c>
       <c r="N116" t="s">
-        <v>1957</v>
+        <v>2247</v>
       </c>
       <c r="P116" t="s">
         <v>46</v>
@@ -16687,13 +18607,13 @@
         <v>48</v>
       </c>
       <c r="T116" t="s">
-        <v>1958</v>
+        <v>2248</v>
       </c>
       <c r="U116" t="s">
-        <v>1959</v>
+        <v>2249</v>
       </c>
       <c r="V116" t="s">
-        <v>1960</v>
+        <v>2250</v>
       </c>
       <c r="W116" s="1" t="s">
         <v>52</v>
@@ -16701,13 +18621,13 @@
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1961</v>
+        <v>2251</v>
       </c>
       <c r="B117" t="s">
-        <v>1962</v>
+        <v>2252</v>
       </c>
       <c r="C117" t="s">
-        <v>1963</v>
+        <v>2253</v>
       </c>
       <c r="D117" t="s">
         <v>35</v>
@@ -16722,22 +18642,22 @@
         <v>331</v>
       </c>
       <c r="I117" t="s">
-        <v>1964</v>
+        <v>2254</v>
       </c>
       <c r="J117" t="s">
-        <v>1965</v>
+        <v>2255</v>
       </c>
       <c r="K117" t="s">
-        <v>1966</v>
+        <v>2256</v>
       </c>
       <c r="L117" t="s">
-        <v>1967</v>
+        <v>2257</v>
       </c>
       <c r="M117" t="s">
-        <v>1968</v>
+        <v>2258</v>
       </c>
       <c r="N117" t="s">
-        <v>1969</v>
+        <v>2259</v>
       </c>
       <c r="O117" t="s">
         <v>141</v>
@@ -16755,13 +18675,13 @@
         <v>167</v>
       </c>
       <c r="T117" t="s">
-        <v>1970</v>
+        <v>2260</v>
       </c>
       <c r="U117" t="s">
-        <v>1971</v>
+        <v>2261</v>
       </c>
       <c r="V117" t="s">
-        <v>1972</v>
+        <v>2262</v>
       </c>
       <c r="W117" s="1" t="s">
         <v>52</v>
@@ -16769,13 +18689,13 @@
     </row>
     <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1973</v>
+        <v>2263</v>
       </c>
       <c r="B118" t="s">
-        <v>1974</v>
+        <v>2264</v>
       </c>
       <c r="C118" t="s">
-        <v>1975</v>
+        <v>2265</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -16790,22 +18710,22 @@
         <v>158</v>
       </c>
       <c r="I118" t="s">
-        <v>1976</v>
+        <v>2266</v>
       </c>
       <c r="J118" t="s">
-        <v>1977</v>
+        <v>2267</v>
       </c>
       <c r="K118" t="s">
-        <v>1978</v>
+        <v>2268</v>
       </c>
       <c r="L118" t="s">
-        <v>1979</v>
+        <v>2269</v>
       </c>
       <c r="M118" t="s">
-        <v>1980</v>
+        <v>2270</v>
       </c>
       <c r="N118" t="s">
-        <v>1981</v>
+        <v>2271</v>
       </c>
       <c r="P118" t="s">
         <v>166</v>
@@ -16820,13 +18740,13 @@
         <v>167</v>
       </c>
       <c r="T118" t="s">
-        <v>1982</v>
+        <v>2272</v>
       </c>
       <c r="U118" t="s">
-        <v>1983</v>
+        <v>2273</v>
       </c>
       <c r="V118" t="s">
-        <v>1984</v>
+        <v>2274</v>
       </c>
       <c r="W118" s="1" t="s">
         <v>52</v>
@@ -16834,13 +18754,13 @@
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1985</v>
+        <v>2275</v>
       </c>
       <c r="B119" t="s">
-        <v>1986</v>
+        <v>2276</v>
       </c>
       <c r="C119" t="s">
-        <v>1987</v>
+        <v>2277</v>
       </c>
       <c r="D119" t="s">
         <v>35</v>
@@ -16855,22 +18775,22 @@
         <v>203</v>
       </c>
       <c r="I119" t="s">
-        <v>1988</v>
+        <v>2278</v>
       </c>
       <c r="J119" t="s">
-        <v>1989</v>
+        <v>2279</v>
       </c>
       <c r="K119" t="s">
-        <v>1990</v>
+        <v>2280</v>
       </c>
       <c r="L119" t="s">
-        <v>1991</v>
+        <v>2281</v>
       </c>
       <c r="M119" t="s">
-        <v>1992</v>
+        <v>2282</v>
       </c>
       <c r="N119" t="s">
-        <v>1993</v>
+        <v>2283</v>
       </c>
       <c r="O119" t="s">
         <v>141</v>
@@ -16885,13 +18805,13 @@
         <v>48</v>
       </c>
       <c r="T119" t="s">
-        <v>1994</v>
+        <v>2284</v>
       </c>
       <c r="U119" t="s">
-        <v>1995</v>
+        <v>2285</v>
       </c>
       <c r="V119" t="s">
-        <v>1996</v>
+        <v>2286</v>
       </c>
       <c r="W119" s="1" t="s">
         <v>52</v>
@@ -16899,13 +18819,13 @@
     </row>
     <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1997</v>
+        <v>2287</v>
       </c>
       <c r="B120" t="s">
-        <v>1998</v>
+        <v>2288</v>
       </c>
       <c r="C120" t="s">
-        <v>1999</v>
+        <v>2289</v>
       </c>
       <c r="D120" t="s">
         <v>65</v>
@@ -16920,22 +18840,22 @@
         <v>203</v>
       </c>
       <c r="I120" t="s">
-        <v>2000</v>
+        <v>2290</v>
       </c>
       <c r="J120" t="s">
-        <v>2001</v>
+        <v>2291</v>
       </c>
       <c r="K120" t="s">
-        <v>2002</v>
+        <v>2292</v>
       </c>
       <c r="L120" t="s">
-        <v>2003</v>
+        <v>2293</v>
       </c>
       <c r="M120" t="s">
-        <v>2004</v>
+        <v>2294</v>
       </c>
       <c r="N120" t="s">
-        <v>2005</v>
+        <v>2295</v>
       </c>
       <c r="P120" t="s">
         <v>46</v>
@@ -16947,13 +18867,13 @@
         <v>48</v>
       </c>
       <c r="T120" t="s">
-        <v>2006</v>
+        <v>2296</v>
       </c>
       <c r="U120" t="s">
-        <v>2007</v>
+        <v>2297</v>
       </c>
       <c r="V120" t="s">
-        <v>2008</v>
+        <v>2298</v>
       </c>
       <c r="W120" s="1" t="s">
         <v>52</v>
@@ -16961,13 +18881,13 @@
     </row>
     <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2009</v>
+        <v>2299</v>
       </c>
       <c r="B121" t="s">
-        <v>2010</v>
+        <v>2300</v>
       </c>
       <c r="C121" t="s">
-        <v>2011</v>
+        <v>2301</v>
       </c>
       <c r="D121" t="s">
         <v>35</v>
@@ -16982,22 +18902,22 @@
         <v>89</v>
       </c>
       <c r="I121" t="s">
-        <v>2012</v>
+        <v>2302</v>
       </c>
       <c r="J121" t="s">
-        <v>2013</v>
+        <v>2303</v>
       </c>
       <c r="K121" t="s">
-        <v>2014</v>
+        <v>2304</v>
       </c>
       <c r="L121" t="s">
-        <v>2015</v>
+        <v>2305</v>
       </c>
       <c r="M121" t="s">
-        <v>2016</v>
+        <v>2306</v>
       </c>
       <c r="N121" t="s">
-        <v>2017</v>
+        <v>2307</v>
       </c>
       <c r="O121" t="s">
         <v>141</v>
@@ -17012,13 +18932,13 @@
         <v>48</v>
       </c>
       <c r="T121" t="s">
-        <v>2018</v>
+        <v>2308</v>
       </c>
       <c r="U121" t="s">
-        <v>2019</v>
+        <v>2309</v>
       </c>
       <c r="V121" t="s">
-        <v>2020</v>
+        <v>2310</v>
       </c>
       <c r="W121" s="1" t="s">
         <v>52</v>
@@ -17026,13 +18946,13 @@
     </row>
     <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>2021</v>
+        <v>2311</v>
       </c>
       <c r="B122" t="s">
-        <v>2022</v>
+        <v>2312</v>
       </c>
       <c r="C122" t="s">
-        <v>2023</v>
+        <v>2313</v>
       </c>
       <c r="D122" t="s">
         <v>65</v>
@@ -17047,22 +18967,22 @@
         <v>331</v>
       </c>
       <c r="I122" t="s">
-        <v>2024</v>
+        <v>2314</v>
       </c>
       <c r="J122" t="s">
-        <v>2025</v>
+        <v>2315</v>
       </c>
       <c r="K122" t="s">
-        <v>2026</v>
+        <v>2316</v>
       </c>
       <c r="L122" t="s">
-        <v>2027</v>
+        <v>2317</v>
       </c>
       <c r="M122" t="s">
-        <v>2028</v>
+        <v>2318</v>
       </c>
       <c r="N122" t="s">
-        <v>2029</v>
+        <v>2319</v>
       </c>
       <c r="P122" t="s">
         <v>46</v>
@@ -17074,13 +18994,13 @@
         <v>48</v>
       </c>
       <c r="T122" t="s">
-        <v>2030</v>
+        <v>2320</v>
       </c>
       <c r="U122" t="s">
-        <v>2031</v>
+        <v>2321</v>
       </c>
       <c r="V122" t="s">
-        <v>2032</v>
+        <v>2322</v>
       </c>
       <c r="W122" s="1" t="s">
         <v>52</v>
@@ -17088,13 +19008,13 @@
     </row>
     <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2033</v>
+        <v>2323</v>
       </c>
       <c r="B123" t="s">
-        <v>2034</v>
+        <v>2324</v>
       </c>
       <c r="C123" t="s">
-        <v>2035</v>
+        <v>2325</v>
       </c>
       <c r="D123" t="s">
         <v>65</v>
@@ -17109,22 +19029,22 @@
         <v>203</v>
       </c>
       <c r="I123" t="s">
-        <v>2036</v>
+        <v>2326</v>
       </c>
       <c r="J123" t="s">
-        <v>2037</v>
+        <v>2327</v>
       </c>
       <c r="K123" t="s">
-        <v>2038</v>
+        <v>2328</v>
       </c>
       <c r="L123" t="s">
-        <v>2039</v>
+        <v>2329</v>
       </c>
       <c r="M123" t="s">
-        <v>2040</v>
+        <v>2330</v>
       </c>
       <c r="N123" t="s">
-        <v>2041</v>
+        <v>2331</v>
       </c>
       <c r="P123" t="s">
         <v>46</v>
@@ -17136,13 +19056,13 @@
         <v>48</v>
       </c>
       <c r="T123" t="s">
-        <v>2042</v>
+        <v>2332</v>
       </c>
       <c r="U123" t="s">
-        <v>2043</v>
+        <v>2333</v>
       </c>
       <c r="V123" t="s">
-        <v>2044</v>
+        <v>2334</v>
       </c>
       <c r="W123" s="1" t="s">
         <v>52</v>
@@ -17150,13 +19070,13 @@
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2045</v>
+        <v>2335</v>
       </c>
       <c r="B124" t="s">
-        <v>2046</v>
+        <v>2336</v>
       </c>
       <c r="C124" t="s">
-        <v>2047</v>
+        <v>2337</v>
       </c>
       <c r="D124" t="s">
         <v>65</v>
@@ -17171,22 +19091,22 @@
         <v>331</v>
       </c>
       <c r="I124" t="s">
-        <v>2048</v>
+        <v>2338</v>
       </c>
       <c r="J124" t="s">
-        <v>2049</v>
+        <v>2339</v>
       </c>
       <c r="K124" t="s">
-        <v>2050</v>
+        <v>2340</v>
       </c>
       <c r="L124" t="s">
-        <v>2051</v>
+        <v>2341</v>
       </c>
       <c r="M124" t="s">
-        <v>2052</v>
+        <v>2342</v>
       </c>
       <c r="N124" t="s">
-        <v>2053</v>
+        <v>2343</v>
       </c>
       <c r="P124" t="s">
         <v>46</v>
@@ -17198,13 +19118,13 @@
         <v>48</v>
       </c>
       <c r="T124" t="s">
-        <v>2054</v>
+        <v>2344</v>
       </c>
       <c r="U124" t="s">
-        <v>2055</v>
+        <v>2345</v>
       </c>
       <c r="V124" t="s">
-        <v>2056</v>
+        <v>2346</v>
       </c>
       <c r="W124" s="1" t="s">
         <v>52</v>
@@ -17212,13 +19132,13 @@
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>2057</v>
+        <v>2347</v>
       </c>
       <c r="B125" t="s">
-        <v>2058</v>
+        <v>2348</v>
       </c>
       <c r="C125" t="s">
-        <v>2059</v>
+        <v>2349</v>
       </c>
       <c r="D125" t="s">
         <v>35</v>
@@ -17233,22 +19153,22 @@
         <v>203</v>
       </c>
       <c r="I125" t="s">
-        <v>2060</v>
+        <v>2350</v>
       </c>
       <c r="J125" t="s">
-        <v>2061</v>
+        <v>2351</v>
       </c>
       <c r="K125" t="s">
-        <v>2062</v>
+        <v>2352</v>
       </c>
       <c r="L125" t="s">
-        <v>2063</v>
+        <v>2353</v>
       </c>
       <c r="M125" t="s">
-        <v>2064</v>
+        <v>2354</v>
       </c>
       <c r="N125" t="s">
-        <v>2065</v>
+        <v>2355</v>
       </c>
       <c r="O125" t="s">
         <v>141</v>
@@ -17263,13 +19183,13 @@
         <v>48</v>
       </c>
       <c r="T125" t="s">
-        <v>2066</v>
+        <v>2356</v>
       </c>
       <c r="U125" t="s">
-        <v>2067</v>
+        <v>2357</v>
       </c>
       <c r="V125" t="s">
-        <v>2068</v>
+        <v>2358</v>
       </c>
       <c r="W125" s="1" t="s">
         <v>52</v>
@@ -17277,13 +19197,13 @@
     </row>
     <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>2069</v>
+        <v>2359</v>
       </c>
       <c r="B126" t="s">
-        <v>2070</v>
+        <v>2360</v>
       </c>
       <c r="C126" t="s">
-        <v>2071</v>
+        <v>2361</v>
       </c>
       <c r="D126" t="s">
         <v>65</v>
@@ -17298,22 +19218,22 @@
         <v>38</v>
       </c>
       <c r="I126" t="s">
-        <v>2072</v>
+        <v>2362</v>
       </c>
       <c r="J126" t="s">
-        <v>2073</v>
+        <v>2363</v>
       </c>
       <c r="K126" t="s">
-        <v>2074</v>
+        <v>2364</v>
       </c>
       <c r="L126" t="s">
-        <v>2075</v>
+        <v>2365</v>
       </c>
       <c r="M126" t="s">
-        <v>2076</v>
+        <v>2366</v>
       </c>
       <c r="N126" t="s">
-        <v>2077</v>
+        <v>2367</v>
       </c>
       <c r="O126" t="s">
         <v>141</v>
@@ -17331,13 +19251,13 @@
         <v>167</v>
       </c>
       <c r="T126" t="s">
-        <v>2078</v>
+        <v>2368</v>
       </c>
       <c r="U126" t="s">
-        <v>2079</v>
+        <v>2369</v>
       </c>
       <c r="V126" t="s">
-        <v>2080</v>
+        <v>2370</v>
       </c>
       <c r="W126" s="1" t="s">
         <v>52</v>
@@ -17345,13 +19265,13 @@
     </row>
     <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2081</v>
+        <v>2371</v>
       </c>
       <c r="B127" t="s">
-        <v>2082</v>
+        <v>2372</v>
       </c>
       <c r="C127" t="s">
-        <v>2083</v>
+        <v>2373</v>
       </c>
       <c r="D127" t="s">
         <v>157</v>
@@ -17360,25 +19280,25 @@
         <v>132</v>
       </c>
       <c r="F127" t="s">
-        <v>1435</v>
+        <v>1527</v>
       </c>
       <c r="G127" t="s">
         <v>158</v>
       </c>
       <c r="I127" t="s">
-        <v>2084</v>
+        <v>2374</v>
       </c>
       <c r="J127" t="s">
-        <v>2085</v>
+        <v>2375</v>
       </c>
       <c r="K127" t="s">
-        <v>2086</v>
+        <v>2376</v>
       </c>
       <c r="M127" t="s">
-        <v>2087</v>
+        <v>2377</v>
       </c>
       <c r="N127" t="s">
-        <v>2088</v>
+        <v>2378</v>
       </c>
       <c r="O127" t="s">
         <v>141</v>
@@ -17393,30 +19313,30 @@
         <v>48</v>
       </c>
       <c r="S127" t="s">
-        <v>1441</v>
+        <v>1534</v>
       </c>
       <c r="T127" t="s">
-        <v>2089</v>
+        <v>2379</v>
       </c>
       <c r="U127" t="s">
-        <v>2090</v>
+        <v>2380</v>
       </c>
       <c r="V127" t="s">
-        <v>2091</v>
+        <v>2381</v>
       </c>
       <c r="W127" s="1" t="s">
-        <v>1445</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>2092</v>
+        <v>2382</v>
       </c>
       <c r="B128" t="s">
-        <v>2093</v>
+        <v>2383</v>
       </c>
       <c r="C128" t="s">
-        <v>2094</v>
+        <v>2384</v>
       </c>
       <c r="D128" t="s">
         <v>65</v>
@@ -17431,22 +19351,22 @@
         <v>203</v>
       </c>
       <c r="I128" t="s">
-        <v>2095</v>
+        <v>2385</v>
       </c>
       <c r="J128" t="s">
-        <v>2096</v>
+        <v>2386</v>
       </c>
       <c r="K128" t="s">
-        <v>2097</v>
+        <v>2387</v>
       </c>
       <c r="L128" t="s">
-        <v>2098</v>
+        <v>2388</v>
       </c>
       <c r="M128" t="s">
-        <v>2099</v>
+        <v>2389</v>
       </c>
       <c r="N128" t="s">
-        <v>2100</v>
+        <v>2390</v>
       </c>
       <c r="P128" t="s">
         <v>46</v>
@@ -17458,13 +19378,13 @@
         <v>48</v>
       </c>
       <c r="T128" t="s">
-        <v>2101</v>
+        <v>2391</v>
       </c>
       <c r="U128" t="s">
-        <v>2102</v>
+        <v>2392</v>
       </c>
       <c r="V128" t="s">
-        <v>2103</v>
+        <v>2393</v>
       </c>
       <c r="W128" s="1" t="s">
         <v>52</v>
@@ -17472,13 +19392,13 @@
     </row>
     <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2104</v>
+        <v>2394</v>
       </c>
       <c r="B129" t="s">
-        <v>2105</v>
+        <v>2395</v>
       </c>
       <c r="C129" t="s">
-        <v>2106</v>
+        <v>2396</v>
       </c>
       <c r="D129" t="s">
         <v>35</v>
@@ -17493,22 +19413,22 @@
         <v>203</v>
       </c>
       <c r="I129" t="s">
-        <v>2107</v>
+        <v>2397</v>
       </c>
       <c r="J129" t="s">
-        <v>2108</v>
+        <v>2398</v>
       </c>
       <c r="K129" t="s">
-        <v>2109</v>
+        <v>2399</v>
       </c>
       <c r="L129" t="s">
-        <v>2110</v>
+        <v>2400</v>
       </c>
       <c r="M129" t="s">
-        <v>2111</v>
+        <v>2401</v>
       </c>
       <c r="N129" t="s">
-        <v>2112</v>
+        <v>2402</v>
       </c>
       <c r="P129" t="s">
         <v>46</v>
@@ -17520,13 +19440,13 @@
         <v>48</v>
       </c>
       <c r="T129" t="s">
-        <v>2113</v>
+        <v>2403</v>
       </c>
       <c r="U129" t="s">
-        <v>2114</v>
+        <v>2404</v>
       </c>
       <c r="V129" t="s">
-        <v>2115</v>
+        <v>2405</v>
       </c>
       <c r="W129" s="1" t="s">
         <v>52</v>

--- a/input/cursos.xlsx
+++ b/input/cursos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3614" uniqueCount="2406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3944" uniqueCount="2675">
   <si>
     <t>course_id</t>
   </si>
@@ -6697,6 +6697,9 @@
     <t>ciencias-biologicas</t>
   </si>
   <si>
+    <t>Pesquise biodiversidade, evolução e biotecnologia em projetos ambientais, de saúde e de conservação da vida.</t>
+  </si>
+  <si>
     <t>O curso de Bacharelado em Ciências Biológicas semipresencial, busca formar profissionais capacitados para lidar com projetos e pesquisas voltados para o meio ambiente,saúde e biotecnologia, habilitado para compreender sobre a diversidade de formas de vida e ação de processos evolutivos, estudando de forma abrangente e completa toda a vida existente no planeta. O curso oferece material didático que fomenta o aprendizado e a curiosidade para realizar pesquisas e diversas atividades extracurriculares. Com duração de 8 semestres (4 anos), o curso fornece o diploma de Bacharel em Ciências Biológicas.</t>
   </si>
   <si>
@@ -6730,6 +6733,27 @@
     <t>Estude Ciências Biológicas a distância com a mesma qualidade do presencial. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Amostragem de biodiversidade em campo de pesquisa</t>
+  </si>
+  <si>
+    <t>Bióloga de cerca de 27 anos, mulher de pele negra, cabelo crespo com boné, camisa de campo, atenção à bandeja de amostras.</t>
+  </si>
+  <si>
+    <t>Trilha organizada de reserva brasileira contemporânea, vegetação, mesa dobrável, céu de manhã, espaço de pesquisa, sem consultório e sem curral.</t>
+  </si>
+  <si>
+    <t>rede entomológica, bandeja de amostras, lupa de campo, caderno, frascos vazios</t>
+  </si>
+  <si>
+    <t>Separa insetos na bandeja com a lupa e anota no caderno, em pé à direita da trilha.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; jaleco hospitalar; microscópio clínico; animal ferido; cirurgia; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional da manhã. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Bióloga, mulher de pele negra, cerca de 27 anos, boné, na trilha de reserva, separando amostras na bandeja com a lupa. Objetos: rede entomológica, bandeja, lupa, caderno e frascos. Sem jaleco hospitalar, sem microscópio clínico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>formacao-pedagogica-geografia-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -6737,6 +6761,9 @@
   </si>
   <si>
     <t>formacao-pedagogica-geografia</t>
+  </si>
+  <si>
+    <t>Monte kits de aula de espaço geográfico, mapas e coordenação escolar para quem já concluiu pedagogia.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Formação Pedagógica em Geografia da Cruzeiro do Sul Virtual está disponível no formato Semipresencial e é destinado especificamente a alunos que já possuem uma graduação em Pedagogia. Ao longo da formação, o curso terá foco em despertar questionamento crítico e reflexivo para os profissionais dessa área da educação acerca de vários temas das geografias humana e física.
@@ -6768,6 +6795,27 @@
     <t>Conquiste sua Formação Pedagógica em Geografia semipresencial na Cruzeiro do Sul Virtual e habilite-se para dar aulas de Geografia no Ensino Fundamental e Médio.</t>
   </si>
   <si>
+    <t>Montagem de sequência didática de geografia</t>
+  </si>
+  <si>
+    <t>Formadora pedagógica de cerca de 31 anos, mulher de pele morena, cabelo pixie preto, camisa listrada, atenção à mapoteca.</t>
+  </si>
+  <si>
+    <t>Sala de mapoteca escolar brasileira contemporânea, gaveteiro de mapas, mesa alta, janela, espaço de preparação, sem turma e sem globo em uso.</t>
+  </si>
+  <si>
+    <t>gaveta de mapas mudos, cartões de aula em branco, tesoura escolar, cola, caderno pedagógico</t>
+  </si>
+  <si>
+    <t>Retira um mapa mudo da gaveta e recorta cartões de aula em branco, em pé à direita da mapoteca.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; globo como ação principal; GPS de campo; giz no quadro de turma; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Formadora pedagógica, mulher de pele morena, cerca de 31 anos, cabelo pixie, camisa listrada, retirando mapa mudo da gaveta e recortando cartões em branco. Objetos: gaveta de mapas, cartões, tesoura, cola e caderno. Sem globo em uso, sem GPS, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>fonoaudiologia-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -6775,6 +6823,9 @@
   </si>
   <si>
     <t>fonoaudiologia</t>
+  </si>
+  <si>
+    <t>Acompanhe práticas de voz, linguagem, audição e deglutição com foco na comunicação e na qualidade de vida.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Fonoaudiologia Semipresencial visa fornecer conhecimentos para que o aluno adquira competências para avaliar, diagnosticar e tratar questões ligadas à fala, voz, linguagem, audição e deglutição, desenvolvendo habilidades clínicas e técnicas para auxiliar os pacientes na melhoria da comunicação e na qualidade de vida. No curso, é proporcionado um embasamento teórico abrangendo anatomia, fisiologia, psicologia, neurologia e outras disciplinas correlatas à saúde.
@@ -6811,6 +6862,27 @@
     <t>Desenvolva habilidades em Fonoaudiologia a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Exercício de articulação e voz com espelho</t>
+  </si>
+  <si>
+    <t>Fonoaudióloga de cerca de 28 anos, mulher de pele morena, cabelo cacheado curto, camisa e colete clínico, atenção ao espelho.</t>
+  </si>
+  <si>
+    <t>Sala de práticas de comunicação em clínica acessível brasileira, espelho de parede, mesa, janela, espaço digno, sem maca de fisioterapia.</t>
+  </si>
+  <si>
+    <t>espelho, diapasão, cartões de articulação sem escritos, copo d'água, caderno</t>
+  </si>
+  <si>
+    <t>Demonstra a articulação diante do espelho e anota o exercício no caderno, em pé à direita, sem aplicar exame clínico.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico; cura; tratamento; elásticos de reabilitação; utensílio de cozinha adaptado; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Fonoaudióloga, mulher de pele morena, cerca de 28 anos, colete clínico, demonstrando articulação no espelho e anotando no caderno. Objetos: espelho, diapasão, cartões sem escritos, copo e caderno. Sem maca, sem exame clínico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-mecanica-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -6818,6 +6890,9 @@
   </si>
   <si>
     <t>engenharia-mecanica</t>
+  </si>
+  <si>
+    <t>Projete, fabrique e conserve máquinas e equipamentos, com operação e decisões de engenharia mecânica.</t>
   </si>
   <si>
     <t>O bacharelado de Engenharia Mecânica semipresencial da Cruzeiro do Sul Virtual, e foca em proporcionar uma formação de qualidade, robusta e que capacita profissionais para tomar decisões criteriosas e bem fundamentadas, garantindo consistência entre ações e objetivos, habilitando-os para atuar em atividades de projeto, fabricação, operação e conservação de máquinas e equipamentos. Ao longo da graduação, os estudantes são introduzidos ao método teórico-prático, sendo preparados para atuar diretamente em questões complexas e ajudar significativamente no crescimento da engenharia mecânica. Com duração de 10 semestres (5 anos), o currículo do curso oferece uma formação ampla e alinhada às necessidades do mercado atual.</t>
@@ -6853,6 +6928,27 @@
     <t>Desenvolva habilidades em Engenharia Mecânica EAD com flexibilidade e baixo custo. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Conferência de conjunto mecânico e desenho técnico</t>
+  </si>
+  <si>
+    <t>Engenheiro mecânico de cerca de 31 anos, homem de pele negra, cabelo curto, camisa e óculos de proteção na testa, atenção à caixa de engrenagens.</t>
+  </si>
+  <si>
+    <t>Oficina de protótipos mecânicos contemporânea brasileira, bancada de metal, desenho técnico na parede, janela industrial, espaço limpo, sem robô e sem painel elétrico.</t>
+  </si>
+  <si>
+    <t>caixa de engrenagens, desenho técnico sem cotas, chave combinada, parafusos, caderno</t>
+  </si>
+  <si>
+    <t>Encaixa uma engrenagem no conjunto e aperta o parafuso com a chave, em pé à direita da bancada.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; braço robótico; quadro de distribuição elétrica; holograma; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheiro mecânico, homem de pele negra, cerca de 31 anos, óculos de proteção na testa, encaixando uma engrenagem e apertando o parafuso com a chave. Objetos: caixa de engrenagens, desenho sem cotas, chave, parafusos e caderno. Sem robô, sem painel elétrico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>estudos-teoricos-psicanaliticos-e-sociais-ead-bacharelado</t>
   </si>
   <si>
@@ -6860,6 +6956,9 @@
   </si>
   <si>
     <t>estudos-teoricos-psicanaliticos-e-sociais</t>
+  </si>
+  <si>
+    <t>Estude teorias da subjetividade, desenvolvimento psíquico e leitura social em pesquisa psicanalítica.</t>
   </si>
   <si>
     <t>O curso de Estudos Teóricos Psicanalíticos e Sociais EAD da Universidade Cruzeiro do Sul Virtual, oferece uma formação completa na teoria e prática psicanalítica. Com ênfase na compreensão da subjetividade humana, o curso aborda teorias como a freudiana, desenvolvimento psicossexual, interpretação dos sonhos e psicopatologia. Ao final dos 8 semestres (4 anos), os alunos estão preparados para atuar em projetos que envolvem a pesquisa psicanalítica em diferentes âmbitos. O curso confere o título de bacharel.</t>
@@ -6894,6 +6993,30 @@
     <t>Estude Psicanálise a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Leitura comparada de teoria psicanalítica e social</t>
+  </si>
+  <si>
+    <t>Pesquisadora teórica de cerca de 26 anos, mulher de pele clara, cabelo pixie loiro escuro, camisa vinho, leitura atenta.</t>
+  </si>
+  <si>
+    <t>Sala de pesquisa com mural de conceitos em branco, mesa, caixas de fotocópias, janela, sem divã, sem consultório e sem mesa de seminário.</t>
+  </si>
+  <si>
+    <t>mural de conceitos, cartões em branco, livro fechado, caixas de fotocópias, caneta</t>
+  </si>
+  <si>
+    <t>Fixa cartões em branco no mural de conceitos e consulta o livro fechado, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; divã; consulta clínica; psicoterapia; jaleco; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Pesquisadora teórica, mulher de pele clara, cerca de 26 anos, cabelo pixie, camisa vinho, fixando cartões em branco no mural de conceitos. Páginas sem escritos visíveis. Objetos: mural, cartões em branco, livro fechado, caixas e caneta. Sem divã, sem consultório, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-da-computacao-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -6901,6 +7024,9 @@
   </si>
   <si>
     <t>engenharia-da-computacao</t>
+  </si>
+  <si>
+    <t>Integre eletrônica e computação no desenvolvimento, análise e operação de sistemas eletrônicos e computacionais.</t>
   </si>
   <si>
     <t>O curso de Engenharia de Computação semipresencial da Cruzeiro do Sul, forma engenheiros por meio da combinação de teoria e prática. Integrando conhecimentos de eletrônica e computação, o curso se especializa no desenvolvimento, análise e operação de sistemas eletrônicos e computacionais. A graduação une ciências exatas a conhecimentos avançados de computação, preparando profissionais completos, competentes e prontos para o mercado e para as inovações do futuro. Com duração de 10 semestres (5 anos), o curso confere o título de bacharel em Engenharia de Computação.</t>
@@ -6939,6 +7065,30 @@
     <t>Aprenda Engenharia da Computação a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem de placa e teste de sistema embarcado</t>
+  </si>
+  <si>
+    <t>Engenheiro da computação de cerca de 26 anos, homem de pele morena clara, cabelo liso curto, polo e jaleco aberto, atenção à placa.</t>
+  </si>
+  <si>
+    <t>Laboratório de hardware contemporâneo brasileiro, bancada antiestática, ferramentas alinhadas, iluminação clara, sem rack de rede e sem quadro de software.</t>
+  </si>
+  <si>
+    <t>placa de circuito, ferro de solda desligado, osciloscópio, pinça, protoboard</t>
+  </si>
+  <si>
+    <t>Encaixa um componente na placa e observa o traço no osciloscópio, sentada à direita da bancada.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentada à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária de laboratório, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; holograma; capuz de hacker; engrenagens como cena principal; quadro de distribuição; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheiro da computação, homem de pele morena clara, cerca de 26 anos, polo, encaixando componente na placa e olhando o osciloscópio. Objetos: placa, ferro desligado, osciloscópio, pinça e protoboard. Sem holograma, sem capuz, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-eletrica-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -6946,6 +7096,9 @@
   </si>
   <si>
     <t>engenharia-eletrica</t>
+  </si>
+  <si>
+    <t>Monte sistemas de geração, transmissão e distribuição de energia, com projetos elétricos e medições.</t>
   </si>
   <si>
     <t>O curso de Engenharia Elétrica semipresencial, prepara engenheiros para inovar e aplicar novas tecnologias, incentivando uma abordagem reflexiva e criativa na resolução de problemas. Considerando aspectos políticos, econômicos, sociais, ambientais e culturais, o profissional é formado com uma visão ética e humanística.Além de projetar sistemas residenciais, industriais, comerciais e de processamento de sinais digitais e analógicos, essa formação capacita os alunos para elaboração de documentação técnica detalhada, oferecendo uma sólida base teórica e prática através de laboratórios modernos e equipados. O curso tem duração de 10 semestres (5 anos) e confere o título de bacharel em Engenharia Elétrica.</t>
@@ -6982,6 +7135,30 @@
     <t>Aprenda Engenharia Elétrica a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Medição em quadro de distribuição elétrica</t>
+  </si>
+  <si>
+    <t>Engenheiro eletricista de cerca de 35 anos, homem de pele clara, barba curta, camisa, protetor auricular e óculos, multímetro na mão.</t>
+  </si>
+  <si>
+    <t>Sala elétrica industrial contemporânea brasileira, quadro aberto organizado, piso limpo, iluminação industrial, sem bancada de solda e sem engrenagens.</t>
+  </si>
+  <si>
+    <t>quadro de distribuição, multímetro, alicate isolado, prancheta, luvas</t>
+  </si>
+  <si>
+    <t>Apoia as pontas do multímetro no quadro e anota a leitura na prancheta, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem em pé à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária industrial, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; choque; fiação precária; placa de circuito como cena principal; holograma; ambiente de luxo.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheiro eletricista, homem de pele clara, cerca de 35 anos, protetor auricular e óculos, medindo o quadro com o multímetro. Objetos: quadro, multímetro, alicate isolado, prancheta e luvas. Sem placa de circuito em destaque, sem holograma, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>letras-portugues-e-espanhol-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -6989,6 +7166,9 @@
   </si>
   <si>
     <t>letras-portugues-e-espanhol</t>
+  </si>
+  <si>
+    <t>Ensine português e espanhol com literatura, cultura e produção de material didático para a educação básica.</t>
   </si>
   <si>
     <t>O curso de Licenciatura em Letras - Português e Espanhol semipresencial da Cruzeiro do Sul Virtual proporciona uma formação abrangente e integrada nas áreas de língua, literatura e cultura dos idiomas português e espanhol. Os estudantes exploram tanto a linguagem oral quanto escrita, estudam obras literárias de diversas épocas e contextos culturais.Além disso, o curso inclui o estudo dos aspectos histórico-culturais da língua espanhola oral e escrita, contribuindo para a produção de material didático de excelência e oferecendo uma orientação teórico-metodológica sólida. Isso prepara os estudantes não apenas para o ensino das línguas, mas também para participar de atividades de pesquisa e promover o intercâmbio cultural entre os povos de língua portuguesa e hispânica. Com duração de 8 semestres (4 anos), a formação confere o título de licenciatura.</t>
@@ -7027,6 +7207,27 @@
     <t>Aprenda Português e Espanhol a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Aula bilíngue com cartões ilustrados de vocabulário</t>
+  </si>
+  <si>
+    <t>Professora de letras de cerca de 25 anos, mulher de pele morena, cabelo liso com franja, blusa azul e calça, mostrando um cartão.</t>
+  </si>
+  <si>
+    <t>Laboratório de idiomas contemporâneo brasileiro, cabines com fones, mesa central, janela, espaço organizado, sem bandeiras e sem carteiras em fileira.</t>
+  </si>
+  <si>
+    <t>fones, microfone de mesa, cartões ilustrados sem escritos, livros fechados, painel de áudio</t>
+  </si>
+  <si>
+    <t>Mostra um cartão ilustrado e aponta o fone na cabine, em pé à direita da mesa central.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; bandeiras; escritos em espanhol; kanji; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de letras, mulher de pele morena, cerca de 25 anos, blusa azul, mostrando cartão ilustrado sem escritos em laboratório de idiomas com cabines. Objetos: fones, microfone de mesa, cartões, livros fechados e painel de áudio. Sem bandeiras, sem escritos estrangeiros, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>letras-portugues-e-japones-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -7034,6 +7235,9 @@
   </si>
   <si>
     <t>letras-portugues-e-japones</t>
+  </si>
+  <si>
+    <t>Explore compreensão oral, pronúncia e práticas de ensino de português e japonês, com didática e metodologia.</t>
   </si>
   <si>
     <t>O curso Letras - Português e Japonês semipresencial da Cruzeiro do Sul Virtual, sendo uma licenciatura, inclui disciplinas como didática, metodologia e práticas de ensino de línguas, preparando os estudantes para atuarem de forma eficaz nas salas de aula, enriquecendo sua vivência e experiência com os idiomas.Além disso, o curso contempla o estudo detalhado dos aspectos histórico-culturais da língua japonesa, tanto oral quanto escrita, abrangendo os sistemas hiragana, katakana e kanji. Os alunos exploram textos e obras de autores clássicos e contemporâneos, proporcionando uma compreensão profunda da cultura japonesa através da literatura e outras expressões artísticas. Com 8 semestres de duração (4 anos), o curso confere o título de licenciatura.</t>
@@ -7072,6 +7276,27 @@
     <t>Estude Português e Japonês a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Compreensão oral e pronúncia em aula bilíngue</t>
+  </si>
+  <si>
+    <t>Professora de cerca de 29 anos, mulher de pele clara, cabelo preto liso preso, camisa e calça, atenção à turma e à caixa de som.</t>
+  </si>
+  <si>
+    <t>Sala de aula com carteiras em U contemporânea brasileira, caixa de som, quadro apagado, janela, espaço organizado, sem bandeiras, sem caligrafia e sem decoração temática.</t>
+  </si>
+  <si>
+    <t>caixa de som, gravador portátil, microfone de mão, livros fechados, caderno de escuta</t>
+  </si>
+  <si>
+    <t>Liga a caixa de som e demonstra a pronúncia no microfone, em pé à direita, quadro apagado.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; caligrafia; pincel; tinteiro; quimono; anime; bandeiras; caracteres legíveis; cabines de áudio; fantoche; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora, mulher de pele clara, cerca de 29 anos, camisa, em sala com carteiras em U, ligando a caixa de som e demonstrando a pronúncia no microfone. Objetos: caixa de som, gravador, microfone de mão, livros fechados e caderno. Sem caligrafia, sem pincel, sem quimono, sem bandeiras, sem caracteres visíveis, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>design-de-experiencia-ead-tecnologo</t>
   </si>
   <si>
@@ -7079,6 +7304,9 @@
   </si>
   <si>
     <t>design-de-experiencia</t>
+  </si>
+  <si>
+    <t>Mapeie jornadas de uso, prototipagem e testes de usabilidade centrados em produtos e serviços digitais.</t>
   </si>
   <si>
     <t>O curso de Design de Experiência EAD da Cruzeiro do Sul Virtual oferece uma formação completa para profissionais interessados em criar experiências impactantes e intuitivas para usuários de produtos e serviços digitais. Com uma abordagem prática e teórica, os alunos aprendem a aplicar princípios de psicologia, design thinking e tecnologia para desenvolver interfaces e interações que atendam às necessidades e expectativas dos usuários. Ao longo de 4 semestres (2 anos), os estudantes exploram temas como pesquisa de mercado, prototipagem, usabilidade e design centrado no usuário, preparando-se para carreiras dinâmicas em um mercado digital em constante evolução. Após a conclusão do curso, os alunos recebem a titulação de tecnólogo em Design de Experiência.</t>
@@ -7115,6 +7343,27 @@
     <t>Aprimore suas habilidades em Design de Experiência EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Mapeamento de jornada e teste de protótipo em papel</t>
+  </si>
+  <si>
+    <t>Designer de experiência de cerca de 26 anos, mulher de pele negra, cabelo black curto, camisa oversized e calça, atenção ao mural de jornada.</t>
+  </si>
+  <si>
+    <t>Sala de pesquisa de usuário contemporânea brasileira, mural, mesa com protótipos de papel, janela, espaço acessível, sem tapete de corte e sem notebook de código.</t>
+  </si>
+  <si>
+    <t>mural de jornada com cartões em branco, protótipo de papel, caneta, cronômetro, adesivos em branco</t>
+  </si>
+  <si>
+    <t>Move um cartão no mural da jornada e observa a pessoa testando o protótipo de papel, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; código na tela; tesoura de diagramação; holograma; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Designer de experiência, mulher de pele negra, cerca de 26 anos, camisa oversized, movendo cartão em branco no mural de jornada. Objetos: mural, protótipo de papel, caneta, cronômetro e adesivos em branco. Sem código, sem tapete de corte, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>historia-ead-bacharelado</t>
   </si>
   <si>
@@ -7122,6 +7371,9 @@
   </si>
   <si>
     <t>historia</t>
+  </si>
+  <si>
+    <t>Analise fontes históricas e seus reflexos sociais, políticos, econômicos e culturais na sociedade atual.</t>
   </si>
   <si>
     <t>A graduação de História EAD na modalidade Bacharelado, Cruzeiro do Sul Virtual, tem duração de 6 semestres (3 anos), e capacita os estudantes para terem clareza sobre os eventos históricos e seu reflexo na sociedade atual. O curso aborda e analisa períodos históricos diversos, a fim de torná-los aptos para a pesquisa histórica e análise crítica. Com uma abordagem integrada, o curso explora aspectos sociais, políticos, religiosos, econômicos e culturais, formando uma base histórica que capacita os graduados para diversas áreas de trabalho.</t>
@@ -7157,6 +7409,30 @@
     <t>Aprofunde-se em História a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Crítica de fontes em arquivo histórico</t>
+  </si>
+  <si>
+    <t>Historiador de cerca de 30 anos, homem de pele clara, cabelo ondulado, camisa e colete, luvas de algodão, atenção ao documento.</t>
+  </si>
+  <si>
+    <t>Sala de arquivo contemporânea brasileira, mesa, caixas de acervo, janela com persiana, espaço sóbrio, sem quadro escolar.</t>
+  </si>
+  <si>
+    <t>documento antigo fechado, lupa, luvas, caderno, caixa de acervo</t>
+  </si>
+  <si>
+    <t>Examina o documento fechado com a lupa e anota no caderno, sentado à direita.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentado à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária natural suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; giz; linha do tempo legível; toga; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Historiador, homem de pele clara, cerca de 30 anos, colete e luvas, examinando o documento fechado com a lupa. Objetos: documento fechado, lupa, luvas, caderno e caixa de acervo. Sem giz, sem linha do tempo, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>gestao-de-turismo-ead-tecnologo</t>
   </si>
   <si>
@@ -7164,6 +7440,9 @@
   </si>
   <si>
     <t>gestao-de-turismo</t>
+  </si>
+  <si>
+    <t>Organize produtos de hospitalidade e lazer, com agenciamento, roteiros e avaliação de potencial turístico.</t>
   </si>
   <si>
     <t>O curso de Gestão de Turismo EAD oferece a titulação de tecnólogo e prepara os alunos para planejar e organizar produtos e serviços relacionados a hospitalidade e lazer, como geri-los e avaliá-los. Além disso, o curso capacita para o desenvolvimento e planejamento de atividades turísticas, agenciamento de viagens, coordenação de transportadoras turísticas, consultoria, podendo também identificar possíveis potenciais turísticos para desenvolvimento local e regional. O curso tem 4 semestres (2 anos) de duração e conta com o conceito 5 de classificação do MEC, juntamente com um material didático digital, com ambiente digital moderno e professores especializados.</t>
@@ -7198,6 +7477,27 @@
     <t>Aprenda a gerir negócios no setor do turismo a distância EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem de roteiro e agenciamento de viagem</t>
+  </si>
+  <si>
+    <t>Gestora de turismo de cerca de 28 anos, mulher de pele morena, cabelo ondulado solto, camisa e lenço, atenção ao mural de roteiro.</t>
+  </si>
+  <si>
+    <t>Agência de turismo contemporânea brasileira, mural, mesa, janela, fotos de paisagens sem legendas, espaço acessível, sem salão de eventos e sem mapa-múndi diplomático.</t>
+  </si>
+  <si>
+    <t>mural de roteiro com cartões em branco, pastas de hospedagem, caneta, calculadora, fotos sem legendas</t>
+  </si>
+  <si>
+    <t>Fixa um cartão no mural do roteiro e confere a pasta de hospedagem, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; palco de evento; fita no chão de salão; fileira de bandeiras; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Gestora de turismo, mulher de pele morena, cerca de 28 anos, camisa e lenço, fixando cartão em branco no mural de roteiro. Objetos: mural, pastas, caneta, calculadora e fotos sem legendas. Sem palco, sem bandeiras, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>historia-licenciatura-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -7205,6 +7505,9 @@
   </si>
   <si>
     <t>historia-licenciatura</t>
+  </si>
+  <si>
+    <t>Apresente períodos históricos no ensino básico, com fontes, análise crítica e metodologias educativas.</t>
   </si>
   <si>
     <t>O curso de Licenciatura em História semipresencial da Universidade Cruzeiro do Sul Virtual, com duração de 8 semestres (4 anos), prepara os futuros professores para o ensino de História no ensino fundamental e médio. Os estudantes exploram diversos períodos históricos, desenvolvendo competências em pesquisa histórica, análise crítica de fontes e metodologias educacionais inovadoras. O curso oferece flexibilidade para que os alunos estudem no seu próprio ritmo, utilizando recursos digitais avançados. Ao concluir, os alunos recebem o título de Licenciatura, capacitados para lecionar e contribuir para a formação de uma consciência histórica crítica na sociedade.</t>
@@ -7241,6 +7544,27 @@
     <t>Prepare-se para lecionar História a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Aula com linha do tempo ilustrada e fonte em fac-símile</t>
+  </si>
+  <si>
+    <t>Professora de história de cerca de 24 anos, mulher de pele negra, cabelo box braids, blusa verde, apontando a linha do tempo.</t>
+  </si>
+  <si>
+    <t>Sala de história com mural ilustrado contemporânea brasileira, carteiras, linha do tempo na parede, janelas, sem arquivo de acervo.</t>
+  </si>
+  <si>
+    <t>linha do tempo ilustrada sem escritos, fac-símile fechado, giz, apagador, livros fechados</t>
+  </si>
+  <si>
+    <t>Aponta um recorte da linha do tempo e mostra o fac-símile fechado à turma, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; luvas de arquivo; caixa de acervo; lupa de pesquisa; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de história, mulher de pele negra, cerca de 24 anos, blusa verde, apontando a linha do tempo ilustrada sem escritos. Objetos: linha do tempo, fac-símile fechado, giz, apagador e livros. Sem luvas de arquivo, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>letras-portugues-e-ingles-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -7248,6 +7572,9 @@
   </si>
   <si>
     <t>letras-portugues-e-ingles</t>
+  </si>
+  <si>
+    <t>Desenvolva práticas orais e literárias de inglês na educação básica, com didática e leitura compartilhada.</t>
   </si>
   <si>
     <t>O curso de Letras - Português e Inglês semipresencial da Cruzeiro do Sul Virtual tem como objetivo desenvolver habilidades para que os alunos possam interagir em diversos contextos sociocomunicativos, preparando-se para uma atuação dinâmica e eficaz como professores.Como uma licenciatura, o curso inclui disciplinas como didática, metodologia e práticas de ensino de línguas, assim como o estudo das respectivas literaturas, para uma formação completa e voltada para a prática em sala de aula. Além disso, contempla o estudo aprofundado dos aspectos histórico-culturais da língua inglesa oral e escrita, abrangendo obras de autores clássicos e contemporâneos das literaturas Inglesa, Norte-americana, literatura Africana em Língua Portuguesa e literatura Infantojuvenil.Todo esse conjunto de conhecimentos contribui para a excelência na produção de material didático e na orientação teórico-metodológica oferecida nos cursos de Letras da Cruzeiro do Sul Virtual. Com duração de 8 semestres (4 anos), o curso confere o título de licenciatura.</t>
@@ -7282,6 +7609,27 @@
     <t>Desenvolva habilidades em Português e Inglês a distância EAD com flexibilidade e baixo custo. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Leitura compartilhada e prática oral em sala</t>
+  </si>
+  <si>
+    <t>Professora de inglês de cerca de 27 anos, mulher de pele morena, cabelo cacheado médio, camisa xadrez, livro fechado na mão.</t>
+  </si>
+  <si>
+    <t>Sala de leitura escolar brasileira contemporânea, tapete, almofadas, estante baixa, janela, espaço claro, sem cabines de áudio.</t>
+  </si>
+  <si>
+    <t>livros fechados, fantoche, cartaz ilustrado sem escritos, almofadas, caderno</t>
+  </si>
+  <si>
+    <t>Senta no tapete com o fantoche e mostra o livro fechado ao grupo, à direita da estante.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; bandeiras; inglês legível; pincel e tinteiro; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de inglês, mulher de pele morena, cerca de 27 anos, camisa xadrez, no tapete com fantoche e livro fechado. Objetos: livros, fantoche, cartaz ilustrado, almofadas e caderno. Sem bandeiras, sem escritos em inglês, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>podologia-semipresencial-tecnologo</t>
   </si>
   <si>
@@ -7289,6 +7637,9 @@
   </si>
   <si>
     <t>podologia</t>
+  </si>
+  <si>
+    <t>Cuide da prevenção e dos cuidados dos pés, com anatomia, fisiologia e práticas especializadas de bem-estar.</t>
   </si>
   <si>
     <t>O curso de Podologia semipresencial da Cruzeiro do Sul Virtual promove uma formação completa e especializada. Ao longo da graduação, os alunos contam com diversas disciplinas que abrangem bases anatômicas e fisiológicas dos pés, aprendendo a identificar, prevenir e tratar patologias, além de oferecer cuidados estéticos e terapêuticos. Com duração de 4 semestres (2 anos), o currículo inclui anatomia, fisiologia, patologia, microbiologia e farmacologia. Com acesso a laboratórios virtuais e práticas supervisionadas, os estudantes desenvolvem habilidades práticas essenciais.</t>
@@ -7323,6 +7674,27 @@
     <t>Estude Podologia a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Preparação de kit e observação do modelo anatômico do pé</t>
+  </si>
+  <si>
+    <t>Podóloga de cerca de 32 anos, mulher de pele negra, cabelo preso em coque, jaleco e touca, atenção ao modelo.</t>
+  </si>
+  <si>
+    <t>Consultório de podologia contemporâneo brasileiro, cadeira vazia, bancada organizada, iluminação clara, sem spa de luxo.</t>
+  </si>
+  <si>
+    <t>modelo anatômico de pé, kit esterilizado fechado, luvas, gazes, lixeira de procedimentos</t>
+  </si>
+  <si>
+    <t>Alinha o kit fechado e aponta uma estrutura no modelo do pé, em pé à direita da bancada, sem intervir em pessoa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico; cura; tratamento; spa; pé ferido; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Podóloga, mulher de pele negra, cerca de 32 anos, jaleco e touca, apontando o modelo anatômico do pé ao lado do kit fechado. Objetos: modelo de pé, kit fechado, luvas, gazes e lixeira. Sem spa, sem ferimento, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>computacao-na-nuvem-ead-tecnologo</t>
   </si>
   <si>
@@ -7330,6 +7702,9 @@
   </si>
   <si>
     <t>computacao-na-nuvem</t>
+  </si>
+  <si>
+    <t>Implemente infraestrutura e aplicações em nuvem, com conectividade, dados e modelos de gestão de TI.</t>
   </si>
   <si>
     <t>O curso de Computação em Nuvem EAD busca capacitar os estudantes para dominar técnicas e ferramentas no segmento da Tecnologia da Informação, fornecendo diversos conhecimentos da área, incluindo fundamentos teóricos da computação em nuvem e aplicação prática das mais avançadas soluções tecnológicas. Com disciplinas como Conectividade e Dados da Nuvem; IoT e Stream de Dados; Modelos de Gestão de TI e Técnicas de Desenvolvimento de Algoritmos, o curso confere a titulação de tecnólogo em Computação em Nuvem e tem duração de 4 semestres (2 anos).</t>
@@ -7367,6 +7742,27 @@
     <t>Desenvolva habilidades em Computação na Nuvem a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Desenho de arquitetura de nuvem em camadas</t>
+  </si>
+  <si>
+    <t>Arquiteto de nuvem de cerca de 28 anos, homem de pele clara, cabelo curto, camisa social, atenção ao diagrama na mesa.</t>
+  </si>
+  <si>
+    <t>Sala de operações de TI contemporânea brasileira, mesa com diagrama impresso, um monitor apagado, persiana, sem quadro branco de camadas e sem sensores físicos.</t>
+  </si>
+  <si>
+    <t>diagrama de nuvens em branco, adesivos em branco, caneta, notebook fechado, copo</t>
+  </si>
+  <si>
+    <t>Organiza adesivos sobre o diagrama impresso de nuvens, sentado à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; holograma; protoboard; sensores; capuz; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Arquiteto de nuvem, homem de pele clara, cerca de 28 anos, camisa social, organizando adesivos sobre o diagrama impresso de nuvens. Objetos: diagrama, adesivos, caneta, notebook fechado e copo. Sem sensores, sem holograma, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciencia-de-dados-ead-tecnologo</t>
   </si>
   <si>
@@ -7374,6 +7770,9 @@
   </si>
   <si>
     <t>ciencia-de-dados</t>
+  </si>
+  <si>
+    <t>Modele estatística, algoritmos e programação para extrair conhecimentos que apoiem decisões nas organizações.</t>
   </si>
   <si>
     <t>O curso de Ciências de Dados EAD forma profissionais inovadores em diversos contextos, fornecendo embasamento teórico e prático em áreas como negócios, estatística, algoritmos, programação, banco de dados e inteligência artificial. O curso qualifica o aluno para construir sistemas, escolher componentes, direcionar estratégias, fazer migrações e desenvolver ambientes seguros.Com duração de 4 semestres (2 anos), o curso confere a titulação de tecnólogo em Ciências de Dados.Assim, ao se formar, o cientista de dados estará apto a trabalhar ferramentas matemáticas, estatísticas e computacionais voltadas a auxiliar no processo de extração de conhecimentos a partir de dados, que auxiliam nas tomadas de decisões das organizações.</t>
@@ -7408,6 +7807,27 @@
     <t>Aprenda Ciência de Dados com qualidade e flexibilidade. Vestibular On-line em EAD líder. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Modelagem estatística e escolha de componentes</t>
+  </si>
+  <si>
+    <t>Cientista de dados de cerca de 29 anos, mulher de pele morena, cabelo liso longo, camisa azul e cardigan, atenção ao caderno de fórmulas.</t>
+  </si>
+  <si>
+    <t>Sala de modelagem em empresa brasileira contemporânea, lousa com símbolos matemáticos ilegíveis, um monitor com dispersão abstrata, persiana, sem mural de calor e sem cilindros de banco.</t>
+  </si>
+  <si>
+    <t>lousa com símbolos, caderno de fórmulas, calculadora científica, caneta, monitor com dispersão</t>
+  </si>
+  <si>
+    <t>Copia um símbolo da lousa para o caderno e confere a dispersão no monitor, sentada à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; três monitores de calor; cilindros de backup; holograma; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Cientista de dados, mulher de pele morena, cerca de 29 anos, cardigan, copiando símbolos da lousa para o caderno e olhando a dispersão no monitor. Objetos: lousa, caderno, calculadora científica, caneta e monitor. Sem mural de calor, sem cilindros, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>administracao-publica-ead-bacharelado</t>
   </si>
   <si>
@@ -7415,6 +7835,9 @@
   </si>
   <si>
     <t>administracao-publica</t>
+  </si>
+  <si>
+    <t>Formule políticas e projetos de interesse público, com análise quantitativa e fundamentos do Estado.</t>
   </si>
   <si>
     <t>O curso de Administração Pública EAD da Cruzeiro do Sul Virtual prepara os alunos para enfrentar desafios do setor público. Durante a graduação, eles aprendem a identificar e resolver problemas de interesse público, o que os tornará aptos a formular e implementar políticas e projetos, utilizando métodos quantitativos para análise de dados. A formação abrange disciplinas como administração, contabilidade, política, economia, direito, filosofia, sociologia, e tecnologia da informação e comunicação.Os graduados saem com uma compreensão completa das estratégias e métodos de gestão pública, prontos para atuar com uma visão ampla dos fundamentos do Estado. Com duração de 8 semestres (4 anos), o curso oferece o título de bacharel em Administração Pública.</t>
@@ -7455,6 +7878,27 @@
     <t>Desenvolva sua carreira na Administração Pública a baixo custo. Vestibular Online em EAD reconhecida. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Planejamento estratégico e orçamento institucional</t>
+  </si>
+  <si>
+    <t>Administradora pública de cerca de 32 anos, mulher de pele negra, cabelo crespo curto, blazer grafite, atenção ao painel de metas vazio.</t>
+  </si>
+  <si>
+    <t>Sala de planejamento em órgão público brasileiro contemporâneo, mesa oval, painel, persiana, espaço institucional sóbrio, sem fila de atendimento e sem tribuna.</t>
+  </si>
+  <si>
+    <t>pastas orçamentárias, gráfico de colunas sem legendas, caneta, copos, notebook fechado</t>
+  </si>
+  <si>
+    <t>Compara tabelas impressas sem números legíveis e anota no caderno orçamentário, sentada à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; fita de fila; totens; palanque; bandeiras; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Administradora pública, mulher de pele negra, cerca de 32 anos, blazer grafite, comparando tabelas impressas e anotando no caderno. Objetos: pastas, gráfico sem legendas, caneta, copos e notebook fechado. Sem fila, sem totens, sem palanque, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>negocios-imobiliarios-ead-tecnologo</t>
   </si>
   <si>
@@ -7462,6 +7906,9 @@
   </si>
   <si>
     <t>negocios-imobiliarios</t>
+  </si>
+  <si>
+    <t>Avalie imóveis e administre condomínios com técnicas de gestão, direito imobiliário e negociação estratégica.</t>
   </si>
   <si>
     <t>O curso de Negócios Imobiliários EAD da Cruzeiro do Sul Virtual é reconhecido pelo Conselho Federal dos Corretores de Imóveis (COFECI) e forma profissionais qualificados para avaliar imóveis, negociações de compra e administração de condomínio. O profissional será apto a aplicar técnicas de gestão, direito imobiliário, corretagem e avaliação imobiliária, traçando estratégias de administração e negociação. Com duração de 4 semestres (2 anos), o curso confere o título de tecnólogo em Negócios Imobiliários.</t>
@@ -7496,6 +7943,27 @@
     <t>Aprenda sobre Negócios Imobiliários a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Avaliação comparativa de plantas de apartamento</t>
+  </si>
+  <si>
+    <t>Analista imobiliário de cerca de 31 anos, homem de pele morena, cabelo curto, camisa social sem gravata, atenção às plantas.</t>
+  </si>
+  <si>
+    <t>Escritório funcional em prédio residencial brasileiro, mesa, janela para fachada comum, espaço acessível, sem cobertura de luxo e sem entrega de chaves.</t>
+  </si>
+  <si>
+    <t>plantas baixas sem nomes, trena, pasta de avaliação, calculadora, caneta</t>
+  </si>
+  <si>
+    <t>Compara duas plantas baixas e confere a trena sobre a mesa, sentado à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; mansão; chave na mão do cliente; aperto de mãos; capacete de obra; ambiente de luxo ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista imobiliário, homem de pele morena, cerca de 31 anos, camisa social, comparando duas plantas baixas e conferindo a trena. Objetos: plantas, trena, pasta, calculadora e caneta. Sem mansão, sem chaves, sem aperto de mãos, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>seguranca-do-trabalho-ead-tecnologo</t>
   </si>
   <si>
@@ -7503,6 +7971,9 @@
   </si>
   <si>
     <t>seguranca-do-trabalho</t>
+  </si>
+  <si>
+    <t>Identifique riscos ocupacionais e organize medidas preventivas para a saúde e a segurança no trabalho.</t>
   </si>
   <si>
     <t>O curso de Segurança no Trabalho EAD da Cruzeiro do Sul Virtual forma profissionais capazes para atuar na prevenção de acidentes e doenças ocupacionais nas diversas áreas de trabalho, desenvolvendo habilidades e competências para identificar riscos ambientais, criação de planos preventivos e implementação de medidas que garantam a saúde e segurança dos trabalhadores. Com disciplinas como Saúde do trabalhador, Doenças ocupacionais, Gestão de pessoas, Psicologia do trabalho e Auditoria, laudos e perícias, o curso tem duração de 6 semestres (3 anos), titulação de tecnologia e conceito 4 na classificação do MEC.</t>
@@ -7536,6 +8007,27 @@
     <t>Desenvolva habilidades em Segurança do Trabalho a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Inspeção preventiva de EPIs e sinalização de risco</t>
+  </si>
+  <si>
+    <t>Técnica de segurança de cerca de 30 anos, mulher de pele clara, cabelo preso, colete e capacete, prancheta na mão.</t>
+  </si>
+  <si>
+    <t>Passarela de indústria brasileira contemporânea, EPIs alinhados, piso sinalizado, iluminação industrial, espaço organizado, sem acidente e sem arma.</t>
+  </si>
+  <si>
+    <t>prancheta de inspeção em branco, capacete extra, luvas, protetor auricular, fita zebrada enrolada</t>
+  </si>
+  <si>
+    <t>Confere o capacete extra e registra a inspeção na prancheta, em pé à direita da passarela.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; acidente; trabalhador ferido; sangue; arma; viatura; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Técnica de segurança, mulher de pele clara, cerca de 30 anos, colete e capacete, conferindo EPI e anotando na prancheta. Objetos: prancheta em branco, capacete extra, luvas, protetor auricular e fita enrolada. Sem acidente, sem ferimento, sem arma, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>administracao-ead-bacharelado</t>
   </si>
   <si>
@@ -7543,6 +8035,9 @@
   </si>
   <si>
     <t>administracao</t>
+  </si>
+  <si>
+    <t>Dirija a gestão estratégica de negócios, com pessoas, finanças, logística e competitividade organizacional.</t>
   </si>
   <si>
     <t>O curso de Bacharelado em Administração EAD da Cruzeiro do Sul Virtual é a escolha ideal para quem busca uma formação de excelência com a flexibilidade do ensino a distância. Com duração de 8 semestres (4 anos), a graduação prepara você para os desafios do mercado corporativo moderno.</t>
@@ -7578,6 +8073,27 @@
     <t>Estude Administração a distância com flexibilidade e qualidade. Vestibular Online em uma instituição de referência. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Reunião de gestão estratégica entre áreas</t>
+  </si>
+  <si>
+    <t>Administrador de cerca de 34 anos, homem de pele negra, cabelo curto, camisa e blazer simples, apontando o painel de áreas.</t>
+  </si>
+  <si>
+    <t>Sala de diretoria acessível em empresa brasileira contemporânea, mesa longa, painel com quatro quadrantes vazios, janela, sem papel pardo de fluxograma.</t>
+  </si>
+  <si>
+    <t>painel de quadrantes em branco, pastas de áreas, caneta, jarra, notebook fechado</t>
+  </si>
+  <si>
+    <t>Aponta um quadrante vazio e distribui pastas de áreas, em pé à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; papel pardo de gargalos; foguete; aperto de mãos; fila de atendimento; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Administrador, homem de pele negra, cerca de 34 anos, blazer simples, apontando quadrante vazio e distribuindo pastas. Objetos: painel, pastas, caneta, jarra e notebook fechado. Sem fluxograma, sem foguete, sem aperto de mãos, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>ciencias-biologicas-licenciatura-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -7585,6 +8101,9 @@
   </si>
   <si>
     <t>ciencias-biologicas-licenciatura</t>
+  </si>
+  <si>
+    <t>Ensine evolução e conservação em estufa escolar, com amostras vegetais e práticas de educação ambiental.</t>
   </si>
   <si>
     <t>O curso de Licenciatura em Ciências Biológicas semipresencial, estudará a vida existente no planeta, através de um olhar científico, contando com laboratórios modernos e equipados, com aulas e visitas técnicas. Sob a visão da educação, o licenciado em Ciências Biológicas pela universidade Cruzeiro do Sul Virtual será estimulado a realizar projetos e pesquisas sobre meio ambiente, saúde e biotecnologia, com foco na conservação e preservação da biodiversidade. Com duração de 8 semestres (4 anos), o profissional será capaz de compreender a complexidade sobre as vidas existentes no planeta, processos evolutivos e muito mais. O curso possui conceito 4 no MEC e confere o título de licenciatura em Ciências Biológicas.</t>
@@ -7620,6 +8139,27 @@
     <t>Prepare-se para ensinar Ciências Biológicas com flexibilidade do EAD e qualidade. Bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Aula de biodiversidade com amostras vegetais</t>
+  </si>
+  <si>
+    <t>Professora de biologia de cerca de 24 anos, mulher de pele morena, cabelo cacheado solto, camisa floral e avental, mostrando a planta.</t>
+  </si>
+  <si>
+    <t>Estufa escolar brasileira contemporânea, bancadas com vasos, mangueira, luz de manhã, espaço de aula ao ar coberto, sem trilha de reserva.</t>
+  </si>
+  <si>
+    <t>vaso com planta, lupa, béquer, giz, bandeja de folhas</t>
+  </si>
+  <si>
+    <t>Mostra a folha na lupa para a turma e aponta o vaso, em pé à direita da bancada, quadro apagado.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; rede entomológica de campo; microscópio clínico; animal ferido; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento aberto, personagem na região superior direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Professora de biologia, mulher de pele morena, cerca de 24 anos, camisa floral e avental, mostrando a folha na lupa à turma na estufa escolar. Objetos: vaso, lupa, béquer, giz e bandeja de folhas. Sem rede de campo, sem microscópio clínico, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-mecatronica-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -7627,6 +8167,9 @@
   </si>
   <si>
     <t>engenharia-mecatronica</t>
+  </si>
+  <si>
+    <t>Automatize linhas produtivas com robôs, sensores de precisão e controle de células industriais robotizadas.</t>
   </si>
   <si>
     <t>O curso de Engenharia Mecatrônica Semipresencial da Cruzeiro do Sul Virtual forma engenheiros capacitados para liderar a Indústria 4.0. Com foco em inovação e eficiência produtiva, a graduação integra os pilares da Engenharia Mecânica, Eletrônica e Computação, preparando o aluno para desenvolver sistemas de automação industrial e robótica avançada.</t>
@@ -7661,6 +8204,27 @@
     <t>Estude Engenharia Mecatrônica a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Ajuste de célula robótica de automação</t>
+  </si>
+  <si>
+    <t>Engenheiro mecatrônico de cerca de 27 anos, homem de pele negra, cabelo black curto, macacão cinza, teach pendant na mão.</t>
+  </si>
+  <si>
+    <t>Célula de automação em indústria brasileira contemporânea, braço robótico parado, grade de proteção, piso limpo, sem caixa de engrenagens solta e sem quadro elétrico aberto.</t>
+  </si>
+  <si>
+    <t>braço robótico, teach pendant, chave allen, cone de segurança, prancheta</t>
+  </si>
+  <si>
+    <t>Ajusta a posição do braço robótico e confere o teach pendant, em pé à direita da grade.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; holograma; capuz; engrenagem como único objeto; fiação exposta; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheiro mecatrônico, homem de pele negra, cerca de 27 anos, macacão, ajustando o braço robótico e conferindo o teach pendant. Objetos: braço robótico, teach pendant, chave allen, cone e prancheta. Sem holograma, sem engrenagens soltas, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>sistemas-para-internet-ead-tecnologo</t>
   </si>
   <si>
@@ -7668,6 +8232,9 @@
   </si>
   <si>
     <t>sistemas-para-internet</t>
+  </si>
+  <si>
+    <t>Construa websites e aplicações online, com programação web, bancos de dados e integração de sistemas.</t>
   </si>
   <si>
     <t>O curso de Sistemas para Internet EAD capacita profissionais para desenvolver soluções tecnológicas voltadas para a web. Com foco no desenvolvimento, instalação de bancos de dados e aplicações online, o currículo engloba disciplinas como programação web, design de interação, banco de dados, segurança de sistemas e gestão da tecnologia da informação. Os alunos adquirem habilidades em desenvolvimento de websites dinâmicos, aplicativos web, e-commerce, marketing digital, e integração de sistemas online. Com duração de 4 semestres (2 anos), conceito 5 na classificação do MEC e conferindo o título de tecnólogo, o curso prepara os graduandos para o mercado de trabalho em grandes empresas.</t>
@@ -7703,6 +8270,27 @@
     <t>Desenvolva habilidades em Sistemas para Internet a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Montagem de páginas e navegação de aplicação web</t>
+  </si>
+  <si>
+    <t>Desenvolvedora web de cerca de 24 anos, mulher de pele clara, cabelo ondulado castanho, moletom verde, atenção ao navegador.</t>
+  </si>
+  <si>
+    <t>Sala de produto digital em agência pequena brasileira, dois monitores com blocos de layout, persiana, espaço contemporâneo, sem coworking e sem mesa alta doméstica.</t>
+  </si>
+  <si>
+    <t>notebook, mouse, fone, caderno de esboço de tela em branco, copo</t>
+  </si>
+  <si>
+    <t>Arrasta blocos no layout do navegador e confere o esboço de tela em branco, sentada à direita, tela sem escritos.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; código de servidor; holograma; capuz; tapete de corte; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Desenvolvedora web, mulher de pele clara, cerca de 24 anos, moletom verde, arrastando blocos no layout do notebook. Tela com blocos coloridos, sem escritos. Objetos: notebook, mouse, fone, caderno em branco e copo. Sem terminal de servidor, sem mural de jornada, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>fisioterapia-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -7710,6 +8298,9 @@
   </si>
   <si>
     <t>fisioterapia</t>
+  </si>
+  <si>
+    <t>Oriente exercícios de mobilidade e reabilitação funcional, com anatomia, fisiologia e biomecânica do movimento.</t>
   </si>
   <si>
     <t>A graduação de Fisioterapia semipresencial da Cruzeiro do Sul Virtual, fornece aos estudantes um ensino pautado na promoção de saúde e bem-estar dos indivíduos, com base em uma compreensão profunda da anatomia humana. Ao longo do curso, os alunos são convidados a refletir e analisar disciplinas imersivas, como anatomia, fisiologia, biomecânica e cinesiologia, o que consolida fortes fundamentos para o completo entendimento do corpo humano. A Cruzeiro do Sul Virtual promove conhecimentos robustos, com o objetivo de transformar seus alunos em profissionais altamente competentes para diagnosticar, prevenir e corrigir distúrbios motores, além de desenvolver técnicas de reabilitação física e exercer uma função essencial na elevação da qualidade de vida das pessoas.</t>
@@ -7744,6 +8335,27 @@
     <t>Estude Fisioterapia a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Orientação de mobilidade em barras paralelas</t>
+  </si>
+  <si>
+    <t>Fisioterapeuta de cerca de 30 anos, mulher de pele negra, cabelo em box braids, jaleco esportivo e calça, postura de orientação.</t>
+  </si>
+  <si>
+    <t>Sala de reabilitação contemporânea brasileira, barras paralelas, colchonete, janela, espaço digno, sem cozinha terapêutica e sem espelho de articulação.</t>
+  </si>
+  <si>
+    <t>barras paralelas, bola de exercícios, faixa elástica, cronômetro, colchonete</t>
+  </si>
+  <si>
+    <t>Guia os pés de uma pessoa adulta nas barras e segura a faixa elástica, em pé à direita, sem aplicar diagnóstico.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; diagnóstico; cura; tratamento; utensílio de cozinha; espelho de fala; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Fisioterapeuta, mulher de pele negra, cerca de 30 anos, jaleco esportivo, guiando a pessoa nas barras paralelas. Objetos: barras, bola, faixa elástica, cronômetro e colchonete. Sem cozinha terapêutica, sem espelho de fala, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>coaching-e-mentoring-ead-tecnologo</t>
   </si>
   <si>
@@ -7751,6 +8363,9 @@
   </si>
   <si>
     <t>coaching-e-mentoring</t>
+  </si>
+  <si>
+    <t>Conduza conversas de desenvolvimento de liderança e desempenho, com acompanhamento de metas e relações de equipe.</t>
   </si>
   <si>
     <t>O curso de Coaching e Mentoring EAD da Cruzeiro do Sul Virtual foi pensado para capacitação do profissional através de conhecimentos sobre o comportamento humano, a fim de auxiliar pessoas de diversas áreas e cargos a atingirem suas metas. O coach graduado pela Cruzeiro do Sul Virtual desempenha a implementação de mudanças organizacionais e seus funcionários, fazendo o uso de ferramentas para que o senso de liderança, autonomia e bem-estar organizacional seja expandido, gerenciando o desempenho e a melhora das relações interpessoais. Com duração de 4 semestres (2 anos), o curso confere o título de tecnólogo em Coaching e Mentoring.</t>
@@ -7785,6 +8400,27 @@
     <t>Aprimore suas habilidades em Coaching e Mentoring a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Sessão de acompanhamento de metas e liderança</t>
+  </si>
+  <si>
+    <t>Coach de cerca de 33 anos, homem de pele clara, cabelo curto, óculos e pulôver, caderno de perguntas na mão.</t>
+  </si>
+  <si>
+    <t>Pátio interno de empresa brasileira contemporânea, bancos, planta, luz da manhã, conversa em pé ao ar livre, sem sala de entrevistas.</t>
+  </si>
+  <si>
+    <t>caderno de perguntas, cartões de meta em branco, caneta, copo, pasta</t>
+  </si>
+  <si>
+    <t>Caminha ao lado da pessoa e mostra um cartão de meta em branco, em pé à direita do corredor.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; aperto de mãos; foguete; cifrão; palco; divã; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Coach, homem de pele clara, cerca de 33 anos, pulôver e óculos, no pátio mostrando cartão de meta em branco. Objetos: caderno, cartões em branco, caneta, copo e pasta. Sem aperto de mãos, sem foguete, sem palco, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>internet-das-coisas-ead-tecnologo</t>
   </si>
   <si>
@@ -7792,6 +8428,9 @@
   </si>
   <si>
     <t>internet-das-coisas</t>
+  </si>
+  <si>
+    <t>Conecte sensores e dispositivos a sistemas organizacionais, com testes de automação e coleta de dados.</t>
   </si>
   <si>
     <t>O Tecnólogo em Internet das Coisas no formato EAD da Cruzeiro do Sul Virtual garante fornecer aos estudantes competências para atividades técnicas e científicas, os tornando aptos a projetar, analisar, desenvolver e testar sistemas para internet das coisas, utilizando tecnologias e conceitos modernos, e dessa forma, aprimorando a eficiência dos sistemas organizacionais. Além do mais, o curso da Cruzeiro do Sul Virtual tem duração de 4 semestres (2 anos) e conta com matriz curricular moderna e alinhada com o mercado, assim como atividades formativas e práticas.</t>
@@ -7825,6 +8464,27 @@
     <t>Estude sobre a Internet das Coisas a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Teste de sensores conectados em bancada</t>
+  </si>
+  <si>
+    <t>Desenvolvedora de IoT de cerca de 25 anos, mulher de pele morena, cabelo cacheado curto, camisa e avental de bancada, atenção ao sensor.</t>
+  </si>
+  <si>
+    <t>Bancada de protótipos IoT em laboratório brasileiro contemporâneo, cabos organizados, janela, espaço técnico, sem desenho de nuvem no quadro.</t>
+  </si>
+  <si>
+    <t>placa com sensores, cabo, display numérico genérico, protoboard, chave de fenda</t>
+  </si>
+  <si>
+    <t>Conecta o cabo ao sensor e observa o display numérico, sentada à direita da bancada.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; holograma; nuvens desenhadas no quadro; capuz; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Desenvolvedora de IoT, mulher de pele morena, cerca de 25 anos, avental de bancada, conectando o cabo ao sensor. Objetos: placa com sensores, cabo, display, protoboard e chave. Sem desenho de nuvem, sem holograma, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>empreendedorismo-ead-tecnologo</t>
   </si>
   <si>
@@ -7832,6 +8492,9 @@
   </si>
   <si>
     <t>empreendedorismo</t>
+  </si>
+  <si>
+    <t>Modele planos de um empreendimento acessível, com gestão, finanças, marketing, inovação e liderança.</t>
   </si>
   <si>
     <t>O curso de Empreendedorismo EAD da Cruzeiro do Sul Virtual, com duração de 4 semestres, confere o título de Tecnólogo e possui conceito 4 na classificação do MEC. Este curso prepara os estudantes para identificar oportunidades de negócio, desenvolver planos estratégicos e gerenciar empresas de forma inovadora e sustentável. Através de uma abordagem prática e teórica, os alunos adquirem competências essenciais em gestão, marketing, finanças e liderança, capacitando-se para atuar em diversos setores do mercado e lançar seus próprios empreendimentos.</t>
@@ -7867,6 +8530,27 @@
     <t>Desenvolva habilidades em Empreendedorismo EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Canvas de negócio e planejamento financeiro simples</t>
+  </si>
+  <si>
+    <t>Empreendedor de cerca de 29 anos, homem de pele negra, cabelo crespo curto, camisa jeans, atenção ao canvas.</t>
+  </si>
+  <si>
+    <t>Pequena oficina de ateliê brasileiro contemporâneo, mesa, prateleira de produtos genéricos, janela, espaço acessível, sem escritório de luxo.</t>
+  </si>
+  <si>
+    <t>canvas com blocos vazios, calculadora, caderno, caneta, amostras genéricas</t>
+  </si>
+  <si>
+    <t>Preenche um bloco vazio do canvas e confere a calculadora, sentada à direita da mesa.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; foguete; aperto de mãos; cifrão; startup de luxo; ambiente precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Empreendedor, homem de pele negra, cerca de 29 anos, camisa jeans, preenchendo bloco vazio do canvas em ateliê simples. Objetos: canvas, calculadora, caderno, caneta e amostras. Sem foguete, sem aperto de mãos, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>engenharia-civil-semipresencial-bacharelado</t>
   </si>
   <si>
@@ -7874,6 +8558,9 @@
   </si>
   <si>
     <t>engenharia-civil</t>
+  </si>
+  <si>
+    <t>Planeje estruturas, fundações e serviços de obras, com vistoria de edificações e sistemas de infraestrutura.</t>
   </si>
   <si>
     <t>O curso de Engenharia Civil semipresencial da Cruzeiro do Sul, fornece uma formação combinada entre teoria e prática, com projetos com foco em uma formação detalhada e completa, alinhados às exigências do mercado da área. Com 10 semestres de duração (5 anos), os alunos são preparados para realizar atividades de planejamento, projeto, direção, vistoria e avaliação de obras e serviços relacionados a edificações, sistemas de transporte, abastecimento de água, drenagem e outros aspectos. O curso oferece a titulação de bacharel em Engenharia Civil.</t>
@@ -7911,6 +8598,27 @@
     <t>Estude Engenharia Civil a distância EAD com a mesma qualidade do presencial. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Vistoria de forma e armadura em canteiro</t>
+  </si>
+  <si>
+    <t>Engenheiro civil de cerca de 30 anos, homem de pele clara, barba curta, óculos de proteção, capacete e colete, prancheta na mão.</t>
+  </si>
+  <si>
+    <t>Canteiro organizado de edifício brasileiro contemporâneo, forma de concreto, armadura visível, piso delimitado, céu claro, sem maquete de ateliê e sem planta de venda.</t>
+  </si>
+  <si>
+    <t>prancheta, trena, capacete, nível de pedreiro, rádio</t>
+  </si>
+  <si>
+    <t>Mede a forma com a trena e anota na prancheta, em pé à direita da armadura.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; maquete de edifício; chave de imóvel; mansão; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio-aberto, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Engenheiro civil, homem de pele clara, cerca de 30 anos, barba, capacete e colete, medindo a forma com a trena. Objetos: prancheta, trena, capacete, nível e rádio. Sem maquete, sem chaves, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>marketing-digital-ead-tecnologo</t>
   </si>
   <si>
@@ -7918,6 +8626,9 @@
   </si>
   <si>
     <t>marketing-digital</t>
+  </si>
+  <si>
+    <t>Defina campanhas e canais digitais, com conteúdo, mídias sociais, publicidade online e leitura de audiência.</t>
   </si>
   <si>
     <t>O curso de Marketing Digital EAD da Cruzeiro do Sul Virtual oferece uma formação completa e atualizada, com disponibilidade das modalidades que contém aulas gravadas e aulas ao vivo, proporcionando flexibilidade e interatividade aos alunos. Com conceito 3 na classificação do MEC, o curso aborda temas como estratégias de marketing online, marketing de conteúdo, gestão de mídias sociais, e análise de dados. Os estudantes têm acesso a uma plataforma virtual com materiais didáticos interativos, videoaulas e suporte de tutores, preparando-os para enfrentar os desafios do mercado de trabalho digital. Com duração de 4 semestres (2 anos), o curso confere o título de Tecnólogo em Marketing Digital.</t>
@@ -7951,6 +8662,27 @@
     <t>Desenvolva habilidades em Marketing Digital a distância EAD com flexibilidade e qualidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Matriz de canais digitais e leitura de audiência</t>
+  </si>
+  <si>
+    <t>Analista de marketing digital de cerca de 26 anos, mulher de pele clara, cabelo curto ondulado, blazer mostarda, atenção ao mural de canais.</t>
+  </si>
+  <si>
+    <t>Sala de planejamento digital contemporânea brasileira, mural, mesa, janela, espaço acessível, sem tripé de influenciador e sem gôndola.</t>
+  </si>
+  <si>
+    <t>mural de canais com cartões em branco, notebook com gráfico abstrato, caneta, tablet, copo</t>
+  </si>
+  <si>
+    <t>Move um cartão no mural de canais e confere o gráfico no notebook, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; ring light; tripé; gôndola; mesa de luz de peças; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de marketing digital, mulher de pele clara, cerca de 26 anos, blazer mostarda, movendo cartão em branco no mural de canais. Objetos: mural, notebook com gráfico abstrato, caneta, tablet e copo. Sem tripé, sem ring light, sem gôndola, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>formacao-pedagogica-letras-port-e-ing-semipresencial-licenciatura</t>
   </si>
   <si>
@@ -7958,6 +8690,9 @@
   </si>
   <si>
     <t>formacao-pedagogica-letras-port-e-ing</t>
+  </si>
+  <si>
+    <t>Organize sequências didáticas bilíngues de português e inglês para quem já possui graduação e atua na formação docente.</t>
   </si>
   <si>
     <t xml:space="preserve">O curso de Formação Pedagógica em Letras (Português e Inglês) da Cruzeiro do Sul Virtual está disponível no formato Semipresencial e é destinado especificamente a alunos que já possuem uma graduação prévia em Pedagogia. Ao longo da formação, o curso foca em proporcionar o domínio das línguas portuguesa e inglesa, bem como de suas respectivas literaturas, despertando um questionamento crítico e reflexivo acerca da linguagem e da cultura.
@@ -7990,6 +8725,27 @@
     <t>Faça Formação Pedagógica em Letras Português e Inglês semipresencial na Cruzeiro do Sul Virtual e habilite-se para lecionar idiomas no Ensino Fundamental e Médio.</t>
   </si>
   <si>
+    <t>Elaboração de sequência didática bilíngue</t>
+  </si>
+  <si>
+    <t>Formadora pedagógica de cerca de 35 anos, mulher de pele morena, cabelo cacheado preso, camisa e saia, atenção à lousa de planejamento.</t>
+  </si>
+  <si>
+    <t>Sala de formação continuada de docentes brasileira contemporânea, mesa de reunião, lousa com duas colunas vazias, janela, colegas adultos ao fundo, sem turma infantil.</t>
+  </si>
+  <si>
+    <t>lousa de duas colunas, cartões de estratégia em branco, dois livros fechados de cores distintas, pasta de formação, canetão</t>
+  </si>
+  <si>
+    <t>Fixa cartões de estratégia nas duas colunas da lousa e folheia a pasta de formação, em pé à direita.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; laminadora; recorte; artesanato; aula infantil; giz no quadro de turma; bandeiras; inglês legível; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Formadora pedagógica, mulher de pele morena, cerca de 35 anos, camisa e saia, fixando cartões de estratégia em branco nas duas colunas da lousa. Objetos: lousa de duas colunas, cartões em branco, dois livros fechados, pasta de formação e canetão. Sem laminadora, sem recorte, sem turma infantil, sem bandeiras, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>desenvolvimento-back-end-ead-tecnologo</t>
   </si>
   <si>
@@ -7997,6 +8753,9 @@
   </si>
   <si>
     <t>desenvolvimento-back-end</t>
+  </si>
+  <si>
+    <t>Estruture a lógica, a segurança, as regras de negócio e as integrações que sustentam sites e aplicações.</t>
   </si>
   <si>
     <t>O curso de Desenvolvedor de Back-End EAD da Cruzeiro do Sul Virtual capacita profissionais para criar e manter códigos e comandos que fazem dispositivos e serviços web funcionarem. Utilizando linguagens de programação, o desenvolvedor de Back-End constrói a estrutura que suporta as ações das máquinas, garantindo o funcionamento adequado de sites e aplicações. Com uma base teórica sólida em computação, números e raciocínio lógico, esses profissionais são essenciais para a manutenção de sistemas eficientes e seguros. O curso, com duração de 4 semestres (2 anos), oferece a titulação de tecnólogo em Desenvolvimento de Back-End e apresenta um plano pedagógico atualizado, alinhado às exigências do mercado. Utilizando tecnologias avançadas, a formação proporciona aos alunos conhecimentos técnicos específicos de programação e inclui laboratórios virtuais para a aplicação prática da teoria, preparando-os para o mercado de trabalho.</t>
@@ -8030,6 +8789,30 @@
     <t>Desenvolva habilidades em Desenvolvimento Back-End EAD com qualidade e flexibilidade. Vestibular On-line com bolsas de até 100%!</t>
   </si>
   <si>
+    <t>Organização de serviços, regras e integração de dados</t>
+  </si>
+  <si>
+    <t>Desenvolvedor back-end de cerca de 27 anos, homem de pele negra, cabelo crespo curto, camisa preta, atenção aos dois monitores.</t>
+  </si>
+  <si>
+    <t>Sala técnica contemporânea brasileira, dois monitores com blocos de código ilegíveis, persiana, espaço sóbrio, sem layout de página e sem mural de jornada.</t>
+  </si>
+  <si>
+    <t>dois monitores, teclado, caderno de regras, cabo de rede, copo</t>
+  </si>
+  <si>
+    <t>Compara blocos nos dois monitores e anota uma regra no caderno, sentado à direita, telas sem escritos legíveis.</t>
+  </si>
+  <si>
+    <t>Formato quadrado 1:1, enquadramento médio, personagem sentado à direita, região inferior esquerda livre, nenhum rosto, mão ou objeto importante na região inferior esquerda, iluminação publicitária suave, separação clara entre assunto e fundo.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; layout de site colorido; holograma; capuz; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Desenvolvedor back-end, homem de pele negra, cerca de 27 anos, camisa preta, comparando dois monitores com blocos ilegíveis. Objetos: dois monitores, teclado, caderno, cabo e copo. Sem layout de página, sem mural de jornada, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
+  </si>
+  <si>
     <t>sistemas-de-informacao-ead-bacharelado</t>
   </si>
   <si>
@@ -8037,6 +8820,9 @@
   </si>
   <si>
     <t>sistemas-de-informacao</t>
+  </si>
+  <si>
+    <t>Coordene a integração de sistemas e informações entre áreas, com arquitetura empresarial, projetos e segurança da informação.</t>
   </si>
   <si>
     <t>O Bacharelado de Sistemas da Informação EAD da Cruzeiro do Sul Virtual, tem como principal objetivo fornecer uma formação de alta qualidade para seus alunos. O curso proporciona conhecimentos avançados para que os estudantes aprendam a projetar, estruturar, implementar e coordenar sistemas computacionais. Com uma perspectiva integrada entre TI e inovação de soluções, o curso engloba conteúdos essenciais, como redes de computadores, inteligência artificial, programação, banco de dados e gestão de projetos. Com o vasto conhecimento adquirido ao longo do curso, principalmente nas áreas de análise e resolução de problemas tecnológicos, organização de dados e segurança cibernética, os graduados estarão à frente no mercado e atualizados com a inovação das tecnologias no Brasil e no mundo.</t>
@@ -8070,6 +8856,27 @@
   </si>
   <si>
     <t>Prepare-se para atuar em Sistemas de Informação a distância EAD com qualidade e reconhecimento. Vestibular On-line com bolsas de até 100%!</t>
+  </si>
+  <si>
+    <t>Integração de sistemas empresariais entre áreas</t>
+  </si>
+  <si>
+    <t>Analista de sistemas de informação de cerca de 32 anos, mulher de pele clara, cabelo castanho em ondas, camisa social e blazer, atenção aos blocos na mesa.</t>
+  </si>
+  <si>
+    <t>Sala de integração empresarial contemporânea brasileira, mesa com maquete de blocos, notebook, persiana, espaço de projeto, sem quadro de camadas e sem rack.</t>
+  </si>
+  <si>
+    <t>diagrama físico de blocos coloridos, notebook aberto, pasta de documentação, caneta, fios de ligação</t>
+  </si>
+  <si>
+    <t>Liga dois blocos do diagrama com um fio e confere a documentação no notebook, em pé à direita, telas e folhas sem escritos.</t>
+  </si>
+  <si>
+    <t>Palavras, textos, logotipos, marcas ou marca-d'água; mãos incorretas ou objetos deformados; interfaces flutuantes; cilindros de banco; backup; servidor como cena principal; papel pardo de gargalos; código na tela; holograma; capuz; ambiente luxuoso ou precário.</t>
+  </si>
+  <si>
+    <t>Fotografia publicitária realista em cenário brasileiro contemporâneo, iluminação natural profissional. Composição quadrada 1:1, enquadramento médio, assunto principal à direita, região inferior esquerda livre, sem rostos, mãos ou objetos importantes nessa área, separação clara entre pessoa e fundo. Analista de sistemas de informação, mulher de pele clara, cerca de 32 anos, blazer, ligando dois blocos coloridos do diagrama com um fio e conferindo o notebook. Objetos: diagrama de blocos, notebook, pasta de documentação, caneta e fios. Sem cilindros, sem backup, sem rack, sem palavras visíveis, sem legendas, sem identificações comerciais, sem elementos gráficos sobrepostos, sem marca-d'água, sem mãos anatomicamente incorretas e sem objetos deformados.</t>
   </si>
 </sst>
 </file>
@@ -17350,23 +18157,26 @@
       <c r="G97" t="s">
         <v>158</v>
       </c>
+      <c r="H97" t="s">
+        <v>2015</v>
+      </c>
       <c r="I97" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="J97" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="K97" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="L97" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="M97" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="N97" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="P97" t="s">
         <v>166</v>
@@ -17381,27 +18191,54 @@
         <v>167</v>
       </c>
       <c r="T97" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="U97" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="V97" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="W97" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X97" t="s">
+        <v>2025</v>
+      </c>
+      <c r="Y97" t="s">
+        <v>2026</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>2027</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>2028</v>
+      </c>
+      <c r="AB97" t="s">
+        <v>2029</v>
+      </c>
+      <c r="AC97" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD97" t="s">
+        <v>2030</v>
+      </c>
+      <c r="AE97" t="s">
+        <v>2031</v>
+      </c>
+      <c r="AF97" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="98" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>2024</v>
+        <v>2032</v>
       </c>
       <c r="B98" t="s">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="C98" t="s">
-        <v>2026</v>
+        <v>2034</v>
       </c>
       <c r="D98" t="s">
         <v>157</v>
@@ -17415,20 +18252,23 @@
       <c r="G98" t="s">
         <v>158</v>
       </c>
+      <c r="H98" t="s">
+        <v>2035</v>
+      </c>
       <c r="I98" t="s">
-        <v>2027</v>
+        <v>2036</v>
       </c>
       <c r="J98" t="s">
-        <v>2028</v>
+        <v>2037</v>
       </c>
       <c r="K98" t="s">
-        <v>2029</v>
+        <v>2038</v>
       </c>
       <c r="M98" t="s">
-        <v>2030</v>
+        <v>2039</v>
       </c>
       <c r="N98" t="s">
-        <v>2031</v>
+        <v>2040</v>
       </c>
       <c r="O98" t="s">
         <v>141</v>
@@ -17446,27 +18286,54 @@
         <v>1534</v>
       </c>
       <c r="T98" t="s">
-        <v>2032</v>
+        <v>2041</v>
       </c>
       <c r="U98" t="s">
-        <v>2033</v>
+        <v>2042</v>
       </c>
       <c r="V98" t="s">
-        <v>2034</v>
+        <v>2043</v>
       </c>
       <c r="W98" s="1" t="s">
         <v>1538</v>
+      </c>
+      <c r="X98" t="s">
+        <v>2044</v>
+      </c>
+      <c r="Y98" t="s">
+        <v>2045</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>2046</v>
+      </c>
+      <c r="AA98" t="s">
+        <v>2047</v>
+      </c>
+      <c r="AB98" t="s">
+        <v>2048</v>
+      </c>
+      <c r="AC98" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD98" t="s">
+        <v>2049</v>
+      </c>
+      <c r="AE98" t="s">
+        <v>2050</v>
+      </c>
+      <c r="AF98" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2035</v>
+        <v>2051</v>
       </c>
       <c r="B99" t="s">
-        <v>2036</v>
+        <v>2052</v>
       </c>
       <c r="C99" t="s">
-        <v>2037</v>
+        <v>2053</v>
       </c>
       <c r="D99" t="s">
         <v>35</v>
@@ -17480,23 +18347,26 @@
       <c r="G99" t="s">
         <v>89</v>
       </c>
+      <c r="H99" t="s">
+        <v>2054</v>
+      </c>
       <c r="I99" t="s">
-        <v>2038</v>
+        <v>2055</v>
       </c>
       <c r="J99" t="s">
-        <v>2039</v>
+        <v>2056</v>
       </c>
       <c r="K99" t="s">
-        <v>2040</v>
+        <v>2057</v>
       </c>
       <c r="L99" t="s">
-        <v>2041</v>
+        <v>2058</v>
       </c>
       <c r="M99" t="s">
-        <v>2042</v>
+        <v>2059</v>
       </c>
       <c r="N99" t="s">
-        <v>2043</v>
+        <v>2060</v>
       </c>
       <c r="O99" t="s">
         <v>141</v>
@@ -17511,27 +18381,54 @@
         <v>48</v>
       </c>
       <c r="T99" t="s">
-        <v>2044</v>
+        <v>2061</v>
       </c>
       <c r="U99" t="s">
-        <v>2045</v>
+        <v>2062</v>
       </c>
       <c r="V99" t="s">
-        <v>2046</v>
+        <v>2063</v>
       </c>
       <c r="W99" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X99" t="s">
+        <v>2064</v>
+      </c>
+      <c r="Y99" t="s">
+        <v>2065</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>2066</v>
+      </c>
+      <c r="AA99" t="s">
+        <v>2067</v>
+      </c>
+      <c r="AB99" t="s">
+        <v>2068</v>
+      </c>
+      <c r="AC99" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD99" t="s">
+        <v>2069</v>
+      </c>
+      <c r="AE99" t="s">
+        <v>2070</v>
+      </c>
+      <c r="AF99" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>2047</v>
+        <v>2071</v>
       </c>
       <c r="B100" t="s">
-        <v>2048</v>
+        <v>2072</v>
       </c>
       <c r="C100" t="s">
-        <v>2049</v>
+        <v>2073</v>
       </c>
       <c r="D100" t="s">
         <v>35</v>
@@ -17545,23 +18442,26 @@
       <c r="G100" t="s">
         <v>203</v>
       </c>
+      <c r="H100" t="s">
+        <v>2074</v>
+      </c>
       <c r="I100" t="s">
-        <v>2050</v>
+        <v>2075</v>
       </c>
       <c r="J100" t="s">
-        <v>2051</v>
+        <v>2076</v>
       </c>
       <c r="K100" t="s">
-        <v>2052</v>
+        <v>2077</v>
       </c>
       <c r="L100" t="s">
-        <v>2053</v>
+        <v>2078</v>
       </c>
       <c r="M100" t="s">
-        <v>2054</v>
+        <v>2079</v>
       </c>
       <c r="N100" t="s">
-        <v>2055</v>
+        <v>2080</v>
       </c>
       <c r="O100" t="s">
         <v>141</v>
@@ -17576,27 +18476,54 @@
         <v>48</v>
       </c>
       <c r="T100" t="s">
-        <v>2056</v>
+        <v>2081</v>
       </c>
       <c r="U100" t="s">
-        <v>2057</v>
+        <v>2082</v>
       </c>
       <c r="V100" t="s">
-        <v>2058</v>
+        <v>2083</v>
       </c>
       <c r="W100" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X100" t="s">
+        <v>2084</v>
+      </c>
+      <c r="Y100" t="s">
+        <v>2085</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>2086</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>2087</v>
+      </c>
+      <c r="AB100" t="s">
+        <v>2088</v>
+      </c>
+      <c r="AC100" t="s">
+        <v>1767</v>
+      </c>
+      <c r="AD100" t="s">
+        <v>2089</v>
+      </c>
+      <c r="AE100" t="s">
+        <v>2090</v>
+      </c>
+      <c r="AF100" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="101" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>2059</v>
+        <v>2091</v>
       </c>
       <c r="B101" t="s">
-        <v>2060</v>
+        <v>2092</v>
       </c>
       <c r="C101" t="s">
-        <v>2061</v>
+        <v>2093</v>
       </c>
       <c r="D101" t="s">
         <v>35</v>
@@ -17610,23 +18537,26 @@
       <c r="G101" t="s">
         <v>89</v>
       </c>
+      <c r="H101" t="s">
+        <v>2094</v>
+      </c>
       <c r="I101" t="s">
-        <v>2062</v>
+        <v>2095</v>
       </c>
       <c r="J101" t="s">
-        <v>2063</v>
+        <v>2096</v>
       </c>
       <c r="K101" t="s">
-        <v>2064</v>
+        <v>2097</v>
       </c>
       <c r="L101" t="s">
-        <v>2065</v>
+        <v>2098</v>
       </c>
       <c r="M101" t="s">
-        <v>2066</v>
+        <v>2099</v>
       </c>
       <c r="N101" t="s">
-        <v>2067</v>
+        <v>2100</v>
       </c>
       <c r="O101" t="s">
         <v>141</v>
@@ -17644,27 +18574,54 @@
         <v>167</v>
       </c>
       <c r="T101" t="s">
-        <v>2068</v>
+        <v>2101</v>
       </c>
       <c r="U101" t="s">
-        <v>2069</v>
+        <v>2102</v>
       </c>
       <c r="V101" t="s">
-        <v>2070</v>
+        <v>2103</v>
       </c>
       <c r="W101" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X101" t="s">
+        <v>2104</v>
+      </c>
+      <c r="Y101" t="s">
+        <v>2105</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>2106</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>2107</v>
+      </c>
+      <c r="AB101" t="s">
+        <v>2108</v>
+      </c>
+      <c r="AC101" t="s">
+        <v>2109</v>
+      </c>
+      <c r="AD101" t="s">
+        <v>2110</v>
+      </c>
+      <c r="AE101" t="s">
+        <v>2111</v>
+      </c>
+      <c r="AF101" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="102" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>2071</v>
+        <v>2112</v>
       </c>
       <c r="B102" t="s">
-        <v>2072</v>
+        <v>2113</v>
       </c>
       <c r="C102" t="s">
-        <v>2073</v>
+        <v>2114</v>
       </c>
       <c r="D102" t="s">
         <v>35</v>
@@ -17678,23 +18635,26 @@
       <c r="G102" t="s">
         <v>203</v>
       </c>
+      <c r="H102" t="s">
+        <v>2115</v>
+      </c>
       <c r="I102" t="s">
-        <v>2074</v>
+        <v>2116</v>
       </c>
       <c r="J102" t="s">
-        <v>2075</v>
+        <v>2117</v>
       </c>
       <c r="K102" t="s">
-        <v>2076</v>
+        <v>2118</v>
       </c>
       <c r="L102" t="s">
-        <v>2077</v>
+        <v>2119</v>
       </c>
       <c r="M102" t="s">
-        <v>2078</v>
+        <v>2120</v>
       </c>
       <c r="N102" t="s">
-        <v>2079</v>
+        <v>2121</v>
       </c>
       <c r="O102" t="s">
         <v>141</v>
@@ -17709,27 +18669,54 @@
         <v>48</v>
       </c>
       <c r="T102" t="s">
-        <v>2080</v>
+        <v>2122</v>
       </c>
       <c r="U102" t="s">
-        <v>2081</v>
+        <v>2123</v>
       </c>
       <c r="V102" t="s">
-        <v>2082</v>
+        <v>2124</v>
       </c>
       <c r="W102" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X102" t="s">
+        <v>2125</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>2126</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>2127</v>
+      </c>
+      <c r="AA102" t="s">
+        <v>2128</v>
+      </c>
+      <c r="AB102" t="s">
+        <v>2129</v>
+      </c>
+      <c r="AC102" t="s">
+        <v>2130</v>
+      </c>
+      <c r="AD102" t="s">
+        <v>2131</v>
+      </c>
+      <c r="AE102" t="s">
+        <v>2132</v>
+      </c>
+      <c r="AF102" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="103" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>2083</v>
+        <v>2133</v>
       </c>
       <c r="B103" t="s">
-        <v>2084</v>
+        <v>2134</v>
       </c>
       <c r="C103" t="s">
-        <v>2085</v>
+        <v>2135</v>
       </c>
       <c r="D103" t="s">
         <v>35</v>
@@ -17743,23 +18730,26 @@
       <c r="G103" t="s">
         <v>203</v>
       </c>
+      <c r="H103" t="s">
+        <v>2136</v>
+      </c>
       <c r="I103" t="s">
-        <v>2086</v>
+        <v>2137</v>
       </c>
       <c r="J103" t="s">
-        <v>2087</v>
+        <v>2138</v>
       </c>
       <c r="K103" t="s">
-        <v>2088</v>
+        <v>2139</v>
       </c>
       <c r="L103" t="s">
-        <v>2089</v>
+        <v>2140</v>
       </c>
       <c r="M103" t="s">
-        <v>2090</v>
+        <v>2141</v>
       </c>
       <c r="N103" t="s">
-        <v>2091</v>
+        <v>2142</v>
       </c>
       <c r="O103" t="s">
         <v>141</v>
@@ -17774,27 +18764,54 @@
         <v>48</v>
       </c>
       <c r="T103" t="s">
-        <v>2092</v>
+        <v>2143</v>
       </c>
       <c r="U103" t="s">
-        <v>2093</v>
+        <v>2144</v>
       </c>
       <c r="V103" t="s">
-        <v>2094</v>
+        <v>2145</v>
       </c>
       <c r="W103" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X103" t="s">
+        <v>2146</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>2147</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>2148</v>
+      </c>
+      <c r="AA103" t="s">
+        <v>2149</v>
+      </c>
+      <c r="AB103" t="s">
+        <v>2150</v>
+      </c>
+      <c r="AC103" t="s">
+        <v>2151</v>
+      </c>
+      <c r="AD103" t="s">
+        <v>2152</v>
+      </c>
+      <c r="AE103" t="s">
+        <v>2153</v>
+      </c>
+      <c r="AF103" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="104" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>2095</v>
+        <v>2154</v>
       </c>
       <c r="B104" t="s">
-        <v>2096</v>
+        <v>2155</v>
       </c>
       <c r="C104" t="s">
-        <v>2097</v>
+        <v>2156</v>
       </c>
       <c r="D104" t="s">
         <v>157</v>
@@ -17808,23 +18825,26 @@
       <c r="G104" t="s">
         <v>158</v>
       </c>
+      <c r="H104" t="s">
+        <v>2157</v>
+      </c>
       <c r="I104" t="s">
-        <v>2098</v>
+        <v>2158</v>
       </c>
       <c r="J104" t="s">
-        <v>2099</v>
+        <v>2159</v>
       </c>
       <c r="K104" t="s">
-        <v>2100</v>
+        <v>2160</v>
       </c>
       <c r="L104" t="s">
-        <v>2101</v>
+        <v>2161</v>
       </c>
       <c r="M104" t="s">
-        <v>2102</v>
+        <v>2162</v>
       </c>
       <c r="N104" t="s">
-        <v>2103</v>
+        <v>2163</v>
       </c>
       <c r="P104" t="s">
         <v>166</v>
@@ -17839,27 +18859,54 @@
         <v>167</v>
       </c>
       <c r="T104" t="s">
-        <v>2104</v>
+        <v>2164</v>
       </c>
       <c r="U104" t="s">
-        <v>2105</v>
+        <v>2165</v>
       </c>
       <c r="V104" t="s">
-        <v>2106</v>
+        <v>2166</v>
       </c>
       <c r="W104" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X104" t="s">
+        <v>2167</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>2168</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>2169</v>
+      </c>
+      <c r="AA104" t="s">
+        <v>2170</v>
+      </c>
+      <c r="AB104" t="s">
+        <v>2171</v>
+      </c>
+      <c r="AC104" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD104" t="s">
+        <v>2172</v>
+      </c>
+      <c r="AE104" t="s">
+        <v>2173</v>
+      </c>
+      <c r="AF104" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="105" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>2107</v>
+        <v>2174</v>
       </c>
       <c r="B105" t="s">
-        <v>2108</v>
+        <v>2175</v>
       </c>
       <c r="C105" t="s">
-        <v>2109</v>
+        <v>2176</v>
       </c>
       <c r="D105" t="s">
         <v>157</v>
@@ -17873,23 +18920,26 @@
       <c r="G105" t="s">
         <v>158</v>
       </c>
+      <c r="H105" t="s">
+        <v>2177</v>
+      </c>
       <c r="I105" t="s">
-        <v>2110</v>
+        <v>2178</v>
       </c>
       <c r="J105" t="s">
-        <v>2111</v>
+        <v>2179</v>
       </c>
       <c r="K105" t="s">
-        <v>2112</v>
+        <v>2180</v>
       </c>
       <c r="L105" t="s">
-        <v>2113</v>
+        <v>2181</v>
       </c>
       <c r="M105" t="s">
-        <v>2114</v>
+        <v>2182</v>
       </c>
       <c r="N105" t="s">
-        <v>2115</v>
+        <v>2183</v>
       </c>
       <c r="P105" t="s">
         <v>166</v>
@@ -17904,27 +18954,54 @@
         <v>167</v>
       </c>
       <c r="T105" t="s">
-        <v>2116</v>
+        <v>2184</v>
       </c>
       <c r="U105" t="s">
-        <v>2117</v>
+        <v>2185</v>
       </c>
       <c r="V105" t="s">
-        <v>2118</v>
+        <v>2186</v>
       </c>
       <c r="W105" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X105" t="s">
+        <v>2187</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>2188</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>2189</v>
+      </c>
+      <c r="AA105" t="s">
+        <v>2190</v>
+      </c>
+      <c r="AB105" t="s">
+        <v>2191</v>
+      </c>
+      <c r="AC105" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD105" t="s">
+        <v>2192</v>
+      </c>
+      <c r="AE105" t="s">
+        <v>2193</v>
+      </c>
+      <c r="AF105" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="106" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>2119</v>
+        <v>2194</v>
       </c>
       <c r="B106" t="s">
-        <v>2120</v>
+        <v>2195</v>
       </c>
       <c r="C106" t="s">
-        <v>2121</v>
+        <v>2196</v>
       </c>
       <c r="D106" t="s">
         <v>65</v>
@@ -17938,23 +19015,26 @@
       <c r="G106" t="s">
         <v>203</v>
       </c>
+      <c r="H106" t="s">
+        <v>2197</v>
+      </c>
       <c r="I106" t="s">
-        <v>2122</v>
+        <v>2198</v>
       </c>
       <c r="J106" t="s">
-        <v>2123</v>
+        <v>2199</v>
       </c>
       <c r="K106" t="s">
-        <v>2124</v>
+        <v>2200</v>
       </c>
       <c r="L106" t="s">
-        <v>2125</v>
+        <v>2201</v>
       </c>
       <c r="M106" t="s">
-        <v>2126</v>
+        <v>2202</v>
       </c>
       <c r="N106" t="s">
-        <v>2127</v>
+        <v>2203</v>
       </c>
       <c r="P106" t="s">
         <v>46</v>
@@ -17966,27 +19046,54 @@
         <v>48</v>
       </c>
       <c r="T106" t="s">
-        <v>2128</v>
+        <v>2204</v>
       </c>
       <c r="U106" t="s">
-        <v>2129</v>
+        <v>2205</v>
       </c>
       <c r="V106" t="s">
-        <v>2130</v>
+        <v>2206</v>
       </c>
       <c r="W106" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X106" t="s">
+        <v>2207</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>2208</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>2209</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>2210</v>
+      </c>
+      <c r="AB106" t="s">
+        <v>2211</v>
+      </c>
+      <c r="AC106" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD106" t="s">
+        <v>2212</v>
+      </c>
+      <c r="AE106" t="s">
+        <v>2213</v>
+      </c>
+      <c r="AF106" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="107" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2131</v>
+        <v>2214</v>
       </c>
       <c r="B107" t="s">
-        <v>2132</v>
+        <v>2215</v>
       </c>
       <c r="C107" t="s">
-        <v>2133</v>
+        <v>2216</v>
       </c>
       <c r="D107" t="s">
         <v>35</v>
@@ -18000,23 +19107,26 @@
       <c r="G107" t="s">
         <v>158</v>
       </c>
+      <c r="H107" t="s">
+        <v>2217</v>
+      </c>
       <c r="I107" t="s">
-        <v>2134</v>
+        <v>2218</v>
       </c>
       <c r="J107" t="s">
-        <v>2135</v>
+        <v>2219</v>
       </c>
       <c r="K107" t="s">
-        <v>2136</v>
+        <v>2220</v>
       </c>
       <c r="L107" t="s">
-        <v>2137</v>
+        <v>2221</v>
       </c>
       <c r="M107" t="s">
-        <v>2138</v>
+        <v>2222</v>
       </c>
       <c r="N107" t="s">
-        <v>2139</v>
+        <v>2223</v>
       </c>
       <c r="P107" t="s">
         <v>46</v>
@@ -18028,27 +19138,54 @@
         <v>48</v>
       </c>
       <c r="T107" t="s">
-        <v>2140</v>
+        <v>2224</v>
       </c>
       <c r="U107" t="s">
-        <v>2141</v>
+        <v>2225</v>
       </c>
       <c r="V107" t="s">
-        <v>2142</v>
+        <v>2226</v>
       </c>
       <c r="W107" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X107" t="s">
+        <v>2227</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>2228</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>2229</v>
+      </c>
+      <c r="AA107" t="s">
+        <v>2230</v>
+      </c>
+      <c r="AB107" t="s">
+        <v>2231</v>
+      </c>
+      <c r="AC107" t="s">
+        <v>2232</v>
+      </c>
+      <c r="AD107" t="s">
+        <v>2233</v>
+      </c>
+      <c r="AE107" t="s">
+        <v>2234</v>
+      </c>
+      <c r="AF107" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="108" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>2143</v>
+        <v>2235</v>
       </c>
       <c r="B108" t="s">
-        <v>2144</v>
+        <v>2236</v>
       </c>
       <c r="C108" t="s">
-        <v>2145</v>
+        <v>2237</v>
       </c>
       <c r="D108" t="s">
         <v>65</v>
@@ -18062,23 +19199,26 @@
       <c r="G108" t="s">
         <v>331</v>
       </c>
+      <c r="H108" t="s">
+        <v>2238</v>
+      </c>
       <c r="I108" t="s">
-        <v>2146</v>
+        <v>2239</v>
       </c>
       <c r="J108" t="s">
-        <v>2147</v>
+        <v>2240</v>
       </c>
       <c r="K108" t="s">
-        <v>2148</v>
+        <v>2241</v>
       </c>
       <c r="L108" t="s">
-        <v>2149</v>
+        <v>2242</v>
       </c>
       <c r="M108" t="s">
-        <v>2150</v>
+        <v>2243</v>
       </c>
       <c r="N108" t="s">
-        <v>2151</v>
+        <v>2244</v>
       </c>
       <c r="P108" t="s">
         <v>46</v>
@@ -18090,27 +19230,54 @@
         <v>48</v>
       </c>
       <c r="T108" t="s">
-        <v>2152</v>
+        <v>2245</v>
       </c>
       <c r="U108" t="s">
-        <v>2153</v>
+        <v>2246</v>
       </c>
       <c r="V108" t="s">
-        <v>2154</v>
+        <v>2247</v>
       </c>
       <c r="W108" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X108" t="s">
+        <v>2248</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>2249</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>2250</v>
+      </c>
+      <c r="AA108" t="s">
+        <v>2251</v>
+      </c>
+      <c r="AB108" t="s">
+        <v>2252</v>
+      </c>
+      <c r="AC108" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD108" t="s">
+        <v>2253</v>
+      </c>
+      <c r="AE108" t="s">
+        <v>2254</v>
+      </c>
+      <c r="AF108" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="109" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>2155</v>
+        <v>2255</v>
       </c>
       <c r="B109" t="s">
-        <v>2156</v>
+        <v>2256</v>
       </c>
       <c r="C109" t="s">
-        <v>2157</v>
+        <v>2257</v>
       </c>
       <c r="D109" t="s">
         <v>157</v>
@@ -18124,23 +19291,26 @@
       <c r="G109" t="s">
         <v>158</v>
       </c>
+      <c r="H109" t="s">
+        <v>2258</v>
+      </c>
       <c r="I109" t="s">
-        <v>2158</v>
+        <v>2259</v>
       </c>
       <c r="J109" t="s">
-        <v>2159</v>
+        <v>2260</v>
       </c>
       <c r="K109" t="s">
-        <v>2160</v>
+        <v>2261</v>
       </c>
       <c r="L109" t="s">
-        <v>2161</v>
+        <v>2262</v>
       </c>
       <c r="M109" t="s">
-        <v>2162</v>
+        <v>2263</v>
       </c>
       <c r="N109" t="s">
-        <v>2163</v>
+        <v>2264</v>
       </c>
       <c r="P109" t="s">
         <v>166</v>
@@ -18155,27 +19325,54 @@
         <v>167</v>
       </c>
       <c r="T109" t="s">
-        <v>2164</v>
+        <v>2265</v>
       </c>
       <c r="U109" t="s">
-        <v>2165</v>
+        <v>2266</v>
       </c>
       <c r="V109" t="s">
-        <v>2166</v>
+        <v>2267</v>
       </c>
       <c r="W109" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X109" t="s">
+        <v>2268</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>2269</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>2270</v>
+      </c>
+      <c r="AA109" t="s">
+        <v>2271</v>
+      </c>
+      <c r="AB109" t="s">
+        <v>2272</v>
+      </c>
+      <c r="AC109" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD109" t="s">
+        <v>2273</v>
+      </c>
+      <c r="AE109" t="s">
+        <v>2274</v>
+      </c>
+      <c r="AF109" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="110" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>2167</v>
+        <v>2275</v>
       </c>
       <c r="B110" t="s">
-        <v>2168</v>
+        <v>2276</v>
       </c>
       <c r="C110" t="s">
-        <v>2169</v>
+        <v>2277</v>
       </c>
       <c r="D110" t="s">
         <v>157</v>
@@ -18189,23 +19386,26 @@
       <c r="G110" t="s">
         <v>158</v>
       </c>
+      <c r="H110" t="s">
+        <v>2278</v>
+      </c>
       <c r="I110" t="s">
-        <v>2170</v>
+        <v>2279</v>
       </c>
       <c r="J110" t="s">
-        <v>2171</v>
+        <v>2280</v>
       </c>
       <c r="K110" t="s">
-        <v>2172</v>
+        <v>2281</v>
       </c>
       <c r="L110" t="s">
-        <v>2173</v>
+        <v>2282</v>
       </c>
       <c r="M110" t="s">
-        <v>2174</v>
+        <v>2283</v>
       </c>
       <c r="N110" t="s">
-        <v>2175</v>
+        <v>2284</v>
       </c>
       <c r="P110" t="s">
         <v>166</v>
@@ -18220,27 +19420,54 @@
         <v>167</v>
       </c>
       <c r="T110" t="s">
-        <v>2176</v>
+        <v>2285</v>
       </c>
       <c r="U110" t="s">
-        <v>2177</v>
+        <v>2286</v>
       </c>
       <c r="V110" t="s">
-        <v>2178</v>
+        <v>2287</v>
       </c>
       <c r="W110" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X110" t="s">
+        <v>2288</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>2289</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>2290</v>
+      </c>
+      <c r="AA110" t="s">
+        <v>2291</v>
+      </c>
+      <c r="AB110" t="s">
+        <v>2292</v>
+      </c>
+      <c r="AC110" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD110" t="s">
+        <v>2293</v>
+      </c>
+      <c r="AE110" t="s">
+        <v>2294</v>
+      </c>
+      <c r="AF110" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="111" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>2179</v>
+        <v>2295</v>
       </c>
       <c r="B111" t="s">
-        <v>2180</v>
+        <v>2296</v>
       </c>
       <c r="C111" t="s">
-        <v>2181</v>
+        <v>2297</v>
       </c>
       <c r="D111" t="s">
         <v>65</v>
@@ -18254,23 +19481,26 @@
       <c r="G111" t="s">
         <v>89</v>
       </c>
+      <c r="H111" t="s">
+        <v>2298</v>
+      </c>
       <c r="I111" t="s">
-        <v>2182</v>
+        <v>2299</v>
       </c>
       <c r="J111" t="s">
-        <v>2183</v>
+        <v>2300</v>
       </c>
       <c r="K111" t="s">
-        <v>2184</v>
+        <v>2301</v>
       </c>
       <c r="L111" t="s">
-        <v>2185</v>
+        <v>2302</v>
       </c>
       <c r="M111" t="s">
-        <v>2186</v>
+        <v>2303</v>
       </c>
       <c r="N111" t="s">
-        <v>2187</v>
+        <v>2304</v>
       </c>
       <c r="P111" t="s">
         <v>166</v>
@@ -18285,27 +19515,54 @@
         <v>167</v>
       </c>
       <c r="T111" t="s">
-        <v>2188</v>
+        <v>2305</v>
       </c>
       <c r="U111" t="s">
-        <v>2189</v>
+        <v>2306</v>
       </c>
       <c r="V111" t="s">
-        <v>2190</v>
+        <v>2307</v>
       </c>
       <c r="W111" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X111" t="s">
+        <v>2308</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>2309</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>2310</v>
+      </c>
+      <c r="AA111" t="s">
+        <v>2311</v>
+      </c>
+      <c r="AB111" t="s">
+        <v>2312</v>
+      </c>
+      <c r="AC111" t="s">
+        <v>1458</v>
+      </c>
+      <c r="AD111" t="s">
+        <v>2313</v>
+      </c>
+      <c r="AE111" t="s">
+        <v>2314</v>
+      </c>
+      <c r="AF111" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="112" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>2191</v>
+        <v>2315</v>
       </c>
       <c r="B112" t="s">
-        <v>2192</v>
+        <v>2316</v>
       </c>
       <c r="C112" t="s">
-        <v>2193</v>
+        <v>2317</v>
       </c>
       <c r="D112" t="s">
         <v>65</v>
@@ -18319,23 +19576,26 @@
       <c r="G112" t="s">
         <v>203</v>
       </c>
+      <c r="H112" t="s">
+        <v>2318</v>
+      </c>
       <c r="I112" t="s">
-        <v>2194</v>
+        <v>2319</v>
       </c>
       <c r="J112" t="s">
-        <v>2195</v>
+        <v>2320</v>
       </c>
       <c r="K112" t="s">
-        <v>2196</v>
+        <v>2321</v>
       </c>
       <c r="L112" t="s">
-        <v>2197</v>
+        <v>2322</v>
       </c>
       <c r="M112" t="s">
-        <v>2198</v>
+        <v>2323</v>
       </c>
       <c r="N112" t="s">
-        <v>2199</v>
+        <v>2324</v>
       </c>
       <c r="O112" t="s">
         <v>141</v>
@@ -18353,27 +19613,54 @@
         <v>167</v>
       </c>
       <c r="T112" t="s">
-        <v>2200</v>
+        <v>2325</v>
       </c>
       <c r="U112" t="s">
-        <v>2201</v>
+        <v>2326</v>
       </c>
       <c r="V112" t="s">
-        <v>2202</v>
+        <v>2327</v>
       </c>
       <c r="W112" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X112" t="s">
+        <v>2328</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>2329</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>2330</v>
+      </c>
+      <c r="AA112" t="s">
+        <v>2331</v>
+      </c>
+      <c r="AB112" t="s">
+        <v>2332</v>
+      </c>
+      <c r="AC112" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD112" t="s">
+        <v>2333</v>
+      </c>
+      <c r="AE112" t="s">
+        <v>2334</v>
+      </c>
+      <c r="AF112" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>2203</v>
+        <v>2335</v>
       </c>
       <c r="B113" t="s">
-        <v>2204</v>
+        <v>2336</v>
       </c>
       <c r="C113" t="s">
-        <v>2205</v>
+        <v>2337</v>
       </c>
       <c r="D113" t="s">
         <v>65</v>
@@ -18387,23 +19674,26 @@
       <c r="G113" t="s">
         <v>203</v>
       </c>
+      <c r="H113" t="s">
+        <v>2338</v>
+      </c>
       <c r="I113" t="s">
-        <v>2206</v>
+        <v>2339</v>
       </c>
       <c r="J113" t="s">
-        <v>2207</v>
+        <v>2340</v>
       </c>
       <c r="K113" t="s">
-        <v>2208</v>
+        <v>2341</v>
       </c>
       <c r="L113" t="s">
-        <v>2209</v>
+        <v>2342</v>
       </c>
       <c r="M113" t="s">
-        <v>2210</v>
+        <v>2343</v>
       </c>
       <c r="N113" t="s">
-        <v>2211</v>
+        <v>2344</v>
       </c>
       <c r="O113" t="s">
         <v>141</v>
@@ -18421,27 +19711,54 @@
         <v>167</v>
       </c>
       <c r="T113" t="s">
-        <v>2212</v>
+        <v>2345</v>
       </c>
       <c r="U113" t="s">
-        <v>2213</v>
+        <v>2346</v>
       </c>
       <c r="V113" t="s">
-        <v>2214</v>
+        <v>2347</v>
       </c>
       <c r="W113" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X113" t="s">
+        <v>2348</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>2349</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>2350</v>
+      </c>
+      <c r="AA113" t="s">
+        <v>2351</v>
+      </c>
+      <c r="AB113" t="s">
+        <v>2352</v>
+      </c>
+      <c r="AC113" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD113" t="s">
+        <v>2353</v>
+      </c>
+      <c r="AE113" t="s">
+        <v>2354</v>
+      </c>
+      <c r="AF113" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>2215</v>
+        <v>2355</v>
       </c>
       <c r="B114" t="s">
-        <v>2216</v>
+        <v>2356</v>
       </c>
       <c r="C114" t="s">
-        <v>2217</v>
+        <v>2357</v>
       </c>
       <c r="D114" t="s">
         <v>35</v>
@@ -18455,23 +19772,26 @@
       <c r="G114" t="s">
         <v>331</v>
       </c>
+      <c r="H114" t="s">
+        <v>2358</v>
+      </c>
       <c r="I114" t="s">
-        <v>2218</v>
+        <v>2359</v>
       </c>
       <c r="J114" t="s">
-        <v>2219</v>
+        <v>2360</v>
       </c>
       <c r="K114" t="s">
-        <v>2220</v>
+        <v>2361</v>
       </c>
       <c r="L114" t="s">
-        <v>2221</v>
+        <v>2362</v>
       </c>
       <c r="M114" t="s">
-        <v>2222</v>
+        <v>2363</v>
       </c>
       <c r="N114" t="s">
-        <v>2223</v>
+        <v>2364</v>
       </c>
       <c r="P114" t="s">
         <v>46</v>
@@ -18483,27 +19803,54 @@
         <v>48</v>
       </c>
       <c r="T114" t="s">
-        <v>2224</v>
+        <v>2365</v>
       </c>
       <c r="U114" t="s">
-        <v>2225</v>
+        <v>2366</v>
       </c>
       <c r="V114" t="s">
-        <v>2226</v>
+        <v>2367</v>
       </c>
       <c r="W114" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X114" t="s">
+        <v>2368</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>2369</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>2370</v>
+      </c>
+      <c r="AA114" t="s">
+        <v>2371</v>
+      </c>
+      <c r="AB114" t="s">
+        <v>2372</v>
+      </c>
+      <c r="AC114" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD114" t="s">
+        <v>2373</v>
+      </c>
+      <c r="AE114" t="s">
+        <v>2374</v>
+      </c>
+      <c r="AF114" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>2227</v>
+        <v>2375</v>
       </c>
       <c r="B115" t="s">
-        <v>2228</v>
+        <v>2376</v>
       </c>
       <c r="C115" t="s">
-        <v>2229</v>
+        <v>2377</v>
       </c>
       <c r="D115" t="s">
         <v>65</v>
@@ -18517,23 +19864,26 @@
       <c r="G115" t="s">
         <v>331</v>
       </c>
+      <c r="H115" t="s">
+        <v>2378</v>
+      </c>
       <c r="I115" t="s">
-        <v>2230</v>
+        <v>2379</v>
       </c>
       <c r="J115" t="s">
-        <v>2231</v>
+        <v>2380</v>
       </c>
       <c r="K115" t="s">
-        <v>2232</v>
+        <v>2381</v>
       </c>
       <c r="L115" t="s">
-        <v>2233</v>
+        <v>2382</v>
       </c>
       <c r="M115" t="s">
-        <v>2234</v>
+        <v>2383</v>
       </c>
       <c r="N115" t="s">
-        <v>2235</v>
+        <v>2384</v>
       </c>
       <c r="P115" t="s">
         <v>46</v>
@@ -18545,27 +19895,54 @@
         <v>48</v>
       </c>
       <c r="T115" t="s">
-        <v>2236</v>
+        <v>2385</v>
       </c>
       <c r="U115" t="s">
-        <v>2237</v>
+        <v>2386</v>
       </c>
       <c r="V115" t="s">
-        <v>2238</v>
+        <v>2387</v>
       </c>
       <c r="W115" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X115" t="s">
+        <v>2388</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>2389</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>2390</v>
+      </c>
+      <c r="AA115" t="s">
+        <v>2391</v>
+      </c>
+      <c r="AB115" t="s">
+        <v>2392</v>
+      </c>
+      <c r="AC115" t="s">
+        <v>473</v>
+      </c>
+      <c r="AD115" t="s">
+        <v>2393</v>
+      </c>
+      <c r="AE115" t="s">
+        <v>2394</v>
+      </c>
+      <c r="AF115" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="116" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>2239</v>
+        <v>2395</v>
       </c>
       <c r="B116" t="s">
-        <v>2240</v>
+        <v>2396</v>
       </c>
       <c r="C116" t="s">
-        <v>2241</v>
+        <v>2397</v>
       </c>
       <c r="D116" t="s">
         <v>65</v>
@@ -18579,23 +19956,26 @@
       <c r="G116" t="s">
         <v>203</v>
       </c>
+      <c r="H116" t="s">
+        <v>2398</v>
+      </c>
       <c r="I116" t="s">
-        <v>2242</v>
+        <v>2399</v>
       </c>
       <c r="J116" t="s">
-        <v>2243</v>
+        <v>2400</v>
       </c>
       <c r="K116" t="s">
-        <v>2244</v>
+        <v>2401</v>
       </c>
       <c r="L116" t="s">
-        <v>2245</v>
+        <v>2402</v>
       </c>
       <c r="M116" t="s">
-        <v>2246</v>
+        <v>2403</v>
       </c>
       <c r="N116" t="s">
-        <v>2247</v>
+        <v>2404</v>
       </c>
       <c r="P116" t="s">
         <v>46</v>
@@ -18607,27 +19987,54 @@
         <v>48</v>
       </c>
       <c r="T116" t="s">
-        <v>2248</v>
+        <v>2405</v>
       </c>
       <c r="U116" t="s">
-        <v>2249</v>
+        <v>2406</v>
       </c>
       <c r="V116" t="s">
-        <v>2250</v>
+        <v>2407</v>
       </c>
       <c r="W116" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X116" t="s">
+        <v>2408</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>2409</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>2410</v>
+      </c>
+      <c r="AA116" t="s">
+        <v>2411</v>
+      </c>
+      <c r="AB116" t="s">
+        <v>2412</v>
+      </c>
+      <c r="AC116" t="s">
+        <v>1788</v>
+      </c>
+      <c r="AD116" t="s">
+        <v>2413</v>
+      </c>
+      <c r="AE116" t="s">
+        <v>2414</v>
+      </c>
+      <c r="AF116" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>2251</v>
+        <v>2415</v>
       </c>
       <c r="B117" t="s">
-        <v>2252</v>
+        <v>2416</v>
       </c>
       <c r="C117" t="s">
-        <v>2253</v>
+        <v>2417</v>
       </c>
       <c r="D117" t="s">
         <v>35</v>
@@ -18641,23 +20048,26 @@
       <c r="G117" t="s">
         <v>331</v>
       </c>
+      <c r="H117" t="s">
+        <v>2418</v>
+      </c>
       <c r="I117" t="s">
-        <v>2254</v>
+        <v>2419</v>
       </c>
       <c r="J117" t="s">
-        <v>2255</v>
+        <v>2420</v>
       </c>
       <c r="K117" t="s">
-        <v>2256</v>
+        <v>2421</v>
       </c>
       <c r="L117" t="s">
-        <v>2257</v>
+        <v>2422</v>
       </c>
       <c r="M117" t="s">
-        <v>2258</v>
+        <v>2423</v>
       </c>
       <c r="N117" t="s">
-        <v>2259</v>
+        <v>2424</v>
       </c>
       <c r="O117" t="s">
         <v>141</v>
@@ -18675,27 +20085,54 @@
         <v>167</v>
       </c>
       <c r="T117" t="s">
-        <v>2260</v>
+        <v>2425</v>
       </c>
       <c r="U117" t="s">
-        <v>2261</v>
+        <v>2426</v>
       </c>
       <c r="V117" t="s">
-        <v>2262</v>
+        <v>2427</v>
       </c>
       <c r="W117" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X117" t="s">
+        <v>2428</v>
+      </c>
+      <c r="Y117" t="s">
+        <v>2429</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AA117" t="s">
+        <v>2431</v>
+      </c>
+      <c r="AB117" t="s">
+        <v>2432</v>
+      </c>
+      <c r="AC117" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD117" t="s">
+        <v>2433</v>
+      </c>
+      <c r="AE117" t="s">
+        <v>2434</v>
+      </c>
+      <c r="AF117" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>2263</v>
+        <v>2435</v>
       </c>
       <c r="B118" t="s">
-        <v>2264</v>
+        <v>2436</v>
       </c>
       <c r="C118" t="s">
-        <v>2265</v>
+        <v>2437</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -18709,23 +20146,26 @@
       <c r="G118" t="s">
         <v>158</v>
       </c>
+      <c r="H118" t="s">
+        <v>2438</v>
+      </c>
       <c r="I118" t="s">
-        <v>2266</v>
+        <v>2439</v>
       </c>
       <c r="J118" t="s">
-        <v>2267</v>
+        <v>2440</v>
       </c>
       <c r="K118" t="s">
-        <v>2268</v>
+        <v>2441</v>
       </c>
       <c r="L118" t="s">
-        <v>2269</v>
+        <v>2442</v>
       </c>
       <c r="M118" t="s">
-        <v>2270</v>
+        <v>2443</v>
       </c>
       <c r="N118" t="s">
-        <v>2271</v>
+        <v>2444</v>
       </c>
       <c r="P118" t="s">
         <v>166</v>
@@ -18740,27 +20180,54 @@
         <v>167</v>
       </c>
       <c r="T118" t="s">
-        <v>2272</v>
+        <v>2445</v>
       </c>
       <c r="U118" t="s">
-        <v>2273</v>
+        <v>2446</v>
       </c>
       <c r="V118" t="s">
-        <v>2274</v>
+        <v>2447</v>
       </c>
       <c r="W118" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X118" t="s">
+        <v>2448</v>
+      </c>
+      <c r="Y118" t="s">
+        <v>2449</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>2450</v>
+      </c>
+      <c r="AA118" t="s">
+        <v>2451</v>
+      </c>
+      <c r="AB118" t="s">
+        <v>2452</v>
+      </c>
+      <c r="AC118" t="s">
+        <v>621</v>
+      </c>
+      <c r="AD118" t="s">
+        <v>2453</v>
+      </c>
+      <c r="AE118" t="s">
+        <v>2454</v>
+      </c>
+      <c r="AF118" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="119" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>2275</v>
+        <v>2455</v>
       </c>
       <c r="B119" t="s">
-        <v>2276</v>
+        <v>2456</v>
       </c>
       <c r="C119" t="s">
-        <v>2277</v>
+        <v>2457</v>
       </c>
       <c r="D119" t="s">
         <v>35</v>
@@ -18774,23 +20241,26 @@
       <c r="G119" t="s">
         <v>203</v>
       </c>
+      <c r="H119" t="s">
+        <v>2458</v>
+      </c>
       <c r="I119" t="s">
-        <v>2278</v>
+        <v>2459</v>
       </c>
       <c r="J119" t="s">
-        <v>2279</v>
+        <v>2460</v>
       </c>
       <c r="K119" t="s">
-        <v>2280</v>
+        <v>2461</v>
       </c>
       <c r="L119" t="s">
-        <v>2281</v>
+        <v>2462</v>
       </c>
       <c r="M119" t="s">
-        <v>2282</v>
+        <v>2463</v>
       </c>
       <c r="N119" t="s">
-        <v>2283</v>
+        <v>2464</v>
       </c>
       <c r="O119" t="s">
         <v>141</v>
@@ -18805,27 +20275,54 @@
         <v>48</v>
       </c>
       <c r="T119" t="s">
-        <v>2284</v>
+        <v>2465</v>
       </c>
       <c r="U119" t="s">
-        <v>2285</v>
+        <v>2466</v>
       </c>
       <c r="V119" t="s">
-        <v>2286</v>
+        <v>2467</v>
       </c>
       <c r="W119" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X119" t="s">
+        <v>2468</v>
+      </c>
+      <c r="Y119" t="s">
+        <v>2469</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>2470</v>
+      </c>
+      <c r="AA119" t="s">
+        <v>2471</v>
+      </c>
+      <c r="AB119" t="s">
+        <v>2472</v>
+      </c>
+      <c r="AC119" t="s">
+        <v>1788</v>
+      </c>
+      <c r="AD119" t="s">
+        <v>2473</v>
+      </c>
+      <c r="AE119" t="s">
+        <v>2474</v>
+      </c>
+      <c r="AF119" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="120" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>2287</v>
+        <v>2475</v>
       </c>
       <c r="B120" t="s">
-        <v>2288</v>
+        <v>2476</v>
       </c>
       <c r="C120" t="s">
-        <v>2289</v>
+        <v>2477</v>
       </c>
       <c r="D120" t="s">
         <v>65</v>
@@ -18839,23 +20336,26 @@
       <c r="G120" t="s">
         <v>203</v>
       </c>
+      <c r="H120" t="s">
+        <v>2478</v>
+      </c>
       <c r="I120" t="s">
-        <v>2290</v>
+        <v>2479</v>
       </c>
       <c r="J120" t="s">
-        <v>2291</v>
+        <v>2480</v>
       </c>
       <c r="K120" t="s">
-        <v>2292</v>
+        <v>2481</v>
       </c>
       <c r="L120" t="s">
-        <v>2293</v>
+        <v>2482</v>
       </c>
       <c r="M120" t="s">
-        <v>2294</v>
+        <v>2483</v>
       </c>
       <c r="N120" t="s">
-        <v>2295</v>
+        <v>2484</v>
       </c>
       <c r="P120" t="s">
         <v>46</v>
@@ -18867,27 +20367,54 @@
         <v>48</v>
       </c>
       <c r="T120" t="s">
-        <v>2296</v>
+        <v>2485</v>
       </c>
       <c r="U120" t="s">
-        <v>2297</v>
+        <v>2486</v>
       </c>
       <c r="V120" t="s">
-        <v>2298</v>
+        <v>2487</v>
       </c>
       <c r="W120" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X120" t="s">
+        <v>2488</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>2489</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>2490</v>
+      </c>
+      <c r="AA120" t="s">
+        <v>2491</v>
+      </c>
+      <c r="AB120" t="s">
+        <v>2492</v>
+      </c>
+      <c r="AC120" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD120" t="s">
+        <v>2493</v>
+      </c>
+      <c r="AE120" t="s">
+        <v>2494</v>
+      </c>
+      <c r="AF120" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="121" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2299</v>
+        <v>2495</v>
       </c>
       <c r="B121" t="s">
-        <v>2300</v>
+        <v>2496</v>
       </c>
       <c r="C121" t="s">
-        <v>2301</v>
+        <v>2497</v>
       </c>
       <c r="D121" t="s">
         <v>35</v>
@@ -18901,23 +20428,26 @@
       <c r="G121" t="s">
         <v>89</v>
       </c>
+      <c r="H121" t="s">
+        <v>2498</v>
+      </c>
       <c r="I121" t="s">
-        <v>2302</v>
+        <v>2499</v>
       </c>
       <c r="J121" t="s">
-        <v>2303</v>
+        <v>2500</v>
       </c>
       <c r="K121" t="s">
-        <v>2304</v>
+        <v>2501</v>
       </c>
       <c r="L121" t="s">
-        <v>2305</v>
+        <v>2502</v>
       </c>
       <c r="M121" t="s">
-        <v>2306</v>
+        <v>2503</v>
       </c>
       <c r="N121" t="s">
-        <v>2307</v>
+        <v>2504</v>
       </c>
       <c r="O121" t="s">
         <v>141</v>
@@ -18932,27 +20462,54 @@
         <v>48</v>
       </c>
       <c r="T121" t="s">
-        <v>2308</v>
+        <v>2505</v>
       </c>
       <c r="U121" t="s">
-        <v>2309</v>
+        <v>2506</v>
       </c>
       <c r="V121" t="s">
-        <v>2310</v>
+        <v>2507</v>
       </c>
       <c r="W121" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X121" t="s">
+        <v>2508</v>
+      </c>
+      <c r="Y121" t="s">
+        <v>2509</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>2510</v>
+      </c>
+      <c r="AA121" t="s">
+        <v>2511</v>
+      </c>
+      <c r="AB121" t="s">
+        <v>2512</v>
+      </c>
+      <c r="AC121" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD121" t="s">
+        <v>2513</v>
+      </c>
+      <c r="AE121" t="s">
+        <v>2514</v>
+      </c>
+      <c r="AF121" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="122" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>2311</v>
+        <v>2515</v>
       </c>
       <c r="B122" t="s">
-        <v>2312</v>
+        <v>2516</v>
       </c>
       <c r="C122" t="s">
-        <v>2313</v>
+        <v>2517</v>
       </c>
       <c r="D122" t="s">
         <v>65</v>
@@ -18966,23 +20523,26 @@
       <c r="G122" t="s">
         <v>331</v>
       </c>
+      <c r="H122" t="s">
+        <v>2518</v>
+      </c>
       <c r="I122" t="s">
-        <v>2314</v>
+        <v>2519</v>
       </c>
       <c r="J122" t="s">
-        <v>2315</v>
+        <v>2520</v>
       </c>
       <c r="K122" t="s">
-        <v>2316</v>
+        <v>2521</v>
       </c>
       <c r="L122" t="s">
-        <v>2317</v>
+        <v>2522</v>
       </c>
       <c r="M122" t="s">
-        <v>2318</v>
+        <v>2523</v>
       </c>
       <c r="N122" t="s">
-        <v>2319</v>
+        <v>2524</v>
       </c>
       <c r="P122" t="s">
         <v>46</v>
@@ -18994,27 +20554,54 @@
         <v>48</v>
       </c>
       <c r="T122" t="s">
-        <v>2320</v>
+        <v>2525</v>
       </c>
       <c r="U122" t="s">
-        <v>2321</v>
+        <v>2526</v>
       </c>
       <c r="V122" t="s">
-        <v>2322</v>
+        <v>2527</v>
       </c>
       <c r="W122" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X122" t="s">
+        <v>2528</v>
+      </c>
+      <c r="Y122" t="s">
+        <v>2529</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>2530</v>
+      </c>
+      <c r="AA122" t="s">
+        <v>2531</v>
+      </c>
+      <c r="AB122" t="s">
+        <v>2532</v>
+      </c>
+      <c r="AC122" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD122" t="s">
+        <v>2533</v>
+      </c>
+      <c r="AE122" t="s">
+        <v>2534</v>
+      </c>
+      <c r="AF122" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="123" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2323</v>
+        <v>2535</v>
       </c>
       <c r="B123" t="s">
-        <v>2324</v>
+        <v>2536</v>
       </c>
       <c r="C123" t="s">
-        <v>2325</v>
+        <v>2537</v>
       </c>
       <c r="D123" t="s">
         <v>65</v>
@@ -19028,23 +20615,26 @@
       <c r="G123" t="s">
         <v>203</v>
       </c>
+      <c r="H123" t="s">
+        <v>2538</v>
+      </c>
       <c r="I123" t="s">
-        <v>2326</v>
+        <v>2539</v>
       </c>
       <c r="J123" t="s">
-        <v>2327</v>
+        <v>2540</v>
       </c>
       <c r="K123" t="s">
-        <v>2328</v>
+        <v>2541</v>
       </c>
       <c r="L123" t="s">
-        <v>2329</v>
+        <v>2542</v>
       </c>
       <c r="M123" t="s">
-        <v>2330</v>
+        <v>2543</v>
       </c>
       <c r="N123" t="s">
-        <v>2331</v>
+        <v>2544</v>
       </c>
       <c r="P123" t="s">
         <v>46</v>
@@ -19056,27 +20646,54 @@
         <v>48</v>
       </c>
       <c r="T123" t="s">
-        <v>2332</v>
+        <v>2545</v>
       </c>
       <c r="U123" t="s">
-        <v>2333</v>
+        <v>2546</v>
       </c>
       <c r="V123" t="s">
-        <v>2334</v>
+        <v>2547</v>
       </c>
       <c r="W123" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X123" t="s">
+        <v>2548</v>
+      </c>
+      <c r="Y123" t="s">
+        <v>2549</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>2550</v>
+      </c>
+      <c r="AA123" t="s">
+        <v>2551</v>
+      </c>
+      <c r="AB123" t="s">
+        <v>2552</v>
+      </c>
+      <c r="AC123" t="s">
+        <v>2130</v>
+      </c>
+      <c r="AD123" t="s">
+        <v>2553</v>
+      </c>
+      <c r="AE123" t="s">
+        <v>2554</v>
+      </c>
+      <c r="AF123" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="124" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2335</v>
+        <v>2555</v>
       </c>
       <c r="B124" t="s">
-        <v>2336</v>
+        <v>2556</v>
       </c>
       <c r="C124" t="s">
-        <v>2337</v>
+        <v>2557</v>
       </c>
       <c r="D124" t="s">
         <v>65</v>
@@ -19090,23 +20707,26 @@
       <c r="G124" t="s">
         <v>331</v>
       </c>
+      <c r="H124" t="s">
+        <v>2558</v>
+      </c>
       <c r="I124" t="s">
-        <v>2338</v>
+        <v>2559</v>
       </c>
       <c r="J124" t="s">
-        <v>2339</v>
+        <v>2560</v>
       </c>
       <c r="K124" t="s">
-        <v>2340</v>
+        <v>2561</v>
       </c>
       <c r="L124" t="s">
-        <v>2341</v>
+        <v>2562</v>
       </c>
       <c r="M124" t="s">
-        <v>2342</v>
+        <v>2563</v>
       </c>
       <c r="N124" t="s">
-        <v>2343</v>
+        <v>2564</v>
       </c>
       <c r="P124" t="s">
         <v>46</v>
@@ -19118,27 +20738,54 @@
         <v>48</v>
       </c>
       <c r="T124" t="s">
-        <v>2344</v>
+        <v>2565</v>
       </c>
       <c r="U124" t="s">
-        <v>2345</v>
+        <v>2566</v>
       </c>
       <c r="V124" t="s">
-        <v>2346</v>
+        <v>2567</v>
       </c>
       <c r="W124" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X124" t="s">
+        <v>2568</v>
+      </c>
+      <c r="Y124" t="s">
+        <v>2569</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>2570</v>
+      </c>
+      <c r="AA124" t="s">
+        <v>2571</v>
+      </c>
+      <c r="AB124" t="s">
+        <v>2572</v>
+      </c>
+      <c r="AC124" t="s">
+        <v>683</v>
+      </c>
+      <c r="AD124" t="s">
+        <v>2573</v>
+      </c>
+      <c r="AE124" t="s">
+        <v>2574</v>
+      </c>
+      <c r="AF124" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="125" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>2347</v>
+        <v>2575</v>
       </c>
       <c r="B125" t="s">
-        <v>2348</v>
+        <v>2576</v>
       </c>
       <c r="C125" t="s">
-        <v>2349</v>
+        <v>2577</v>
       </c>
       <c r="D125" t="s">
         <v>35</v>
@@ -19152,23 +20799,26 @@
       <c r="G125" t="s">
         <v>203</v>
       </c>
+      <c r="H125" t="s">
+        <v>2578</v>
+      </c>
       <c r="I125" t="s">
-        <v>2350</v>
+        <v>2579</v>
       </c>
       <c r="J125" t="s">
-        <v>2351</v>
+        <v>2580</v>
       </c>
       <c r="K125" t="s">
-        <v>2352</v>
+        <v>2581</v>
       </c>
       <c r="L125" t="s">
-        <v>2353</v>
+        <v>2582</v>
       </c>
       <c r="M125" t="s">
-        <v>2354</v>
+        <v>2583</v>
       </c>
       <c r="N125" t="s">
-        <v>2355</v>
+        <v>2584</v>
       </c>
       <c r="O125" t="s">
         <v>141</v>
@@ -19183,27 +20833,54 @@
         <v>48</v>
       </c>
       <c r="T125" t="s">
-        <v>2356</v>
+        <v>2585</v>
       </c>
       <c r="U125" t="s">
-        <v>2357</v>
+        <v>2586</v>
       </c>
       <c r="V125" t="s">
-        <v>2358</v>
+        <v>2587</v>
       </c>
       <c r="W125" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X125" t="s">
+        <v>2588</v>
+      </c>
+      <c r="Y125" t="s">
+        <v>2589</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>2590</v>
+      </c>
+      <c r="AA125" t="s">
+        <v>2591</v>
+      </c>
+      <c r="AB125" t="s">
+        <v>2592</v>
+      </c>
+      <c r="AC125" t="s">
+        <v>1746</v>
+      </c>
+      <c r="AD125" t="s">
+        <v>2593</v>
+      </c>
+      <c r="AE125" t="s">
+        <v>2594</v>
+      </c>
+      <c r="AF125" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="126" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>2359</v>
+        <v>2595</v>
       </c>
       <c r="B126" t="s">
-        <v>2360</v>
+        <v>2596</v>
       </c>
       <c r="C126" t="s">
-        <v>2361</v>
+        <v>2597</v>
       </c>
       <c r="D126" t="s">
         <v>65</v>
@@ -19217,23 +20894,26 @@
       <c r="G126" t="s">
         <v>38</v>
       </c>
+      <c r="H126" t="s">
+        <v>2598</v>
+      </c>
       <c r="I126" t="s">
-        <v>2362</v>
+        <v>2599</v>
       </c>
       <c r="J126" t="s">
-        <v>2363</v>
+        <v>2600</v>
       </c>
       <c r="K126" t="s">
-        <v>2364</v>
+        <v>2601</v>
       </c>
       <c r="L126" t="s">
-        <v>2365</v>
+        <v>2602</v>
       </c>
       <c r="M126" t="s">
-        <v>2366</v>
+        <v>2603</v>
       </c>
       <c r="N126" t="s">
-        <v>2367</v>
+        <v>2604</v>
       </c>
       <c r="O126" t="s">
         <v>141</v>
@@ -19251,27 +20931,54 @@
         <v>167</v>
       </c>
       <c r="T126" t="s">
-        <v>2368</v>
+        <v>2605</v>
       </c>
       <c r="U126" t="s">
-        <v>2369</v>
+        <v>2606</v>
       </c>
       <c r="V126" t="s">
-        <v>2370</v>
+        <v>2607</v>
       </c>
       <c r="W126" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X126" t="s">
+        <v>2608</v>
+      </c>
+      <c r="Y126" t="s">
+        <v>2609</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>2610</v>
+      </c>
+      <c r="AA126" t="s">
+        <v>2611</v>
+      </c>
+      <c r="AB126" t="s">
+        <v>2612</v>
+      </c>
+      <c r="AC126" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD126" t="s">
+        <v>2613</v>
+      </c>
+      <c r="AE126" t="s">
+        <v>2614</v>
+      </c>
+      <c r="AF126" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="127" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2371</v>
+        <v>2615</v>
       </c>
       <c r="B127" t="s">
-        <v>2372</v>
+        <v>2616</v>
       </c>
       <c r="C127" t="s">
-        <v>2373</v>
+        <v>2617</v>
       </c>
       <c r="D127" t="s">
         <v>157</v>
@@ -19285,20 +20992,23 @@
       <c r="G127" t="s">
         <v>158</v>
       </c>
+      <c r="H127" t="s">
+        <v>2618</v>
+      </c>
       <c r="I127" t="s">
-        <v>2374</v>
+        <v>2619</v>
       </c>
       <c r="J127" t="s">
-        <v>2375</v>
+        <v>2620</v>
       </c>
       <c r="K127" t="s">
-        <v>2376</v>
+        <v>2621</v>
       </c>
       <c r="M127" t="s">
-        <v>2377</v>
+        <v>2622</v>
       </c>
       <c r="N127" t="s">
-        <v>2378</v>
+        <v>2623</v>
       </c>
       <c r="O127" t="s">
         <v>141</v>
@@ -19316,27 +21026,54 @@
         <v>1534</v>
       </c>
       <c r="T127" t="s">
-        <v>2379</v>
+        <v>2624</v>
       </c>
       <c r="U127" t="s">
-        <v>2380</v>
+        <v>2625</v>
       </c>
       <c r="V127" t="s">
-        <v>2381</v>
+        <v>2626</v>
       </c>
       <c r="W127" s="1" t="s">
         <v>1538</v>
+      </c>
+      <c r="X127" t="s">
+        <v>2627</v>
+      </c>
+      <c r="Y127" t="s">
+        <v>2628</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>2629</v>
+      </c>
+      <c r="AA127" t="s">
+        <v>2630</v>
+      </c>
+      <c r="AB127" t="s">
+        <v>2631</v>
+      </c>
+      <c r="AC127" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD127" t="s">
+        <v>2632</v>
+      </c>
+      <c r="AE127" t="s">
+        <v>2633</v>
+      </c>
+      <c r="AF127" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="128" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>2382</v>
+        <v>2634</v>
       </c>
       <c r="B128" t="s">
-        <v>2383</v>
+        <v>2635</v>
       </c>
       <c r="C128" t="s">
-        <v>2384</v>
+        <v>2636</v>
       </c>
       <c r="D128" t="s">
         <v>65</v>
@@ -19350,23 +21087,26 @@
       <c r="G128" t="s">
         <v>203</v>
       </c>
+      <c r="H128" t="s">
+        <v>2637</v>
+      </c>
       <c r="I128" t="s">
-        <v>2385</v>
+        <v>2638</v>
       </c>
       <c r="J128" t="s">
-        <v>2386</v>
+        <v>2639</v>
       </c>
       <c r="K128" t="s">
-        <v>2387</v>
+        <v>2640</v>
       </c>
       <c r="L128" t="s">
-        <v>2388</v>
+        <v>2641</v>
       </c>
       <c r="M128" t="s">
-        <v>2389</v>
+        <v>2642</v>
       </c>
       <c r="N128" t="s">
-        <v>2390</v>
+        <v>2643</v>
       </c>
       <c r="P128" t="s">
         <v>46</v>
@@ -19378,27 +21118,54 @@
         <v>48</v>
       </c>
       <c r="T128" t="s">
-        <v>2391</v>
+        <v>2644</v>
       </c>
       <c r="U128" t="s">
-        <v>2392</v>
+        <v>2645</v>
       </c>
       <c r="V128" t="s">
-        <v>2393</v>
+        <v>2646</v>
       </c>
       <c r="W128" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X128" t="s">
+        <v>2647</v>
+      </c>
+      <c r="Y128" t="s">
+        <v>2648</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>2649</v>
+      </c>
+      <c r="AA128" t="s">
+        <v>2650</v>
+      </c>
+      <c r="AB128" t="s">
+        <v>2651</v>
+      </c>
+      <c r="AC128" t="s">
+        <v>2652</v>
+      </c>
+      <c r="AD128" t="s">
+        <v>2653</v>
+      </c>
+      <c r="AE128" t="s">
+        <v>2654</v>
+      </c>
+      <c r="AF128" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="129" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2394</v>
+        <v>2655</v>
       </c>
       <c r="B129" t="s">
-        <v>2395</v>
+        <v>2656</v>
       </c>
       <c r="C129" t="s">
-        <v>2396</v>
+        <v>2657</v>
       </c>
       <c r="D129" t="s">
         <v>35</v>
@@ -19412,23 +21179,26 @@
       <c r="G129" t="s">
         <v>203</v>
       </c>
+      <c r="H129" t="s">
+        <v>2658</v>
+      </c>
       <c r="I129" t="s">
-        <v>2397</v>
+        <v>2659</v>
       </c>
       <c r="J129" t="s">
-        <v>2398</v>
+        <v>2660</v>
       </c>
       <c r="K129" t="s">
-        <v>2399</v>
+        <v>2661</v>
       </c>
       <c r="L129" t="s">
-        <v>2400</v>
+        <v>2662</v>
       </c>
       <c r="M129" t="s">
-        <v>2401</v>
+        <v>2663</v>
       </c>
       <c r="N129" t="s">
-        <v>2402</v>
+        <v>2664</v>
       </c>
       <c r="P129" t="s">
         <v>46</v>
@@ -19440,16 +21210,43 @@
         <v>48</v>
       </c>
       <c r="T129" t="s">
-        <v>2403</v>
+        <v>2665</v>
       </c>
       <c r="U129" t="s">
-        <v>2404</v>
+        <v>2666</v>
       </c>
       <c r="V129" t="s">
-        <v>2405</v>
+        <v>2667</v>
       </c>
       <c r="W129" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="X129" t="s">
+        <v>2668</v>
+      </c>
+      <c r="Y129" t="s">
+        <v>2669</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>2670</v>
+      </c>
+      <c r="AA129" t="s">
+        <v>2671</v>
+      </c>
+      <c r="AB129" t="s">
+        <v>2672</v>
+      </c>
+      <c r="AC129" t="s">
+        <v>787</v>
+      </c>
+      <c r="AD129" t="s">
+        <v>2673</v>
+      </c>
+      <c r="AE129" t="s">
+        <v>2674</v>
+      </c>
+      <c r="AF129" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
